--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High Hype Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -648,6 +648,9 @@
     <xf numFmtId="166" fontId="10" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -676,16 +679,13 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1581,7 +1581,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 12, 2026  ·  10:16 UTC</t>
+          <t>Generated September 13, 2026  ·  11:17 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1621,20 +1621,20 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="16" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>$181</t>
+          <t>$180</t>
         </is>
       </c>
       <c r="H5" s="19" t="n"/>
@@ -1737,7 +1737,7 @@
         <v>46290</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “University Red”</t>
+          <t>Yuto Horigome x Nike SB Air Force 1 “Iron Grey”</t>
         </is>
       </c>
       <c r="B12" s="30" t="inlineStr">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="C12" s="31" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>7</v>
       </c>
       <c r="G12" s="33" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="H12" s="34" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Wagyu x Nike Air Max 90</t>
+          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="40" t="inlineStr">
         <is>
@@ -1848,18 +1848,18 @@
         <v>7</v>
       </c>
       <c r="G13" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="H13" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>125</v>
+      </c>
+      <c r="H13" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Bucks”</t>
+          <t>Air Jordan 6 Low “Metamorphosis”</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="C14" s="31" t="n">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
@@ -1882,9 +1882,9 @@
         <v>7</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>215</v>
-      </c>
-      <c r="H14" s="42" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="H14" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -1893,19 +1893,19 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 “Iron Grey”</t>
+          <t>Air Jordan 4 “London”</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>7</v>
       </c>
       <c r="G15" s="41" t="n">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="H15" s="38" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="C16" s="31" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
@@ -1950,9 +1950,9 @@
         <v>7</v>
       </c>
       <c r="G16" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="H16" s="42" t="inlineStr">
+        <v>250</v>
+      </c>
+      <c r="H16" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2006,7 +2006,7 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>Nike</t>
         </is>
@@ -2022,23 +2022,23 @@
       <c r="E20" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="44" t="inlineStr">
+      <c r="G20" s="45" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="45" t="inlineStr">
+      <c r="A21" s="46" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
       <c r="B21" s="35" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
@@ -2046,35 +2046,35 @@
         </is>
       </c>
       <c r="E21" s="35" t="n">
-        <v>71</v>
-      </c>
-      <c r="G21" s="46" t="inlineStr">
+        <v>73</v>
+      </c>
+      <c r="G21" s="47" t="inlineStr">
         <is>
           <t>SNKRS App</t>
         </is>
       </c>
       <c r="H21" s="35" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>Adidas</t>
         </is>
       </c>
       <c r="B22" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="D22" s="47" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
       <c r="E22" s="30" t="n">
-        <v>46</v>
-      </c>
-      <c r="G22" s="48" t="inlineStr">
+        <v>45</v>
+      </c>
+      <c r="G22" s="49" t="inlineStr">
         <is>
           <t>Confirmed App</t>
         </is>
@@ -2084,41 +2084,41 @@
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="45" t="inlineStr">
+      <c r="A23" s="46" t="inlineStr">
         <is>
           <t>Vans</t>
         </is>
       </c>
       <c r="B23" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="D23" s="49" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="D23" s="50" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="E23" s="35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>Reebok</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="46" t="inlineStr">
         <is>
           <t>Converse</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="45" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
       <c r="B25" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" ht="10" customHeight="1"/>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B29" s="30" t="inlineStr">
         <is>
-          <t>9/12 – 9/18</t>
+          <t>9/13 – 9/19</t>
         </is>
       </c>
       <c r="C29" s="30" t="n">
@@ -2181,7 +2181,7 @@
         <v>13</v>
       </c>
       <c r="E29" s="30" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
@@ -2192,14 +2192,14 @@
       </c>
       <c r="B30" s="35" t="inlineStr">
         <is>
-          <t>9/19 – 9/25</t>
+          <t>9/20 – 9/26</t>
         </is>
       </c>
       <c r="C30" s="35" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D30" s="40" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E30" s="35" t="n">
         <v>5.5</v>
@@ -2213,17 +2213,17 @@
       </c>
       <c r="B31" s="30" t="inlineStr">
         <is>
-          <t>9/26 – 10/2</t>
+          <t>9/27 – 10/3</t>
         </is>
       </c>
       <c r="C31" s="30" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D31" s="39" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E31" s="30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="B32" s="35" t="inlineStr">
         <is>
-          <t>10/3 – 10/9</t>
+          <t>10/4 – 10/10</t>
         </is>
       </c>
       <c r="C32" s="35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" s="40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" s="35" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="B33" s="30" t="inlineStr">
         <is>
-          <t>10/10 – 10/16</t>
+          <t>10/11 – 10/17</t>
         </is>
       </c>
       <c r="C33" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="D33" s="39" t="n">
-        <v>6</v>
-      </c>
       <c r="E33" s="30" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="B34" s="35" t="inlineStr">
         <is>
-          <t>10/17 – 10/23</t>
+          <t>10/18 – 10/24</t>
         </is>
       </c>
       <c r="C34" s="35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D34" s="40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E34" s="35" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="B35" s="30" t="inlineStr">
         <is>
-          <t>10/24 – 10/30</t>
+          <t>10/25 – 10/31</t>
         </is>
       </c>
       <c r="C35" s="30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D35" s="39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="30" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -2318,17 +2318,17 @@
       </c>
       <c r="B36" s="35" t="inlineStr">
         <is>
-          <t>10/31 – 11/6</t>
+          <t>11/1 – 11/7</t>
         </is>
       </c>
       <c r="C36" s="35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D36" s="40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="35" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="B37" s="30" t="inlineStr">
         <is>
-          <t>11/7 – 11/13</t>
+          <t>11/8 – 11/14</t>
         </is>
       </c>
       <c r="C37" s="30" t="n">
@@ -2349,7 +2349,7 @@
         <v>4</v>
       </c>
       <c r="E37" s="30" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B38" s="35" t="inlineStr">
         <is>
-          <t>11/14 – 11/20</t>
+          <t>11/15 – 11/21</t>
         </is>
       </c>
       <c r="C38" s="35" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D38" s="40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E38" s="35" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="B39" s="30" t="inlineStr">
         <is>
-          <t>11/21 – 11/27</t>
+          <t>11/22 – 11/28</t>
         </is>
       </c>
       <c r="C39" s="30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" s="39" t="n">
         <v>6</v>
       </c>
       <c r="E39" s="30" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -2402,17 +2402,17 @@
       </c>
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>11/28 – 12/4</t>
+          <t>11/29 – 12/5</t>
         </is>
       </c>
       <c r="C40" s="35" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D40" s="40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E40" s="35" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>12/5 – 12/11</t>
+          <t>12/6 – 12/12</t>
         </is>
       </c>
       <c r="C41" s="30" t="n">
@@ -2483,42 +2483,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="50" t="inlineStr">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="B1" s="50" t="inlineStr">
+      <c r="B1" s="51" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
       </c>
-      <c r="D1" s="50" t="inlineStr">
+      <c r="D1" s="51" t="inlineStr">
         <is>
           <t>Hype Level</t>
         </is>
       </c>
-      <c r="E1" s="50" t="inlineStr">
+      <c r="E1" s="51" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
       </c>
-      <c r="G1" s="50" t="inlineStr">
+      <c r="G1" s="51" t="inlineStr">
         <is>
           <t>Sale Method</t>
         </is>
       </c>
-      <c r="H1" s="50" t="inlineStr">
+      <c r="H1" s="51" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
       </c>
-      <c r="J1" s="50" t="inlineStr">
+      <c r="J1" s="51" t="inlineStr">
         <is>
           <t>Price Range</t>
         </is>
       </c>
-      <c r="K1" s="50" t="inlineStr">
+      <c r="K1" s="51" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2655,11 +2655,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2673,11 +2673,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2692,7 +2692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2716,9 +2716,9 @@
       <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="51" t="inlineStr">
-        <is>
-          <t>Generated September 12, 2026  ·  10:16 UTC</t>
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>Generated September 13, 2026  ·  11:17 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2761,101 +2761,101 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>160</v>
-      </c>
-      <c r="C4" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>125</v>
+      </c>
+      <c r="C4" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D4" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Larry June x adidas Adistar Control 5 “Watermelon Smoothie”</t>
+          <t>Yuto Horigome x Nike SB Air Force 1 “Iron Grey”</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D5" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>120</v>
+      </c>
+      <c r="C5" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D5" s="54" t="inlineStr">
+        <is>
+          <t>Confirmed App</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “University Red”</t>
+          <t>Bad Bunny x adidas Badbo 1.1 Low “Chalk White”</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C6" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Wagyu x Nike Air Max 90</t>
+          <t>adidas Anthony Edwards 3 “Cold Blooded”</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="36" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C7" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D7" s="54" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2867,165 +2867,165 @@
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Nike Air More Uptempo “Cobalt Bliss” 2026</t>
+          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="31" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>215</v>
-      </c>
-      <c r="C8" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D8" s="42" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C8" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Bucks”</t>
+          <t>Nike First Sight Shadow “Light Crimson” (W)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="36" t="n">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>160</v>
-      </c>
-      <c r="C9" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D9" s="54" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Larry June x adidas Adistar Control 5</t>
+          <t>Air Jordan 6 Low “Metamorphosis”</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="31" t="n">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C10" s="47" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Mera Mera”</t>
+          <t>Reebok Brutus Low “Philadelphia Eagles”</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="36" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>120</v>
-      </c>
-      <c r="C11" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D11" s="55" t="inlineStr">
-        <is>
-          <t>Confirmed App</t>
+        <v>220</v>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D11" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.1 Low “Chalk White”</t>
+          <t>Air Jordan 4 “London”</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="31" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C12" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="42" t="inlineStr">
+        <v>250</v>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Cold Blooded”</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="36" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="C13" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E13" s="35" t="inlineStr">
@@ -3035,109 +3035,109 @@
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 “Iron Grey”</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="31" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D14" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="36" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C15" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D15" s="54" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Nike First Sight Shadow “Light Crimson” (W)</t>
+          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="31" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C16" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D16" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>135</v>
+      </c>
+      <c r="C16" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 Low “Metamorphosis”</t>
+          <t>PSG x Nike KD 6</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="36" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C17" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D17" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D17" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>APB x Air Jordan 11 Low</t>
         </is>
       </c>
     </row>
@@ -3156,26 +3156,26 @@
         <v>46283</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C18" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D18" s="42" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C18" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>Nike A’Two “Dawn Staley”</t>
         </is>
       </c>
     </row>
@@ -3184,26 +3184,26 @@
         <v>46283</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>135</v>
-      </c>
-      <c r="C19" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D19" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>65</v>
+      </c>
+      <c r="C19" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>PSG x Nike KD 6</t>
+          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
         </is>
       </c>
     </row>
@@ -3212,42 +3212,42 @@
         <v>46283</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D20" s="42" t="inlineStr">
+      <c r="D20" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>Nike Air Foamposite Pro “Green Camo”</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C21" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D21" s="54" t="inlineStr">
+        <v>122</v>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3259,163 +3259,163 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Nike A’Two “Dawn Staley”</t>
+          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>65</v>
-      </c>
-      <c r="C22" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D22" s="42" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
+          <t>Nike Kobe 8 Protro “Mambacurial”</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C23" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>205</v>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D23" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
+          <t>APB x Air Jordan 11 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>250</v>
-      </c>
-      <c r="C24" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D24" s="42" t="inlineStr">
+        <v>300</v>
+      </c>
+      <c r="C24" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D24" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E24" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C25" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D25" s="54" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C25" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>Air Jordan 9 OG “Space Jam” 2026</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C26" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D26" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>110</v>
+      </c>
+      <c r="C26" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D26" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Pokémon x adidas 30th Anniversary Collection</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="C27" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D27" s="54" t="inlineStr">
+      <c r="D27" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3427,181 +3427,181 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws”</t>
+          <t>One Piece x Nike Air Max Plus “Ope Ope”</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>250</v>
-      </c>
-      <c r="C28" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D28" s="42" t="inlineStr">
+        <v>300</v>
+      </c>
+      <c r="C28" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D28" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo”</t>
+          <t>Pharrell x adidas Adistar Jellyfish</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="36" t="n">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="C29" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D29" s="54" t="inlineStr">
+      <c r="D29" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
+          <t>Nike GT Future “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="31" t="n">
-        <v>46284</v>
+        <v>46288</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>215</v>
-      </c>
-      <c r="C30" s="47" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C30" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D30" s="42" t="inlineStr">
+      <c r="D30" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 9 OG “Space Jam” 2026</t>
+          <t>Nike GT Future “Unseen Hours”</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="36" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>110</v>
-      </c>
-      <c r="C31" s="49" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C31" s="50" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D31" s="54" t="inlineStr">
+      <c r="D31" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Pokémon x adidas 30th Anniversary Collection</t>
+          <t>Converse SHAI 001 “Green Beam”</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>122</v>
-      </c>
-      <c r="C32" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D32" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C32" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>Converse SHAI 001 “Ghosted”</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="36" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C33" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D33" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C33" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D33" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="31" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B34" s="33" t="n">
         <v>205</v>
@@ -3611,9 +3611,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D34" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D34" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
@@ -3623,79 +3623,79 @@
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C35" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D35" s="54" t="inlineStr">
+        <v>120</v>
+      </c>
+      <c r="C35" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Ope Ope”</t>
+          <t>Billionaire Boys Club x Reebok Club C 85</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="31" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B36" s="33" t="n">
-        <v>300</v>
-      </c>
-      <c r="C36" s="47" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D36" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C36" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="C37" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D37" s="54" t="inlineStr">
+      <c r="D37" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3707,35 +3707,35 @@
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Nike GT Future “Unseen Hours”</t>
+          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="31" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B38" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C38" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D38" s="42" t="inlineStr">
+      <c r="C38" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E38" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Ghosted”</t>
+          <t>Nike Ja 4 “Jaws”</t>
         </is>
       </c>
     </row>
@@ -3744,128 +3744,128 @@
         <v>46290</v>
       </c>
       <c r="B39" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C39" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D39" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C39" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>225</v>
-      </c>
-      <c r="C40" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D40" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>160</v>
+      </c>
+      <c r="C40" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D40" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D41" s="54" t="inlineStr">
+      <c r="D41" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C42" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D42" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>125</v>
+      </c>
+      <c r="C42" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E42" s="30" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Billionaire Boys Club x Reebok Club C 85</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B43" s="41" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="C43" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D43" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D43" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
@@ -3883,25 +3883,27 @@
       <c r="A44" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B44" s="33" t="inlineStr"/>
-      <c r="C44" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D44" s="42" t="inlineStr">
+      <c r="B44" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="C44" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D44" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E44" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -3909,27 +3911,25 @@
       <c r="A45" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B45" s="41" t="n">
-        <v>145</v>
-      </c>
+      <c r="B45" s="41" t="inlineStr"/>
       <c r="C45" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D45" s="54" t="inlineStr">
+      <c r="D45" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -3937,17 +3937,15 @@
       <c r="A46" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B46" s="33" t="n">
-        <v>150</v>
-      </c>
+      <c r="B46" s="33" t="inlineStr"/>
       <c r="C46" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D46" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D46" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
@@ -3957,7 +3955,7 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
@@ -3973,9 +3971,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D47" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D47" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
@@ -3985,7 +3983,7 @@
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -3994,9 +3992,9 @@
         <v>46291</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C48" s="47" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C48" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4013,7 +4011,7 @@
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
         </is>
       </c>
     </row>
@@ -4022,26 +4020,26 @@
         <v>46291</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>160</v>
-      </c>
-      <c r="C49" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D49" s="54" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C49" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D49" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -4049,27 +4047,25 @@
       <c r="A50" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B50" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C50" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D50" s="42" t="inlineStr">
+      <c r="B50" s="33" t="inlineStr"/>
+      <c r="C50" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D50" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
@@ -4078,26 +4074,26 @@
         <v>46291</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C51" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D51" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>155</v>
+      </c>
+      <c r="C51" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D51" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -4106,11 +4102,11 @@
         <v>46291</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C52" s="47" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>150</v>
+      </c>
+      <c r="C52" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D52" s="34" t="inlineStr">
@@ -4125,7 +4121,7 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -4134,14 +4130,14 @@
         <v>46291</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="54" t="inlineStr">
+      <c r="D53" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4153,7 +4149,7 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -4161,15 +4157,17 @@
       <c r="A54" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B54" s="33" t="inlineStr"/>
-      <c r="C54" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D54" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B54" s="33" t="n">
+        <v>155</v>
+      </c>
+      <c r="C54" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
@@ -4179,7 +4177,7 @@
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
@@ -4187,25 +4185,27 @@
       <c r="A55" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B55" s="41" t="inlineStr"/>
-      <c r="C55" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D55" s="54" t="inlineStr">
+      <c r="B55" s="41" t="n">
+        <v>120</v>
+      </c>
+      <c r="C55" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D55" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
         </is>
       </c>
     </row>
@@ -4221,9 +4221,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D56" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D56" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
@@ -4233,25 +4233,25 @@
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="C57" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D57" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D57" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
@@ -4261,69 +4261,69 @@
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
+          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="31" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C58" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D58" s="42" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C58" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D58" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Nike Air Bakin “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>120</v>
+        <v>249</v>
       </c>
       <c r="C59" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D59" s="54" t="inlineStr">
+      <c r="D59" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
+          <t>Hyperice x Nike Air Zoom Hyperslide</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B60" s="33" t="n">
         <v>210</v>
@@ -4333,35 +4333,35 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D60" s="42" t="inlineStr">
+      <c r="D60" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C61" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D61" s="54" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D61" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4373,23 +4373,21 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B62" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C62" s="47" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D62" s="42" t="inlineStr">
+        <v>46295</v>
+      </c>
+      <c r="B62" s="33" t="inlineStr"/>
+      <c r="C62" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D62" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4401,23 +4399,23 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Red”</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="36" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>249</v>
-      </c>
-      <c r="C63" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D63" s="54" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="C63" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D63" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4429,7 +4427,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Hyperice x Nike Air Zoom Hyperslide</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
@@ -4437,15 +4435,17 @@
       <c r="A64" s="31" t="n">
         <v>46295</v>
       </c>
-      <c r="B64" s="33" t="inlineStr"/>
-      <c r="C64" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D64" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B64" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="C64" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
@@ -4455,53 +4455,53 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>MoMA x Nike Air Rift 2 Pack</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="36" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D65" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D65" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Air Jordan 1 Low OG “Howard” 2026</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C66" s="47" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C66" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D66" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D66" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E66" s="30" t="inlineStr">
@@ -4511,23 +4511,23 @@
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>MoMA x Nike Air Rift 2 Pack</t>
+          <t>Nike Caitlin 1 “Racer Blue”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D67" s="54" t="inlineStr">
+      <c r="D67" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4539,79 +4539,79 @@
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C68" s="47" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D68" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>240</v>
+      </c>
+      <c r="C68" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D68" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Racer Blue”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B69" s="41" t="inlineStr"/>
-      <c r="C69" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D69" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>46300</v>
+      </c>
+      <c r="B69" s="41" t="n">
+        <v>200</v>
+      </c>
+      <c r="C69" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D69" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan “Black Pack”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46298</v>
-      </c>
-      <c r="B70" s="33" t="n">
-        <v>240</v>
-      </c>
+        <v>46303</v>
+      </c>
+      <c r="B70" s="33" t="inlineStr"/>
       <c r="C70" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D70" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D70" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E70" s="30" t="inlineStr">
@@ -4621,51 +4621,51 @@
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46298</v>
+        <v>46303</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C71" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D71" s="54" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C71" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D71" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C72" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D72" s="42" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C72" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D72" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4677,163 +4677,165 @@
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B73" s="41" t="inlineStr"/>
-      <c r="C73" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D73" s="54" t="inlineStr">
+        <v>46304</v>
+      </c>
+      <c r="B73" s="41" t="n">
+        <v>130</v>
+      </c>
+      <c r="C73" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D73" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C74" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D74" s="42" t="inlineStr">
+        <v>180</v>
+      </c>
+      <c r="C74" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D74" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46304</v>
+        <v>46310</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="C75" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D75" s="54" t="inlineStr">
+      <c r="D75" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="31" t="n">
-        <v>46304</v>
+        <v>46310</v>
       </c>
       <c r="B76" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C76" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D76" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>125</v>
+      </c>
+      <c r="C76" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D76" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="36" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="B77" s="41" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="C77" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D77" s="54" t="inlineStr">
+      <c r="D77" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="31" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="C78" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D78" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D78" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E78" s="30" t="inlineStr">
@@ -4843,35 +4845,35 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="36" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B79" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C79" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D79" s="54" t="inlineStr">
+        <v>240</v>
+      </c>
+      <c r="C79" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D79" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E79" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4889,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D80" s="42" t="inlineStr">
+      <c r="D80" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4899,107 +4901,105 @@
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="36" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B81" s="41" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C81" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D81" s="54" t="inlineStr">
+      <c r="D81" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E81" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F81" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="31" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B82" s="33" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C82" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D82" s="42" t="inlineStr">
+      <c r="D82" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E82" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="36" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B83" s="41" t="n">
-        <v>250</v>
-      </c>
-      <c r="C83" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D83" s="54" t="inlineStr">
+        <v>46317</v>
+      </c>
+      <c r="B83" s="41" t="inlineStr"/>
+      <c r="C83" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D83" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E83" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F83" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>SZA x Vans VANSZA Collection</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="31" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B84" s="33" t="n">
-        <v>220</v>
+        <v>125</v>
       </c>
       <c r="C84" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D84" s="42" t="inlineStr">
+      <c r="D84" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5011,35 +5011,35 @@
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="36" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B85" s="41" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C85" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D85" s="54" t="inlineStr">
+      <c r="D85" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E85" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
@@ -5048,14 +5048,14 @@
         <v>46319</v>
       </c>
       <c r="B86" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C86" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D86" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C86" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D86" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
@@ -5076,26 +5076,26 @@
         <v>46319</v>
       </c>
       <c r="B87" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C87" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D87" s="54" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C87" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D87" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E87" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
@@ -5104,26 +5104,26 @@
         <v>46319</v>
       </c>
       <c r="B88" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C88" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D88" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>150</v>
+      </c>
+      <c r="C88" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D88" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E88" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
@@ -5132,11 +5132,11 @@
         <v>46319</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="C89" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>170</v>
+      </c>
+      <c r="C89" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D89" s="38" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
@@ -5160,16 +5160,16 @@
         <v>46319</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C90" s="47" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C90" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D90" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D90" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E90" s="30" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
@@ -5188,14 +5188,14 @@
         <v>46319</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C91" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D91" s="54" t="inlineStr">
+        <v>190</v>
+      </c>
+      <c r="C91" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D91" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D92" s="42" t="inlineStr">
+      <c r="D92" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5244,16 +5244,16 @@
         <v>46325</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C93" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D93" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D93" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E93" s="35" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
+          <t>Nike Ja 4 High “University Red”</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       <c r="B94" s="33" t="n">
         <v>155</v>
       </c>
-      <c r="C94" s="47" t="inlineStr">
+      <c r="C94" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D94" s="42" t="inlineStr">
+      <c r="D94" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5291,63 +5291,63 @@
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Halloween”</t>
+          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="36" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="B95" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C95" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D95" s="54" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="C95" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D95" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E95" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F95" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Nike Book 2 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="31" t="n">
-        <v>46329</v>
+        <v>46326</v>
       </c>
       <c r="B96" s="33" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C96" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D96" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D96" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E96" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
@@ -5363,9 +5363,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D97" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D97" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E97" s="35" t="inlineStr">
@@ -5375,23 +5375,23 @@
       </c>
       <c r="F97" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="31" t="n">
-        <v>46331</v>
+        <v>46329</v>
       </c>
       <c r="B98" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C98" s="47" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D98" s="42" t="inlineStr">
+        <v>240</v>
+      </c>
+      <c r="C98" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D98" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D99" s="54" t="inlineStr">
+      <c r="D99" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5431,119 +5431,119 @@
       </c>
       <c r="F99" s="35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="31" t="n">
-        <v>46333</v>
+        <v>46331</v>
       </c>
       <c r="B100" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C100" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D100" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C100" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D100" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E100" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="36" t="n">
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="B101" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C101" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D101" s="54" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C101" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D101" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E101" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Book 2 “Desert Night”</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="31" t="n">
-        <v>46334</v>
+        <v>46333</v>
       </c>
       <c r="B102" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C102" s="47" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D102" s="42" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C102" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D102" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E102" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Desert Night”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="36" t="n">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="B103" s="41" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C103" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D103" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D103" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E103" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F103" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D104" s="42" t="inlineStr">
+      <c r="D104" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5577,19 +5577,19 @@
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="36" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B105" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C105" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D105" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>200</v>
+      </c>
+      <c r="C105" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D105" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E105" s="35" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal” 2026</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
@@ -5608,26 +5608,26 @@
         <v>46338</v>
       </c>
       <c r="B106" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C106" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D106" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>170</v>
+      </c>
+      <c r="C106" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D106" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E106" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F106" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
+          <t>Nike Air Bakin “Varsity Royal” 2026</t>
         </is>
       </c>
     </row>
@@ -5636,54 +5636,54 @@
         <v>46338</v>
       </c>
       <c r="B107" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C107" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D107" s="54" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C107" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D107" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E107" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F107" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal”</t>
+          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="31" t="n">
-        <v>46340</v>
+        <v>46338</v>
       </c>
       <c r="B108" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C108" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D108" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C108" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D108" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E108" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F108" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Air Bakin “Varsity Royal”</t>
         </is>
       </c>
     </row>
@@ -5692,11 +5692,11 @@
         <v>46340</v>
       </c>
       <c r="B109" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C109" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>255</v>
+      </c>
+      <c r="C109" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D109" s="38" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
@@ -5720,11 +5720,11 @@
         <v>46340</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>220</v>
-      </c>
-      <c r="C110" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>240</v>
+      </c>
+      <c r="C110" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D110" s="34" t="inlineStr">
@@ -5739,20 +5739,20 @@
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
         </is>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="36" t="n">
-        <v>46341</v>
+        <v>46340</v>
       </c>
       <c r="B111" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C111" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>220</v>
+      </c>
+      <c r="C111" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D111" s="38" t="inlineStr">
@@ -5762,25 +5762,25 @@
       </c>
       <c r="E111" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>Playa Society x Nike A’Two</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="31" t="n">
-        <v>46342</v>
+        <v>46341</v>
       </c>
       <c r="B112" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C112" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>155</v>
+      </c>
+      <c r="C112" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D112" s="34" t="inlineStr">
@@ -5790,96 +5790,96 @@
       </c>
       <c r="E112" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F112" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Playa Society x Nike A’Two</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="36" t="n">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="B113" s="41" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C113" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D113" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D113" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E113" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F113" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="31" t="n">
-        <v>46345</v>
+        <v>46343</v>
       </c>
       <c r="B114" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C114" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D114" s="42" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C114" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D114" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E114" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F114" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Navy”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="36" t="n">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="B115" s="41" t="n">
         <v>130</v>
       </c>
-      <c r="C115" s="49" t="inlineStr">
+      <c r="C115" s="50" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D115" s="54" t="inlineStr">
+      <c r="D115" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E115" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F115" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
+          <t>Vans Old Skool 36 Pearlized “Navy”</t>
         </is>
       </c>
     </row>
@@ -5890,12 +5890,12 @@
       <c r="B116" s="33" t="n">
         <v>145</v>
       </c>
-      <c r="C116" s="47" t="inlineStr">
+      <c r="C116" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D116" s="42" t="inlineStr">
+      <c r="D116" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5907,35 +5907,35 @@
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Be Legendary”</t>
+          <t>Nike Book 2 Be “Legendary”</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="36" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B117" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C117" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D117" s="54" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C117" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D117" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E117" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F117" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Snow White”</t>
+          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
         </is>
       </c>
     </row>
@@ -5944,26 +5944,26 @@
         <v>46347</v>
       </c>
       <c r="B118" s="33" t="n">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="C118" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D118" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D118" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F118" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -5972,26 +5972,26 @@
         <v>46347</v>
       </c>
       <c r="B119" s="41" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C119" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D119" s="54" t="inlineStr">
+      <c r="D119" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E119" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       <c r="B120" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C120" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D120" s="42" t="inlineStr">
+      <c r="C120" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D120" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="F120" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
@@ -6028,26 +6028,26 @@
         <v>46347</v>
       </c>
       <c r="B121" s="41" t="n">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="C121" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D121" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D121" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E121" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F121" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -6056,42 +6056,42 @@
         <v>46347</v>
       </c>
       <c r="B122" s="33" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C122" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D122" s="42" t="inlineStr">
+      <c r="D122" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F122" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="36" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B123" s="41" t="n">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="C123" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D123" s="54" t="inlineStr">
+      <c r="D123" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F123" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
@@ -6112,54 +6112,54 @@
         <v>46353</v>
       </c>
       <c r="B124" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C124" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D124" s="42" t="inlineStr">
+        <v>240</v>
+      </c>
+      <c r="C124" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D124" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E124" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F124" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Black”</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="36" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B125" s="41" t="n">
-        <v>230</v>
-      </c>
-      <c r="C125" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D125" s="54" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C125" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D125" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E125" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F125" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Vans Old Skool 36 Pearlized “Black”</t>
         </is>
       </c>
     </row>
@@ -6167,13 +6167,15 @@
       <c r="A126" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B126" s="33" t="inlineStr"/>
-      <c r="C126" s="47" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D126" s="42" t="inlineStr">
+      <c r="B126" s="33" t="n">
+        <v>190</v>
+      </c>
+      <c r="C126" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D126" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6185,7 +6187,7 @@
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Aunt Pearl” 2026</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
@@ -6194,16 +6196,16 @@
         <v>46354</v>
       </c>
       <c r="B127" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C127" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D127" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C127" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D127" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E127" s="35" t="inlineStr">
@@ -6213,7 +6215,7 @@
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Nike Caitlin 1 “Yellow Zest”</t>
         </is>
       </c>
     </row>
@@ -6221,10 +6223,12 @@
       <c r="A128" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B128" s="33" t="inlineStr"/>
-      <c r="C128" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
+      <c r="B128" s="33" t="n">
+        <v>120</v>
+      </c>
+      <c r="C128" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D128" s="34" t="inlineStr">
@@ -6234,12 +6238,12 @@
       </c>
       <c r="E128" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F128" s="30" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -6248,26 +6252,26 @@
         <v>46354</v>
       </c>
       <c r="B129" s="41" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="C129" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D129" s="54" t="inlineStr">
+      <c r="D129" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E129" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F129" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
@@ -6275,15 +6279,13 @@
       <c r="A130" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B130" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C130" s="47" t="inlineStr">
+      <c r="B130" s="33" t="inlineStr"/>
+      <c r="C130" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D130" s="42" t="inlineStr">
+      <c r="D130" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6295,7 +6297,7 @@
       </c>
       <c r="F130" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Yellow Zest”</t>
+          <t>Nike KD 6 “Aunt Pearl” 2026</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6306,7 @@
         <v>46354</v>
       </c>
       <c r="B131" s="41" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C131" s="40" t="inlineStr">
         <is>
@@ -6323,51 +6325,49 @@
       </c>
       <c r="F131" s="35" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1">
       <c r="A132" s="31" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B132" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C132" s="47" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D132" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>46354</v>
+      </c>
+      <c r="B132" s="33" t="inlineStr"/>
+      <c r="C132" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D132" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E132" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F132" s="30" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Texas”</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1">
       <c r="A133" s="36" t="n">
-        <v>46359</v>
+        <v>46357</v>
       </c>
       <c r="B133" s="41" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="C133" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D133" s="54" t="inlineStr">
+      <c r="D133" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6379,51 +6379,53 @@
       </c>
       <c r="F133" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Black/White”</t>
+          <t>Nike KD 6 “Texas”</t>
         </is>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="31" t="n">
-        <v>46361</v>
+        <v>46359</v>
       </c>
       <c r="B134" s="33" t="n">
-        <v>215</v>
-      </c>
-      <c r="C134" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D134" s="42" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C134" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D134" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E134" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F134" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Nike Air Bakin “Black/White”</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c r="A135" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B135" s="41" t="inlineStr"/>
+        <v>46361</v>
+      </c>
+      <c r="B135" s="41" t="n">
+        <v>215</v>
+      </c>
       <c r="C135" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D135" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D135" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E135" s="35" t="inlineStr">
@@ -6433,7 +6435,7 @@
       </c>
       <c r="F135" s="35" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
@@ -6469,32 +6471,86 @@
       <c r="A137" s="36" t="n">
         <v>46367</v>
       </c>
-      <c r="B137" s="41" t="n">
+      <c r="B137" s="41" t="inlineStr"/>
+      <c r="C137" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D137" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E137" s="35" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F137" s="35" t="inlineStr">
+        <is>
+          <t>Free The Youth x Air Jordan 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="15" customHeight="1">
+      <c r="A138" s="31" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B138" s="33" t="n">
         <v>190</v>
       </c>
-      <c r="C137" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D137" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E137" s="35" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="F137" s="35" t="inlineStr">
+      <c r="C138" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D138" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E138" s="30" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F138" s="30" t="inlineStr">
         <is>
           <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
+    <row r="139" ht="15" customHeight="1">
+      <c r="A139" s="36" t="n">
+        <v>46368</v>
+      </c>
+      <c r="B139" s="41" t="n">
+        <v>235</v>
+      </c>
+      <c r="C139" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D139" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E139" s="35" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F139" s="35" t="inlineStr">
+        <is>
+          <t>Air Jordan 11 “Space Jam” 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:F137"/>
+  <autoFilter ref="A3:F139"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -6509,7 +6565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6533,9 +6589,9 @@
       <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="51" t="inlineStr">
-        <is>
-          <t>Generated September 12, 2026  ·  10:16 UTC</t>
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>Generated September 13, 2026  ·  11:17 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -6578,10 +6634,10 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C4" s="39" t="inlineStr">
         <is>
@@ -6600,25 +6656,25 @@
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “University Red”</t>
+          <t>Yuto Horigome x Nike SB Air Force 1 “Iron Grey”</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
@@ -6628,23 +6684,23 @@
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Wagyu x Nike Air Max 90</t>
+          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="n">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
+      <c r="D6" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6656,16 +6712,16 @@
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Bucks”</t>
+          <t>Air Jordan 6 Low “Metamorphosis”</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="36" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
@@ -6679,28 +6735,28 @@
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 “Iron Grey”</t>
+          <t>Air Jordan 4 “London”</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="31" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="D8" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6712,44 +6768,44 @@
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="36" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D9" s="54" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 Low “Metamorphosis”</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="31" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
@@ -6768,7 +6824,7 @@
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6840,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D11" s="54" t="inlineStr">
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6812,7 +6868,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D12" s="42" t="inlineStr">
+      <c r="D12" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6840,7 +6896,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D13" s="54" t="inlineStr">
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6852,23 +6908,23 @@
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>Nike Air Foamposite Pro “Green Camo”</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>210</v>
+        <v>122</v>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D14" s="42" t="inlineStr">
+      <c r="D14" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6880,128 +6936,128 @@
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C15" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D15" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D15" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Nike Kobe 8 Protro “Mambacurial”</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="C16" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D16" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo”</t>
+          <t>APB x Air Jordan 11 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="36" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>122</v>
-      </c>
-      <c r="C17" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D17" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D17" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="31" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C18" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D18" s="42" t="inlineStr">
+      <c r="D18" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="36" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="C19" s="40" t="inlineStr">
         <is>
@@ -7020,91 +7076,89 @@
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D20" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>225</v>
-      </c>
-      <c r="C21" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D21" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="31" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B22" s="33" t="n">
-        <v>205</v>
-      </c>
+        <v>46291</v>
+      </c>
+      <c r="B22" s="33" t="inlineStr"/>
       <c r="C22" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D22" s="42" t="inlineStr">
+      <c r="D22" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -7112,27 +7166,25 @@
       <c r="A23" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B23" s="41" t="n">
-        <v>145</v>
-      </c>
+      <c r="B23" s="41" t="inlineStr"/>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="54" t="inlineStr">
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7193,7 @@
         <v>46291</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
@@ -7160,7 +7212,7 @@
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -7169,26 +7221,26 @@
         <v>46291</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D25" s="54" t="inlineStr">
+      <c r="D25" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -7197,26 +7249,26 @@
         <v>46291</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="C26" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D26" s="42" t="inlineStr">
+      <c r="D26" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -7225,16 +7277,16 @@
         <v>46291</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D27" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D27" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
@@ -7244,7 +7296,7 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -7252,13 +7304,15 @@
       <c r="A28" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B28" s="33" t="inlineStr"/>
+      <c r="B28" s="33" t="n">
+        <v>210</v>
+      </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D28" s="42" t="inlineStr">
+      <c r="D28" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7270,7 +7324,7 @@
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -7278,13 +7332,15 @@
       <c r="A29" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B29" s="41" t="inlineStr"/>
+      <c r="B29" s="41" t="n">
+        <v>210</v>
+      </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D29" s="54" t="inlineStr">
+      <c r="D29" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7296,13 +7352,13 @@
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B30" s="33" t="n">
         <v>210</v>
@@ -7312,63 +7368,61 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D30" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="36" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="C31" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D31" s="54" t="inlineStr">
+      <c r="D31" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B32" s="33" t="n">
-        <v>210</v>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="B32" s="33" t="inlineStr"/>
       <c r="C32" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D32" s="42" t="inlineStr">
+      <c r="D32" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7380,7 +7434,7 @@
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
@@ -7388,13 +7442,15 @@
       <c r="A33" s="36" t="n">
         <v>46295</v>
       </c>
-      <c r="B33" s="41" t="inlineStr"/>
+      <c r="B33" s="41" t="n">
+        <v>155</v>
+      </c>
       <c r="C33" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D33" s="54" t="inlineStr">
+      <c r="D33" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7406,51 +7462,51 @@
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="31" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C34" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D34" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Air Jordan 1 Low OG “Howard” 2026</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D35" s="54" t="inlineStr">
+      <c r="D35" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7462,7 +7518,7 @@
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
@@ -7496,71 +7552,71 @@
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C37" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D37" s="54" t="inlineStr">
+      <c r="D37" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="31" t="n">
-        <v>46300</v>
-      </c>
-      <c r="B38" s="33" t="n">
-        <v>200</v>
-      </c>
+        <v>46303</v>
+      </c>
+      <c r="B38" s="33" t="inlineStr"/>
       <c r="C38" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D38" s="42" t="inlineStr">
+      <c r="D38" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E38" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B39" s="41" t="inlineStr"/>
+        <v>46305</v>
+      </c>
+      <c r="B39" s="41" t="n">
+        <v>180</v>
+      </c>
       <c r="C39" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D39" s="54" t="inlineStr">
+      <c r="D39" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7572,53 +7628,53 @@
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>180</v>
+        <v>125</v>
       </c>
       <c r="C40" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D40" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="36" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D41" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D41" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
@@ -7628,7 +7684,7 @@
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -7637,14 +7693,14 @@
         <v>46311</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C42" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D42" s="42" t="inlineStr">
+      <c r="D42" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7656,7 +7712,7 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7728,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D43" s="54" t="inlineStr">
+      <c r="D43" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7684,7 +7740,7 @@
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
@@ -7693,14 +7749,14 @@
         <v>46311</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D44" s="42" t="inlineStr">
+      <c r="D44" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7712,35 +7768,35 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D45" s="54" t="inlineStr">
+      <c r="D45" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
@@ -7749,14 +7805,14 @@
         <v>46312</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D46" s="42" t="inlineStr">
+      <c r="D46" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7768,23 +7824,23 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="36" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D47" s="54" t="inlineStr">
+      <c r="D47" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7796,7 +7852,7 @@
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7868,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D48" s="42" t="inlineStr">
+      <c r="D48" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7858,45 +7914,45 @@
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="31" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="C50" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D50" s="42" t="inlineStr">
+      <c r="D50" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46326</v>
+        <v>46320</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D51" s="54" t="inlineStr">
+      <c r="D51" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7908,35 +7964,35 @@
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="31" t="n">
-        <v>46329</v>
+        <v>46326</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D52" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D52" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
@@ -7952,9 +8008,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D53" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
@@ -7964,13 +8020,13 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="31" t="n">
-        <v>46333</v>
+        <v>46329</v>
       </c>
       <c r="B54" s="33" t="n">
         <v>240</v>
@@ -7980,19 +8036,19 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D54" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D54" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8064,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D55" s="54" t="inlineStr">
+      <c r="D55" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8026,29 +8082,29 @@
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C56" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D56" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D56" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8120,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D57" s="54" t="inlineStr">
+      <c r="D57" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8082,29 +8138,29 @@
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="31" t="n">
-        <v>46340</v>
+        <v>46337</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C58" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D58" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D58" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8169,7 @@
         <v>46340</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
@@ -8132,16 +8188,16 @@
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46342</v>
+        <v>46340</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
@@ -8160,53 +8216,53 @@
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D61" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D61" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46347</v>
+        <v>46343</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="C62" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D62" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D62" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
@@ -8216,7 +8272,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
@@ -8225,14 +8281,14 @@
         <v>46347</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D63" s="54" t="inlineStr">
+      <c r="D63" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8244,7 +8300,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -8253,14 +8309,14 @@
         <v>46347</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D64" s="42" t="inlineStr">
+      <c r="D64" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8272,7 +8328,7 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -8281,26 +8337,26 @@
         <v>46347</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D65" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D65" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -8309,42 +8365,42 @@
         <v>46347</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D66" s="42" t="inlineStr">
+      <c r="D66" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D67" s="54" t="inlineStr">
+      <c r="D67" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8356,35 +8412,35 @@
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D68" s="42" t="inlineStr">
+      <c r="D68" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
@@ -8393,16 +8449,16 @@
         <v>46354</v>
       </c>
       <c r="B69" s="41" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D69" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D69" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
@@ -8412,7 +8468,7 @@
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
@@ -8420,10 +8476,12 @@
       <c r="A70" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B70" s="33" t="inlineStr"/>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
+      <c r="B70" s="33" t="n">
+        <v>120</v>
+      </c>
+      <c r="C70" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
@@ -8433,12 +8491,12 @@
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -8447,26 +8505,26 @@
         <v>46354</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D71" s="54" t="inlineStr">
+      <c r="D71" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8533,7 @@
         <v>46354</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C72" s="39" t="inlineStr">
         <is>
@@ -8494,25 +8552,23 @@
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B73" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C73" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D73" s="54" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>46354</v>
+      </c>
+      <c r="B73" s="41" t="inlineStr"/>
+      <c r="C73" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D73" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
@@ -8522,23 +8578,25 @@
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B74" s="33" t="inlineStr"/>
+        <v>46361</v>
+      </c>
+      <c r="B74" s="33" t="n">
+        <v>215</v>
+      </c>
       <c r="C74" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D74" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D74" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
@@ -8548,7 +8606,7 @@
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
@@ -8584,32 +8642,86 @@
       <c r="A76" s="31" t="n">
         <v>46367</v>
       </c>
-      <c r="B76" s="33" t="n">
+      <c r="B76" s="33" t="inlineStr"/>
+      <c r="C76" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D76" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>Free The Youth x Air Jordan 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="36" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B77" s="41" t="n">
         <v>190</v>
       </c>
-      <c r="C76" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D76" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="C77" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D77" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E77" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F77" s="35" t="inlineStr">
         <is>
           <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="31" t="n">
+        <v>46368</v>
+      </c>
+      <c r="B78" s="33" t="n">
+        <v>235</v>
+      </c>
+      <c r="C78" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D78" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E78" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F78" s="30" t="inlineStr">
+        <is>
+          <t>Air Jordan 11 “Space Jam” 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:F76"/>
+  <autoFilter ref="A3:F78"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -1581,7 +1581,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 13, 2026  ·  11:17 UTC</t>
+          <t>Generated September 14, 2026  ·  12:06 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1737,7 +1737,7 @@
         <v>46290</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46280</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46280</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="40" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>46281</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>46282</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
@@ -1927,19 +1927,19 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C16" s="31" t="n">
         <v>46283</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
@@ -1950,11 +1950,11 @@
         <v>7</v>
       </c>
       <c r="G16" s="33" t="n">
-        <v>250</v>
-      </c>
-      <c r="H16" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B29" s="30" t="inlineStr">
         <is>
-          <t>9/13 – 9/19</t>
+          <t>9/14 – 9/20</t>
         </is>
       </c>
       <c r="C29" s="30" t="n">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B30" s="35" t="inlineStr">
         <is>
-          <t>9/20 – 9/26</t>
+          <t>9/21 – 9/27</t>
         </is>
       </c>
       <c r="C30" s="35" t="n">
@@ -2213,14 +2213,14 @@
       </c>
       <c r="B31" s="30" t="inlineStr">
         <is>
-          <t>9/27 – 10/3</t>
+          <t>9/28 – 10/4</t>
         </is>
       </c>
       <c r="C31" s="30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31" s="39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E31" s="30" t="n">
         <v>5.8</v>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B32" s="35" t="inlineStr">
         <is>
-          <t>10/4 – 10/10</t>
+          <t>10/5 – 10/11</t>
         </is>
       </c>
       <c r="C32" s="35" t="n">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B33" s="30" t="inlineStr">
         <is>
-          <t>10/11 – 10/17</t>
+          <t>10/12 – 10/18</t>
         </is>
       </c>
       <c r="C33" s="30" t="n">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="B34" s="35" t="inlineStr">
         <is>
-          <t>10/18 – 10/24</t>
+          <t>10/19 – 10/25</t>
         </is>
       </c>
       <c r="C34" s="35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34" s="40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" s="35" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="B35" s="30" t="inlineStr">
         <is>
-          <t>10/25 – 10/31</t>
+          <t>10/26 – 11/1</t>
         </is>
       </c>
       <c r="C35" s="30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" s="30" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B36" s="35" t="inlineStr">
         <is>
-          <t>11/1 – 11/7</t>
+          <t>11/2 – 11/8</t>
         </is>
       </c>
       <c r="C36" s="35" t="n">
@@ -2339,17 +2339,17 @@
       </c>
       <c r="B37" s="30" t="inlineStr">
         <is>
-          <t>11/8 – 11/14</t>
+          <t>11/9 – 11/15</t>
         </is>
       </c>
       <c r="C37" s="30" t="n">
         <v>8</v>
       </c>
       <c r="D37" s="39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" s="30" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B38" s="35" t="inlineStr">
         <is>
-          <t>11/15 – 11/21</t>
+          <t>11/16 – 11/22</t>
         </is>
       </c>
       <c r="C38" s="35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D38" s="40" t="n">
         <v>7</v>
       </c>
       <c r="E38" s="35" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B39" s="30" t="inlineStr">
         <is>
-          <t>11/22 – 11/28</t>
+          <t>11/23 – 11/29</t>
         </is>
       </c>
       <c r="C39" s="30" t="n">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>11/29 – 12/5</t>
+          <t>11/30 – 12/6</t>
         </is>
       </c>
       <c r="C40" s="35" t="n">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>12/6 – 12/12</t>
+          <t>12/7 – 12/13</t>
         </is>
       </c>
       <c r="C41" s="30" t="n">
@@ -2718,7 +2718,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 13, 2026  ·  11:17 UTC</t>
+          <t>Generated September 14, 2026  ·  12:06 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2988,26 +2988,26 @@
         <v>46283</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="C12" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
         <v>46283</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C13" s="40" t="inlineStr">
         <is>
@@ -3030,12 +3030,12 @@
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
         </is>
       </c>
     </row>
@@ -3044,11 +3044,11 @@
         <v>46283</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C14" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>135</v>
+      </c>
+      <c r="C14" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D14" s="34" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>PSG x Nike KD 6</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
         <v>46283</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C15" s="40" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>APB x Air Jordan 11 Low</t>
         </is>
       </c>
     </row>
@@ -3100,16 +3100,16 @@
         <v>46283</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C16" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D16" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>PSG x Nike KD 6</t>
+          <t>Nike A’Two “Dawn Staley”</t>
         </is>
       </c>
     </row>
@@ -3128,11 +3128,11 @@
         <v>46283</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C17" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>65</v>
+      </c>
+      <c r="C17" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D17" s="42" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
         </is>
       </c>
     </row>
@@ -3156,11 +3156,11 @@
         <v>46283</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C18" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>250</v>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D18" s="43" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Nike A’Two “Dawn Staley”</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
     </row>
@@ -3184,11 +3184,11 @@
         <v>46283</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>65</v>
-      </c>
-      <c r="C19" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>210</v>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D19" s="42" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
     </row>
@@ -3772,26 +3772,26 @@
         <v>46291</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="C40" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D40" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
         <v>46291</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -3827,17 +3827,15 @@
       <c r="A42" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B42" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C42" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D42" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B42" s="33" t="inlineStr"/>
+      <c r="C42" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D42" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E42" s="30" t="inlineStr">
@@ -3847,7 +3845,7 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -3855,17 +3853,15 @@
       <c r="A43" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B43" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C43" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D43" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B43" s="41" t="inlineStr"/>
+      <c r="C43" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D43" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
@@ -3875,7 +3871,7 @@
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
@@ -3884,16 +3880,16 @@
         <v>46291</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D44" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E44" s="30" t="inlineStr">
@@ -3903,7 +3899,7 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -3911,15 +3907,17 @@
       <c r="A45" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B45" s="41" t="inlineStr"/>
-      <c r="C45" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D45" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B45" s="41" t="n">
+        <v>200</v>
+      </c>
+      <c r="C45" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D45" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
@@ -3929,7 +3927,7 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3935,9 @@
       <c r="A46" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B46" s="33" t="inlineStr"/>
+      <c r="B46" s="33" t="n">
+        <v>200</v>
+      </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -3963,27 +3963,25 @@
       <c r="A47" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B47" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C47" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D47" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B47" s="41" t="inlineStr"/>
+      <c r="C47" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D47" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
@@ -3992,26 +3990,26 @@
         <v>46291</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C48" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D48" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>155</v>
+      </c>
+      <c r="C48" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -4020,26 +4018,26 @@
         <v>46291</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D49" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D49" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -4047,10 +4045,12 @@
       <c r="A50" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B50" s="33" t="inlineStr"/>
-      <c r="C50" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B50" s="33" t="n">
+        <v>210</v>
+      </c>
+      <c r="C50" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D50" s="43" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -4076,24 +4076,24 @@
       <c r="B51" s="41" t="n">
         <v>155</v>
       </c>
-      <c r="C51" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D51" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="C51" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D51" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
@@ -4102,26 +4102,26 @@
         <v>46291</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C52" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D52" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>160</v>
+      </c>
+      <c r="C52" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D52" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
         <v>46291</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
         <v>46291</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C54" s="48" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -4517,19 +4517,19 @@
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D67" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D67" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
@@ -4548,16 +4548,16 @@
         <v>46298</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D68" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D68" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
@@ -4567,43 +4567,45 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="B69" s="41" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D69" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D69" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B70" s="33" t="inlineStr"/>
+        <v>46300</v>
+      </c>
+      <c r="B70" s="33" t="n">
+        <v>200</v>
+      </c>
       <c r="C70" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -4616,12 +4618,12 @@
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
@@ -4629,12 +4631,10 @@
       <c r="A71" s="36" t="n">
         <v>46303</v>
       </c>
-      <c r="B71" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C71" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B71" s="41" t="inlineStr"/>
+      <c r="C71" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D71" s="42" t="inlineStr">
@@ -4644,25 +4644,25 @@
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C72" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C72" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D72" s="43" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
+          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
         </is>
       </c>
     </row>
@@ -4686,11 +4686,11 @@
         <v>46304</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C73" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>170</v>
+      </c>
+      <c r="C73" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D73" s="42" t="inlineStr">
@@ -4700,25 +4700,25 @@
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
+          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C74" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>130</v>
+      </c>
+      <c r="C74" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D74" s="43" t="inlineStr">
@@ -4728,25 +4728,25 @@
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46310</v>
+        <v>46305</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C75" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>180</v>
+      </c>
+      <c r="C75" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D75" s="42" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
@@ -4772,42 +4772,42 @@
       <c r="B76" s="33" t="n">
         <v>125</v>
       </c>
-      <c r="C76" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D76" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C76" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D76" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="36" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B77" s="41" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="C77" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D77" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D77" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
         <v>46311</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C78" s="39" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
         <v>46311</v>
       </c>
       <c r="B80" s="33" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C80" s="39" t="inlineStr">
         <is>
@@ -4901,16 +4901,16 @@
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="36" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B81" s="41" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C81" s="40" t="inlineStr">
         <is>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="E81" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F81" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
         <v>46312</v>
       </c>
       <c r="B82" s="33" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C82" s="39" t="inlineStr">
         <is>
@@ -4957,18 +4957,20 @@
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="36" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B83" s="41" t="inlineStr"/>
-      <c r="C83" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>46312</v>
+      </c>
+      <c r="B83" s="41" t="n">
+        <v>215</v>
+      </c>
+      <c r="C83" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D83" s="42" t="inlineStr">
@@ -4978,25 +4980,23 @@
       </c>
       <c r="E83" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F83" s="35" t="inlineStr">
         <is>
-          <t>SZA x Vans VANSZA Collection</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="31" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B84" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C84" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46317</v>
+      </c>
+      <c r="B84" s="33" t="inlineStr"/>
+      <c r="C84" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D84" s="43" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>SZA x Vans VANSZA Collection</t>
         </is>
       </c>
     </row>
@@ -5020,11 +5020,11 @@
         <v>46319</v>
       </c>
       <c r="B85" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C85" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>140</v>
+      </c>
+      <c r="C85" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D85" s="42" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
@@ -5048,11 +5048,11 @@
         <v>46319</v>
       </c>
       <c r="B86" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C86" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C86" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D86" s="43" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E86" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
@@ -5076,26 +5076,26 @@
         <v>46319</v>
       </c>
       <c r="B87" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C87" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D87" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>150</v>
+      </c>
+      <c r="C87" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D87" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E87" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
@@ -5104,11 +5104,11 @@
         <v>46319</v>
       </c>
       <c r="B88" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C88" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>170</v>
+      </c>
+      <c r="C88" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D88" s="34" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
@@ -5132,16 +5132,16 @@
         <v>46319</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="C89" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D89" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D89" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E89" s="35" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
@@ -5160,11 +5160,11 @@
         <v>46319</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C90" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>190</v>
+      </c>
+      <c r="C90" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D90" s="43" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
         <v>46319</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="C91" s="40" t="inlineStr">
         <is>
@@ -5202,21 +5202,21 @@
       </c>
       <c r="E91" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="31" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B92" s="33" t="n">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="C92" s="39" t="inlineStr">
         <is>
@@ -5230,40 +5230,40 @@
       </c>
       <c r="E92" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="36" t="n">
-        <v>46325</v>
+        <v>46320</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C93" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D93" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>205</v>
+      </c>
+      <c r="C93" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D93" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E93" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 High “University Red”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
@@ -5300,16 +5300,16 @@
         <v>46325</v>
       </c>
       <c r="B95" s="41" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C95" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D95" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D95" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E95" s="35" t="inlineStr">
@@ -5319,20 +5319,20 @@
       </c>
       <c r="F95" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Halloween”</t>
+          <t>Nike Ja 4 High “University Red”</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="31" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="B96" s="33" t="n">
-        <v>215</v>
-      </c>
-      <c r="C96" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>155</v>
+      </c>
+      <c r="C96" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D96" s="43" t="inlineStr">
@@ -5342,40 +5342,40 @@
       </c>
       <c r="E96" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Nike Book 2 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="36" t="n">
-        <v>46329</v>
+        <v>46326</v>
       </c>
       <c r="B97" s="41" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C97" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D97" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D97" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E97" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F97" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
@@ -5391,9 +5391,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D98" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D98" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E98" s="30" t="inlineStr">
@@ -5403,20 +5403,20 @@
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="36" t="n">
-        <v>46331</v>
+        <v>46329</v>
       </c>
       <c r="B99" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C99" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>240</v>
+      </c>
+      <c r="C99" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D99" s="42" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F99" s="35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
@@ -5459,16 +5459,16 @@
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="36" t="n">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="B101" s="41" t="n">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="C101" s="53" t="inlineStr">
         <is>
@@ -5487,20 +5487,20 @@
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Desert Night”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="31" t="n">
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="B102" s="33" t="n">
-        <v>215</v>
-      </c>
-      <c r="C102" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>145</v>
+      </c>
+      <c r="C102" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D102" s="43" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E102" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Book 2 “Desert Night”</t>
         </is>
       </c>
     </row>
@@ -5524,16 +5524,16 @@
         <v>46333</v>
       </c>
       <c r="B103" s="41" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C103" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D103" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D103" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E103" s="35" t="inlineStr">
@@ -5543,25 +5543,25 @@
       </c>
       <c r="F103" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="31" t="n">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="B104" s="33" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C104" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D104" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D104" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E104" s="30" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="F104" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Lapis”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
         <v>46337</v>
       </c>
       <c r="B105" s="41" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="C105" s="40" t="inlineStr">
         <is>
@@ -5594,30 +5594,30 @@
       </c>
       <c r="E105" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 11 “Lapis”</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="31" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B106" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C106" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D106" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>200</v>
+      </c>
+      <c r="C106" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D106" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E106" s="30" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="F106" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal” 2026</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
@@ -5636,26 +5636,26 @@
         <v>46338</v>
       </c>
       <c r="B107" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C107" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D107" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>170</v>
+      </c>
+      <c r="C107" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D107" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E107" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F107" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
+          <t>Nike Air Bakin “Varsity Royal” 2026</t>
         </is>
       </c>
     </row>
@@ -5664,11 +5664,11 @@
         <v>46338</v>
       </c>
       <c r="B108" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C108" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C108" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D108" s="43" t="inlineStr">
@@ -5678,40 +5678,40 @@
       </c>
       <c r="E108" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F108" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal”</t>
+          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
         </is>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="36" t="n">
-        <v>46340</v>
+        <v>46338</v>
       </c>
       <c r="B109" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C109" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D109" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C109" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D109" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E109" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Air Bakin “Varsity Royal”</t>
         </is>
       </c>
     </row>
@@ -5720,11 +5720,11 @@
         <v>46340</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C110" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>255</v>
+      </c>
+      <c r="C110" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D110" s="34" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
@@ -5748,11 +5748,11 @@
         <v>46340</v>
       </c>
       <c r="B111" s="41" t="n">
-        <v>220</v>
-      </c>
-      <c r="C111" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>240</v>
+      </c>
+      <c r="C111" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D111" s="38" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 Be “Legendary”</t>
+          <t>Nike Book 2 “Be Legendary”</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
         <v>46347</v>
       </c>
       <c r="B118" s="33" t="n">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="C118" s="39" t="inlineStr">
         <is>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F118" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -5972,11 +5972,11 @@
         <v>46347</v>
       </c>
       <c r="B119" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C119" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>140</v>
+      </c>
+      <c r="C119" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D119" s="42" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
@@ -6000,16 +6000,16 @@
         <v>46347</v>
       </c>
       <c r="B120" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C120" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D120" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>230</v>
+      </c>
+      <c r="C120" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D120" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E120" s="30" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="F120" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Snow White”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -6028,26 +6028,26 @@
         <v>46347</v>
       </c>
       <c r="B121" s="41" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C121" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D121" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D121" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E121" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F121" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
         <v>46347</v>
       </c>
       <c r="B122" s="33" t="n">
-        <v>215</v>
+        <v>140</v>
       </c>
       <c r="C122" s="39" t="inlineStr">
         <is>
@@ -6070,12 +6070,12 @@
       </c>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F122" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
         <v>46347</v>
       </c>
       <c r="B123" s="41" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C123" s="40" t="inlineStr">
         <is>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E123" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F123" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
         <v>46353</v>
       </c>
       <c r="B124" s="33" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C124" s="39" t="inlineStr">
         <is>
@@ -6126,12 +6126,12 @@
       </c>
       <c r="E124" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F124" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
@@ -6140,11 +6140,11 @@
         <v>46353</v>
       </c>
       <c r="B125" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C125" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>240</v>
+      </c>
+      <c r="C125" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D125" s="42" t="inlineStr">
@@ -6154,25 +6154,25 @@
       </c>
       <c r="E125" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F125" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Black”</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="31" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B126" s="33" t="n">
-        <v>190</v>
-      </c>
-      <c r="C126" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>130</v>
+      </c>
+      <c r="C126" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D126" s="43" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="E126" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Vans Old Skool 36 Pearlized “Black”</t>
         </is>
       </c>
     </row>
@@ -6251,12 +6251,10 @@
       <c r="A129" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B129" s="41" t="n">
-        <v>230</v>
-      </c>
-      <c r="C129" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B129" s="41" t="inlineStr"/>
+      <c r="C129" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D129" s="42" t="inlineStr">
@@ -6266,12 +6264,12 @@
       </c>
       <c r="E129" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F129" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike KD 6 “Aunt Pearl” 2026</t>
         </is>
       </c>
     </row>
@@ -6279,15 +6277,17 @@
       <c r="A130" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B130" s="33" t="inlineStr"/>
-      <c r="C130" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D130" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B130" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="C130" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D130" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E130" s="30" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="F130" s="30" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Aunt Pearl” 2026</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,10 @@
       <c r="A131" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B131" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C131" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B131" s="41" t="inlineStr"/>
+      <c r="C131" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
         </is>
       </c>
       <c r="D131" s="38" t="inlineStr">
@@ -6320,12 +6318,12 @@
       </c>
       <c r="E131" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F131" s="35" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
@@ -6333,25 +6331,27 @@
       <c r="A132" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B132" s="33" t="inlineStr"/>
-      <c r="C132" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D132" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B132" s="33" t="n">
+        <v>190</v>
+      </c>
+      <c r="C132" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D132" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E132" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F132" s="30" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
@@ -6443,9 +6443,7 @@
       <c r="A136" s="31" t="n">
         <v>46367</v>
       </c>
-      <c r="B136" s="33" t="n">
-        <v>150</v>
-      </c>
+      <c r="B136" s="33" t="inlineStr"/>
       <c r="C136" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6463,7 +6461,7 @@
       </c>
       <c r="F136" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6469,9 @@
       <c r="A137" s="36" t="n">
         <v>46367</v>
       </c>
-      <c r="B137" s="41" t="inlineStr"/>
+      <c r="B137" s="41" t="n">
+        <v>150</v>
+      </c>
       <c r="C137" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="F137" s="35" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 13, 2026  ·  11:17 UTC</t>
+          <t>Generated September 14, 2026  ·  12:06 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -6749,26 +6749,26 @@
         <v>46283</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
         <v>46283</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
@@ -6791,12 +6791,12 @@
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
         </is>
       </c>
     </row>
@@ -6805,16 +6805,16 @@
         <v>46283</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>APB x Air Jordan 11 Low</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
         <v>46283</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
@@ -6847,12 +6847,12 @@
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
         <v>46283</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C12" s="39" t="inlineStr">
         <is>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7085,7 @@
         <v>46291</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -7112,9 +7112,7 @@
       <c r="A21" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B21" s="41" t="n">
-        <v>140</v>
-      </c>
+      <c r="B21" s="41" t="inlineStr"/>
       <c r="C21" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -7132,7 +7130,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7156,7 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
@@ -7166,15 +7164,17 @@
       <c r="A23" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B23" s="41" t="inlineStr"/>
+      <c r="B23" s="41" t="n">
+        <v>210</v>
+      </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D23" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -7193,26 +7193,26 @@
         <v>46291</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D24" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D24" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E24" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
         <v>46291</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -7249,26 +7249,26 @@
         <v>46291</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C26" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D26" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -7277,16 +7277,16 @@
         <v>46291</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D27" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D27" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
         <v>46291</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -7496,19 +7496,19 @@
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D35" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D35" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
@@ -7527,16 +7527,16 @@
         <v>46298</v>
       </c>
       <c r="B36" s="33" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C36" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D36" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D36" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
@@ -7546,43 +7546,45 @@
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C37" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D37" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D37" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="31" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B38" s="33" t="inlineStr"/>
+        <v>46300</v>
+      </c>
+      <c r="B38" s="33" t="n">
+        <v>200</v>
+      </c>
       <c r="C38" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -7595,22 +7597,20 @@
       </c>
       <c r="E38" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>46305</v>
-      </c>
-      <c r="B39" s="41" t="n">
-        <v>180</v>
-      </c>
+        <v>46303</v>
+      </c>
+      <c r="B39" s="41" t="inlineStr"/>
       <c r="C39" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -7628,53 +7628,53 @@
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46310</v>
+        <v>46305</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="C40" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D40" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D40" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="36" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D41" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D41" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
         <v>46311</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C42" s="39" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
         <v>46311</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
@@ -7768,16 +7768,16 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
@@ -7791,12 +7791,12 @@
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
         <v>46312</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
@@ -7824,16 +7824,16 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="36" t="n">
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
@@ -7861,16 +7861,16 @@
         <v>46319</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D48" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
@@ -7889,16 +7889,16 @@
         <v>46319</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D49" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D49" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
@@ -7917,7 +7917,7 @@
         <v>46319</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="C50" s="39" t="inlineStr">
         <is>
@@ -7931,21 +7931,21 @@
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
@@ -7959,21 +7959,21 @@
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="31" t="n">
-        <v>46326</v>
+        <v>46320</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
@@ -7992,35 +7992,35 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="36" t="n">
-        <v>46329</v>
+        <v>46326</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D53" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
@@ -8036,9 +8036,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D54" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
@@ -8048,16 +8048,16 @@
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46333</v>
+        <v>46329</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
@@ -8071,12 +8071,12 @@
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
@@ -8085,16 +8085,16 @@
         <v>46333</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C56" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D56" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D56" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
@@ -8104,25 +8104,25 @@
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C57" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D57" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D57" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Lapis”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
         <v>46337</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="C58" s="39" t="inlineStr">
         <is>
@@ -8155,40 +8155,40 @@
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 11 “Lapis”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46340</v>
+        <v>46337</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D59" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D59" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8197,7 @@
         <v>46340</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
         <v>46347</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -8309,16 +8309,16 @@
         <v>46347</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>125</v>
+        <v>230</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D64" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -8337,26 +8337,26 @@
         <v>46347</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D65" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D65" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
         <v>46347</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>215</v>
+        <v>140</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
@@ -8393,7 +8393,7 @@
         <v>46347</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8421,7 @@
         <v>46353</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
@@ -8435,21 +8435,21 @@
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B69" s="41" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
@@ -8505,26 +8505,26 @@
         <v>46354</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D71" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D71" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
@@ -8532,12 +8532,10 @@
       <c r="A72" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B72" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C72" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B72" s="33" t="inlineStr"/>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
         </is>
       </c>
       <c r="D72" s="34" t="inlineStr">
@@ -8547,12 +8545,12 @@
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
@@ -8560,25 +8558,27 @@
       <c r="A73" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B73" s="41" t="inlineStr"/>
-      <c r="C73" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D73" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B73" s="41" t="n">
+        <v>190</v>
+      </c>
+      <c r="C73" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D73" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
@@ -8614,9 +8614,7 @@
       <c r="A75" s="36" t="n">
         <v>46367</v>
       </c>
-      <c r="B75" s="41" t="n">
-        <v>150</v>
-      </c>
+      <c r="B75" s="41" t="inlineStr"/>
       <c r="C75" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -8634,7 +8632,7 @@
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8640,9 @@
       <c r="A76" s="31" t="n">
         <v>46367</v>
       </c>
-      <c r="B76" s="33" t="inlineStr"/>
+      <c r="B76" s="33" t="n">
+        <v>150</v>
+      </c>
       <c r="C76" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>

--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High Hype Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$139</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -648,10 +648,10 @@
     <xf numFmtId="166" fontId="10" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -808,12 +808,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Charts'!$A$2:$A$7</f>
+              <f>'Charts'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$B$2:$B$7</f>
+              <f>'Charts'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1581,7 +1581,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 14, 2026  ·  12:06 UTC</t>
+          <t>Generated September 15, 2026  ·  11:19 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1621,20 +1621,20 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="16" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>$180</t>
+          <t>$179</t>
         </is>
       </c>
       <c r="H5" s="19" t="n"/>
@@ -1737,7 +1737,7 @@
         <v>46290</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="30" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 “Iron Grey”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
       <c r="B12" s="30" t="inlineStr">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="C12" s="31" t="n">
-        <v>46280</v>
+        <v>46295</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="F12" s="30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" s="33" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H12" s="34" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
+          <t>Yuto Horigome x Nike SB Air Force 1 “Iron Grey”</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
@@ -1837,7 +1837,7 @@
         <v>46280</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="40" t="inlineStr">
         <is>
@@ -1850,28 +1850,28 @@
       <c r="G13" s="41" t="n">
         <v>125</v>
       </c>
-      <c r="H13" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="H13" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 Low “Metamorphosis”</t>
+          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="C14" s="31" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
@@ -1882,9 +1882,9 @@
         <v>7</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="H14" s="43" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="H14" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -1893,7 +1893,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>Air Jordan 6 Low “Metamorphosis”</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
@@ -1916,18 +1916,18 @@
         <v>7</v>
       </c>
       <c r="G15" s="41" t="n">
-        <v>220</v>
-      </c>
-      <c r="H15" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>205</v>
+      </c>
+      <c r="H15" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Air Jordan 4 “London”</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="C16" s="31" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>7</v>
       </c>
       <c r="G16" s="33" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="H16" s="34" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B20" s="30" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="E21" s="35" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G21" s="47" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="H21" s="35" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="B22" s="30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="E22" s="30" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G22" s="49" t="inlineStr">
         <is>
@@ -2098,341 +2098,351 @@
         </is>
       </c>
       <c r="E23" s="35" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="B24" s="30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="46" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="B25" s="35" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="26" ht="10" customHeight="1"/>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>ASICS</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="10" customHeight="1"/>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>Weekly Outlook (Next 13 Weeks)</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>Dates</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="C29" s="29" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
       </c>
-      <c r="D28" s="29" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t>HIGH+EXTREME</t>
         </is>
       </c>
-      <c r="E28" s="29" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>Avg Hype Score</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="30" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="B29" s="30" t="inlineStr">
-        <is>
-          <t>9/14 – 9/20</t>
-        </is>
-      </c>
-      <c r="C29" s="30" t="n">
-        <v>25</v>
-      </c>
-      <c r="D29" s="39" t="n">
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>9/15 – 9/21</t>
+        </is>
+      </c>
+      <c r="C30" s="30" t="n">
+        <v>26</v>
+      </c>
+      <c r="D30" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="E29" s="30" t="n">
+      <c r="E30" s="30" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>9/22 – 9/28</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="D31" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" s="35" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>9/29 – 10/5</t>
+        </is>
+      </c>
+      <c r="C32" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="D32" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>10/6 – 10/12</t>
+        </is>
+      </c>
+      <c r="C33" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="35" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>10/13 – 10/19</t>
+        </is>
+      </c>
+      <c r="C34" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" s="30" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="35" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="B35" s="35" t="inlineStr">
+        <is>
+          <t>10/20 – 10/26</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="35" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>10/27 – 11/2</t>
+        </is>
+      </c>
+      <c r="C36" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="30" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="35" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="B37" s="35" t="inlineStr">
+        <is>
+          <t>11/3 – 11/9</t>
+        </is>
+      </c>
+      <c r="C37" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" s="35" t="n">
         <v>5.7</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="35" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="B30" s="35" t="inlineStr">
-        <is>
-          <t>9/21 – 9/27</t>
-        </is>
-      </c>
-      <c r="C30" s="35" t="n">
-        <v>28</v>
-      </c>
-      <c r="D30" s="40" t="n">
-        <v>13</v>
-      </c>
-      <c r="E30" s="35" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>9/28 – 10/4</t>
-        </is>
-      </c>
-      <c r="C31" s="30" t="n">
-        <v>13</v>
-      </c>
-      <c r="D31" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="E31" s="30" t="n">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="35" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="B32" s="35" t="inlineStr">
-        <is>
-          <t>10/5 – 10/11</t>
-        </is>
-      </c>
-      <c r="C32" s="35" t="n">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="inlineStr">
+        <is>
+          <t>11/10 – 11/16</t>
+        </is>
+      </c>
+      <c r="C38" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" s="30" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>11/17 – 11/23</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D39" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="D32" s="40" t="n">
+      <c r="E39" s="35" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
+        <is>
+          <t>11/24 – 11/30</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" s="30" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>12/1 – 12/7</t>
+        </is>
+      </c>
+      <c r="C41" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="35" t="n">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="B33" s="30" t="inlineStr">
-        <is>
-          <t>10/12 – 10/18</t>
-        </is>
-      </c>
-      <c r="C33" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="E33" s="30" t="n">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="35" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="B34" s="35" t="inlineStr">
-        <is>
-          <t>10/19 – 10/25</t>
-        </is>
-      </c>
-      <c r="C34" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="D34" s="40" t="n">
+      <c r="D41" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" s="35" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>12/8 – 12/14</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="E34" s="35" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="B35" s="30" t="inlineStr">
-        <is>
-          <t>10/26 – 11/1</t>
-        </is>
-      </c>
-      <c r="C35" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="30" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="35" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="B36" s="35" t="inlineStr">
-        <is>
-          <t>11/2 – 11/8</t>
-        </is>
-      </c>
-      <c r="C36" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="D36" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" s="35" t="n">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t>Week 9</t>
-        </is>
-      </c>
-      <c r="B37" s="30" t="inlineStr">
-        <is>
-          <t>11/9 – 11/15</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" s="30" t="n">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="35" t="inlineStr">
-        <is>
-          <t>Week 10</t>
-        </is>
-      </c>
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>11/16 – 11/22</t>
-        </is>
-      </c>
-      <c r="C38" s="35" t="n">
-        <v>11</v>
-      </c>
-      <c r="D38" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="E38" s="35" t="n">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="30" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="inlineStr">
-        <is>
-          <t>11/23 – 11/29</t>
-        </is>
-      </c>
-      <c r="C39" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="D39" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E39" s="30" t="n">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="35" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>11/30 – 12/6</t>
-        </is>
-      </c>
-      <c r="C40" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D40" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="35" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="B41" s="30" t="inlineStr">
-        <is>
-          <t>12/7 – 12/13</t>
-        </is>
-      </c>
-      <c r="C41" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="D41" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="30" t="n">
+      <c r="D42" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" s="30" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2449,9 +2459,9 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C4:D4"/>
@@ -2466,7 +2476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2531,7 +2541,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2547,7 +2557,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2573,7 +2583,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2581,7 +2591,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2589,7 +2599,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -2599,7 +2609,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2607,7 +2617,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2641,7 +2651,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2649,17 +2659,17 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2673,11 +2683,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ASICS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2692,7 +2712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2718,7 +2738,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 14, 2026  ·  12:06 UTC</t>
+          <t>Generated September 15, 2026  ·  11:19 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2820,26 +2840,26 @@
         <v>46280</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C6" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="43" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Cold Blooded”</t>
+          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
         </is>
       </c>
     </row>
@@ -2848,14 +2868,14 @@
         <v>46280</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D7" s="42" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C7" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2867,35 +2887,35 @@
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
+          <t>Nike First Sight Shadow “Light Crimson” (W)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="31" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C8" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D8" s="43" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Nike First Sight Shadow “Light Crimson” (W)</t>
+          <t>Air Jordan 6 Low “Metamorphosis”</t>
         </is>
       </c>
     </row>
@@ -2904,82 +2924,82 @@
         <v>46281</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C9" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D9" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C9" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 Low “Metamorphosis”</t>
+          <t>Reebok Brutus Low “Philadelphia Eagles”</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="31" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C10" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>220</v>
+      </c>
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Reebok Brutus Low “Philadelphia Eagles”</t>
+          <t>Air Jordan 4 “London”</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="36" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D11" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3043,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D13" s="42" t="inlineStr">
+      <c r="D13" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3079,7 +3099,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D15" s="42" t="inlineStr">
+      <c r="D15" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3100,26 +3120,26 @@
         <v>46283</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C16" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D16" s="43" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C16" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Nike A’Two “Dawn Staley”</t>
+          <t>adidas Anthony Edwards 3 “Cold Blooded”</t>
         </is>
       </c>
     </row>
@@ -3128,26 +3148,26 @@
         <v>46283</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>65</v>
-      </c>
-      <c r="C17" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="42" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C17" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
+          <t>Nike A’Two “Dawn Staley”</t>
         </is>
       </c>
     </row>
@@ -3156,26 +3176,26 @@
         <v>46283</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>250</v>
-      </c>
-      <c r="C18" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D18" s="43" t="inlineStr">
+        <v>65</v>
+      </c>
+      <c r="C18" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
         </is>
       </c>
     </row>
@@ -3184,14 +3204,14 @@
         <v>46283</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="C19" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D19" s="42" t="inlineStr">
+      <c r="D19" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3203,7 +3223,7 @@
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
     </row>
@@ -3212,42 +3232,42 @@
         <v>46283</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>250</v>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D20" s="43" t="inlineStr">
+        <v>110</v>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo”</t>
+          <t>Anthony Edwards x adidas Superstar “Cold Blooded”</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="36" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>122</v>
+        <v>250</v>
       </c>
       <c r="C21" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D21" s="42" t="inlineStr">
+      <c r="D21" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3259,7 +3279,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>Nike Air Foamposite Pro “Green Camo”</t>
         </is>
       </c>
     </row>
@@ -3268,14 +3288,14 @@
         <v>46284</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>200</v>
+        <v>122</v>
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D22" s="43" t="inlineStr">
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3287,7 +3307,7 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
         </is>
       </c>
     </row>
@@ -3296,26 +3316,26 @@
         <v>46284</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>Nike Kobe 8 Protro “Mambacurial”</t>
         </is>
       </c>
     </row>
@@ -3324,26 +3344,26 @@
         <v>46284</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>300</v>
-      </c>
-      <c r="C24" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D24" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>205</v>
+      </c>
+      <c r="C24" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D24" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E24" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
+          <t>APB x Air Jordan 11 Low Pack</t>
         </is>
       </c>
     </row>
@@ -3352,26 +3372,26 @@
         <v>46284</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>215</v>
+        <v>300</v>
       </c>
       <c r="C25" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D25" s="42" t="inlineStr">
+      <c r="D25" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 9 OG “Space Jam” 2026</t>
+          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
         </is>
       </c>
     </row>
@@ -3380,26 +3400,26 @@
         <v>46284</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>110</v>
-      </c>
-      <c r="C26" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D26" s="43" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C26" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Pokémon x adidas 30th Anniversary Collection</t>
+          <t>Air Jordan 9 OG “Space Jam” 2026</t>
         </is>
       </c>
     </row>
@@ -3408,26 +3428,26 @@
         <v>46284</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C27" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D27" s="42" t="inlineStr">
+        <v>110</v>
+      </c>
+      <c r="C27" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Ope Ope”</t>
+          <t>Pokémon x adidas 30th Anniversary Collection</t>
         </is>
       </c>
     </row>
@@ -3436,60 +3456,60 @@
         <v>46284</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="C28" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
+      <c r="D28" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish</t>
+          <t>One Piece x Nike Air Max Plus “Ope Ope”</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="36" t="n">
-        <v>46287</v>
+        <v>46284</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="C29" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D29" s="42" t="inlineStr">
+      <c r="D29" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Nike GT Future “Varsity Red”</t>
+          <t>Pharrell x adidas Adistar Jellyfish</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="31" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B30" s="33" t="n">
         <v>210</v>
@@ -3499,7 +3519,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D30" s="43" t="inlineStr">
+      <c r="D30" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3511,35 +3531,35 @@
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Nike GT Future “Unseen Hours”</t>
+          <t>Nike GT Future “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="36" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C31" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D31" s="42" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C31" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Green Beam”</t>
+          <t>Nike GT Future “Unseen Hours”</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3575,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D32" s="43" t="inlineStr">
+      <c r="D32" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3567,91 +3587,91 @@
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Ghosted”</t>
+          <t>Converse SHAI 001 “Green Beam”</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="36" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>225</v>
-      </c>
-      <c r="C33" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D33" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C33" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Converse SHAI 001 “Ghosted”</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="31" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C34" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D34" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C34" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Converse SHAI 001 Shroud “Shock”</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C35" s="50" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D35" s="42" t="inlineStr">
+      <c r="D35" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Billionaire Boys Club x Reebok Club C 85</t>
+          <t>Converse SHAI 001 “Spark”</t>
         </is>
       </c>
     </row>
@@ -3660,11 +3680,11 @@
         <v>46290</v>
       </c>
       <c r="B36" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C36" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>225</v>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
         </is>
       </c>
       <c r="D36" s="34" t="inlineStr">
@@ -3679,7 +3699,7 @@
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
@@ -3688,26 +3708,26 @@
         <v>46290</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C37" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D37" s="42" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D37" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
@@ -3716,26 +3736,26 @@
         <v>46290</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C38" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D38" s="43" t="inlineStr">
+        <v>120</v>
+      </c>
+      <c r="C38" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E38" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws”</t>
+          <t>Billionaire Boys Club x Reebok Club C 85</t>
         </is>
       </c>
     </row>
@@ -3744,44 +3764,44 @@
         <v>46290</v>
       </c>
       <c r="B39" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C39" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D39" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C39" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D39" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="C40" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D40" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D40" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
@@ -3791,23 +3811,23 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="36" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B41" s="41" t="n">
         <v>140</v>
       </c>
-      <c r="C41" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D41" s="42" t="inlineStr">
+      <c r="C41" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D41" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3819,21 +3839,23 @@
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Nike Ja 4 “Jaws”</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="31" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B42" s="33" t="inlineStr"/>
-      <c r="C42" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D42" s="43" t="inlineStr">
+        <v>46290</v>
+      </c>
+      <c r="B42" s="33" t="n">
+        <v>210</v>
+      </c>
+      <c r="C42" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D42" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3845,7 +3867,7 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
         </is>
       </c>
     </row>
@@ -3853,15 +3875,17 @@
       <c r="A43" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B43" s="41" t="inlineStr"/>
-      <c r="C43" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D43" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B43" s="41" t="n">
+        <v>180</v>
+      </c>
+      <c r="C43" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D43" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
@@ -3871,7 +3895,7 @@
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
@@ -3880,16 +3904,16 @@
         <v>46291</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D44" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D44" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E44" s="30" t="inlineStr">
@@ -3899,7 +3923,7 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -3907,17 +3931,15 @@
       <c r="A45" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B45" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C45" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D45" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B45" s="41" t="inlineStr"/>
+      <c r="C45" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D45" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
@@ -3927,7 +3949,7 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -3936,26 +3958,26 @@
         <v>46291</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D46" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -3963,25 +3985,27 @@
       <c r="A47" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B47" s="41" t="inlineStr"/>
-      <c r="C47" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D47" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B47" s="41" t="n">
+        <v>200</v>
+      </c>
+      <c r="C47" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D47" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
         </is>
       </c>
     </row>
@@ -3990,14 +4014,14 @@
         <v>46291</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D48" s="43" t="inlineStr">
+      <c r="D48" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4009,7 +4033,7 @@
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -4017,27 +4041,25 @@
       <c r="A49" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B49" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="C49" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D49" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B49" s="41" t="inlineStr"/>
+      <c r="C49" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D49" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
@@ -4046,26 +4068,26 @@
         <v>46291</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="C50" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D50" s="43" t="inlineStr">
+      <c r="D50" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -4074,11 +4096,11 @@
         <v>46291</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C51" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>150</v>
+      </c>
+      <c r="C51" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D51" s="38" t="inlineStr">
@@ -4093,7 +4115,7 @@
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -4102,26 +4124,26 @@
         <v>46291</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>160</v>
-      </c>
-      <c r="C52" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D52" s="43" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C52" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D52" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -4130,16 +4152,16 @@
         <v>46291</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C53" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D53" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>155</v>
+      </c>
+      <c r="C53" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D53" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
@@ -4149,7 +4171,7 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
@@ -4158,26 +4180,26 @@
         <v>46291</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="C54" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D54" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D54" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
         </is>
       </c>
     </row>
@@ -4186,26 +4208,26 @@
         <v>46291</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>120</v>
-      </c>
-      <c r="C55" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D55" s="42" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C55" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D55" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -4214,16 +4236,16 @@
         <v>46291</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C56" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D56" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>125</v>
+      </c>
+      <c r="C56" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D56" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
@@ -4233,51 +4255,51 @@
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="C57" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D57" s="42" t="inlineStr">
+      <c r="D57" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
+          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="31" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C58" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D58" s="43" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C58" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D58" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4289,79 +4311,77 @@
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Red”</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B59" s="41" t="n">
-        <v>249</v>
-      </c>
+        <v>46293</v>
+      </c>
+      <c r="B59" s="41" t="inlineStr"/>
       <c r="C59" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D59" s="42" t="inlineStr">
+      <c r="D59" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Hyperice x Nike Air Zoom Hyperslide</t>
+          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C60" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D60" s="43" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C60" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D60" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C61" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D61" s="42" t="inlineStr">
+        <v>249</v>
+      </c>
+      <c r="C61" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D61" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4373,21 +4393,23 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Hyperice x Nike Air Zoom Hyperslide</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B62" s="33" t="inlineStr"/>
-      <c r="C62" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D62" s="43" t="inlineStr">
+        <v>46294</v>
+      </c>
+      <c r="B62" s="33" t="n">
+        <v>170</v>
+      </c>
+      <c r="C62" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D62" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4399,7 +4421,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Nike Air Bakin “Varsity Red”</t>
         </is>
       </c>
     </row>
@@ -4408,16 +4430,16 @@
         <v>46295</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D63" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D63" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
@@ -4427,7 +4449,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -4436,70 +4458,68 @@
         <v>46295</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C64" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D64" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C64" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D64" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>MoMA x Nike Air Rift 2 Pack</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="36" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D65" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D65" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Howard” 2026</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B66" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C66" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D66" s="43" t="inlineStr">
+        <v>46295</v>
+      </c>
+      <c r="B66" s="33" t="inlineStr"/>
+      <c r="C66" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D66" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4511,72 +4531,72 @@
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Racer Blue”</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D67" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D67" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C68" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D68" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>130</v>
+      </c>
+      <c r="C68" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D68" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>MoMA x Nike Air Rift 2 Pack</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="B69" s="41" t="n">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
@@ -4595,23 +4615,23 @@
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 1 Low OG “Howard” 2026</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="B70" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C70" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D70" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C70" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D70" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4623,23 +4643,25 @@
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Nike Caitlin 1 “Racer Blue”</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B71" s="41" t="inlineStr"/>
+        <v>46297</v>
+      </c>
+      <c r="B71" s="41" t="n">
+        <v>220</v>
+      </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D71" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D71" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
@@ -4649,191 +4671,191 @@
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46303</v>
+        <v>46298</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C72" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D72" s="43" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C72" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D72" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46304</v>
+        <v>46298</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C73" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D73" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>240</v>
+      </c>
+      <c r="C73" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D73" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46304</v>
+        <v>46300</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C74" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D74" s="43" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C74" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D74" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46305</v>
+        <v>46303</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C75" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D75" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C75" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D75" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="31" t="n">
-        <v>46310</v>
+        <v>46304</v>
       </c>
       <c r="B76" s="33" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="C76" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D76" s="43" t="inlineStr">
+      <c r="D76" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="36" t="n">
-        <v>46310</v>
+        <v>46304</v>
       </c>
       <c r="B77" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C77" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D77" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C77" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D77" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="31" t="n">
-        <v>46311</v>
+        <v>46305</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>250</v>
-      </c>
-      <c r="C78" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D78" s="43" t="inlineStr">
+        <v>135</v>
+      </c>
+      <c r="C78" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D78" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4845,81 +4867,81 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike KD 6 “Texas”</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="36" t="n">
-        <v>46311</v>
+        <v>46305</v>
       </c>
       <c r="B79" s="41" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="C79" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D79" s="42" t="inlineStr">
+      <c r="D79" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E79" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="31" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B80" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C80" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D80" s="43" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C80" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D80" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E80" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="36" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B81" s="41" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="C81" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D81" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D81" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E81" s="35" t="inlineStr">
@@ -4929,105 +4951,107 @@
       </c>
       <c r="F81" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="31" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B82" s="33" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C82" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D82" s="43" t="inlineStr">
+      <c r="D82" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E82" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="36" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B83" s="41" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C83" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D83" s="42" t="inlineStr">
+      <c r="D83" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E83" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F83" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="31" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B84" s="33" t="inlineStr"/>
-      <c r="C84" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D84" s="43" t="inlineStr">
+        <v>46311</v>
+      </c>
+      <c r="B84" s="33" t="n">
+        <v>240</v>
+      </c>
+      <c r="C84" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D84" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>SZA x Vans VANSZA Collection</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="36" t="n">
-        <v>46319</v>
+        <v>46311</v>
       </c>
       <c r="B85" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C85" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D85" s="42" t="inlineStr">
+        <v>250</v>
+      </c>
+      <c r="C85" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D85" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5039,91 +5063,89 @@
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="31" t="n">
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="B86" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C86" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D86" s="43" t="inlineStr">
+        <v>220</v>
+      </c>
+      <c r="C86" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D86" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E86" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="36" t="n">
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="B87" s="41" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C87" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D87" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D87" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E87" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="31" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B88" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C88" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D88" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>46317</v>
+      </c>
+      <c r="B88" s="33" t="inlineStr"/>
+      <c r="C88" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D88" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E88" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>SZA x Vans VANSZA Collection</t>
         </is>
       </c>
     </row>
@@ -5132,14 +5154,14 @@
         <v>46319</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C89" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D89" s="42" t="inlineStr">
+      <c r="D89" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5151,7 +5173,7 @@
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
@@ -5160,26 +5182,26 @@
         <v>46319</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>190</v>
-      </c>
-      <c r="C90" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D90" s="43" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C90" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D90" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E90" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
@@ -5188,26 +5210,26 @@
         <v>46319</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C91" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D91" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D91" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E91" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
@@ -5216,16 +5238,16 @@
         <v>46319</v>
       </c>
       <c r="B92" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C92" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D92" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>170</v>
+      </c>
+      <c r="C92" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D92" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E92" s="30" t="inlineStr">
@@ -5235,51 +5257,51 @@
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="36" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C93" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D93" s="42" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C93" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D93" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E93" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="31" t="n">
-        <v>46325</v>
+        <v>46319</v>
       </c>
       <c r="B94" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C94" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D94" s="43" t="inlineStr">
+        <v>190</v>
+      </c>
+      <c r="C94" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D94" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5291,25 +5313,25 @@
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="36" t="n">
-        <v>46325</v>
+        <v>46319</v>
       </c>
       <c r="B95" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C95" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D95" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>125</v>
+      </c>
+      <c r="C95" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D95" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E95" s="35" t="inlineStr">
@@ -5319,51 +5341,51 @@
       </c>
       <c r="F95" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 High “University Red”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="31" t="n">
-        <v>46325</v>
+        <v>46319</v>
       </c>
       <c r="B96" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C96" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D96" s="43" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C96" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D96" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E96" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Halloween”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="36" t="n">
-        <v>46326</v>
+        <v>46320</v>
       </c>
       <c r="B97" s="41" t="n">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C97" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D97" s="42" t="inlineStr">
+      <c r="D97" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5375,20 +5397,20 @@
       </c>
       <c r="F97" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="31" t="n">
-        <v>46329</v>
+        <v>46325</v>
       </c>
       <c r="B98" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C98" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>180</v>
+      </c>
+      <c r="C98" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D98" s="34" t="inlineStr">
@@ -5403,23 +5425,23 @@
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Nike Ja 4 High “University Red”</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="36" t="n">
-        <v>46329</v>
+        <v>46325</v>
       </c>
       <c r="B99" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C99" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D99" s="42" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="C99" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D99" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5431,23 +5453,23 @@
       </c>
       <c r="F99" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="31" t="n">
-        <v>46331</v>
+        <v>46325</v>
       </c>
       <c r="B100" s="33" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="C100" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D100" s="43" t="inlineStr">
+      <c r="D100" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5459,51 +5481,51 @@
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
+          <t>Nike Book 2 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="36" t="n">
-        <v>46331</v>
+        <v>46326</v>
       </c>
       <c r="B101" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C101" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D101" s="42" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C101" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D101" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E101" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="31" t="n">
-        <v>46332</v>
+        <v>46329</v>
       </c>
       <c r="B102" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C102" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D102" s="43" t="inlineStr">
+        <v>240</v>
+      </c>
+      <c r="C102" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D102" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5515,132 +5537,132 @@
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Desert Night”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="36" t="n">
-        <v>46333</v>
+        <v>46331</v>
       </c>
       <c r="B103" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C103" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D103" s="42" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C103" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D103" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E103" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F103" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="31" t="n">
-        <v>46333</v>
+        <v>46331</v>
       </c>
       <c r="B104" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C104" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D104" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C104" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D104" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E104" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F104" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="36" t="n">
-        <v>46337</v>
+        <v>46332</v>
       </c>
       <c r="B105" s="41" t="n">
-        <v>235</v>
-      </c>
-      <c r="C105" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D105" s="42" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C105" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D105" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E105" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Lapis”</t>
+          <t>Nike Book 2 “Desert Night”</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="31" t="n">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="B106" s="33" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C106" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D106" s="43" t="inlineStr">
+      <c r="D106" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E106" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F106" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="36" t="n">
-        <v>46338</v>
+        <v>46333</v>
       </c>
       <c r="B107" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C107" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>240</v>
+      </c>
+      <c r="C107" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D107" s="38" t="inlineStr">
@@ -5650,105 +5672,105 @@
       </c>
       <c r="E107" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F107" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal” 2026</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="31" t="n">
-        <v>46338</v>
+        <v>46335</v>
       </c>
       <c r="B108" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C108" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D108" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>240</v>
+      </c>
+      <c r="C108" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D108" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E108" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F108" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="36" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B109" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C109" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D109" s="42" t="inlineStr">
+        <v>235</v>
+      </c>
+      <c r="C109" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D109" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E109" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal”</t>
+          <t>Air Jordan 11 “Lapis”</t>
         </is>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="31" t="n">
-        <v>46340</v>
+        <v>46337</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C110" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D110" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D110" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E110" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="36" t="n">
-        <v>46340</v>
+        <v>46338</v>
       </c>
       <c r="B111" s="41" t="n">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C111" s="53" t="inlineStr">
         <is>
@@ -5762,142 +5784,142 @@
       </c>
       <c r="E111" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
+          <t>Nike Air Bakin “Varsity Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="31" t="n">
-        <v>46341</v>
+        <v>46338</v>
       </c>
       <c r="B112" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C112" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D112" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C112" s="55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D112" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E112" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F112" s="30" t="inlineStr">
         <is>
-          <t>Playa Society x Nike A’Two</t>
+          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="36" t="n">
-        <v>46342</v>
+        <v>46338</v>
       </c>
       <c r="B113" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C113" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D113" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C113" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D113" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E113" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F113" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Nike Air Bakin “Varsity Royal”</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="31" t="n">
-        <v>46343</v>
+        <v>46340</v>
       </c>
       <c r="B114" s="33" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C114" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D114" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D114" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E114" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F114" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="36" t="n">
-        <v>46345</v>
+        <v>46340</v>
       </c>
       <c r="B115" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C115" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D115" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>240</v>
+      </c>
+      <c r="C115" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D115" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E115" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F115" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Navy”</t>
+          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="31" t="n">
-        <v>46346</v>
+        <v>46341</v>
       </c>
       <c r="B116" s="33" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C116" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D116" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D116" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E116" s="30" t="inlineStr">
@@ -5907,51 +5929,51 @@
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Be Legendary”</t>
+          <t>Playa Society x Nike A’Two</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="36" t="n">
-        <v>46346</v>
+        <v>46342</v>
       </c>
       <c r="B117" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C117" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D117" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C117" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D117" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E117" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F117" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="31" t="n">
-        <v>46347</v>
+        <v>46343</v>
       </c>
       <c r="B118" s="33" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="C118" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D118" s="43" t="inlineStr">
+      <c r="D118" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5963,53 +5985,53 @@
       </c>
       <c r="F118" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="36" t="n">
-        <v>46347</v>
+        <v>46345</v>
       </c>
       <c r="B119" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C119" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D119" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C119" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D119" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E119" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Snow White”</t>
+          <t>Vans Old Skool 36 Pearlized “Navy”</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="31" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B120" s="33" t="n">
-        <v>230</v>
-      </c>
-      <c r="C120" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D120" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>145</v>
+      </c>
+      <c r="C120" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D120" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E120" s="30" t="inlineStr">
@@ -6019,35 +6041,35 @@
       </c>
       <c r="F120" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Nike Book 2 “Be Legendary”</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="36" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B121" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C121" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D121" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C121" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D121" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E121" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F121" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
         </is>
       </c>
     </row>
@@ -6056,14 +6078,14 @@
         <v>46347</v>
       </c>
       <c r="B122" s="33" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C122" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D122" s="43" t="inlineStr">
+      <c r="D122" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6075,7 +6097,7 @@
       </c>
       <c r="F122" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -6084,32 +6106,32 @@
         <v>46347</v>
       </c>
       <c r="B123" s="41" t="n">
-        <v>165</v>
-      </c>
-      <c r="C123" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D123" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C123" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D123" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E123" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F123" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1">
       <c r="A124" s="31" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B124" s="33" t="n">
         <v>230</v>
@@ -6119,175 +6141,175 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D124" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D124" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E124" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F124" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="36" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B125" s="41" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C125" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D125" s="42" t="inlineStr">
+      <c r="D125" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E125" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F125" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="31" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B126" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C126" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D126" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C126" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D126" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E126" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Black”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="36" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B127" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C127" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D127" s="42" t="inlineStr">
+        <v>46347</v>
+      </c>
+      <c r="B127" s="41" t="inlineStr"/>
+      <c r="C127" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D127" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E127" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Yellow Zest”</t>
+          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" s="31" t="n">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B128" s="33" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="C128" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D128" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D128" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E128" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F128" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="36" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B129" s="41" t="inlineStr"/>
-      <c r="C129" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D129" s="42" t="inlineStr">
+        <v>46353</v>
+      </c>
+      <c r="B129" s="41" t="n">
+        <v>230</v>
+      </c>
+      <c r="C129" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D129" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E129" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F129" s="35" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Aunt Pearl” 2026</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" s="31" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B130" s="33" t="n">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="C130" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D130" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D130" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E130" s="30" t="inlineStr">
@@ -6297,33 +6319,35 @@
       </c>
       <c r="F130" s="30" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1">
       <c r="A131" s="36" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B131" s="41" t="inlineStr"/>
-      <c r="C131" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D131" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>46353</v>
+      </c>
+      <c r="B131" s="41" t="n">
+        <v>130</v>
+      </c>
+      <c r="C131" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D131" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E131" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F131" s="35" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Vans Old Skool 36 Pearlized “Black”</t>
         </is>
       </c>
     </row>
@@ -6332,14 +6356,14 @@
         <v>46354</v>
       </c>
       <c r="B132" s="33" t="n">
-        <v>190</v>
-      </c>
-      <c r="C132" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D132" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C132" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D132" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6351,23 +6375,21 @@
       </c>
       <c r="F132" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Nike Caitlin 1 “Warning Code”</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1">
       <c r="A133" s="36" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B133" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C133" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D133" s="42" t="inlineStr">
+        <v>46354</v>
+      </c>
+      <c r="B133" s="41" t="inlineStr"/>
+      <c r="C133" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D133" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6379,25 +6401,25 @@
       </c>
       <c r="F133" s="35" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Texas”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="31" t="n">
-        <v>46359</v>
+        <v>46354</v>
       </c>
       <c r="B134" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C134" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D134" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>120</v>
+      </c>
+      <c r="C134" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D134" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E134" s="30" t="inlineStr">
@@ -6407,43 +6429,43 @@
       </c>
       <c r="F134" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Black/White”</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c r="A135" s="36" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B135" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C135" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D135" s="42" t="inlineStr">
+        <v>46354</v>
+      </c>
+      <c r="B135" s="41" t="inlineStr"/>
+      <c r="C135" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D135" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E135" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F135" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Nike KD 6 “Aunt Pearl” 2026</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="31" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B136" s="33" t="inlineStr"/>
+        <v>46354</v>
+      </c>
+      <c r="B136" s="33" t="n">
+        <v>130</v>
+      </c>
       <c r="C136" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6456,25 +6478,23 @@
       </c>
       <c r="E136" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F136" s="30" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B137" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="C137" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46354</v>
+      </c>
+      <c r="B137" s="41" t="inlineStr"/>
+      <c r="C137" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
         </is>
       </c>
       <c r="D137" s="38" t="inlineStr">
@@ -6489,13 +6509,13 @@
       </c>
       <c r="F137" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="A138" s="31" t="n">
-        <v>46367</v>
+        <v>46354</v>
       </c>
       <c r="B138" s="33" t="n">
         <v>190</v>
@@ -6505,7 +6525,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D138" s="43" t="inlineStr">
+      <c r="D138" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6517,40 +6537,232 @@
       </c>
       <c r="F138" s="30" t="inlineStr">
         <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1">
       <c r="A139" s="36" t="n">
+        <v>46359</v>
+      </c>
+      <c r="B139" s="41" t="n">
+        <v>170</v>
+      </c>
+      <c r="C139" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D139" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E139" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F139" s="35" t="inlineStr">
+        <is>
+          <t>Nike Air Bakin “Black/White”</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="15" customHeight="1">
+      <c r="A140" s="31" t="n">
+        <v>46361</v>
+      </c>
+      <c r="B140" s="33" t="inlineStr"/>
+      <c r="C140" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D140" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E140" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F140" s="30" t="inlineStr">
+        <is>
+          <t>SoleFly x Air Jordan 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="15" customHeight="1">
+      <c r="A141" s="36" t="n">
+        <v>46361</v>
+      </c>
+      <c r="B141" s="41" t="n">
+        <v>215</v>
+      </c>
+      <c r="C141" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D141" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E141" s="35" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F141" s="35" t="inlineStr">
+        <is>
+          <t>Air Jordan 10 “Sacramento”</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="15" customHeight="1">
+      <c r="A142" s="31" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B142" s="33" t="n">
+        <v>240</v>
+      </c>
+      <c r="C142" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D142" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E142" s="30" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F142" s="30" t="inlineStr">
+        <is>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="15" customHeight="1">
+      <c r="A143" s="36" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B143" s="41" t="inlineStr"/>
+      <c r="C143" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D143" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E143" s="35" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F143" s="35" t="inlineStr">
+        <is>
+          <t>Free The Youth x Air Jordan 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="15" customHeight="1">
+      <c r="A144" s="31" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B144" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="C144" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D144" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E144" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F144" s="30" t="inlineStr">
+        <is>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="15" customHeight="1">
+      <c r="A145" s="36" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B145" s="41" t="n">
+        <v>190</v>
+      </c>
+      <c r="C145" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D145" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E145" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F145" s="35" t="inlineStr">
+        <is>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="15" customHeight="1">
+      <c r="A146" s="31" t="n">
         <v>46368</v>
       </c>
-      <c r="B139" s="41" t="n">
+      <c r="B146" s="33" t="n">
         <v>235</v>
       </c>
-      <c r="C139" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D139" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E139" s="35" t="inlineStr">
+      <c r="C146" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D146" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E146" s="30" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="F139" s="35" t="inlineStr">
+      <c r="F146" s="30" t="inlineStr">
         <is>
           <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F139"/>
+  <autoFilter ref="A3:F146"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -6565,7 +6777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6591,7 +6803,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 14, 2026  ·  12:06 UTC</t>
+          <t>Generated September 15, 2026  ·  11:19 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -6672,7 +6884,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6700,7 +6912,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6749,26 +6961,26 @@
         <v>46283</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
     </row>
@@ -6777,16 +6989,16 @@
         <v>46283</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D9" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
@@ -6796,7 +7008,7 @@
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -6805,14 +7017,14 @@
         <v>46283</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D10" s="43" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6824,7 +7036,7 @@
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
         </is>
       </c>
     </row>
@@ -6833,26 +7045,26 @@
         <v>46283</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D11" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>APB x Air Jordan 11 Low</t>
         </is>
       </c>
     </row>
@@ -6861,14 +7073,14 @@
         <v>46283</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="C12" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
+      <c r="D12" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6880,7 +7092,7 @@
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
     </row>
@@ -6896,7 +7108,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D13" s="42" t="inlineStr">
+      <c r="D13" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6924,7 +7136,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D14" s="43" t="inlineStr">
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6952,7 +7164,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D15" s="42" t="inlineStr">
+      <c r="D15" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7036,7 +7248,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D18" s="43" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7092,7 +7304,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D20" s="43" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7118,7 +7330,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D21" s="42" t="inlineStr">
+      <c r="D21" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7138,15 +7350,17 @@
       <c r="A22" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B22" s="33" t="inlineStr"/>
+      <c r="B22" s="33" t="n">
+        <v>210</v>
+      </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D22" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
@@ -7156,7 +7370,7 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -7165,26 +7379,26 @@
         <v>46291</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -7193,14 +7407,14 @@
         <v>46291</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D24" s="43" t="inlineStr">
+      <c r="D24" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7212,7 +7426,7 @@
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -7221,26 +7435,26 @@
         <v>46291</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D25" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D25" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -7249,16 +7463,16 @@
         <v>46291</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="C26" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D26" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D26" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
@@ -7268,7 +7482,7 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -7277,14 +7491,14 @@
         <v>46291</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D27" s="42" t="inlineStr">
+      <c r="D27" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7296,7 +7510,7 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -7305,14 +7519,14 @@
         <v>46291</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
+      <c r="D28" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7324,25 +7538,25 @@
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="36" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D29" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D29" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -7352,7 +7566,7 @@
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7582,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D30" s="43" t="inlineStr">
+      <c r="D30" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7396,7 +7610,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D31" s="42" t="inlineStr">
+      <c r="D31" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7422,7 +7636,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D32" s="43" t="inlineStr">
+      <c r="D32" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7450,7 +7664,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D33" s="42" t="inlineStr">
+      <c r="D33" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7534,7 +7748,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D36" s="43" t="inlineStr">
+      <c r="D36" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7590,7 +7804,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D38" s="43" t="inlineStr">
+      <c r="D38" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7608,15 +7822,17 @@
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B39" s="41" t="inlineStr"/>
+        <v>46305</v>
+      </c>
+      <c r="B39" s="41" t="n">
+        <v>180</v>
+      </c>
       <c r="C39" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D39" s="42" t="inlineStr">
+      <c r="D39" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7628,53 +7844,53 @@
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>180</v>
+        <v>125</v>
       </c>
       <c r="C40" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D40" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="36" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D41" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D41" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
@@ -7684,7 +7900,7 @@
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -7693,14 +7909,14 @@
         <v>46311</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C42" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D42" s="43" t="inlineStr">
+      <c r="D42" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7712,7 +7928,7 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7944,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D43" s="42" t="inlineStr">
+      <c r="D43" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7740,7 +7956,7 @@
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
@@ -7749,14 +7965,14 @@
         <v>46311</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D44" s="43" t="inlineStr">
+      <c r="D44" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7768,35 +7984,35 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D45" s="42" t="inlineStr">
+      <c r="D45" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
@@ -7805,14 +8021,14 @@
         <v>46312</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D46" s="43" t="inlineStr">
+      <c r="D46" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7824,35 +8040,35 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="36" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D47" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D47" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
@@ -7861,16 +8077,16 @@
         <v>46319</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D48" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
@@ -7880,7 +8096,7 @@
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
@@ -7889,14 +8105,14 @@
         <v>46319</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D49" s="42" t="inlineStr">
+      <c r="D49" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7908,7 +8124,7 @@
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
@@ -7924,7 +8140,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D50" s="43" t="inlineStr">
+      <c r="D50" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7942,45 +8158,45 @@
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D51" s="42" t="inlineStr">
+      <c r="D51" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="31" t="n">
-        <v>46320</v>
+        <v>46326</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D52" s="43" t="inlineStr">
+      <c r="D52" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7992,69 +8208,69 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="36" t="n">
-        <v>46326</v>
+        <v>46329</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="42" t="inlineStr">
+      <c r="D53" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="31" t="n">
-        <v>46329</v>
+        <v>46333</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D54" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D54" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46329</v>
+        <v>46333</v>
       </c>
       <c r="B55" s="41" t="n">
         <v>240</v>
@@ -8064,65 +8280,65 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D55" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D55" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46333</v>
+        <v>46335</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C56" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D56" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D56" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46333</v>
+        <v>46337</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C57" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D57" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D57" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
@@ -8132,7 +8348,7 @@
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Air Jordan 11 “Lapis”</t>
         </is>
       </c>
     </row>
@@ -8141,60 +8357,60 @@
         <v>46337</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="C58" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D58" s="43" t="inlineStr">
+      <c r="D58" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Lapis”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46337</v>
+        <v>46340</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D59" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D59" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46340</v>
+        <v>46342</v>
       </c>
       <c r="B60" s="33" t="n">
         <v>255</v>
@@ -8216,51 +8432,51 @@
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46342</v>
+        <v>46343</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D61" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D61" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46343</v>
+        <v>46347</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="C62" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D62" s="43" t="inlineStr">
+      <c r="D62" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8272,7 +8488,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -8281,16 +8497,16 @@
         <v>46347</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>125</v>
+        <v>230</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D63" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D63" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
@@ -8300,7 +8516,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -8309,26 +8525,26 @@
         <v>46347</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D64" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D64" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
@@ -8337,26 +8553,26 @@
         <v>46347</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>215</v>
+        <v>140</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D65" s="42" t="inlineStr">
+      <c r="D65" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
@@ -8365,42 +8581,42 @@
         <v>46347</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D66" s="43" t="inlineStr">
+      <c r="D66" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D67" s="42" t="inlineStr">
+      <c r="D67" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8412,7 +8628,7 @@
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
@@ -8421,42 +8637,40 @@
         <v>46353</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D68" s="43" t="inlineStr">
+      <c r="D68" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46353</v>
-      </c>
-      <c r="B69" s="41" t="n">
-        <v>240</v>
-      </c>
+        <v>46354</v>
+      </c>
+      <c r="B69" s="41" t="inlineStr"/>
       <c r="C69" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D69" s="42" t="inlineStr">
+      <c r="D69" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8468,7 +8682,7 @@
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8780,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D73" s="42" t="inlineStr">
+      <c r="D73" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8586,15 +8800,13 @@
       <c r="A74" s="31" t="n">
         <v>46361</v>
       </c>
-      <c r="B74" s="33" t="n">
-        <v>215</v>
-      </c>
+      <c r="B74" s="33" t="inlineStr"/>
       <c r="C74" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D74" s="43" t="inlineStr">
+      <c r="D74" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8606,23 +8818,25 @@
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B75" s="41" t="inlineStr"/>
+        <v>46361</v>
+      </c>
+      <c r="B75" s="41" t="n">
+        <v>215</v>
+      </c>
       <c r="C75" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D75" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D75" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
@@ -8632,7 +8846,7 @@
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
@@ -8641,26 +8855,26 @@
         <v>46367</v>
       </c>
       <c r="B76" s="33" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="C76" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D76" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D76" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
         </is>
       </c>
     </row>
@@ -8668,60 +8882,114 @@
       <c r="A77" s="36" t="n">
         <v>46367</v>
       </c>
-      <c r="B77" s="41" t="n">
-        <v>190</v>
-      </c>
+      <c r="B77" s="41" t="inlineStr"/>
       <c r="C77" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D77" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D77" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="31" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B78" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="C78" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D78" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E78" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F78" s="30" t="inlineStr">
+        <is>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="36" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B79" s="41" t="n">
+        <v>190</v>
+      </c>
+      <c r="C79" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D79" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E79" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F79" s="35" t="inlineStr">
+        <is>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="31" t="n">
         <v>46368</v>
       </c>
-      <c r="B78" s="33" t="n">
+      <c r="B80" s="33" t="n">
         <v>235</v>
       </c>
-      <c r="C78" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D78" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
+      <c r="C80" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D80" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E80" s="30" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="F78" s="30" t="inlineStr">
+      <c r="F80" s="30" t="inlineStr">
         <is>
           <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F78"/>
+  <autoFilter ref="A3:F80"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High Hype Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="M/D/YYYY"/>
     <numFmt numFmtId="166" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,12 +122,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00D4A000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="003B9EFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -549,7 +543,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -648,10 +642,10 @@
     <xf numFmtId="166" fontId="10" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -669,23 +663,17 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1011,12 +999,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Charts'!$G$2:$G$4</f>
+              <f>'Charts'!$G$2:$G$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$H$2:$H$4</f>
+              <f>'Charts'!$H$2:$H$3</f>
             </numRef>
           </val>
         </ser>
@@ -1581,7 +1569,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 15, 2026  ·  11:19 UTC</t>
+          <t>Generated September 16, 2026  ·  11:01 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1621,20 +1609,20 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="16" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>$179</t>
+          <t>$181</t>
         </is>
       </c>
       <c r="H5" s="19" t="n"/>
@@ -1737,7 +1725,7 @@
         <v>46290</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1771,7 +1759,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1803,7 +1791,7 @@
         <v>46295</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1825,16 +1813,16 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 “Iron Grey”</t>
+          <t>Air Jordan 6 Low “Metamorphosis”</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D13" s="35" t="n">
         <v>0</v>
@@ -1848,30 +1836,30 @@
         <v>7</v>
       </c>
       <c r="G13" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="H13" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>205</v>
+      </c>
+      <c r="H13" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
+          <t>Air Jordan 4 “London”</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C14" s="31" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
@@ -1882,18 +1870,18 @@
         <v>7</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="H14" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>220</v>
+      </c>
+      <c r="H14" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 Low “Metamorphosis”</t>
+          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
@@ -1902,10 +1890,10 @@
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
@@ -1918,7 +1906,7 @@
       <c r="G15" s="41" t="n">
         <v>205</v>
       </c>
-      <c r="H15" s="43" t="inlineStr">
+      <c r="H15" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -1927,7 +1915,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>APB x Air Jordan 11 Low</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
@@ -1936,7 +1924,7 @@
         </is>
       </c>
       <c r="C16" s="31" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D16" s="30" t="n">
         <v>2</v>
@@ -1950,11 +1938,11 @@
         <v>7</v>
       </c>
       <c r="G16" s="33" t="n">
-        <v>220</v>
-      </c>
-      <c r="H16" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>200</v>
+      </c>
+      <c r="H16" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2000,7 @@
         </is>
       </c>
       <c r="B20" s="30" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
@@ -2028,7 +2016,7 @@
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -2038,7 +2026,7 @@
         </is>
       </c>
       <c r="B21" s="35" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
@@ -2046,7 +2034,7 @@
         </is>
       </c>
       <c r="E21" s="35" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G21" s="47" t="inlineStr">
         <is>
@@ -2064,7 +2052,7 @@
         </is>
       </c>
       <c r="B22" s="30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
@@ -2074,14 +2062,6 @@
       <c r="E22" s="30" t="n">
         <v>46</v>
       </c>
-      <c r="G22" s="49" t="inlineStr">
-        <is>
-          <t>Confirmed App</t>
-        </is>
-      </c>
-      <c r="H22" s="30" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="46" t="inlineStr">
@@ -2092,7 +2072,7 @@
       <c r="B23" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="50" t="inlineStr">
+      <c r="D23" s="49" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2181,17 +2161,17 @@
       </c>
       <c r="B30" s="30" t="inlineStr">
         <is>
-          <t>9/15 – 9/21</t>
+          <t>9/16 – 9/22</t>
         </is>
       </c>
       <c r="C30" s="30" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D30" s="39" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E30" s="30" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
@@ -2202,17 +2182,17 @@
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>9/22 – 9/28</t>
+          <t>9/23 – 9/29</t>
         </is>
       </c>
       <c r="C31" s="35" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D31" s="40" t="n">
         <v>12</v>
       </c>
       <c r="E31" s="35" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -2223,17 +2203,17 @@
       </c>
       <c r="B32" s="30" t="inlineStr">
         <is>
-          <t>9/29 – 10/5</t>
+          <t>9/30 – 10/6</t>
         </is>
       </c>
       <c r="C32" s="30" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D32" s="39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32" s="30" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
@@ -2244,7 +2224,7 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>10/6 – 10/12</t>
+          <t>10/7 – 10/13</t>
         </is>
       </c>
       <c r="C33" s="35" t="n">
@@ -2265,7 +2245,7 @@
       </c>
       <c r="B34" s="30" t="inlineStr">
         <is>
-          <t>10/13 – 10/19</t>
+          <t>10/14 – 10/20</t>
         </is>
       </c>
       <c r="C34" s="30" t="n">
@@ -2286,7 +2266,7 @@
       </c>
       <c r="B35" s="35" t="inlineStr">
         <is>
-          <t>10/20 – 10/26</t>
+          <t>10/21 – 10/27</t>
         </is>
       </c>
       <c r="C35" s="35" t="n">
@@ -2307,17 +2287,17 @@
       </c>
       <c r="B36" s="30" t="inlineStr">
         <is>
-          <t>10/27 – 11/2</t>
+          <t>10/28 – 11/3</t>
         </is>
       </c>
       <c r="C36" s="30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="30" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -2328,7 +2308,7 @@
       </c>
       <c r="B37" s="35" t="inlineStr">
         <is>
-          <t>11/3 – 11/9</t>
+          <t>11/4 – 11/10</t>
         </is>
       </c>
       <c r="C37" s="35" t="n">
@@ -2349,17 +2329,17 @@
       </c>
       <c r="B38" s="30" t="inlineStr">
         <is>
-          <t>11/10 – 11/16</t>
+          <t>11/11 – 11/17</t>
         </is>
       </c>
       <c r="C38" s="30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38" s="30" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -2370,17 +2350,17 @@
       </c>
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>11/17 – 11/23</t>
+          <t>11/18 – 11/24</t>
         </is>
       </c>
       <c r="C39" s="35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D39" s="40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" s="35" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -2391,7 +2371,7 @@
       </c>
       <c r="B40" s="30" t="inlineStr">
         <is>
-          <t>11/24 – 11/30</t>
+          <t>11/25 – 12/1</t>
         </is>
       </c>
       <c r="C40" s="30" t="n">
@@ -2412,7 +2392,7 @@
       </c>
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>12/1 – 12/7</t>
+          <t>12/2 – 12/8</t>
         </is>
       </c>
       <c r="C41" s="35" t="n">
@@ -2433,7 +2413,7 @@
       </c>
       <c r="B42" s="30" t="inlineStr">
         <is>
-          <t>12/8 – 12/14</t>
+          <t>12/9 – 12/15</t>
         </is>
       </c>
       <c r="C42" s="30" t="n">
@@ -2493,42 +2473,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="B1" s="51" t="inlineStr">
+      <c r="B1" s="50" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
       </c>
-      <c r="D1" s="51" t="inlineStr">
+      <c r="D1" s="50" t="inlineStr">
         <is>
           <t>Hype Level</t>
         </is>
       </c>
-      <c r="E1" s="51" t="inlineStr">
+      <c r="E1" s="50" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
       </c>
-      <c r="G1" s="51" t="inlineStr">
+      <c r="G1" s="50" t="inlineStr">
         <is>
           <t>Sale Method</t>
         </is>
       </c>
-      <c r="H1" s="51" t="inlineStr">
+      <c r="H1" s="50" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
       </c>
-      <c r="J1" s="51" t="inlineStr">
+      <c r="J1" s="50" t="inlineStr">
         <is>
           <t>Price Range</t>
         </is>
       </c>
-      <c r="K1" s="51" t="inlineStr">
+      <c r="K1" s="50" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
@@ -2541,7 +2521,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2557,7 +2537,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2575,7 +2555,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2583,7 +2563,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2599,7 +2579,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -2609,7 +2589,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2619,14 +2599,6 @@
       <c r="E4" t="n">
         <v>46</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Confirmed App</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>$150–$199</t>
@@ -2659,7 +2631,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2736,9 +2708,9 @@
       <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="52" t="inlineStr">
-        <is>
-          <t>Generated September 15, 2026  ·  11:19 UTC</t>
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t>Generated September 16, 2026  ·  11:01 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2781,197 +2753,197 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="C4" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D4" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 “Iron Grey”</t>
+          <t>Air Jordan 6 Low “Metamorphosis”</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>120</v>
-      </c>
-      <c r="C5" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D5" s="54" t="inlineStr">
-        <is>
-          <t>Confirmed App</t>
+        <v>130</v>
+      </c>
+      <c r="C5" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.1 Low “Chalk White”</t>
+          <t>Reebok Brutus Low “Philadelphia Eagles”</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
+          <t>Air Jordan 4 “London”</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="36" t="n">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C7" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D7" s="43" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Nike First Sight Shadow “Light Crimson” (W)</t>
+          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="31" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C8" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D8" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>135</v>
+      </c>
+      <c r="C8" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 Low “Metamorphosis”</t>
+          <t>PSG x Nike KD 6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="36" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C9" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D9" s="43" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Reebok Brutus Low “Philadelphia Eagles”</t>
+          <t>APB x Air Jordan 11 Low</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="31" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>220</v>
-      </c>
-      <c r="C10" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D10" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C10" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>adidas Anthony Edwards 3 “Cold Blooded”</t>
         </is>
       </c>
     </row>
@@ -2980,14 +2952,14 @@
         <v>46283</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C11" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D11" s="43" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C11" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2999,7 +2971,7 @@
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>Nike A’Two “Dawn Staley”</t>
         </is>
       </c>
     </row>
@@ -3008,26 +2980,26 @@
         <v>46283</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C12" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D12" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>65</v>
+      </c>
+      <c r="C12" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
         </is>
       </c>
     </row>
@@ -3036,26 +3008,26 @@
         <v>46283</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="C13" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D13" s="43" t="inlineStr">
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
     </row>
@@ -3064,16 +3036,16 @@
         <v>46283</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>135</v>
-      </c>
-      <c r="C14" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D14" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E14" s="30" t="inlineStr">
@@ -3083,7 +3055,7 @@
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>PSG x Nike KD 6</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
     </row>
@@ -3092,16 +3064,16 @@
         <v>46283</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C15" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D15" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D15" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
@@ -3111,7 +3083,7 @@
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -3120,14 +3092,14 @@
         <v>46283</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C16" s="55" t="inlineStr">
+        <v>110</v>
+      </c>
+      <c r="C16" s="52" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="42" t="inlineStr">
+      <c r="D16" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3139,7 +3111,7 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Cold Blooded”</t>
+          <t>Anthony Edwards x adidas Superstar “Cold Blooded”</t>
         </is>
       </c>
     </row>
@@ -3148,14 +3120,14 @@
         <v>46283</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C17" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D17" s="43" t="inlineStr">
+        <v>250</v>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3167,79 +3139,79 @@
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Nike A’Two “Dawn Staley”</t>
+          <t>Nike Air Foamposite Pro “Green Camo”</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>65</v>
-      </c>
-      <c r="C18" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="42" t="inlineStr">
+        <v>300</v>
+      </c>
+      <c r="C18" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
+          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>250</v>
-      </c>
-      <c r="C19" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D19" s="43" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C19" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>Air Jordan 9 OG “Space Jam” 2026</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B20" s="33" t="n">
         <v>110</v>
       </c>
-      <c r="C20" s="55" t="inlineStr">
+      <c r="C20" s="52" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D20" s="42" t="inlineStr">
+      <c r="D20" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3251,23 +3223,23 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Anthony Edwards x adidas Superstar “Cold Blooded”</t>
+          <t>Pokémon x adidas 30th Anniversary Collection</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>250</v>
+        <v>122</v>
       </c>
       <c r="C21" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D21" s="43" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3279,7 +3251,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo”</t>
+          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
         </is>
       </c>
     </row>
@@ -3288,14 +3260,14 @@
         <v>46284</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D22" s="42" t="inlineStr">
+      <c r="D22" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3307,7 +3279,7 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>Nike Kobe 8 Protro “Mambacurial”</t>
         </is>
       </c>
     </row>
@@ -3316,26 +3288,26 @@
         <v>46284</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D23" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>APB x Air Jordan 11 Low Pack</t>
         </is>
       </c>
     </row>
@@ -3344,26 +3316,26 @@
         <v>46284</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C24" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D24" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C24" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D24" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E24" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>One Piece x Nike Air Max Plus “Ope Ope”</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3351,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D25" s="43" t="inlineStr">
+      <c r="D25" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3391,287 +3363,287 @@
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
+          <t>Pharrell x adidas Adistar Jellyfish</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="31" t="n">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C26" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D26" s="42" t="inlineStr">
+      <c r="D26" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 9 OG “Space Jam” 2026</t>
+          <t>Nike GT Future “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="36" t="n">
-        <v>46284</v>
+        <v>46288</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>110</v>
-      </c>
-      <c r="C27" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D27" s="43" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C27" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D27" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Pokémon x adidas 30th Anniversary Collection</t>
+          <t>Nike GT Future “Unseen Hours”</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="31" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C28" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D28" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C28" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D28" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Ope Ope”</t>
+          <t>Converse SHAI 001 “Ghosted”</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="36" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>300</v>
-      </c>
-      <c r="C29" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D29" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C29" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish</t>
+          <t>Converse SHAI 001 “Green Beam”</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="31" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C30" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D30" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C30" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D30" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Nike GT Future “Varsity Red”</t>
+          <t>Converse SHAI 001 Shroud “Shock”</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="36" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C31" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D31" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C31" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Nike GT Future “Unseen Hours”</t>
+          <t>Converse SHAI 001 “Spark”</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C32" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D32" s="42" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C32" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Green Beam”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="36" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C33" s="50" t="inlineStr">
+        <v>120</v>
+      </c>
+      <c r="C33" s="49" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
+      <c r="D33" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Ghosted”</t>
+          <t>Billionaire Boys Club x Reebok Club C 85</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="31" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B34" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C34" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D34" s="42" t="inlineStr">
+      <c r="C34" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D34" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 Shroud “Shock”</t>
+          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C35" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D35" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D35" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Spark”</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
@@ -3708,26 +3680,26 @@
         <v>46290</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C37" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D37" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C37" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D37" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Nike Ja 4 “Jaws”</t>
         </is>
       </c>
     </row>
@@ -3736,26 +3708,26 @@
         <v>46290</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="C38" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D38" s="42" t="inlineStr">
+        <v>185</v>
+      </c>
+      <c r="C38" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E38" s="30" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Billionaire Boys Club x Reebok Club C 85</t>
+          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
         </is>
       </c>
     </row>
@@ -3764,100 +3736,100 @@
         <v>46290</v>
       </c>
       <c r="B39" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C39" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D39" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C39" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C40" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D40" s="42" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C40" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D40" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C41" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D41" s="43" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="C41" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D41" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws”</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C42" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D42" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>150</v>
+      </c>
+      <c r="C42" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E42" s="30" t="inlineStr">
@@ -3867,7 +3839,7 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -3875,27 +3847,25 @@
       <c r="A43" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B43" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C43" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D43" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B43" s="41" t="inlineStr"/>
+      <c r="C43" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D43" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
@@ -3904,16 +3874,16 @@
         <v>46291</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C44" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D44" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>155</v>
+      </c>
+      <c r="C44" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E44" s="30" t="inlineStr">
@@ -3923,7 +3893,7 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
@@ -3931,13 +3901,15 @@
       <c r="A45" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B45" s="41" t="inlineStr"/>
+      <c r="B45" s="41" t="n">
+        <v>210</v>
+      </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D45" s="43" t="inlineStr">
+      <c r="D45" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3949,7 +3921,7 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -3958,26 +3930,26 @@
         <v>46291</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C46" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D46" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>160</v>
+      </c>
+      <c r="C46" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
         </is>
       </c>
     </row>
@@ -3988,14 +3960,14 @@
       <c r="B47" s="41" t="n">
         <v>200</v>
       </c>
-      <c r="C47" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D47" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C47" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D47" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
@@ -4005,7 +3977,7 @@
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -4014,26 +3986,26 @@
         <v>46291</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C48" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D48" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>125</v>
+      </c>
+      <c r="C48" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -4041,25 +4013,27 @@
       <c r="A49" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B49" s="41" t="inlineStr"/>
-      <c r="C49" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D49" s="43" t="inlineStr">
+      <c r="B49" s="41" t="n">
+        <v>140</v>
+      </c>
+      <c r="C49" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D49" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -4068,26 +4042,26 @@
         <v>46291</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C50" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D50" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C50" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D50" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
@@ -4095,17 +4069,15 @@
       <c r="A51" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B51" s="41" t="n">
-        <v>150</v>
-      </c>
+      <c r="B51" s="41" t="inlineStr"/>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D51" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D51" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
@@ -4115,7 +4087,7 @@
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -4131,9 +4103,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D52" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D52" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
@@ -4143,7 +4115,7 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4124,7 @@
         <v>46291</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="C53" s="53" t="inlineStr">
         <is>
@@ -4171,7 +4143,7 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
         </is>
       </c>
     </row>
@@ -4180,14 +4152,14 @@
         <v>46291</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="C54" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D54" s="42" t="inlineStr">
+      <c r="D54" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4199,7 +4171,7 @@
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
+          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
         </is>
       </c>
     </row>
@@ -4208,14 +4180,14 @@
         <v>46291</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D55" s="43" t="inlineStr">
+      <c r="D55" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4227,79 +4199,77 @@
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B56" s="33" t="n">
-        <v>125</v>
-      </c>
+        <v>46293</v>
+      </c>
+      <c r="B56" s="33" t="inlineStr"/>
       <c r="C56" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D56" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D56" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="C57" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D57" s="43" t="inlineStr">
+      <c r="D57" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
+          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="31" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C58" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D58" s="42" t="inlineStr">
+        <v>249</v>
+      </c>
+      <c r="C58" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D58" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4311,49 +4281,51 @@
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Hyperice x Nike Air Zoom Hyperslide</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B59" s="41" t="inlineStr"/>
+        <v>46294</v>
+      </c>
+      <c r="B59" s="41" t="n">
+        <v>170</v>
+      </c>
       <c r="C59" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D59" s="43" t="inlineStr">
+      <c r="D59" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
+          <t>Nike Air Bakin “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C60" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D60" s="42" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C60" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D60" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4365,23 +4337,21 @@
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B61" s="41" t="n">
-        <v>249</v>
-      </c>
-      <c r="C61" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D61" s="43" t="inlineStr">
+        <v>46295</v>
+      </c>
+      <c r="B61" s="41" t="inlineStr"/>
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D61" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4393,25 +4363,25 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Hyperice x Nike Air Zoom Hyperslide</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="C62" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D62" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D62" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
@@ -4421,7 +4391,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Red”</t>
+          <t>MoMA x Nike Air Rift 2 Pack</t>
         </is>
       </c>
     </row>
@@ -4430,16 +4400,16 @@
         <v>46295</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D63" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D63" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
@@ -4449,7 +4419,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
@@ -4458,26 +4428,26 @@
         <v>46295</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D64" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -4486,40 +4456,42 @@
         <v>46295</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D65" s="43" t="inlineStr">
+      <c r="D65" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B66" s="33" t="inlineStr"/>
-      <c r="C66" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D66" s="42" t="inlineStr">
+        <v>46296</v>
+      </c>
+      <c r="B66" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="C66" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D66" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4531,48 +4503,46 @@
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Nike Caitlin 1 “Racer Blue”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B67" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C67" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D67" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>46296</v>
+      </c>
+      <c r="B67" s="41" t="inlineStr"/>
+      <c r="C67" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D67" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Air Jordan “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C68" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>220</v>
+      </c>
+      <c r="C68" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D68" s="34" t="inlineStr">
@@ -4582,21 +4552,21 @@
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>MoMA x Nike Air Rift 2 Pack</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B69" s="41" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
@@ -4615,135 +4585,135 @@
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Howard” 2026</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B70" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C70" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D70" s="42" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C70" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D70" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Racer Blue”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D71" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D71" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46298</v>
+        <v>46303</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C72" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D72" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C72" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D72" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46298</v>
+        <v>46304</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C73" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D73" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C73" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D73" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C74" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D74" s="42" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C74" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D74" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4755,51 +4725,51 @@
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C75" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D75" s="43" t="inlineStr">
+        <v>180</v>
+      </c>
+      <c r="C75" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D75" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="31" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B76" s="33" t="n">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="C76" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D76" s="42" t="inlineStr">
+      <c r="D76" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4811,53 +4781,53 @@
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
+          <t>Nike KD 6 “Texas”</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="36" t="n">
-        <v>46304</v>
+        <v>46310</v>
       </c>
       <c r="B77" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C77" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D77" s="43" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C77" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D77" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="31" t="n">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>135</v>
-      </c>
-      <c r="C78" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D78" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>125</v>
+      </c>
+      <c r="C78" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D78" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E78" s="30" t="inlineStr">
@@ -4867,81 +4837,81 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Texas”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="36" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="B79" s="41" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="C79" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D79" s="43" t="inlineStr">
+      <c r="D79" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E79" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="31" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B80" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C80" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D80" s="42" t="inlineStr">
+        <v>250</v>
+      </c>
+      <c r="C80" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D80" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E80" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="36" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B81" s="41" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="C81" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D81" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D81" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E81" s="35" t="inlineStr">
@@ -4951,7 +4921,7 @@
       </c>
       <c r="F81" s="35" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
@@ -4967,7 +4937,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D82" s="42" t="inlineStr">
+      <c r="D82" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4979,173 +4949,173 @@
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="36" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B83" s="41" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C83" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D83" s="43" t="inlineStr">
+      <c r="D83" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E83" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F83" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="31" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B84" s="33" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C84" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D84" s="42" t="inlineStr">
+      <c r="D84" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="36" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B85" s="41" t="n">
-        <v>250</v>
-      </c>
-      <c r="C85" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D85" s="43" t="inlineStr">
+        <v>46317</v>
+      </c>
+      <c r="B85" s="41" t="inlineStr"/>
+      <c r="C85" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D85" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E85" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>SZA x Vans VANSZA Collection</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="31" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B86" s="33" t="n">
-        <v>220</v>
-      </c>
-      <c r="C86" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D86" s="42" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C86" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D86" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E86" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="36" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B87" s="41" t="n">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="C87" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D87" s="43" t="inlineStr">
+      <c r="D87" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E87" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="31" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B88" s="33" t="inlineStr"/>
-      <c r="C88" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D88" s="42" t="inlineStr">
+        <v>46319</v>
+      </c>
+      <c r="B88" s="33" t="n">
+        <v>125</v>
+      </c>
+      <c r="C88" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D88" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E88" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>SZA x Vans VANSZA Collection</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
@@ -5154,26 +5124,26 @@
         <v>46319</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C89" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D89" s="43" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C89" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D89" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E89" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
@@ -5182,26 +5152,26 @@
         <v>46319</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C90" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D90" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C90" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D90" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E90" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
@@ -5210,26 +5180,26 @@
         <v>46319</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="C91" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D91" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C91" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D91" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E91" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
@@ -5238,11 +5208,11 @@
         <v>46319</v>
       </c>
       <c r="B92" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C92" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>150</v>
+      </c>
+      <c r="C92" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D92" s="34" t="inlineStr">
@@ -5257,7 +5227,7 @@
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
@@ -5266,16 +5236,16 @@
         <v>46319</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C93" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D93" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D93" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E93" s="35" t="inlineStr">
@@ -5285,51 +5255,51 @@
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="31" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B94" s="33" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C94" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D94" s="42" t="inlineStr">
+      <c r="D94" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E94" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="36" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="B95" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C95" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D95" s="43" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="C95" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D95" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5341,107 +5311,107 @@
       </c>
       <c r="F95" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="31" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="B96" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C96" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D96" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C96" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D96" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E96" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Nike Ja 4 High “University Red”</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="36" t="n">
-        <v>46320</v>
+        <v>46325</v>
       </c>
       <c r="B97" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C97" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D97" s="43" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="C97" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D97" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E97" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F97" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Nike Book 2 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="31" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="B98" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C98" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D98" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>215</v>
+      </c>
+      <c r="C98" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D98" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E98" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 High “University Red”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="36" t="n">
-        <v>46325</v>
+        <v>46329</v>
       </c>
       <c r="B99" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C99" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D99" s="43" t="inlineStr">
+        <v>240</v>
+      </c>
+      <c r="C99" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D99" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5453,23 +5423,23 @@
       </c>
       <c r="F99" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="31" t="n">
-        <v>46325</v>
+        <v>46331</v>
       </c>
       <c r="B100" s="33" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="C100" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D100" s="42" t="inlineStr">
+      <c r="D100" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5481,51 +5451,51 @@
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Halloween”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="36" t="n">
-        <v>46326</v>
+        <v>46331</v>
       </c>
       <c r="B101" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C101" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D101" s="43" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C101" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D101" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E101" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="31" t="n">
-        <v>46329</v>
+        <v>46332</v>
       </c>
       <c r="B102" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C102" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D102" s="42" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C102" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D102" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5537,231 +5507,231 @@
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Nike Book 2 “Desert Night”</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="36" t="n">
-        <v>46331</v>
+        <v>46333</v>
       </c>
       <c r="B103" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C103" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D103" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>245</v>
+      </c>
+      <c r="C103" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D103" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E103" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F103" s="35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="31" t="n">
-        <v>46331</v>
+        <v>46333</v>
       </c>
       <c r="B104" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C104" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D104" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>240</v>
+      </c>
+      <c r="C104" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D104" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E104" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F104" s="30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="36" t="n">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="B105" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C105" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D105" s="43" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C105" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D105" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E105" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Desert Night”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="31" t="n">
-        <v>46333</v>
+        <v>46335</v>
       </c>
       <c r="B106" s="33" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C106" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D106" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D106" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E106" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F106" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="36" t="n">
-        <v>46333</v>
+        <v>46337</v>
       </c>
       <c r="B107" s="41" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C107" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D107" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D107" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E107" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F107" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="31" t="n">
-        <v>46335</v>
+        <v>46337</v>
       </c>
       <c r="B108" s="33" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C108" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D108" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D108" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E108" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F108" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="36" t="n">
-        <v>46337</v>
+        <v>46338</v>
       </c>
       <c r="B109" s="41" t="n">
-        <v>235</v>
-      </c>
-      <c r="C109" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D109" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>170</v>
+      </c>
+      <c r="C109" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D109" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E109" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Lapis”</t>
+          <t>Nike Air Bakin “Varsity Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="31" t="n">
-        <v>46337</v>
+        <v>46338</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C110" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D110" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C110" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D110" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E110" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
         </is>
       </c>
     </row>
@@ -5777,9 +5747,9 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D111" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D111" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E111" s="35" t="inlineStr">
@@ -5789,76 +5759,76 @@
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal” 2026</t>
+          <t>Nike Air Bakin “Varsity Royal”</t>
         </is>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="31" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="B112" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C112" s="55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D112" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C112" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D112" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E112" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F112" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="36" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="B113" s="41" t="n">
-        <v>170</v>
+        <v>240</v>
       </c>
       <c r="C113" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D113" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D113" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E113" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F113" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal”</t>
+          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="31" t="n">
-        <v>46340</v>
+        <v>46341</v>
       </c>
       <c r="B114" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C114" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>155</v>
+      </c>
+      <c r="C114" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D114" s="34" t="inlineStr">
@@ -5868,25 +5838,25 @@
       </c>
       <c r="E114" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F114" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Playa Society x Nike A’Two</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="36" t="n">
-        <v>46340</v>
+        <v>46342</v>
       </c>
       <c r="B115" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C115" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>255</v>
+      </c>
+      <c r="C115" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D115" s="38" t="inlineStr">
@@ -5901,25 +5871,25 @@
       </c>
       <c r="F115" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="31" t="n">
-        <v>46341</v>
+        <v>46343</v>
       </c>
       <c r="B116" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C116" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D116" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>200</v>
+      </c>
+      <c r="C116" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D116" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E116" s="30" t="inlineStr">
@@ -5929,51 +5899,51 @@
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>Playa Society x Nike A’Two</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="36" t="n">
-        <v>46342</v>
+        <v>46345</v>
       </c>
       <c r="B117" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C117" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D117" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C117" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D117" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E117" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F117" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Vans Old Skool 36 Pearlized “Navy”</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="31" t="n">
-        <v>46343</v>
+        <v>46346</v>
       </c>
       <c r="B118" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C118" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D118" s="42" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C118" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D118" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5985,51 +5955,51 @@
       </c>
       <c r="F118" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Nike Book 2 “Be Legendary”</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="36" t="n">
-        <v>46345</v>
+        <v>46346</v>
       </c>
       <c r="B119" s="41" t="n">
         <v>130</v>
       </c>
-      <c r="C119" s="50" t="inlineStr">
+      <c r="C119" s="49" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D119" s="43" t="inlineStr">
+      <c r="D119" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E119" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Navy”</t>
+          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="31" t="n">
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="B120" s="33" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C120" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D120" s="42" t="inlineStr">
+      <c r="D120" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6041,35 +6011,35 @@
       </c>
       <c r="F120" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Be Legendary”</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="36" t="n">
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="B121" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C121" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D121" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>230</v>
+      </c>
+      <c r="C121" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D121" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E121" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F121" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -6078,26 +6048,26 @@
         <v>46347</v>
       </c>
       <c r="B122" s="33" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C122" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D122" s="42" t="inlineStr">
+      <c r="D122" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F122" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
@@ -6108,12 +6078,12 @@
       <c r="B123" s="41" t="n">
         <v>140</v>
       </c>
-      <c r="C123" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D123" s="43" t="inlineStr">
+      <c r="C123" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D123" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6125,7 +6095,7 @@
       </c>
       <c r="F123" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Snow White”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
@@ -6133,27 +6103,25 @@
       <c r="A124" s="31" t="n">
         <v>46347</v>
       </c>
-      <c r="B124" s="33" t="n">
-        <v>230</v>
-      </c>
-      <c r="C124" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D124" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B124" s="33" t="inlineStr"/>
+      <c r="C124" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D124" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E124" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F124" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
         </is>
       </c>
     </row>
@@ -6162,14 +6130,14 @@
         <v>46347</v>
       </c>
       <c r="B125" s="41" t="n">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="C125" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D125" s="43" t="inlineStr">
+      <c r="D125" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6181,7 +6149,7 @@
       </c>
       <c r="F125" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -6190,14 +6158,14 @@
         <v>46347</v>
       </c>
       <c r="B126" s="33" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C126" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D126" s="42" t="inlineStr">
+      <c r="D126" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6209,61 +6177,63 @@
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="36" t="n">
-        <v>46347</v>
-      </c>
-      <c r="B127" s="41" t="inlineStr"/>
-      <c r="C127" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D127" s="43" t="inlineStr">
+        <v>46353</v>
+      </c>
+      <c r="B127" s="41" t="n">
+        <v>230</v>
+      </c>
+      <c r="C127" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D127" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E127" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" s="31" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B128" s="33" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="C128" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D128" s="42" t="inlineStr">
+      <c r="D128" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E128" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F128" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
@@ -6272,42 +6242,40 @@
         <v>46353</v>
       </c>
       <c r="B129" s="41" t="n">
-        <v>230</v>
-      </c>
-      <c r="C129" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D129" s="43" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C129" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D129" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E129" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F129" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Vans Old Skool 36 Pearlized “Black”</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" s="31" t="n">
-        <v>46353</v>
-      </c>
-      <c r="B130" s="33" t="n">
-        <v>240</v>
-      </c>
+        <v>46354</v>
+      </c>
+      <c r="B130" s="33" t="inlineStr"/>
       <c r="C130" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D130" s="42" t="inlineStr">
+      <c r="D130" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6319,35 +6287,35 @@
       </c>
       <c r="F130" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1">
       <c r="A131" s="36" t="n">
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="B131" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C131" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D131" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>120</v>
+      </c>
+      <c r="C131" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D131" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E131" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F131" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Black”</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -6356,16 +6324,16 @@
         <v>46354</v>
       </c>
       <c r="B132" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C132" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D132" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>130</v>
+      </c>
+      <c r="C132" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D132" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E132" s="30" t="inlineStr">
@@ -6375,7 +6343,7 @@
       </c>
       <c r="F132" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Warning Code”</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
@@ -6384,12 +6352,12 @@
         <v>46354</v>
       </c>
       <c r="B133" s="41" t="inlineStr"/>
-      <c r="C133" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D133" s="43" t="inlineStr">
+      <c r="C133" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D133" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6401,7 +6369,7 @@
       </c>
       <c r="F133" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Nike KD 6 “Aunt Pearl” 2026</t>
         </is>
       </c>
     </row>
@@ -6409,12 +6377,10 @@
       <c r="A134" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B134" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="C134" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B134" s="33" t="inlineStr"/>
+      <c r="C134" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
         </is>
       </c>
       <c r="D134" s="34" t="inlineStr">
@@ -6424,12 +6390,12 @@
       </c>
       <c r="E134" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F134" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
@@ -6437,13 +6403,15 @@
       <c r="A135" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B135" s="41" t="inlineStr"/>
-      <c r="C135" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D135" s="43" t="inlineStr">
+      <c r="B135" s="41" t="n">
+        <v>190</v>
+      </c>
+      <c r="C135" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D135" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6455,7 +6423,7 @@
       </c>
       <c r="F135" s="35" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Aunt Pearl” 2026</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
@@ -6464,16 +6432,16 @@
         <v>46354</v>
       </c>
       <c r="B136" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C136" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D136" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C136" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D136" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E136" s="30" t="inlineStr">
@@ -6483,95 +6451,95 @@
       </c>
       <c r="F136" s="30" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Nike Caitlin 1 “Warning Code”</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="36" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B137" s="41" t="inlineStr"/>
-      <c r="C137" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D137" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>46359</v>
+      </c>
+      <c r="B137" s="41" t="n">
+        <v>170</v>
+      </c>
+      <c r="C137" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D137" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E137" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F137" s="35" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Nike Air Bakin “Black/White”</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="A138" s="31" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B138" s="33" t="n">
-        <v>190</v>
-      </c>
+        <v>46361</v>
+      </c>
+      <c r="B138" s="33" t="inlineStr"/>
       <c r="C138" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D138" s="42" t="inlineStr">
+      <c r="D138" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E138" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F138" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1">
       <c r="A139" s="36" t="n">
-        <v>46359</v>
+        <v>46361</v>
       </c>
       <c r="B139" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C139" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D139" s="43" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C139" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D139" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E139" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F139" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Black/White”</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" s="31" t="n">
-        <v>46361</v>
+        <v>46367</v>
       </c>
       <c r="B140" s="33" t="inlineStr"/>
       <c r="C140" s="39" t="inlineStr">
@@ -6579,9 +6547,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D140" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D140" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E140" s="30" t="inlineStr">
@@ -6591,25 +6559,25 @@
       </c>
       <c r="F140" s="30" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1">
       <c r="A141" s="36" t="n">
-        <v>46361</v>
+        <v>46367</v>
       </c>
       <c r="B141" s="41" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="C141" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D141" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D141" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E141" s="35" t="inlineStr">
@@ -6619,7 +6587,7 @@
       </c>
       <c r="F141" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6603,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D142" s="42" t="inlineStr">
+      <c r="D142" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6655,43 +6623,45 @@
       <c r="A143" s="36" t="n">
         <v>46367</v>
       </c>
-      <c r="B143" s="41" t="inlineStr"/>
+      <c r="B143" s="41" t="n">
+        <v>190</v>
+      </c>
       <c r="C143" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D143" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D143" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E143" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F143" s="35" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1">
       <c r="A144" s="31" t="n">
-        <v>46367</v>
+        <v>46368</v>
       </c>
       <c r="B144" s="33" t="n">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="C144" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D144" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D144" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E144" s="30" t="inlineStr">
@@ -6701,68 +6671,12 @@
       </c>
       <c r="F144" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B145" s="41" t="n">
-        <v>190</v>
-      </c>
-      <c r="C145" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D145" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E145" s="35" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="F145" s="35" t="inlineStr">
-        <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="15" customHeight="1">
-      <c r="A146" s="31" t="n">
-        <v>46368</v>
-      </c>
-      <c r="B146" s="33" t="n">
-        <v>235</v>
-      </c>
-      <c r="C146" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D146" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E146" s="30" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F146" s="30" t="inlineStr">
-        <is>
           <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F146"/>
+  <autoFilter ref="A3:F144"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -6777,7 +6691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6801,9 +6715,9 @@
       <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="52" t="inlineStr">
-        <is>
-          <t>Generated September 15, 2026  ·  11:19 UTC</t>
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t>Generated September 16, 2026  ·  11:01 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -6846,63 +6760,63 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="C4" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D4" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 “Iron Grey”</t>
+          <t>Air Jordan 6 Low “Metamorphosis”</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D5" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Yuto Horigome x Nike SB Air Force 1 Low</t>
+          <t>Air Jordan 4 “London”</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B6" s="33" t="n">
         <v>205</v>
@@ -6912,7 +6826,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
+      <c r="D6" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6924,25 +6838,25 @@
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 Low “Metamorphosis”</t>
+          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="36" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D7" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
@@ -6952,7 +6866,7 @@
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>APB x Air Jordan 11 Low</t>
         </is>
       </c>
     </row>
@@ -6961,14 +6875,14 @@
         <v>46283</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="D8" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6980,7 +6894,7 @@
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
     </row>
@@ -6989,26 +6903,26 @@
         <v>46283</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
     </row>
@@ -7017,16 +6931,16 @@
         <v>46283</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D10" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
@@ -7036,7 +6950,7 @@
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -7045,42 +6959,42 @@
         <v>46283</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D11" s="43" t="inlineStr">
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>Nike Air Foamposite Pro “Green Camo”</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>250</v>
+        <v>122</v>
       </c>
       <c r="C12" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D12" s="42" t="inlineStr">
+      <c r="D12" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7092,23 +7006,23 @@
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C13" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D13" s="43" t="inlineStr">
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7120,7 +7034,7 @@
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo”</t>
+          <t>Nike Kobe 8 Protro “Mambacurial”</t>
         </is>
       </c>
     </row>
@@ -7129,63 +7043,63 @@
         <v>46284</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D14" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>APB x Air Jordan 11 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="36" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C15" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D15" s="43" t="inlineStr">
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="31" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="C16" s="39" t="inlineStr">
         <is>
@@ -7204,7 +7118,7 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
@@ -7238,17 +7152,17 @@
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C18" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D18" s="42" t="inlineStr">
+      <c r="D18" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7260,25 +7174,25 @@
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>255</v>
+        <v>155</v>
       </c>
       <c r="C19" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D19" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D19" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
@@ -7288,7 +7202,7 @@
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -7297,16 +7211,16 @@
         <v>46291</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D20" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
@@ -7316,7 +7230,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -7324,13 +7238,15 @@
       <c r="A21" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B21" s="41" t="inlineStr"/>
+      <c r="B21" s="41" t="n">
+        <v>210</v>
+      </c>
       <c r="C21" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D21" s="43" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7342,7 +7258,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -7351,16 +7267,16 @@
         <v>46291</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D22" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
@@ -7370,7 +7286,7 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -7379,26 +7295,26 @@
         <v>46291</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="43" t="inlineStr">
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -7406,27 +7322,25 @@
       <c r="A24" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B24" s="33" t="n">
-        <v>155</v>
-      </c>
+      <c r="B24" s="33" t="inlineStr"/>
       <c r="C24" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D24" s="42" t="inlineStr">
+      <c r="D24" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E24" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -7435,7 +7349,7 @@
         <v>46291</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
@@ -7454,7 +7368,7 @@
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7384,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D26" s="42" t="inlineStr">
+      <c r="D26" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7482,23 +7396,23 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="36" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D27" s="43" t="inlineStr">
+      <c r="D27" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7510,23 +7424,21 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="31" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B28" s="33" t="n">
-        <v>210</v>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="B28" s="33" t="inlineStr"/>
       <c r="C28" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D28" s="42" t="inlineStr">
+      <c r="D28" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7538,7 +7450,7 @@
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7459,16 @@
         <v>46295</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D29" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D29" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -7566,7 +7478,7 @@
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
@@ -7575,26 +7487,26 @@
         <v>46295</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="C30" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D30" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -7603,98 +7515,100 @@
         <v>46295</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="C31" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D31" s="43" t="inlineStr">
+      <c r="D31" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B32" s="33" t="inlineStr"/>
+        <v>46297</v>
+      </c>
+      <c r="B32" s="33" t="n">
+        <v>220</v>
+      </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D32" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D32" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="36" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="C33" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D33" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="31" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="C34" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D34" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D34" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
@@ -7704,51 +7618,51 @@
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Howard” 2026</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D35" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D35" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="31" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="B36" s="33" t="n">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="C36" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D36" s="42" t="inlineStr">
+      <c r="D36" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7760,16 +7674,16 @@
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46298</v>
+        <v>46310</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>240</v>
+        <v>125</v>
       </c>
       <c r="C37" s="40" t="inlineStr">
         <is>
@@ -7783,28 +7697,28 @@
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="31" t="n">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C38" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D38" s="42" t="inlineStr">
+      <c r="D38" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7816,53 +7730,53 @@
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="B39" s="41" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="C39" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D39" s="43" t="inlineStr">
+      <c r="D39" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="C40" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D40" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D40" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
@@ -7872,7 +7786,7 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7802,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D41" s="43" t="inlineStr">
+      <c r="D41" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7900,79 +7814,79 @@
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="31" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C42" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D42" s="42" t="inlineStr">
+      <c r="D42" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E42" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="36" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B43" s="41" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C43" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D43" s="43" t="inlineStr">
+      <c r="D43" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="31" t="n">
-        <v>46311</v>
+        <v>46319</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D44" s="42" t="inlineStr">
+      <c r="D44" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7984,51 +7898,51 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>220</v>
+        <v>125</v>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D45" s="43" t="inlineStr">
+      <c r="D45" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="31" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D46" s="42" t="inlineStr">
+      <c r="D46" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8040,7 +7954,7 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
@@ -8074,103 +7988,103 @@
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="31" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D48" s="42" t="inlineStr">
+      <c r="D48" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="36" t="n">
-        <v>46319</v>
+        <v>46326</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D49" s="43" t="inlineStr">
+      <c r="D49" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="31" t="n">
-        <v>46319</v>
+        <v>46329</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="C50" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D50" s="42" t="inlineStr">
+      <c r="D50" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46320</v>
+        <v>46333</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>205</v>
+        <v>245</v>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D51" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D51" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
@@ -8180,25 +8094,25 @@
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="31" t="n">
-        <v>46326</v>
+        <v>46333</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D52" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D52" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
@@ -8208,137 +8122,137 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="36" t="n">
-        <v>46329</v>
+        <v>46333</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="43" t="inlineStr">
+      <c r="D53" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="31" t="n">
-        <v>46333</v>
+        <v>46335</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D54" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46333</v>
+        <v>46337</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D55" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D55" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46335</v>
+        <v>46337</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C56" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D56" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D56" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46337</v>
+        <v>46340</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="C57" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D57" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D57" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
@@ -8348,72 +8262,72 @@
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Lapis”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="31" t="n">
-        <v>46337</v>
+        <v>46342</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C58" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D58" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D58" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46340</v>
+        <v>46343</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D59" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D59" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46342</v>
+        <v>46347</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
@@ -8427,40 +8341,40 @@
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46343</v>
+        <v>46347</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D61" s="43" t="inlineStr">
+      <c r="D61" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
@@ -8469,14 +8383,14 @@
         <v>46347</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C62" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D62" s="42" t="inlineStr">
+      <c r="D62" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8488,7 +8402,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
@@ -8497,26 +8411,26 @@
         <v>46347</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D63" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D63" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -8525,128 +8439,126 @@
         <v>46347</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D64" s="42" t="inlineStr">
+      <c r="D64" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="36" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D65" s="43" t="inlineStr">
+      <c r="D65" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D66" s="42" t="inlineStr">
+      <c r="D66" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46353</v>
-      </c>
-      <c r="B67" s="41" t="n">
-        <v>230</v>
-      </c>
+        <v>46354</v>
+      </c>
+      <c r="B67" s="41" t="inlineStr"/>
       <c r="C67" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D67" s="43" t="inlineStr">
+      <c r="D67" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D68" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D68" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
@@ -8656,7 +8568,7 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -8664,15 +8576,17 @@
       <c r="A69" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B69" s="41" t="inlineStr"/>
+      <c r="B69" s="41" t="n">
+        <v>130</v>
+      </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D69" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D69" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
@@ -8682,7 +8596,7 @@
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
@@ -8690,12 +8604,10 @@
       <c r="A70" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B70" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="C70" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B70" s="33" t="inlineStr"/>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
@@ -8705,12 +8617,12 @@
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
@@ -8719,16 +8631,16 @@
         <v>46354</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D71" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D71" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
@@ -8738,23 +8650,23 @@
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46354</v>
+        <v>46361</v>
       </c>
       <c r="B72" s="33" t="inlineStr"/>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D72" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C72" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D72" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E72" s="30" t="inlineStr">
@@ -8764,41 +8676,41 @@
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46354</v>
+        <v>46361</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D73" s="43" t="inlineStr">
+      <c r="D73" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46361</v>
+        <v>46367</v>
       </c>
       <c r="B74" s="33" t="inlineStr"/>
       <c r="C74" s="39" t="inlineStr">
@@ -8806,9 +8718,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D74" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D74" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
@@ -8818,25 +8730,25 @@
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46361</v>
+        <v>46367</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="C75" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D75" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D75" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
@@ -8846,7 +8758,7 @@
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8774,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D76" s="42" t="inlineStr">
+      <c r="D76" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8882,43 +8794,45 @@
       <c r="A77" s="36" t="n">
         <v>46367</v>
       </c>
-      <c r="B77" s="41" t="inlineStr"/>
+      <c r="B77" s="41" t="n">
+        <v>190</v>
+      </c>
       <c r="C77" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D77" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D77" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="31" t="n">
-        <v>46367</v>
+        <v>46368</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="C78" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D78" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D78" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E78" s="30" t="inlineStr">
@@ -8928,68 +8842,12 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B79" s="41" t="n">
-        <v>190</v>
-      </c>
-      <c r="C79" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D79" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E79" s="35" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="F79" s="35" t="inlineStr">
-        <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="31" t="n">
-        <v>46368</v>
-      </c>
-      <c r="B80" s="33" t="n">
-        <v>235</v>
-      </c>
-      <c r="C80" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D80" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E80" s="30" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F80" s="30" t="inlineStr">
-        <is>
           <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F80"/>
+  <autoFilter ref="A3:F78"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$144</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -642,10 +642,10 @@
     <xf numFmtId="166" fontId="10" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -670,10 +670,10 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1569,7 +1569,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 16, 2026  ·  11:01 UTC</t>
+          <t>Generated September 17, 2026  ·  11:12 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1613,11 +1613,11 @@
       </c>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="14" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="16" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="18" t="inlineStr">
@@ -1725,7 +1725,7 @@
         <v>46290</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>46295</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 Low “Metamorphosis”</t>
+          <t>Air Jordan 4 “London”</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D13" s="35" t="n">
         <v>0</v>
@@ -1836,27 +1836,27 @@
         <v>7</v>
       </c>
       <c r="G13" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="H13" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>220</v>
+      </c>
+      <c r="H13" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="C14" s="31" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D14" s="30" t="n">
         <v>1</v>
@@ -1870,30 +1870,30 @@
         <v>7</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>220</v>
-      </c>
-      <c r="H14" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>250</v>
+      </c>
+      <c r="H14" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
         <v>46283</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
@@ -1904,9 +1904,9 @@
         <v>7</v>
       </c>
       <c r="G15" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="H15" s="42" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="H15" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -1915,7 +1915,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
@@ -1927,7 +1927,7 @@
         <v>46283</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
@@ -1938,11 +1938,11 @@
         <v>7</v>
       </c>
       <c r="G16" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="H16" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="B20" s="30" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="B21" s="35" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E21" s="35" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G21" s="47" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="E22" s="30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="E23" s="35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="B25" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -2161,17 +2161,17 @@
       </c>
       <c r="B30" s="30" t="inlineStr">
         <is>
-          <t>9/16 – 9/22</t>
+          <t>9/17 – 9/23</t>
         </is>
       </c>
       <c r="C30" s="30" t="n">
         <v>23</v>
       </c>
       <c r="D30" s="39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E30" s="30" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
@@ -2182,17 +2182,17 @@
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>9/23 – 9/29</t>
+          <t>9/24 – 9/30</t>
         </is>
       </c>
       <c r="C31" s="35" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D31" s="40" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E31" s="35" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -2203,17 +2203,17 @@
       </c>
       <c r="B32" s="30" t="inlineStr">
         <is>
-          <t>9/30 – 10/6</t>
+          <t>10/1 – 10/7</t>
         </is>
       </c>
       <c r="C32" s="30" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D32" s="39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E32" s="30" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>10/7 – 10/13</t>
+          <t>10/8 – 10/14</t>
         </is>
       </c>
       <c r="C33" s="35" t="n">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="B34" s="30" t="inlineStr">
         <is>
-          <t>10/14 – 10/20</t>
+          <t>10/15 – 10/21</t>
         </is>
       </c>
       <c r="C34" s="30" t="n">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B35" s="35" t="inlineStr">
         <is>
-          <t>10/21 – 10/27</t>
+          <t>10/22 – 10/28</t>
         </is>
       </c>
       <c r="C35" s="35" t="n">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="B36" s="30" t="inlineStr">
         <is>
-          <t>10/28 – 11/3</t>
+          <t>10/29 – 11/4</t>
         </is>
       </c>
       <c r="C36" s="30" t="n">
@@ -2308,17 +2308,17 @@
       </c>
       <c r="B37" s="35" t="inlineStr">
         <is>
-          <t>11/4 – 11/10</t>
+          <t>11/5 – 11/11</t>
         </is>
       </c>
       <c r="C37" s="35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D37" s="40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E37" s="35" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
@@ -2329,17 +2329,17 @@
       </c>
       <c r="B38" s="30" t="inlineStr">
         <is>
-          <t>11/11 – 11/17</t>
+          <t>11/12 – 11/18</t>
         </is>
       </c>
       <c r="C38" s="30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D38" s="39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E38" s="30" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>11/18 – 11/24</t>
+          <t>11/19 – 11/25</t>
         </is>
       </c>
       <c r="C39" s="35" t="n">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B40" s="30" t="inlineStr">
         <is>
-          <t>11/25 – 12/1</t>
+          <t>11/26 – 12/2</t>
         </is>
       </c>
       <c r="C40" s="30" t="n">
@@ -2392,17 +2392,17 @@
       </c>
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>12/2 – 12/8</t>
+          <t>12/3 – 12/9</t>
         </is>
       </c>
       <c r="C41" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" s="40" t="n">
         <v>2</v>
       </c>
       <c r="E41" s="35" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="B42" s="30" t="inlineStr">
         <is>
-          <t>12/9 – 12/15</t>
+          <t>12/10 – 12/16</t>
         </is>
       </c>
       <c r="C42" s="30" t="n">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2710,7 +2710,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="51" t="inlineStr">
         <is>
-          <t>Generated September 16, 2026  ·  11:01 UTC</t>
+          <t>Generated September 17, 2026  ·  11:12 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2753,19 +2753,19 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C4" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D4" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
@@ -2775,63 +2775,63 @@
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 Low “Metamorphosis”</t>
+          <t>Air Jordan 4 “London”</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C5" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D5" s="42" t="inlineStr">
+        <v>250</v>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Reebok Brutus Low “Philadelphia Eagles”</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
     </row>
@@ -2840,16 +2840,16 @@
         <v>46283</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D7" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -2868,26 +2868,26 @@
         <v>46283</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>135</v>
-      </c>
-      <c r="C8" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D8" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>205</v>
+      </c>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>PSG x Nike KD 6</t>
+          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
         </is>
       </c>
     </row>
@@ -2896,26 +2896,26 @@
         <v>46283</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C9" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D9" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>135</v>
+      </c>
+      <c r="C9" s="52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D9" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>PSG x Nike KD 6</t>
         </is>
       </c>
     </row>
@@ -2924,26 +2924,26 @@
         <v>46283</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C10" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="43" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Cold Blooded”</t>
+          <t>APB x Air Jordan 11 Low</t>
         </is>
       </c>
     </row>
@@ -2952,26 +2952,26 @@
         <v>46283</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C11" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D11" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C11" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Nike A’Two “Dawn Staley”</t>
+          <t>adidas Anthony Edwards 3 “Cold Blooded”</t>
         </is>
       </c>
     </row>
@@ -2980,26 +2980,26 @@
         <v>46283</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>65</v>
-      </c>
-      <c r="C12" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="43" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C12" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
+          <t>Nike A’Two “Dawn Staley”</t>
         </is>
       </c>
     </row>
@@ -3008,26 +3008,26 @@
         <v>46283</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>250</v>
-      </c>
-      <c r="C13" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D13" s="42" t="inlineStr">
+        <v>65</v>
+      </c>
+      <c r="C13" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
         </is>
       </c>
     </row>
@@ -3036,14 +3036,14 @@
         <v>46283</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D14" s="43" t="inlineStr">
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>Nike Air Foamposite One "Green Camo"</t>
         </is>
       </c>
     </row>
@@ -3064,26 +3064,26 @@
         <v>46283</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C15" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D15" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>110</v>
+      </c>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Anthony Edwards x adidas Superstar “Cold Blooded”</t>
         </is>
       </c>
     </row>
@@ -3092,42 +3092,42 @@
         <v>46283</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>110</v>
-      </c>
-      <c r="C16" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="43" t="inlineStr">
+        <v>250</v>
+      </c>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Anthony Edwards x adidas Superstar “Cold Blooded”</t>
+          <t>Nike Air Foamposite Pro “Green Camo”</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>250</v>
+        <v>122</v>
       </c>
       <c r="C17" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D17" s="42" t="inlineStr">
+      <c r="D17" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo”</t>
+          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
         </is>
       </c>
     </row>
@@ -3148,26 +3148,26 @@
         <v>46284</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>300</v>
-      </c>
-      <c r="C18" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D18" s="43" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
+          <t>Nike Kobe 8 Protro “Mambacurial”</t>
         </is>
       </c>
     </row>
@@ -3176,16 +3176,16 @@
         <v>46284</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C19" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D19" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>205</v>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D19" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 9 OG “Space Jam” 2026</t>
+          <t>APB x Air Jordan 11 Low Pack</t>
         </is>
       </c>
     </row>
@@ -3204,14 +3204,14 @@
         <v>46284</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>110</v>
-      </c>
-      <c r="C20" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="43" t="inlineStr">
+        <v>300</v>
+      </c>
+      <c r="C20" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Pokémon x adidas 30th Anniversary Collection</t>
+          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
         </is>
       </c>
     </row>
@@ -3232,26 +3232,26 @@
         <v>46284</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>122</v>
-      </c>
-      <c r="C21" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D21" s="42" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C21" s="52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>Air Jordan 9 OG “Space Jam” 2026</t>
         </is>
       </c>
     </row>
@@ -3260,26 +3260,26 @@
         <v>46284</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C22" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D22" s="43" t="inlineStr">
+        <v>110</v>
+      </c>
+      <c r="C22" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>Pokémon x adidas 30th Anniversary Collection</t>
         </is>
       </c>
     </row>
@@ -3288,26 +3288,26 @@
         <v>46284</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D24" s="43" t="inlineStr">
+      <c r="D24" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3341,35 +3341,35 @@
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="36" t="n">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>300</v>
-      </c>
-      <c r="C25" s="53" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C25" s="52" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D25" s="42" t="inlineStr">
+      <c r="D25" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish</t>
+          <t>Nike GT Future “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="31" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B26" s="33" t="n">
         <v>210</v>
@@ -3379,7 +3379,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D26" s="43" t="inlineStr">
+      <c r="D26" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3391,35 +3391,35 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Nike GT Future “Varsity Red”</t>
+          <t>Nike GT Future “Unseen Hours”</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="36" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C27" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D27" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C27" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Nike GT Future “Unseen Hours”</t>
+          <t>Converse SHAI 001 “Green Beam”</t>
         </is>
       </c>
     </row>
@@ -3430,12 +3430,12 @@
       <c r="B28" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C28" s="52" t="inlineStr">
+      <c r="C28" s="53" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
+      <c r="D28" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3463,7 +3463,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D29" s="42" t="inlineStr">
+      <c r="D29" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Green Beam”</t>
+          <t>Converse SHAI 001 Shroud “Shock”</t>
         </is>
       </c>
     </row>
@@ -3486,12 +3486,12 @@
       <c r="B30" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C30" s="52" t="inlineStr">
+      <c r="C30" s="53" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D30" s="43" t="inlineStr">
+      <c r="D30" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3503,35 +3503,35 @@
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 Shroud “Shock”</t>
+          <t>Converse SHAI 001 “Spark”</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="36" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C31" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D31" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C31" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D31" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Spark”</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D32" s="43" t="inlineStr">
+      <c r="D32" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3575,7 +3575,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D33" s="42" t="inlineStr">
+      <c r="D33" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3603,7 +3603,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D34" s="43" t="inlineStr">
+      <c r="D34" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3652,26 +3652,26 @@
         <v>46290</v>
       </c>
       <c r="B36" s="33" t="n">
-        <v>225</v>
-      </c>
-      <c r="C36" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D36" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C36" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D36" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Nike Ja 4 “Jaws”</t>
         </is>
       </c>
     </row>
@@ -3680,14 +3680,14 @@
         <v>46290</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C37" s="53" t="inlineStr">
+        <v>185</v>
+      </c>
+      <c r="C37" s="52" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D37" s="42" t="inlineStr">
+      <c r="D37" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws”</t>
+          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
         </is>
       </c>
     </row>
@@ -3708,14 +3708,14 @@
         <v>46290</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="C38" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D38" s="43" t="inlineStr">
+      <c r="D38" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3727,23 +3727,23 @@
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
+          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B39" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C39" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D39" s="42" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C39" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D39" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -3764,26 +3764,26 @@
         <v>46291</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C40" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D40" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>125</v>
+      </c>
+      <c r="C40" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -3792,26 +3792,26 @@
         <v>46291</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D41" s="42" t="inlineStr">
+      <c r="D41" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -3820,11 +3820,11 @@
         <v>46291</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C42" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>180</v>
+      </c>
+      <c r="C42" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D42" s="34" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
@@ -3848,24 +3848,24 @@
         <v>46291</v>
       </c>
       <c r="B43" s="41" t="inlineStr"/>
-      <c r="C43" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D43" s="42" t="inlineStr">
+      <c r="C43" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D43" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -3874,11 +3874,11 @@
         <v>46291</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C44" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>210</v>
+      </c>
+      <c r="C44" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D44" s="34" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -3902,16 +3902,16 @@
         <v>46291</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C45" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D45" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>200</v>
+      </c>
+      <c r="C45" s="52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D45" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
         </is>
       </c>
     </row>
@@ -3930,26 +3930,26 @@
         <v>46291</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>160</v>
-      </c>
-      <c r="C46" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D46" s="43" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C46" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D46" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -3958,26 +3958,26 @@
         <v>46291</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D47" s="42" t="inlineStr">
+      <c r="D47" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -3986,11 +3986,11 @@
         <v>46291</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C48" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>150</v>
+      </c>
+      <c r="C48" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -4013,27 +4013,25 @@
       <c r="A49" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B49" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C49" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D49" s="42" t="inlineStr">
+      <c r="B49" s="41" t="inlineStr"/>
+      <c r="C49" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D49" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4040,7 @@
         <v>46291</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="C50" s="48" t="inlineStr">
         <is>
@@ -4061,7 +4059,7 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
@@ -4069,13 +4067,15 @@
       <c r="A51" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B51" s="41" t="inlineStr"/>
+      <c r="B51" s="41" t="n">
+        <v>210</v>
+      </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D51" s="42" t="inlineStr">
+      <c r="D51" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -4096,26 +4096,26 @@
         <v>46291</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C52" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D52" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>160</v>
+      </c>
+      <c r="C52" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D52" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
         </is>
       </c>
     </row>
@@ -4124,26 +4124,26 @@
         <v>46291</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C53" s="53" t="inlineStr">
+        <v>120</v>
+      </c>
+      <c r="C53" s="52" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D53" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D53" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
+          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
         </is>
       </c>
     </row>
@@ -4152,80 +4152,80 @@
         <v>46291</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="C54" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D54" s="43" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C54" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D54" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B55" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C55" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D55" s="42" t="inlineStr">
+        <v>46293</v>
+      </c>
+      <c r="B55" s="41" t="inlineStr"/>
+      <c r="C55" s="52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D55" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B56" s="33" t="inlineStr"/>
+        <v>46294</v>
+      </c>
+      <c r="B56" s="33" t="n">
+        <v>170</v>
+      </c>
       <c r="C56" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D56" s="43" t="inlineStr">
+      <c r="D56" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
+          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
         </is>
       </c>
     </row>
@@ -4234,14 +4234,14 @@
         <v>46294</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C57" s="53" t="inlineStr">
+        <v>249</v>
+      </c>
+      <c r="C57" s="52" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D57" s="42" t="inlineStr">
+      <c r="D57" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
+          <t>Hyperice x Nike Air Zoom Hyperslide</t>
         </is>
       </c>
     </row>
@@ -4262,14 +4262,14 @@
         <v>46294</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>249</v>
+        <v>170</v>
       </c>
       <c r="C58" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D58" s="43" t="inlineStr">
+      <c r="D58" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4281,25 +4281,25 @@
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Hyperice x Nike Air Zoom Hyperslide</t>
+          <t>Nike Air Bakin “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C59" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D59" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>135</v>
+      </c>
+      <c r="C59" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D59" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Red”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -4318,26 +4318,26 @@
         <v>46295</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D60" s="43" t="inlineStr">
+      <c r="D60" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
@@ -4345,13 +4345,15 @@
       <c r="A61" s="36" t="n">
         <v>46295</v>
       </c>
-      <c r="B61" s="41" t="inlineStr"/>
+      <c r="B61" s="41" t="n">
+        <v>125</v>
+      </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D61" s="42" t="inlineStr">
+      <c r="D61" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4363,7 +4365,7 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
@@ -4371,17 +4373,15 @@
       <c r="A62" s="31" t="n">
         <v>46295</v>
       </c>
-      <c r="B62" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C62" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D62" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B62" s="33" t="inlineStr"/>
+      <c r="C62" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D62" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>MoMA x Nike Air Rift 2 Pack</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
@@ -4400,16 +4400,16 @@
         <v>46295</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C63" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D63" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>130</v>
+      </c>
+      <c r="C63" s="52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D63" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>MoMA x Nike Air Rift 2 Pack</t>
         </is>
       </c>
     </row>
@@ -4428,16 +4428,16 @@
         <v>46295</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D64" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D64" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
@@ -4447,25 +4447,25 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="36" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D65" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D65" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Air Jordan 1 Low OG “Howard” 2026</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D66" s="43" t="inlineStr">
+      <c r="D66" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4509,12 +4509,14 @@
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B67" s="41" t="inlineStr"/>
-      <c r="C67" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>46297</v>
+      </c>
+      <c r="B67" s="41" t="n">
+        <v>220</v>
+      </c>
+      <c r="C67" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D67" s="38" t="inlineStr">
@@ -4529,25 +4531,25 @@
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan “Black Pack”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D68" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D68" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
@@ -4557,7 +4559,7 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
@@ -4591,85 +4593,85 @@
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="B70" s="33" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C70" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D70" s="43" t="inlineStr">
+      <c r="D70" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46300</v>
+        <v>46303</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C71" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D71" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C71" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D71" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C72" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D72" s="43" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C72" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D72" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
+          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4687,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D73" s="42" t="inlineStr">
+      <c r="D73" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4703,17 +4705,17 @@
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="C74" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D74" s="43" t="inlineStr">
+      <c r="D74" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4725,7 +4727,7 @@
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
+          <t>Nike KD 6 “Texas”</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4743,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D75" s="42" t="inlineStr">
+      <c r="D75" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4759,29 +4761,29 @@
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="31" t="n">
-        <v>46305</v>
+        <v>46310</v>
       </c>
       <c r="B76" s="33" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C76" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D76" s="43" t="inlineStr">
+      <c r="D76" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Texas”</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
@@ -4792,42 +4794,42 @@
       <c r="B77" s="41" t="n">
         <v>125</v>
       </c>
-      <c r="C77" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D77" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="C77" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D77" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="31" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="C78" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D78" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D78" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E78" s="30" t="inlineStr">
@@ -4837,7 +4839,7 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
@@ -4846,14 +4848,14 @@
         <v>46311</v>
       </c>
       <c r="B79" s="41" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C79" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D79" s="42" t="inlineStr">
+      <c r="D79" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4865,7 +4867,7 @@
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -4874,14 +4876,14 @@
         <v>46311</v>
       </c>
       <c r="B80" s="33" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C80" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D80" s="43" t="inlineStr">
+      <c r="D80" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4893,7 +4895,7 @@
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
@@ -4902,14 +4904,14 @@
         <v>46311</v>
       </c>
       <c r="B81" s="41" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C81" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D81" s="42" t="inlineStr">
+      <c r="D81" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4921,35 +4923,35 @@
       </c>
       <c r="F81" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="31" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B82" s="33" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="C82" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D82" s="43" t="inlineStr">
+      <c r="D82" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E82" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4967,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D83" s="42" t="inlineStr">
+      <c r="D83" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4983,55 +4985,55 @@
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="31" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B84" s="33" t="n">
-        <v>220</v>
-      </c>
-      <c r="C84" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D84" s="43" t="inlineStr">
+        <v>46317</v>
+      </c>
+      <c r="B84" s="33" t="inlineStr"/>
+      <c r="C84" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D84" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>SZA x Vans VANSZA Collection</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="36" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B85" s="41" t="inlineStr"/>
-      <c r="C85" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D85" s="42" t="inlineStr">
+        <v>46319</v>
+      </c>
+      <c r="B85" s="41" t="n">
+        <v>125</v>
+      </c>
+      <c r="C85" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D85" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E85" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>SZA x Vans VANSZA Collection</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
@@ -5040,26 +5042,26 @@
         <v>46319</v>
       </c>
       <c r="B86" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C86" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D86" s="43" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C86" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D86" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E86" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
@@ -5068,14 +5070,14 @@
         <v>46319</v>
       </c>
       <c r="B87" s="41" t="n">
-        <v>190</v>
-      </c>
-      <c r="C87" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D87" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C87" s="52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D87" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5087,7 +5089,7 @@
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
@@ -5096,26 +5098,26 @@
         <v>46319</v>
       </c>
       <c r="B88" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C88" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D88" s="43" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C88" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D88" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E88" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
@@ -5124,26 +5126,26 @@
         <v>46319</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C89" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D89" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D89" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E89" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
@@ -5152,16 +5154,16 @@
         <v>46319</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="C90" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D90" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D90" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E90" s="30" t="inlineStr">
@@ -5171,7 +5173,7 @@
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
@@ -5180,26 +5182,26 @@
         <v>46319</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C91" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D91" s="42" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C91" s="52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D91" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E91" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
@@ -5208,16 +5210,16 @@
         <v>46319</v>
       </c>
       <c r="B92" s="33" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C92" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D92" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D92" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E92" s="30" t="inlineStr">
@@ -5227,63 +5229,63 @@
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="36" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C93" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D93" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>205</v>
+      </c>
+      <c r="C93" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D93" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E93" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="31" t="n">
-        <v>46320</v>
+        <v>46325</v>
       </c>
       <c r="B94" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C94" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D94" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C94" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D94" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E94" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Nike Ja 4 High “University Red”</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5296,12 @@
       <c r="B95" s="41" t="n">
         <v>155</v>
       </c>
-      <c r="C95" s="53" t="inlineStr">
+      <c r="C95" s="52" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D95" s="42" t="inlineStr">
+      <c r="D95" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5320,16 +5322,16 @@
         <v>46325</v>
       </c>
       <c r="B96" s="33" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="C96" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D96" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D96" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E96" s="30" t="inlineStr">
@@ -5339,79 +5341,79 @@
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 High “University Red”</t>
+          <t>Nike Book 2 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="36" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="B97" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C97" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D97" s="42" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C97" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D97" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E97" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F97" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Halloween”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="31" t="n">
-        <v>46326</v>
+        <v>46329</v>
       </c>
       <c r="B98" s="33" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C98" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D98" s="43" t="inlineStr">
+      <c r="D98" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E98" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="36" t="n">
-        <v>46329</v>
+        <v>46331</v>
       </c>
       <c r="B99" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C99" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D99" s="42" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C99" s="52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D99" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5423,7 +5425,7 @@
       </c>
       <c r="F99" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5441,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D100" s="43" t="inlineStr">
+      <c r="D100" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5451,23 +5453,23 @@
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="36" t="n">
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="B101" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C101" s="53" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C101" s="52" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D101" s="42" t="inlineStr">
+      <c r="D101" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5479,35 +5481,35 @@
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
+          <t>Nike Book 2 “Desert Night”</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="31" t="n">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="B102" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C102" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D102" s="43" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C102" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D102" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E102" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Desert Night”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
@@ -5569,57 +5571,57 @@
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="36" t="n">
-        <v>46333</v>
+        <v>46335</v>
       </c>
       <c r="B105" s="41" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C105" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D105" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D105" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E105" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="31" t="n">
-        <v>46335</v>
+        <v>46337</v>
       </c>
       <c r="B106" s="33" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C106" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D106" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D106" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E106" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F106" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5637,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D107" s="42" t="inlineStr">
+      <c r="D107" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5653,29 +5655,29 @@
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="31" t="n">
-        <v>46337</v>
+        <v>46338</v>
       </c>
       <c r="B108" s="33" t="n">
-        <v>235</v>
-      </c>
-      <c r="C108" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D108" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>170</v>
+      </c>
+      <c r="C108" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D108" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E108" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F108" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Nike Air Bakin “Varsity Royal” 2026</t>
         </is>
       </c>
     </row>
@@ -5684,26 +5686,26 @@
         <v>46338</v>
       </c>
       <c r="B109" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C109" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D109" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C109" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D109" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E109" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal” 2026</t>
+          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
         </is>
       </c>
     </row>
@@ -5712,54 +5714,54 @@
         <v>46338</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C110" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D110" s="43" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C110" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D110" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E110" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
+          <t>Nike Air Bakin “Varsity Royal”</t>
         </is>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="36" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="B111" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C111" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D111" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C111" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D111" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E111" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
@@ -5768,11 +5770,11 @@
         <v>46340</v>
       </c>
       <c r="B112" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C112" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>240</v>
+      </c>
+      <c r="C112" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D112" s="34" t="inlineStr">
@@ -5787,18 +5789,18 @@
       </c>
       <c r="F112" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="36" t="n">
-        <v>46340</v>
+        <v>46341</v>
       </c>
       <c r="B113" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C113" s="53" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="C113" s="52" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5810,25 +5812,25 @@
       </c>
       <c r="E113" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F113" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
+          <t>Playa Society x Nike A’Two</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="31" t="n">
-        <v>46341</v>
+        <v>46342</v>
       </c>
       <c r="B114" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C114" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>255</v>
+      </c>
+      <c r="C114" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D114" s="34" t="inlineStr">
@@ -5838,96 +5840,96 @@
       </c>
       <c r="E114" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F114" s="30" t="inlineStr">
         <is>
-          <t>Playa Society x Nike A’Two</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="36" t="n">
-        <v>46342</v>
+        <v>46343</v>
       </c>
       <c r="B115" s="41" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C115" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D115" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D115" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E115" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F115" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="31" t="n">
-        <v>46343</v>
+        <v>46345</v>
       </c>
       <c r="B116" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C116" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D116" s="43" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C116" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D116" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E116" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Vans Old Skool 36 Pearlized “Navy”</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="36" t="n">
-        <v>46345</v>
+        <v>46346</v>
       </c>
       <c r="B117" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C117" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D117" s="42" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C117" s="52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D117" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E117" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F117" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Navy”</t>
+          <t>Nike Book 2 “Be Legendary”</t>
         </is>
       </c>
     </row>
@@ -5936,54 +5938,54 @@
         <v>46346</v>
       </c>
       <c r="B118" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C118" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D118" s="43" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C118" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D118" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F118" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Be Legendary”</t>
+          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="36" t="n">
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="B119" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C119" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D119" s="42" t="inlineStr">
+        <v>165</v>
+      </c>
+      <c r="C119" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D119" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E119" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -5992,14 +5994,14 @@
         <v>46347</v>
       </c>
       <c r="B120" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C120" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D120" s="43" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C120" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D120" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6011,7 +6013,7 @@
       </c>
       <c r="F120" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Snow White”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -6020,16 +6022,16 @@
         <v>46347</v>
       </c>
       <c r="B121" s="41" t="n">
-        <v>230</v>
-      </c>
-      <c r="C121" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D121" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C121" s="52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D121" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E121" s="35" t="inlineStr">
@@ -6039,7 +6041,7 @@
       </c>
       <c r="F121" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
@@ -6048,26 +6050,26 @@
         <v>46347</v>
       </c>
       <c r="B122" s="33" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C122" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D122" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D122" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F122" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -6076,26 +6078,26 @@
         <v>46347</v>
       </c>
       <c r="B123" s="41" t="n">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="C123" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D123" s="42" t="inlineStr">
+      <c r="D123" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E123" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F123" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
@@ -6103,25 +6105,27 @@
       <c r="A124" s="31" t="n">
         <v>46347</v>
       </c>
-      <c r="B124" s="33" t="inlineStr"/>
-      <c r="C124" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D124" s="43" t="inlineStr">
+      <c r="B124" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="C124" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D124" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E124" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F124" s="30" t="inlineStr">
         <is>
-          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
@@ -6129,55 +6133,53 @@
       <c r="A125" s="36" t="n">
         <v>46347</v>
       </c>
-      <c r="B125" s="41" t="n">
-        <v>165</v>
-      </c>
-      <c r="C125" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D125" s="42" t="inlineStr">
+      <c r="B125" s="41" t="inlineStr"/>
+      <c r="C125" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D125" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E125" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F125" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="31" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B126" s="33" t="n">
-        <v>125</v>
+        <v>230</v>
       </c>
       <c r="C126" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D126" s="43" t="inlineStr">
+      <c r="D126" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E126" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
@@ -6186,26 +6188,26 @@
         <v>46353</v>
       </c>
       <c r="B127" s="41" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C127" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D127" s="42" t="inlineStr">
+      <c r="D127" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E127" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
@@ -6214,54 +6216,54 @@
         <v>46353</v>
       </c>
       <c r="B128" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C128" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D128" s="43" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C128" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D128" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E128" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F128" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Vans Old Skool 36 Pearlized “Black”</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="36" t="n">
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="B129" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C129" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D129" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C129" s="52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D129" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E129" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F129" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Black”</t>
+          <t>Nike Caitlin 1 “Warning Code”</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6277,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D130" s="43" t="inlineStr">
+      <c r="D130" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6352,12 +6354,12 @@
         <v>46354</v>
       </c>
       <c r="B133" s="41" t="inlineStr"/>
-      <c r="C133" s="53" t="inlineStr">
+      <c r="C133" s="52" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D133" s="42" t="inlineStr">
+      <c r="D133" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6411,7 +6413,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D135" s="42" t="inlineStr">
+      <c r="D135" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6429,17 +6431,17 @@
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="31" t="n">
-        <v>46354</v>
+        <v>46359</v>
       </c>
       <c r="B136" s="33" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="C136" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D136" s="43" t="inlineStr">
+      <c r="D136" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6451,35 +6453,33 @@
       </c>
       <c r="F136" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Warning Code”</t>
+          <t>Nike Air Bakin “Black/White”</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="36" t="n">
-        <v>46359</v>
-      </c>
-      <c r="B137" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C137" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D137" s="42" t="inlineStr">
+        <v>46361</v>
+      </c>
+      <c r="B137" s="41" t="inlineStr"/>
+      <c r="C137" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D137" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E137" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F137" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Black/White”</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
@@ -6487,13 +6487,15 @@
       <c r="A138" s="31" t="n">
         <v>46361</v>
       </c>
-      <c r="B138" s="33" t="inlineStr"/>
+      <c r="B138" s="33" t="n">
+        <v>215</v>
+      </c>
       <c r="C138" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D138" s="43" t="inlineStr">
+      <c r="D138" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6505,7 +6507,7 @@
       </c>
       <c r="F138" s="30" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
@@ -6514,26 +6516,26 @@
         <v>46361</v>
       </c>
       <c r="B139" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C139" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D139" s="42" t="inlineStr">
+        <v>300</v>
+      </c>
+      <c r="C139" s="52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D139" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E139" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F139" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Pharrell x adidas Adistar Jellyfish</t>
         </is>
       </c>
     </row>
@@ -6541,25 +6543,27 @@
       <c r="A140" s="31" t="n">
         <v>46367</v>
       </c>
-      <c r="B140" s="33" t="inlineStr"/>
+      <c r="B140" s="33" t="n">
+        <v>240</v>
+      </c>
       <c r="C140" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D140" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D140" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E140" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F140" s="30" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
         </is>
       </c>
     </row>
@@ -6567,9 +6571,7 @@
       <c r="A141" s="36" t="n">
         <v>46367</v>
       </c>
-      <c r="B141" s="41" t="n">
-        <v>150</v>
-      </c>
+      <c r="B141" s="41" t="inlineStr"/>
       <c r="C141" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6587,7 +6589,7 @@
       </c>
       <c r="F141" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
@@ -6596,26 +6598,26 @@
         <v>46367</v>
       </c>
       <c r="B142" s="33" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="C142" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D142" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D142" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E142" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F142" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Floral” 2026</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6633,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D143" s="42" t="inlineStr">
+      <c r="D143" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6659,7 +6661,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D144" s="43" t="inlineStr">
+      <c r="D144" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6691,7 +6693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6717,7 +6719,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="51" t="inlineStr">
         <is>
-          <t>Generated September 16, 2026  ·  11:01 UTC</t>
+          <t>Generated September 17, 2026  ·  11:12 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -6760,19 +6762,19 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C4" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D4" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
@@ -6782,35 +6784,35 @@
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 Low “Metamorphosis”</t>
+          <t>Air Jordan 4 “London”</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D5" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
     </row>
@@ -6819,26 +6821,26 @@
         <v>46283</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
     </row>
@@ -6847,16 +6849,16 @@
         <v>46283</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D7" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
@@ -6866,7 +6868,7 @@
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -6875,26 +6877,26 @@
         <v>46283</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
         </is>
       </c>
     </row>
@@ -6903,26 +6905,26 @@
         <v>46283</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="D9" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>APB x Air Jordan 11 Low</t>
         </is>
       </c>
     </row>
@@ -6931,26 +6933,26 @@
         <v>46283</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D10" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Nike Air Foamposite One "Green Camo"</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6968,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D11" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6994,7 +6996,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
+      <c r="D12" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7022,7 +7024,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D13" s="42" t="inlineStr">
+      <c r="D13" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7068,29 +7070,29 @@
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="36" t="n">
-        <v>46290</v>
+        <v>46284</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="C15" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D15" s="42" t="inlineStr">
+      <c r="D15" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
         </is>
       </c>
     </row>
@@ -7099,11 +7101,11 @@
         <v>46290</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C16" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>225</v>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
         </is>
       </c>
       <c r="D16" s="34" t="inlineStr">
@@ -7118,7 +7120,7 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
@@ -7127,16 +7129,16 @@
         <v>46290</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>225</v>
-      </c>
-      <c r="C17" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D17" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>205</v>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
@@ -7146,25 +7148,25 @@
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="31" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C18" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D18" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
@@ -7174,7 +7176,7 @@
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
@@ -7183,26 +7185,26 @@
         <v>46291</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="C19" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D19" s="42" t="inlineStr">
+      <c r="D19" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -7211,16 +7213,16 @@
         <v>46291</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
@@ -7230,7 +7232,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -7238,15 +7240,13 @@
       <c r="A21" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B21" s="41" t="n">
-        <v>210</v>
-      </c>
+      <c r="B21" s="41" t="inlineStr"/>
       <c r="C21" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D21" s="42" t="inlineStr">
+      <c r="D21" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -7267,16 +7267,16 @@
         <v>46291</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D22" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -7295,26 +7295,26 @@
         <v>46291</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="42" t="inlineStr">
+      <c r="D23" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -7322,25 +7322,27 @@
       <c r="A24" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B24" s="33" t="inlineStr"/>
+      <c r="B24" s="33" t="n">
+        <v>155</v>
+      </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D24" s="43" t="inlineStr">
+      <c r="D24" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E24" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7351,7 @@
         <v>46291</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
@@ -7368,7 +7370,7 @@
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7386,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D26" s="43" t="inlineStr">
+      <c r="D26" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7396,23 +7398,23 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="36" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D27" s="42" t="inlineStr">
+      <c r="D27" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7424,7 +7426,7 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
@@ -7432,15 +7434,17 @@
       <c r="A28" s="31" t="n">
         <v>46295</v>
       </c>
-      <c r="B28" s="33" t="inlineStr"/>
+      <c r="B28" s="33" t="n">
+        <v>135</v>
+      </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D28" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
@@ -7450,7 +7454,7 @@
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -7459,26 +7463,26 @@
         <v>46295</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D29" s="42" t="inlineStr">
+      <c r="D29" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
@@ -7487,16 +7491,16 @@
         <v>46295</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C30" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D30" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
@@ -7506,7 +7510,7 @@
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
@@ -7514,64 +7518,62 @@
       <c r="A31" s="36" t="n">
         <v>46295</v>
       </c>
-      <c r="B31" s="41" t="n">
-        <v>210</v>
-      </c>
+      <c r="B31" s="41" t="inlineStr"/>
       <c r="C31" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D31" s="42" t="inlineStr">
+      <c r="D31" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D32" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D32" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="36" t="n">
-        <v>46298</v>
+        <v>46296</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="C33" s="40" t="inlineStr">
         <is>
@@ -7590,25 +7592,25 @@
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 1 Low OG “Howard” 2026</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="31" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C34" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D34" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
@@ -7618,53 +7620,53 @@
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D35" s="42" t="inlineStr">
+      <c r="D35" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="31" t="n">
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="B36" s="33" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="C36" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D36" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
@@ -7674,25 +7676,25 @@
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46310</v>
+        <v>46300</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="C37" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D37" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D37" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
@@ -7702,53 +7704,53 @@
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="31" t="n">
-        <v>46311</v>
+        <v>46305</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="C38" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D38" s="43" t="inlineStr">
+      <c r="D38" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E38" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B39" s="41" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="C39" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D39" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D39" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
@@ -7758,7 +7760,7 @@
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7776,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D40" s="43" t="inlineStr">
+      <c r="D40" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7786,7 +7788,7 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7804,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D41" s="42" t="inlineStr">
+      <c r="D41" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7814,119 +7816,119 @@
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="31" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C42" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D42" s="43" t="inlineStr">
+      <c r="D42" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E42" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="36" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B43" s="41" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C43" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D43" s="42" t="inlineStr">
+      <c r="D43" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="31" t="n">
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D44" s="43" t="inlineStr">
+      <c r="D44" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E44" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D45" s="42" t="inlineStr">
+      <c r="D45" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
@@ -7942,19 +7944,19 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D46" s="43" t="inlineStr">
+      <c r="D46" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
@@ -7963,128 +7965,128 @@
         <v>46319</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D47" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D47" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="31" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>205</v>
+        <v>150</v>
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D48" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="36" t="n">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D49" s="42" t="inlineStr">
+      <c r="D49" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="31" t="n">
-        <v>46329</v>
+        <v>46320</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C50" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D50" s="43" t="inlineStr">
+      <c r="D50" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D51" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D51" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
@@ -8094,13 +8096,13 @@
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="31" t="n">
-        <v>46333</v>
+        <v>46329</v>
       </c>
       <c r="B52" s="33" t="n">
         <v>240</v>
@@ -8110,19 +8112,19 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D52" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D52" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8140,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="42" t="inlineStr">
+      <c r="D53" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8156,10 +8158,10 @@
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="31" t="n">
-        <v>46335</v>
+        <v>46333</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
@@ -8173,86 +8175,86 @@
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D55" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D55" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46337</v>
+        <v>46335</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C56" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D56" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D56" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46340</v>
+        <v>46337</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="C57" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D57" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D57" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
@@ -8262,72 +8264,72 @@
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="31" t="n">
-        <v>46342</v>
+        <v>46337</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C58" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D58" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D58" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46343</v>
+        <v>46340</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D59" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D59" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46347</v>
+        <v>46342</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
@@ -8341,40 +8343,40 @@
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46347</v>
+        <v>46343</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D61" s="42" t="inlineStr">
+      <c r="D61" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
@@ -8383,26 +8385,26 @@
         <v>46347</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C62" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D62" s="43" t="inlineStr">
+      <c r="D62" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -8411,26 +8413,26 @@
         <v>46347</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D63" s="42" t="inlineStr">
+      <c r="D63" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -8439,16 +8441,16 @@
         <v>46347</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>125</v>
+        <v>230</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D64" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
@@ -8458,23 +8460,23 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="36" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D65" s="42" t="inlineStr">
+      <c r="D65" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8486,23 +8488,23 @@
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D66" s="43" t="inlineStr">
+      <c r="D66" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8514,51 +8516,53 @@
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B67" s="41" t="inlineStr"/>
+        <v>46353</v>
+      </c>
+      <c r="B67" s="41" t="n">
+        <v>230</v>
+      </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D67" s="42" t="inlineStr">
+      <c r="D67" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D68" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D68" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
@@ -8568,7 +8572,7 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
@@ -8576,17 +8580,15 @@
       <c r="A69" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B69" s="41" t="n">
-        <v>130</v>
-      </c>
+      <c r="B69" s="41" t="inlineStr"/>
       <c r="C69" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D69" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D69" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
@@ -8596,7 +8598,7 @@
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
@@ -8604,10 +8606,12 @@
       <c r="A70" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B70" s="33" t="inlineStr"/>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
+      <c r="B70" s="33" t="n">
+        <v>120</v>
+      </c>
+      <c r="C70" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D70" s="34" t="inlineStr">
@@ -8617,12 +8621,12 @@
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -8631,16 +8635,16 @@
         <v>46354</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D71" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D71" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
@@ -8650,23 +8654,23 @@
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46361</v>
+        <v>46354</v>
       </c>
       <c r="B72" s="33" t="inlineStr"/>
-      <c r="C72" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D72" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D72" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E72" s="30" t="inlineStr">
@@ -8676,41 +8680,41 @@
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46361</v>
+        <v>46354</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D73" s="42" t="inlineStr">
+      <c r="D73" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46367</v>
+        <v>46361</v>
       </c>
       <c r="B74" s="33" t="inlineStr"/>
       <c r="C74" s="39" t="inlineStr">
@@ -8718,9 +8722,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D74" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D74" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
@@ -8730,25 +8734,25 @@
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46367</v>
+        <v>46361</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C75" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D75" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D75" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
@@ -8758,7 +8762,7 @@
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8778,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D76" s="43" t="inlineStr">
+      <c r="D76" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8794,60 +8798,114 @@
       <c r="A77" s="36" t="n">
         <v>46367</v>
       </c>
-      <c r="B77" s="41" t="n">
-        <v>190</v>
-      </c>
+      <c r="B77" s="41" t="inlineStr"/>
       <c r="C77" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D77" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D77" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="31" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B78" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="C78" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D78" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E78" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F78" s="30" t="inlineStr">
+        <is>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="36" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B79" s="41" t="n">
+        <v>190</v>
+      </c>
+      <c r="C79" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D79" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E79" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F79" s="35" t="inlineStr">
+        <is>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="31" t="n">
         <v>46368</v>
       </c>
-      <c r="B78" s="33" t="n">
+      <c r="B80" s="33" t="n">
         <v>235</v>
       </c>
-      <c r="C78" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D78" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
+      <c r="C80" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D80" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E80" s="30" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="F78" s="30" t="inlineStr">
+      <c r="F80" s="30" t="inlineStr">
         <is>
           <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F78"/>
+  <autoFilter ref="A3:F80"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High Hype Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -670,10 +670,10 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1569,7 +1569,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 17, 2026  ·  11:12 UTC</t>
+          <t>Generated September 18, 2026  ·  10:45 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1609,11 +1609,11 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="14" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="16" t="n">
@@ -1622,7 +1622,7 @@
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>$181</t>
+          <t>$180</t>
         </is>
       </c>
       <c r="H5" s="19" t="n"/>
@@ -1725,7 +1725,7 @@
         <v>46290</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>46295</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D13" s="35" t="n">
         <v>0</v>
@@ -1836,7 +1836,7 @@
         <v>7</v>
       </c>
       <c r="G13" s="41" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="H13" s="38" t="inlineStr">
         <is>
@@ -1847,19 +1847,19 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C14" s="31" t="n">
         <v>46283</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>7</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="H14" s="42" t="inlineStr">
         <is>
@@ -1881,19 +1881,19 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>APB x Air Jordan 11 Low</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
         <v>46283</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>7</v>
       </c>
       <c r="G15" s="41" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H15" s="43" t="inlineStr">
         <is>
@@ -1915,19 +1915,19 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="C16" s="31" t="n">
         <v>46283</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
@@ -1938,11 +1938,11 @@
         <v>7</v>
       </c>
       <c r="G16" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="H16" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>250</v>
+      </c>
+      <c r="H16" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="B20" s="30" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="B21" s="35" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="H21" s="35" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="B22" s="30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="E22" s="30" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
@@ -2161,17 +2161,17 @@
       </c>
       <c r="B30" s="30" t="inlineStr">
         <is>
-          <t>9/17 – 9/23</t>
+          <t>9/18 – 9/24</t>
         </is>
       </c>
       <c r="C30" s="30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D30" s="39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" s="30" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
@@ -2182,17 +2182,17 @@
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>9/24 – 9/30</t>
+          <t>9/25 – 10/1</t>
         </is>
       </c>
       <c r="C31" s="35" t="n">
         <v>38</v>
       </c>
       <c r="D31" s="40" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E31" s="35" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -2203,17 +2203,17 @@
       </c>
       <c r="B32" s="30" t="inlineStr">
         <is>
-          <t>10/1 – 10/7</t>
+          <t>10/2 – 10/8</t>
         </is>
       </c>
       <c r="C32" s="30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32" s="39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" s="30" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
@@ -2224,17 +2224,17 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>10/8 – 10/14</t>
+          <t>10/9 – 10/15</t>
         </is>
       </c>
       <c r="C33" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" s="40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="35" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
@@ -2245,17 +2245,17 @@
       </c>
       <c r="B34" s="30" t="inlineStr">
         <is>
-          <t>10/15 – 10/21</t>
+          <t>10/16 – 10/22</t>
         </is>
       </c>
       <c r="C34" s="30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34" s="39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E34" s="30" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -2266,17 +2266,17 @@
       </c>
       <c r="B35" s="35" t="inlineStr">
         <is>
-          <t>10/22 – 10/28</t>
+          <t>10/23 – 10/29</t>
         </is>
       </c>
       <c r="C35" s="35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35" s="40" t="n">
         <v>5</v>
       </c>
       <c r="E35" s="35" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -2287,17 +2287,17 @@
       </c>
       <c r="B36" s="30" t="inlineStr">
         <is>
-          <t>10/29 – 11/4</t>
+          <t>10/30 – 11/5</t>
         </is>
       </c>
       <c r="C36" s="30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D36" s="39" t="n">
         <v>2</v>
       </c>
       <c r="E36" s="30" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -2308,17 +2308,17 @@
       </c>
       <c r="B37" s="35" t="inlineStr">
         <is>
-          <t>11/5 – 11/11</t>
+          <t>11/6 – 11/12</t>
         </is>
       </c>
       <c r="C37" s="35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="40" t="n">
         <v>6</v>
       </c>
       <c r="E37" s="35" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
@@ -2329,17 +2329,17 @@
       </c>
       <c r="B38" s="30" t="inlineStr">
         <is>
-          <t>11/12 – 11/18</t>
+          <t>11/13 – 11/19</t>
         </is>
       </c>
       <c r="C38" s="30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D38" s="39" t="n">
         <v>3</v>
       </c>
       <c r="E38" s="30" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>11/19 – 11/25</t>
+          <t>11/20 – 11/26</t>
         </is>
       </c>
       <c r="C39" s="35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D39" s="40" t="n">
         <v>5</v>
       </c>
       <c r="E39" s="35" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="B40" s="30" t="inlineStr">
         <is>
-          <t>11/26 – 12/2</t>
+          <t>11/27 – 12/3</t>
         </is>
       </c>
       <c r="C40" s="30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D40" s="39" t="n">
         <v>7</v>
       </c>
       <c r="E40" s="30" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -2392,17 +2392,17 @@
       </c>
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>12/3 – 12/9</t>
+          <t>12/4 – 12/10</t>
         </is>
       </c>
       <c r="C41" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41" s="40" t="n">
         <v>2</v>
       </c>
       <c r="E41" s="35" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="B42" s="30" t="inlineStr">
         <is>
-          <t>12/10 – 12/16</t>
+          <t>12/11 – 12/17</t>
         </is>
       </c>
       <c r="C42" s="30" t="n">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -2684,7 +2684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2710,7 +2710,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="51" t="inlineStr">
         <is>
-          <t>Generated September 17, 2026  ·  11:12 UTC</t>
+          <t>Generated September 18, 2026  ·  10:45 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="C4" s="39" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
         <v>46283</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
@@ -2798,12 +2798,12 @@
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
         </is>
       </c>
     </row>
@@ -2812,16 +2812,16 @@
         <v>46283</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C6" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D6" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>135</v>
+      </c>
+      <c r="C6" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>PSG x Nike KD 6</t>
         </is>
       </c>
     </row>
@@ -2840,16 +2840,16 @@
         <v>46283</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D7" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>APB x Air Jordan 11 Low</t>
         </is>
       </c>
     </row>
@@ -2868,11 +2868,11 @@
         <v>46283</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C8" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>130</v>
+      </c>
+      <c r="C8" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
@@ -2882,12 +2882,12 @@
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>adidas Anthony Edwards 3 “Cold Blooded”</t>
         </is>
       </c>
     </row>
@@ -2896,16 +2896,16 @@
         <v>46283</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>135</v>
-      </c>
-      <c r="C9" s="52" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>PSG x Nike KD 6</t>
+          <t>Nike A’Two “Dawn Staley”</t>
         </is>
       </c>
     </row>
@@ -2924,11 +2924,11 @@
         <v>46283</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C10" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>65</v>
+      </c>
+      <c r="C10" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
         </is>
       </c>
     </row>
@@ -2952,11 +2952,11 @@
         <v>46283</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C11" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>250</v>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D11" s="43" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Cold Blooded”</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
     </row>
@@ -2980,11 +2980,11 @@
         <v>46283</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C12" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>210</v>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D12" s="42" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Nike A’Two “Dawn Staley”</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
     </row>
@@ -3008,11 +3008,11 @@
         <v>46283</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>65</v>
-      </c>
-      <c r="C13" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>240</v>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D13" s="43" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
+          <t>Nike Air Foamposite One "Green Camo"</t>
         </is>
       </c>
     </row>
@@ -3036,11 +3036,11 @@
         <v>46283</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C14" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>110</v>
+      </c>
+      <c r="C14" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D14" s="42" t="inlineStr">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One "Green Camo"</t>
+          <t>Anthony Edwards x adidas Superstar “Cold Blooded”</t>
         </is>
       </c>
     </row>
@@ -3064,11 +3064,11 @@
         <v>46283</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>110</v>
-      </c>
-      <c r="C15" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>250</v>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D15" s="43" t="inlineStr">
@@ -3078,21 +3078,21 @@
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Anthony Edwards x adidas Superstar “Cold Blooded”</t>
+          <t>Nike Air Foamposite Pro “Green Camo”</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C16" s="39" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo”</t>
+          <t>Nike Kobe 8 Protro “Mambacurial”</t>
         </is>
       </c>
     </row>
@@ -3120,26 +3120,26 @@
         <v>46284</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="C17" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D17" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D17" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>APB x Air Jordan 11 Low Pack</t>
         </is>
       </c>
     </row>
@@ -3148,11 +3148,11 @@
         <v>46284</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C18" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>300</v>
+      </c>
+      <c r="C18" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D18" s="42" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
         </is>
       </c>
     </row>
@@ -3176,16 +3176,16 @@
         <v>46284</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C19" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D19" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>215</v>
+      </c>
+      <c r="C19" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>Air Jordan 9 OG “Space Jam” 2026</t>
         </is>
       </c>
     </row>
@@ -3204,11 +3204,11 @@
         <v>46284</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>300</v>
-      </c>
-      <c r="C20" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>110</v>
+      </c>
+      <c r="C20" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D20" s="42" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
+          <t>Pokémon x adidas 30th Anniversary Collection</t>
         </is>
       </c>
     </row>
@@ -3232,11 +3232,11 @@
         <v>46284</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C21" s="52" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>122</v>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D21" s="43" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 9 OG “Space Jam” 2026</t>
+          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
         </is>
       </c>
     </row>
@@ -3260,11 +3260,11 @@
         <v>46284</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>110</v>
-      </c>
-      <c r="C22" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>122</v>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D22" s="42" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Pokémon x adidas 30th Anniversary Collection</t>
+          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         <v>46284</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>122</v>
-      </c>
-      <c r="C23" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>210</v>
+      </c>
+      <c r="C23" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D23" s="43" t="inlineStr">
@@ -3307,13 +3307,13 @@
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
+          <t>One Piece x Nike Air Max Plus “Ope Ope”</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="31" t="n">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="B24" s="33" t="n">
         <v>210</v>
@@ -3335,18 +3335,18 @@
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Ope Ope”</t>
+          <t>Nike GT Future “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="36" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B25" s="41" t="n">
         <v>210</v>
       </c>
-      <c r="C25" s="52" t="inlineStr">
+      <c r="C25" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3363,20 +3363,20 @@
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Nike GT Future “Varsity Red”</t>
+          <t>Nike GT Future “Unseen Hours”</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="31" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C26" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>140</v>
+      </c>
+      <c r="C26" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D26" s="42" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Nike GT Future “Unseen Hours”</t>
+          <t>Converse SHAI 001 “Green Beam”</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Green Beam”</t>
+          <t>Converse SHAI 001 “Ghosted”</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       <c r="B28" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C28" s="53" t="inlineStr">
+      <c r="C28" s="52" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Ghosted”</t>
+          <t>Converse SHAI 001 Shroud “Shock”</t>
         </is>
       </c>
     </row>
@@ -3475,35 +3475,35 @@
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 Shroud “Shock”</t>
+          <t>Converse SHAI 001 “Spark”</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="31" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C30" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D30" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Spark”</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
@@ -3512,16 +3512,16 @@
         <v>46290</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>225</v>
-      </c>
-      <c r="C31" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D31" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>205</v>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
@@ -3540,11 +3540,11 @@
         <v>46290</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C32" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>120</v>
+      </c>
+      <c r="C32" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D32" s="42" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Billionaire Boys Club x Reebok Club C 85</t>
         </is>
       </c>
     </row>
@@ -3568,11 +3568,11 @@
         <v>46290</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>120</v>
-      </c>
-      <c r="C33" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>140</v>
+      </c>
+      <c r="C33" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D33" s="43" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Billionaire Boys Club x Reebok Club C 85</t>
+          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
         </is>
       </c>
     </row>
@@ -3596,26 +3596,26 @@
         <v>46290</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C34" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D34" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C34" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
@@ -3624,26 +3624,26 @@
         <v>46290</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C35" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D35" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C35" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Nike Ja 4 “Jaws”</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
         <v>46290</v>
       </c>
       <c r="B36" s="33" t="n">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="C36" s="48" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws”</t>
+          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
         </is>
       </c>
     </row>
@@ -3680,9 +3680,9 @@
         <v>46290</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>185</v>
-      </c>
-      <c r="C37" s="52" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C37" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3699,25 +3699,25 @@
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
+          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B38" s="33" t="n">
         <v>210</v>
       </c>
-      <c r="C38" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D38" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="C38" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D38" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E38" s="30" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -3738,14 +3738,14 @@
       <c r="B39" s="41" t="n">
         <v>200</v>
       </c>
-      <c r="C39" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D39" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="C39" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D39" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
         </is>
       </c>
     </row>
@@ -3764,26 +3764,26 @@
         <v>46291</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C40" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D40" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>200</v>
+      </c>
+      <c r="C40" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D40" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
         <v>46291</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -3820,11 +3820,11 @@
         <v>46291</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C42" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>150</v>
+      </c>
+      <c r="C42" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D42" s="34" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -3848,9 +3848,9 @@
         <v>46291</v>
       </c>
       <c r="B43" s="41" t="inlineStr"/>
-      <c r="C43" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="C43" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D43" s="43" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
@@ -3874,11 +3874,11 @@
         <v>46291</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C44" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>155</v>
+      </c>
+      <c r="C44" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D44" s="34" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
@@ -3902,16 +3902,16 @@
         <v>46291</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C45" s="52" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D45" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C45" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D45" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -3930,11 +3930,11 @@
         <v>46291</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C46" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>160</v>
+      </c>
+      <c r="C46" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D46" s="42" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
         <v>46291</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -3986,11 +3986,11 @@
         <v>46291</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C48" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>125</v>
+      </c>
+      <c r="C48" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -4013,10 +4013,12 @@
       <c r="A49" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B49" s="41" t="inlineStr"/>
-      <c r="C49" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B49" s="41" t="n">
+        <v>140</v>
+      </c>
+      <c r="C49" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D49" s="43" t="inlineStr">
@@ -4026,12 +4028,12 @@
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4042,7 @@
         <v>46291</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C50" s="48" t="inlineStr">
         <is>
@@ -4059,7 +4061,7 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
@@ -4067,9 +4069,7 @@
       <c r="A51" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B51" s="41" t="n">
-        <v>210</v>
-      </c>
+      <c r="B51" s="41" t="inlineStr"/>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
         <v>46291</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="C52" s="48" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
+          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
         </is>
       </c>
     </row>
@@ -4124,9 +4124,9 @@
         <v>46291</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>120</v>
-      </c>
-      <c r="C53" s="52" t="inlineStr">
+        <v>160</v>
+      </c>
+      <c r="C53" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
         <v>46293</v>
       </c>
       <c r="B55" s="41" t="inlineStr"/>
-      <c r="C55" s="52" t="inlineStr">
+      <c r="C55" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4236,7 +4236,7 @@
       <c r="B57" s="41" t="n">
         <v>249</v>
       </c>
-      <c r="C57" s="52" t="inlineStr">
+      <c r="C57" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4290,26 +4290,26 @@
         <v>46295</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D59" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D59" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
         <v>46295</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
@@ -4332,12 +4332,12 @@
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
@@ -4345,9 +4345,7 @@
       <c r="A61" s="36" t="n">
         <v>46295</v>
       </c>
-      <c r="B61" s="41" t="n">
-        <v>125</v>
-      </c>
+      <c r="B61" s="41" t="inlineStr"/>
       <c r="C61" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -4365,7 +4363,7 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
@@ -4373,15 +4371,17 @@
       <c r="A62" s="31" t="n">
         <v>46295</v>
       </c>
-      <c r="B62" s="33" t="inlineStr"/>
-      <c r="C62" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D62" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B62" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="C62" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D62" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>MoMA x Nike Air Rift 2 Pack</t>
         </is>
       </c>
     </row>
@@ -4400,16 +4400,16 @@
         <v>46295</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C63" s="52" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D63" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>155</v>
+      </c>
+      <c r="C63" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D63" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>MoMA x Nike Air Rift 2 Pack</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
@@ -4428,16 +4428,16 @@
         <v>46295</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D64" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -4509,47 +4509,47 @@
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>220</v>
+        <v>125</v>
       </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D67" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D67" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Nike Kobe Air Force 1 Low</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D68" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D68" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
@@ -4568,16 +4568,16 @@
         <v>46298</v>
       </c>
       <c r="B69" s="41" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D69" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D69" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
@@ -4587,48 +4587,48 @@
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="B70" s="33" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C70" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D70" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D70" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46303</v>
+        <v>46300</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C71" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>200</v>
+      </c>
+      <c r="C71" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D71" s="43" t="inlineStr">
@@ -4638,25 +4638,25 @@
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C72" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C72" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D72" s="42" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
+          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
         </is>
       </c>
     </row>
@@ -4705,10 +4705,10 @@
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="C74" s="48" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Texas”</t>
+          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
         </is>
       </c>
     </row>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="31" t="n">
-        <v>46310</v>
+        <v>46305</v>
       </c>
       <c r="B76" s="33" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C76" s="48" t="inlineStr">
         <is>
@@ -4778,12 +4778,12 @@
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>Nike KD 6 “Texas”</t>
         </is>
       </c>
     </row>
@@ -4794,42 +4794,42 @@
       <c r="B77" s="41" t="n">
         <v>125</v>
       </c>
-      <c r="C77" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D77" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C77" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D77" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="31" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>240</v>
+        <v>125</v>
       </c>
       <c r="C78" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D78" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D78" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E78" s="30" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4848,7 @@
         <v>46311</v>
       </c>
       <c r="B79" s="41" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C79" s="40" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
         <v>46311</v>
       </c>
       <c r="B80" s="33" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C80" s="39" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
         <v>46311</v>
       </c>
       <c r="B81" s="41" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C81" s="40" t="inlineStr">
         <is>
@@ -4923,16 +4923,16 @@
       </c>
       <c r="F81" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="31" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B82" s="33" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C82" s="39" t="inlineStr">
         <is>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E82" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -4985,12 +4985,14 @@
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="31" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B84" s="33" t="inlineStr"/>
-      <c r="C84" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>46312</v>
+      </c>
+      <c r="B84" s="33" t="n">
+        <v>220</v>
+      </c>
+      <c r="C84" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D84" s="42" t="inlineStr">
@@ -5000,25 +5002,23 @@
       </c>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>SZA x Vans VANSZA Collection</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="36" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B85" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C85" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46317</v>
+      </c>
+      <c r="B85" s="41" t="inlineStr"/>
+      <c r="C85" s="49" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D85" s="43" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="E85" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>SZA x Vans VANSZA Collection</t>
         </is>
       </c>
     </row>
@@ -5042,26 +5042,26 @@
         <v>46319</v>
       </c>
       <c r="B86" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C86" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D86" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>170</v>
+      </c>
+      <c r="C86" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D86" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E86" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
@@ -5070,9 +5070,9 @@
         <v>46319</v>
       </c>
       <c r="B87" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C87" s="52" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C87" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
@@ -5098,11 +5098,11 @@
         <v>46319</v>
       </c>
       <c r="B88" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C88" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>190</v>
+      </c>
+      <c r="C88" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D88" s="42" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="E88" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
@@ -5126,16 +5126,16 @@
         <v>46319</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C89" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D89" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D89" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E89" s="35" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
@@ -5154,26 +5154,26 @@
         <v>46319</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C90" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D90" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>125</v>
+      </c>
+      <c r="C90" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D90" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E90" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
@@ -5182,9 +5182,9 @@
         <v>46319</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C91" s="52" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C91" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
@@ -5210,11 +5210,11 @@
         <v>46319</v>
       </c>
       <c r="B92" s="33" t="n">
-        <v>190</v>
-      </c>
-      <c r="C92" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>130</v>
+      </c>
+      <c r="C92" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D92" s="42" t="inlineStr">
@@ -5224,68 +5224,68 @@
       </c>
       <c r="E92" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="36" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>205</v>
+        <v>150</v>
       </c>
       <c r="C93" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D93" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D93" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E93" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="31" t="n">
-        <v>46325</v>
+        <v>46320</v>
       </c>
       <c r="B94" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C94" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D94" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>205</v>
+      </c>
+      <c r="C94" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D94" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E94" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 High “University Red”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       <c r="B95" s="41" t="n">
         <v>155</v>
       </c>
-      <c r="C95" s="52" t="inlineStr">
+      <c r="C95" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5322,16 +5322,16 @@
         <v>46325</v>
       </c>
       <c r="B96" s="33" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C96" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D96" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D96" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E96" s="30" t="inlineStr">
@@ -5341,20 +5341,20 @@
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Halloween”</t>
+          <t>Nike Ja 4 High “University Red”</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="36" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="B97" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C97" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>155</v>
+      </c>
+      <c r="C97" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D97" s="43" t="inlineStr">
@@ -5364,21 +5364,21 @@
       </c>
       <c r="E97" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F97" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Nike Book 2 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="31" t="n">
-        <v>46329</v>
+        <v>46326</v>
       </c>
       <c r="B98" s="33" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C98" s="39" t="inlineStr">
         <is>
@@ -5392,25 +5392,25 @@
       </c>
       <c r="E98" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="36" t="n">
-        <v>46331</v>
+        <v>46329</v>
       </c>
       <c r="B99" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C99" s="52" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>240</v>
+      </c>
+      <c r="C99" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D99" s="43" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="F99" s="35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
@@ -5453,18 +5453,18 @@
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="36" t="n">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="B101" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C101" s="52" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C101" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5481,20 +5481,20 @@
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Desert Night”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="31" t="n">
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="B102" s="33" t="n">
-        <v>215</v>
-      </c>
-      <c r="C102" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>145</v>
+      </c>
+      <c r="C102" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D102" s="42" t="inlineStr">
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E102" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Book 2 “Desert Night”</t>
         </is>
       </c>
     </row>
@@ -5571,57 +5571,57 @@
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="36" t="n">
-        <v>46335</v>
+        <v>46333</v>
       </c>
       <c r="B105" s="41" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C105" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D105" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D105" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E105" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="31" t="n">
-        <v>46337</v>
+        <v>46335</v>
       </c>
       <c r="B106" s="33" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C106" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D106" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D106" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E106" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F106" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
         <v>46337</v>
       </c>
       <c r="B107" s="41" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="C107" s="40" t="inlineStr">
         <is>
@@ -5644,30 +5644,30 @@
       </c>
       <c r="E107" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F107" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="31" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B108" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C108" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D108" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>200</v>
+      </c>
+      <c r="C108" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D108" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E108" s="30" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="F108" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal” 2026</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
@@ -5686,26 +5686,26 @@
         <v>46338</v>
       </c>
       <c r="B109" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C109" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D109" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>170</v>
+      </c>
+      <c r="C109" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D109" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E109" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
+          <t>Nike Air Bakin “Varsity Royal” 2026</t>
         </is>
       </c>
     </row>
@@ -5714,11 +5714,11 @@
         <v>46338</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C110" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C110" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D110" s="42" t="inlineStr">
@@ -5728,81 +5728,81 @@
       </c>
       <c r="E110" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal”</t>
+          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
         </is>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="36" t="n">
-        <v>46340</v>
+        <v>46338</v>
       </c>
       <c r="B111" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C111" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D111" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C111" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D111" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E111" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Air Bakin “Varsity Royal”</t>
         </is>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="31" t="n">
-        <v>46340</v>
+        <v>46339</v>
       </c>
       <c r="B112" s="33" t="n">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C112" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D112" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D112" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E112" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F112" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
+          <t>Nike Air Diamond Turf 2</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="36" t="n">
-        <v>46341</v>
+        <v>46340</v>
       </c>
       <c r="B113" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C113" s="52" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>255</v>
+      </c>
+      <c r="C113" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D113" s="38" t="inlineStr">
@@ -5812,25 +5812,25 @@
       </c>
       <c r="E113" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F113" s="35" t="inlineStr">
         <is>
-          <t>Playa Society x Nike A’Two</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="31" t="n">
-        <v>46342</v>
+        <v>46340</v>
       </c>
       <c r="B114" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C114" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>240</v>
+      </c>
+      <c r="C114" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D114" s="34" t="inlineStr">
@@ -5845,25 +5845,25 @@
       </c>
       <c r="F114" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="36" t="n">
-        <v>46343</v>
+        <v>46341</v>
       </c>
       <c r="B115" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C115" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D115" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>155</v>
+      </c>
+      <c r="C115" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D115" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E115" s="35" t="inlineStr">
@@ -5873,48 +5873,48 @@
       </c>
       <c r="F115" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Playa Society x Nike A’Two</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="31" t="n">
-        <v>46345</v>
+        <v>46342</v>
       </c>
       <c r="B116" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C116" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D116" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C116" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D116" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E116" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Navy”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="36" t="n">
-        <v>46346</v>
+        <v>46343</v>
       </c>
       <c r="B117" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C117" s="52" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>200</v>
+      </c>
+      <c r="C117" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D117" s="43" t="inlineStr">
@@ -5929,18 +5929,18 @@
       </c>
       <c r="F117" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Be Legendary”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="31" t="n">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="B118" s="33" t="n">
         <v>130</v>
       </c>
-      <c r="C118" s="53" t="inlineStr">
+      <c r="C118" s="52" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5952,25 +5952,25 @@
       </c>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F118" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
+          <t>Vans Old Skool 36 Pearlized “Navy”</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="36" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B119" s="41" t="n">
-        <v>165</v>
-      </c>
-      <c r="C119" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>145</v>
+      </c>
+      <c r="C119" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D119" s="43" t="inlineStr">
@@ -5980,25 +5980,25 @@
       </c>
       <c r="E119" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Nike Book 2 “Be Legendary”</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="31" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B120" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C120" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>130</v>
+      </c>
+      <c r="C120" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D120" s="42" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="E120" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F120" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
         </is>
       </c>
     </row>
@@ -6022,11 +6022,11 @@
         <v>46347</v>
       </c>
       <c r="B121" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C121" s="52" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>125</v>
+      </c>
+      <c r="C121" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D121" s="43" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F121" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Snow White”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -6050,16 +6050,16 @@
         <v>46347</v>
       </c>
       <c r="B122" s="33" t="n">
-        <v>230</v>
-      </c>
-      <c r="C122" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D122" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C122" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D122" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E122" s="30" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="F122" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
@@ -6078,26 +6078,26 @@
         <v>46347</v>
       </c>
       <c r="B123" s="41" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C123" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D123" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D123" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E123" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F123" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
         <v>46347</v>
       </c>
       <c r="B124" s="33" t="n">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="C124" s="39" t="inlineStr">
         <is>
@@ -6120,12 +6120,12 @@
       </c>
       <c r="E124" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F124" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
@@ -6133,10 +6133,12 @@
       <c r="A125" s="36" t="n">
         <v>46347</v>
       </c>
-      <c r="B125" s="41" t="inlineStr"/>
-      <c r="C125" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B125" s="41" t="n">
+        <v>140</v>
+      </c>
+      <c r="C125" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D125" s="43" t="inlineStr">
@@ -6146,25 +6148,23 @@
       </c>
       <c r="E125" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F125" s="35" t="inlineStr">
         <is>
-          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="31" t="n">
-        <v>46353</v>
-      </c>
-      <c r="B126" s="33" t="n">
-        <v>230</v>
-      </c>
-      <c r="C126" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46347</v>
+      </c>
+      <c r="B126" s="33" t="inlineStr"/>
+      <c r="C126" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D126" s="42" t="inlineStr">
@@ -6174,21 +6174,21 @@
       </c>
       <c r="E126" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="36" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B127" s="41" t="n">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="C127" s="40" t="inlineStr">
         <is>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E127" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -6216,11 +6216,11 @@
         <v>46353</v>
       </c>
       <c r="B128" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C128" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>230</v>
+      </c>
+      <c r="C128" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D128" s="42" t="inlineStr">
@@ -6230,25 +6230,25 @@
       </c>
       <c r="E128" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F128" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Black”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="36" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B129" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C129" s="52" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>240</v>
+      </c>
+      <c r="C129" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D129" s="43" t="inlineStr">
@@ -6263,18 +6263,20 @@
       </c>
       <c r="F129" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Warning Code”</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" s="31" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B130" s="33" t="inlineStr"/>
-      <c r="C130" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46353</v>
+      </c>
+      <c r="B130" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="C130" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D130" s="42" t="inlineStr">
@@ -6284,12 +6286,12 @@
       </c>
       <c r="E130" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F130" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Vans Old Skool 36 Pearlized “Black”</t>
         </is>
       </c>
     </row>
@@ -6297,17 +6299,15 @@
       <c r="A131" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B131" s="41" t="n">
-        <v>120</v>
-      </c>
+      <c r="B131" s="41" t="inlineStr"/>
       <c r="C131" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D131" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D131" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E131" s="35" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="F131" s="35" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
         <v>46354</v>
       </c>
       <c r="B132" s="33" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C132" s="39" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="F132" s="30" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -6353,15 +6353,17 @@
       <c r="A133" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B133" s="41" t="inlineStr"/>
-      <c r="C133" s="52" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D133" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B133" s="41" t="n">
+        <v>130</v>
+      </c>
+      <c r="C133" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D133" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E133" s="35" t="inlineStr">
@@ -6371,7 +6373,7 @@
       </c>
       <c r="F133" s="35" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Aunt Pearl” 2026</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
@@ -6380,24 +6382,24 @@
         <v>46354</v>
       </c>
       <c r="B134" s="33" t="inlineStr"/>
-      <c r="C134" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D134" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C134" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D134" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E134" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F134" s="30" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Nike KD 6 “Aunt Pearl” 2026</t>
         </is>
       </c>
     </row>
@@ -6405,40 +6407,38 @@
       <c r="A135" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B135" s="41" t="n">
-        <v>190</v>
-      </c>
-      <c r="C135" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D135" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B135" s="41" t="inlineStr"/>
+      <c r="C135" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D135" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E135" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F135" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="31" t="n">
-        <v>46359</v>
+        <v>46354</v>
       </c>
       <c r="B136" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C136" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>190</v>
+      </c>
+      <c r="C136" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D136" s="42" t="inlineStr">
@@ -6453,18 +6453,20 @@
       </c>
       <c r="F136" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Black/White”</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="36" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B137" s="41" t="inlineStr"/>
-      <c r="C137" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46354</v>
+      </c>
+      <c r="B137" s="41" t="n">
+        <v>140</v>
+      </c>
+      <c r="C137" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D137" s="43" t="inlineStr">
@@ -6474,25 +6476,25 @@
       </c>
       <c r="E137" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F137" s="35" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Nike Caitlin 1 “Warning Code”</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="A138" s="31" t="n">
-        <v>46361</v>
+        <v>46359</v>
       </c>
       <c r="B138" s="33" t="n">
-        <v>215</v>
-      </c>
-      <c r="C138" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>170</v>
+      </c>
+      <c r="C138" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D138" s="42" t="inlineStr">
@@ -6502,12 +6504,12 @@
       </c>
       <c r="E138" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F138" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Nike Air Bakin “Black/White”</t>
         </is>
       </c>
     </row>
@@ -6515,12 +6517,10 @@
       <c r="A139" s="36" t="n">
         <v>46361</v>
       </c>
-      <c r="B139" s="41" t="n">
-        <v>300</v>
-      </c>
-      <c r="C139" s="52" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B139" s="41" t="inlineStr"/>
+      <c r="C139" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D139" s="43" t="inlineStr">
@@ -6530,21 +6530,21 @@
       </c>
       <c r="E139" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F139" s="35" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" s="31" t="n">
-        <v>46367</v>
+        <v>46361</v>
       </c>
       <c r="B140" s="33" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C140" s="39" t="inlineStr">
         <is>
@@ -6558,38 +6558,40 @@
       </c>
       <c r="E140" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F140" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Floral” 2026</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1">
       <c r="A141" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B141" s="41" t="inlineStr"/>
-      <c r="C141" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D141" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>46361</v>
+      </c>
+      <c r="B141" s="41" t="n">
+        <v>300</v>
+      </c>
+      <c r="C141" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D141" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E141" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F141" s="35" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Pharrell x adidas Adistar Jellyfish</t>
         </is>
       </c>
     </row>
@@ -6598,26 +6600,26 @@
         <v>46367</v>
       </c>
       <c r="B142" s="33" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="C142" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D142" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D142" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E142" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F142" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
         </is>
       </c>
     </row>
@@ -6625,60 +6627,114 @@
       <c r="A143" s="36" t="n">
         <v>46367</v>
       </c>
-      <c r="B143" s="41" t="n">
-        <v>190</v>
-      </c>
+      <c r="B143" s="41" t="inlineStr"/>
       <c r="C143" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D143" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D143" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E143" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F143" s="35" t="inlineStr">
         <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1">
       <c r="A144" s="31" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B144" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="C144" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D144" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E144" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F144" s="30" t="inlineStr">
+        <is>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="15" customHeight="1">
+      <c r="A145" s="36" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B145" s="41" t="n">
+        <v>190</v>
+      </c>
+      <c r="C145" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D145" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E145" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F145" s="35" t="inlineStr">
+        <is>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="15" customHeight="1">
+      <c r="A146" s="31" t="n">
         <v>46368</v>
       </c>
-      <c r="B144" s="33" t="n">
+      <c r="B146" s="33" t="n">
         <v>235</v>
       </c>
-      <c r="C144" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D144" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E144" s="30" t="inlineStr">
+      <c r="C146" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D146" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E146" s="30" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="F144" s="30" t="inlineStr">
+      <c r="F146" s="30" t="inlineStr">
         <is>
           <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F144"/>
+  <autoFilter ref="A3:F146"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -6719,7 +6775,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="51" t="inlineStr">
         <is>
-          <t>Generated September 17, 2026  ·  11:12 UTC</t>
+          <t>Generated September 18, 2026  ·  10:45 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -6762,10 +6818,10 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="C4" s="39" t="inlineStr">
         <is>
@@ -6784,7 +6840,7 @@
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “London”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6849,7 @@
         <v>46283</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
@@ -6807,12 +6863,12 @@
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6877,7 @@
         <v>46283</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
@@ -6835,12 +6891,12 @@
       </c>
       <c r="E6" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>APB x Air Jordan 11 Low</t>
         </is>
       </c>
     </row>
@@ -6849,26 +6905,26 @@
         <v>46283</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D7" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6933,7 @@
         <v>46283</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
@@ -6891,12 +6947,12 @@
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>Nike LeBron 23 “Laser”</t>
         </is>
       </c>
     </row>
@@ -6905,7 +6961,7 @@
         <v>46283</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
@@ -6919,12 +6975,12 @@
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>Nike Air Foamposite One "Green Camo"</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6989,7 @@
         <v>46283</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
@@ -6952,16 +7008,16 @@
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One "Green Camo"</t>
+          <t>Nike Air Foamposite Pro “Green Camo”</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
@@ -6980,7 +7036,7 @@
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo”</t>
+          <t>Nike Kobe 8 Protro “Mambacurial”</t>
         </is>
       </c>
     </row>
@@ -6989,26 +7045,26 @@
         <v>46284</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="C12" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D12" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>APB x Air Jordan 11 Low Pack</t>
         </is>
       </c>
     </row>
@@ -7017,7 +7073,7 @@
         <v>46284</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>200</v>
+        <v>122</v>
       </c>
       <c r="C13" s="40" t="inlineStr">
         <is>
@@ -7036,7 +7092,7 @@
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
         </is>
       </c>
     </row>
@@ -7045,54 +7101,54 @@
         <v>46284</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D14" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D14" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="36" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>122</v>
-      </c>
-      <c r="C15" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D15" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D15" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
@@ -7101,16 +7157,16 @@
         <v>46290</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>225</v>
-      </c>
-      <c r="C16" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D16" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>205</v>
+      </c>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
@@ -7120,7 +7176,7 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
@@ -7129,16 +7185,16 @@
         <v>46290</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="C17" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D17" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D17" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
@@ -7148,16 +7204,16 @@
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="C18" s="39" t="inlineStr">
         <is>
@@ -7171,12 +7227,12 @@
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7255,12 @@
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7269,7 @@
         <v>46291</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
@@ -7227,12 +7283,12 @@
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -7240,15 +7296,17 @@
       <c r="A21" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B21" s="41" t="inlineStr"/>
+      <c r="B21" s="41" t="n">
+        <v>150</v>
+      </c>
       <c r="C21" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D21" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D21" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
@@ -7258,7 +7316,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -7274,9 +7332,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D22" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
@@ -7286,7 +7344,7 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -7309,12 +7367,12 @@
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7381,7 @@
         <v>46291</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
@@ -7337,12 +7395,12 @@
       </c>
       <c r="E24" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -7350,17 +7408,15 @@
       <c r="A25" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B25" s="41" t="n">
-        <v>150</v>
-      </c>
+      <c r="B25" s="41" t="inlineStr"/>
       <c r="C25" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D25" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D25" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
@@ -7370,7 +7426,7 @@
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -7398,13 +7454,13 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="36" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B27" s="41" t="n">
         <v>210</v>
@@ -7421,12 +7477,12 @@
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
@@ -7435,16 +7491,16 @@
         <v>46295</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D28" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D28" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
@@ -7454,7 +7510,7 @@
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
@@ -7462,9 +7518,7 @@
       <c r="A29" s="36" t="n">
         <v>46295</v>
       </c>
-      <c r="B29" s="41" t="n">
-        <v>210</v>
-      </c>
+      <c r="B29" s="41" t="inlineStr"/>
       <c r="C29" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -7477,12 +7531,12 @@
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7545,7 @@
         <v>46295</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="C30" s="39" t="inlineStr">
         <is>
@@ -7510,7 +7564,7 @@
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
@@ -7518,15 +7572,17 @@
       <c r="A31" s="36" t="n">
         <v>46295</v>
       </c>
-      <c r="B31" s="41" t="inlineStr"/>
+      <c r="B31" s="41" t="n">
+        <v>135</v>
+      </c>
       <c r="C31" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D31" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D31" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -7536,35 +7592,35 @@
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D32" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D32" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Air Jordan 1 Low OG “Howard” 2026</t>
         </is>
       </c>
     </row>
@@ -7573,26 +7629,26 @@
         <v>46296</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="C33" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D33" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Howard” 2026</t>
+          <t>Nike Kobe Air Force 1 Low</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7937,7 @@
         <v>46312</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
@@ -7900,7 +7956,7 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7965,7 @@
         <v>46312</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
@@ -7928,7 +7984,7 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
@@ -7937,7 +7993,7 @@
         <v>46319</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
@@ -7956,7 +8012,7 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
@@ -7979,12 +8035,12 @@
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
@@ -7993,26 +8049,26 @@
         <v>46319</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D48" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
@@ -8021,16 +8077,16 @@
         <v>46319</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D49" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D49" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -8040,7 +8096,7 @@
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
@@ -8133,16 +8189,16 @@
         <v>46333</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D53" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
@@ -8152,7 +8208,7 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
@@ -8161,7 +8217,7 @@
         <v>46333</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
@@ -8180,7 +8236,7 @@
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
@@ -8189,16 +8245,16 @@
         <v>46333</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D55" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D55" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
@@ -8208,7 +8264,7 @@
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8441,7 @@
         <v>46347</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="C62" s="39" t="inlineStr">
         <is>
@@ -8399,12 +8455,12 @@
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -8413,16 +8469,16 @@
         <v>46347</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>125</v>
+        <v>230</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D63" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D63" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
@@ -8432,7 +8488,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -8441,26 +8497,26 @@
         <v>46347</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D64" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D64" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
@@ -8469,7 +8525,7 @@
         <v>46347</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>215</v>
+        <v>140</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
@@ -8483,12 +8539,12 @@
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
@@ -8497,7 +8553,7 @@
         <v>46347</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
@@ -8511,12 +8567,12 @@
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>

--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High Hype Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="M/D/YYYY"/>
     <numFmt numFmtId="166" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,6 +122,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00D4A000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="003B9EFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -543,7 +549,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -642,10 +648,10 @@
     <xf numFmtId="166" fontId="10" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -663,17 +669,23 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -796,12 +808,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Charts'!$A$2:$A$8</f>
+              <f>'Charts'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$B$2:$B$8</f>
+              <f>'Charts'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -999,12 +1011,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Charts'!$G$2:$G$3</f>
+              <f>'Charts'!$G$2:$G$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$H$2:$H$3</f>
+              <f>'Charts'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -1539,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1569,7 +1581,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 18, 2026  ·  10:45 UTC</t>
+          <t>Generated September 19, 2026  ·  10:30 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1609,20 +1621,20 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="14" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="16" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>$180</t>
+          <t>$182</t>
         </is>
       </c>
       <c r="H5" s="19" t="n"/>
@@ -1725,7 +1737,7 @@
         <v>46290</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1759,7 +1771,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1791,7 +1803,7 @@
         <v>46295</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1813,16 +1825,16 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D13" s="35" t="n">
         <v>0</v>
@@ -1836,27 +1848,27 @@
         <v>7</v>
       </c>
       <c r="G13" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="H13" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>122</v>
+      </c>
+      <c r="H13" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>Nike Kobe 8 Protro “Mambacurial”</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="C14" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D14" s="30" t="n">
         <v>0</v>
@@ -1870,9 +1882,9 @@
         <v>7</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="H14" s="42" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="H14" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -1881,7 +1893,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>APB x Air Jordan 11 Low Pack</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
@@ -1890,7 +1902,7 @@
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D15" s="35" t="n">
         <v>0</v>
@@ -1904,18 +1916,18 @@
         <v>7</v>
       </c>
       <c r="G15" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="H15" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>205</v>
+      </c>
+      <c r="H15" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
@@ -1924,7 +1936,7 @@
         </is>
       </c>
       <c r="C16" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D16" s="30" t="n">
         <v>0</v>
@@ -1938,9 +1950,9 @@
         <v>7</v>
       </c>
       <c r="G16" s="33" t="n">
-        <v>250</v>
-      </c>
-      <c r="H16" s="42" t="inlineStr">
+        <v>122</v>
+      </c>
+      <c r="H16" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2000,7 +2012,7 @@
         </is>
       </c>
       <c r="B20" s="30" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
@@ -2016,7 +2028,7 @@
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -2026,7 +2038,7 @@
         </is>
       </c>
       <c r="B21" s="35" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
@@ -2034,7 +2046,7 @@
         </is>
       </c>
       <c r="E21" s="35" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G21" s="47" t="inlineStr">
         <is>
@@ -2052,7 +2064,7 @@
         </is>
       </c>
       <c r="B22" s="30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
@@ -2060,7 +2072,15 @@
         </is>
       </c>
       <c r="E22" s="30" t="n">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="G22" s="49" t="inlineStr">
+        <is>
+          <t>Confirmed App</t>
+        </is>
+      </c>
+      <c r="H22" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
@@ -2070,15 +2090,15 @@
         </is>
       </c>
       <c r="B23" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="D23" s="49" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="D23" s="50" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="E23" s="35" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -2098,7 +2118,7 @@
         </is>
       </c>
       <c r="B25" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -2111,318 +2131,328 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="10" customHeight="1"/>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B27" s="35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="10" customHeight="1"/>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>Weekly Outlook (Next 13 Weeks)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>Dates</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C30" s="29" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
       </c>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="D30" s="29" t="inlineStr">
         <is>
           <t>HIGH+EXTREME</t>
         </is>
       </c>
-      <c r="E29" s="29" t="inlineStr">
+      <c r="E30" s="29" t="inlineStr">
         <is>
           <t>Avg Hype Score</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="B30" s="30" t="inlineStr">
-        <is>
-          <t>9/18 – 9/24</t>
-        </is>
-      </c>
-      <c r="C30" s="30" t="n">
-        <v>26</v>
-      </c>
-      <c r="D30" s="39" t="n">
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>9/19 – 9/25</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>21</v>
+      </c>
+      <c r="D31" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" s="30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="35" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>9/26 – 10/2</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="D32" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="E32" s="35" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>10/3 – 10/9</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="30" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="35" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="B34" s="35" t="inlineStr">
+        <is>
+          <t>10/10 – 10/16</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="35" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>10/17 – 10/23</t>
+        </is>
+      </c>
+      <c r="C35" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="30" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="35" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="B36" s="35" t="inlineStr">
+        <is>
+          <t>10/24 – 10/30</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" s="35" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>10/31 – 11/6</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="30" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>11/7 – 11/13</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="E30" s="30" t="n">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="35" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="B31" s="35" t="inlineStr">
-        <is>
-          <t>9/25 – 10/1</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="n">
-        <v>38</v>
-      </c>
-      <c r="D31" s="40" t="n">
-        <v>19</v>
-      </c>
-      <c r="E31" s="35" t="n">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>10/2 – 10/8</t>
-        </is>
-      </c>
-      <c r="C32" s="30" t="n">
+      <c r="D38" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" s="35" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>11/14 – 11/20</t>
+        </is>
+      </c>
+      <c r="C39" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="30" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>11/21 – 11/27</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" s="35" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>11/28 – 12/4</t>
+        </is>
+      </c>
+      <c r="C41" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" s="30" t="n">
+      <c r="E41" s="30" t="n">
         <v>6.2</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="35" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="B33" s="35" t="inlineStr">
-        <is>
-          <t>10/9 – 10/15</t>
-        </is>
-      </c>
-      <c r="C33" s="35" t="n">
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="B42" s="35" t="inlineStr">
+        <is>
+          <t>12/5 – 12/11</t>
+        </is>
+      </c>
+      <c r="C42" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="D42" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="D33" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" s="35" t="n">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="B34" s="30" t="inlineStr">
-        <is>
-          <t>10/16 – 10/22</t>
-        </is>
-      </c>
-      <c r="C34" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="D34" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E34" s="30" t="n">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="35" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="B35" s="35" t="inlineStr">
-        <is>
-          <t>10/23 – 10/29</t>
-        </is>
-      </c>
-      <c r="C35" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="D35" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="E35" s="35" t="n">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="30" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="B36" s="30" t="inlineStr">
-        <is>
-          <t>10/30 – 11/5</t>
-        </is>
-      </c>
-      <c r="C36" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="D36" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="30" t="n">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="35" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="B37" s="35" t="inlineStr">
-        <is>
-          <t>11/6 – 11/12</t>
-        </is>
-      </c>
-      <c r="C37" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="D37" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="E37" s="35" t="n">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="30" t="inlineStr">
-        <is>
-          <t>Week 9</t>
-        </is>
-      </c>
-      <c r="B38" s="30" t="inlineStr">
-        <is>
-          <t>11/13 – 11/19</t>
-        </is>
-      </c>
-      <c r="C38" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="D38" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" s="30" t="n">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="35" t="inlineStr">
-        <is>
-          <t>Week 10</t>
-        </is>
-      </c>
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>11/20 – 11/26</t>
-        </is>
-      </c>
-      <c r="C39" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="D39" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="E39" s="35" t="n">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="B40" s="30" t="inlineStr">
-        <is>
-          <t>11/27 – 12/3</t>
-        </is>
-      </c>
-      <c r="C40" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="D40" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="E40" s="30" t="n">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="35" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>12/4 – 12/10</t>
-        </is>
-      </c>
-      <c r="C41" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D41" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" s="35" t="n">
+      <c r="E42" s="35" t="n">
         <v>6.3</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="30" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>Week 13</t>
         </is>
       </c>
-      <c r="B42" s="30" t="inlineStr">
-        <is>
-          <t>12/11 – 12/17</t>
-        </is>
-      </c>
-      <c r="C42" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D42" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="E42" s="30" t="n">
+      <c r="B43" s="30" t="inlineStr">
+        <is>
+          <t>12/12 – 12/18</t>
+        </is>
+      </c>
+      <c r="C43" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="30" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2434,12 +2464,12 @@
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A28:H28"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A8:H8"/>
@@ -2456,7 +2486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2473,42 +2503,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="50" t="inlineStr">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="B1" s="50" t="inlineStr">
+      <c r="B1" s="51" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
       </c>
-      <c r="D1" s="50" t="inlineStr">
+      <c r="D1" s="51" t="inlineStr">
         <is>
           <t>Hype Level</t>
         </is>
       </c>
-      <c r="E1" s="50" t="inlineStr">
+      <c r="E1" s="51" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
       </c>
-      <c r="G1" s="50" t="inlineStr">
+      <c r="G1" s="51" t="inlineStr">
         <is>
           <t>Sale Method</t>
         </is>
       </c>
-      <c r="H1" s="50" t="inlineStr">
+      <c r="H1" s="51" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
       </c>
-      <c r="J1" s="50" t="inlineStr">
+      <c r="J1" s="51" t="inlineStr">
         <is>
           <t>Price Range</t>
         </is>
       </c>
-      <c r="K1" s="50" t="inlineStr">
+      <c r="K1" s="51" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
@@ -2521,7 +2551,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2537,7 +2567,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2545,7 +2575,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2555,7 +2585,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2563,7 +2593,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2579,7 +2609,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -2589,7 +2619,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2597,7 +2627,15 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Confirmed App</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2605,7 +2643,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -2615,7 +2653,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2623,7 +2661,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2631,7 +2669,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -2649,7 +2687,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2659,7 +2697,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2669,6 +2707,16 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2684,7 +2732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2708,9 +2756,9 @@
       <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="51" t="inlineStr">
-        <is>
-          <t>Generated September 18, 2026  ·  10:45 UTC</t>
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>Generated September 19, 2026  ·  10:30 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2753,19 +2801,19 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C4" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D4" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>215</v>
+      </c>
+      <c r="C4" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D4" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
@@ -2775,53 +2823,53 @@
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Air Jordan 9 OG “Space Jam” 2026</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D5" s="43" t="inlineStr">
+        <v>110</v>
+      </c>
+      <c r="C5" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>Pokémon x adidas 30th Anniversary Collection</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>135</v>
-      </c>
-      <c r="C6" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>122</v>
+      </c>
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
@@ -2831,13 +2879,13 @@
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>PSG x Nike KD 6</t>
+          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B7" s="41" t="n">
         <v>200</v>
@@ -2847,119 +2895,119 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>Nike Kobe 8 Protro “Mambacurial”</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C8" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>205</v>
+      </c>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Cold Blooded”</t>
+          <t>APB x Air Jordan 11 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="C9" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D9" s="43" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Nike A’Two “Dawn Staley”</t>
+          <t>Air Jordan 9 OG "Space Jam"</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>65</v>
-      </c>
-      <c r="C10" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
+        <v>122</v>
+      </c>
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>K-Pop Demon Hunters x Vans Fall 2026 Collection</t>
+          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>250</v>
-      </c>
-      <c r="C11" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D11" s="43" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C11" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2971,23 +3019,23 @@
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>One Piece x Nike Air Max Plus “Ope Ope”</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="31" t="n">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="B12" s="33" t="n">
         <v>210</v>
       </c>
-      <c r="C12" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D12" s="42" t="inlineStr">
+      <c r="C12" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2999,23 +3047,23 @@
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>Nike GT Future “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="36" t="n">
-        <v>46283</v>
+        <v>46288</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C13" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D13" s="43" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C13" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3027,247 +3075,247 @@
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One "Green Camo"</t>
+          <t>Nike GT Future “Unseen Hours”</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="31" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>110</v>
-      </c>
-      <c r="C14" s="52" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C14" s="54" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="42" t="inlineStr">
+      <c r="D14" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Anthony Edwards x adidas Superstar “Cold Blooded”</t>
+          <t>Converse SHAI 001 “Ghosted”</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="36" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>250</v>
-      </c>
-      <c r="C15" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D15" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C15" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo”</t>
+          <t>Converse SHAI 001 “Green Beam”</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="31" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C16" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D16" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C16" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>Converse SHAI 001 Shroud “Shock”</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="36" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C17" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D17" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C17" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>Converse SHAI 001 “Spark”</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="31" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>300</v>
-      </c>
-      <c r="C18" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D18" s="42" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="36" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C19" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D19" s="43" t="inlineStr">
+        <v>120</v>
+      </c>
+      <c r="C19" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 9 OG “Space Jam” 2026</t>
+          <t>Billionaire Boys Club x Reebok Club C 85</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="31" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>110</v>
-      </c>
-      <c r="C20" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C20" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Pokémon x adidas 30th Anniversary Collection</t>
+          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="36" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>122</v>
-      </c>
-      <c r="C21" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D21" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C21" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D21" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="31" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>122</v>
-      </c>
-      <c r="C22" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D22" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C22" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3279,23 +3327,23 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
+          <t>Nike Ja 4 “Jaws”</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="36" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="C23" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D23" s="43" t="inlineStr">
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3307,13 +3355,13 @@
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Ope Ope”</t>
+          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="31" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="B24" s="33" t="n">
         <v>210</v>
@@ -3323,7 +3371,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D24" s="42" t="inlineStr">
+      <c r="D24" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3335,160 +3383,158 @@
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Nike GT Future “Varsity Red”</t>
+          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="36" t="n">
-        <v>46288</v>
+        <v>46291</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C25" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D25" s="43" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Nike GT Future “Unseen Hours”</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="31" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C26" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D26" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>150</v>
+      </c>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Green Beam”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="36" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B27" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C27" s="49" t="inlineStr">
+        <v>46291</v>
+      </c>
+      <c r="B27" s="41" t="inlineStr"/>
+      <c r="C27" s="50" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D27" s="43" t="inlineStr">
+      <c r="D27" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Ghosted”</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="31" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C28" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D28" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>155</v>
+      </c>
+      <c r="C28" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D28" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 Shroud “Shock”</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="36" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C29" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D29" s="43" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Spark”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>225</v>
-      </c>
-      <c r="C30" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
+        <v>255</v>
+      </c>
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
@@ -3503,81 +3549,81 @@
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C31" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D31" s="43" t="inlineStr">
+        <v>160</v>
+      </c>
+      <c r="C31" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="C32" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D32" s="42" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C32" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Billionaire Boys Club x Reebok Club C 85</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C33" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D33" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
@@ -3587,53 +3633,53 @@
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="C34" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D34" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D34" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="C35" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D35" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D35" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
@@ -3643,23 +3689,21 @@
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws”</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="31" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B36" s="33" t="n">
-        <v>185</v>
-      </c>
-      <c r="C36" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D36" s="42" t="inlineStr">
+        <v>46291</v>
+      </c>
+      <c r="B36" s="33" t="inlineStr"/>
+      <c r="C36" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D36" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3671,35 +3715,35 @@
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C37" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D37" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D37" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3815,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D40" s="42" t="inlineStr">
+      <c r="D40" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3792,26 +3836,26 @@
         <v>46291</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C41" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D41" s="43" t="inlineStr">
+        <v>120</v>
+      </c>
+      <c r="C41" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D41" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
         </is>
       </c>
     </row>
@@ -3820,16 +3864,16 @@
         <v>46291</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="C42" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D42" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D42" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E42" s="30" t="inlineStr">
@@ -3839,51 +3883,51 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="36" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="B43" s="41" t="inlineStr"/>
-      <c r="C43" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D43" s="43" t="inlineStr">
+      <c r="C43" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D43" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="31" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C44" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D44" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D44" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E44" s="30" t="inlineStr">
@@ -3893,23 +3937,23 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C45" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D45" s="43" t="inlineStr">
+        <v>249</v>
+      </c>
+      <c r="C45" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D45" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3921,53 +3965,53 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Hyperice x Nike Air Zoom Hyperslide</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="31" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C46" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D46" s="42" t="inlineStr">
+      <c r="D46" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Night Navy”</t>
+          <t>Nike Air Bakin “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="36" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D47" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D47" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
@@ -3977,25 +4021,25 @@
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B48" s="33" t="n">
         <v>125</v>
       </c>
-      <c r="C48" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D48" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C48" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
@@ -4005,23 +4049,21 @@
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="36" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B49" s="41" t="n">
-        <v>140</v>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="B49" s="41" t="inlineStr"/>
       <c r="C49" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D49" s="43" t="inlineStr">
+      <c r="D49" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4033,16 +4075,16 @@
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="C50" s="48" t="inlineStr">
         <is>
@@ -4061,21 +4103,23 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>MoMA x Nike Air Rift 2 Pack</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B51" s="41" t="inlineStr"/>
+        <v>46295</v>
+      </c>
+      <c r="B51" s="41" t="n">
+        <v>155</v>
+      </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D51" s="43" t="inlineStr">
+      <c r="D51" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4087,69 +4131,69 @@
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="C52" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D52" s="42" t="inlineStr">
+      <c r="D52" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
+          <t>Nike Zoom Huarache 2K4 “UCLA”</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="36" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>160</v>
-      </c>
-      <c r="C53" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D53" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>135</v>
+      </c>
+      <c r="C53" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D53" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B54" s="33" t="n">
         <v>210</v>
@@ -4159,89 +4203,89 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D54" s="42" t="inlineStr">
+      <c r="D54" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B55" s="41" t="inlineStr"/>
+        <v>46296</v>
+      </c>
+      <c r="B55" s="41" t="n">
+        <v>140</v>
+      </c>
       <c r="C55" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D55" s="43" t="inlineStr">
+      <c r="D55" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
+          <t>Nike Caitlin 1 “Racer Blue”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B56" s="33" t="n">
-        <v>170</v>
-      </c>
+        <v>46296</v>
+      </c>
+      <c r="B56" s="33" t="inlineStr"/>
       <c r="C56" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D56" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D56" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
+          <t>Air Jordan “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>249</v>
-      </c>
-      <c r="C57" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D57" s="43" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C57" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D57" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4253,53 +4297,53 @@
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Hyperice x Nike Air Zoom Hyperslide</t>
+          <t>Nike Kobe Air Force 1 Low</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="31" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C58" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D58" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>220</v>
+      </c>
+      <c r="C58" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D58" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Red”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D59" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D59" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
@@ -4309,49 +4353,51 @@
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D60" s="42" t="inlineStr">
+      <c r="D60" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B61" s="41" t="inlineStr"/>
+        <v>46300</v>
+      </c>
+      <c r="B61" s="41" t="n">
+        <v>200</v>
+      </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D61" s="43" t="inlineStr">
+      <c r="D61" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4363,81 +4409,81 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46295</v>
+        <v>46303</v>
       </c>
       <c r="B62" s="33" t="n">
         <v>130</v>
       </c>
-      <c r="C62" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D62" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C62" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D62" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>MoMA x Nike Air Rift 2 Pack</t>
+          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="36" t="n">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C63" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D63" s="43" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C63" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D63" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="31" t="n">
-        <v>46295</v>
+        <v>46304</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>135</v>
-      </c>
-      <c r="C64" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D64" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C64" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D64" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
@@ -4447,79 +4493,79 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="36" t="n">
-        <v>46296</v>
+        <v>46304</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>165</v>
-      </c>
-      <c r="C65" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D65" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>220</v>
+      </c>
+      <c r="C65" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D65" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Howard” 2026</t>
+          <t>Aminé x New Balance 992 “Outdoor School”</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46296</v>
+        <v>46305</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C66" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D66" s="42" t="inlineStr">
+        <v>180</v>
+      </c>
+      <c r="C66" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D66" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Racer Blue”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46296</v>
+        <v>46305</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C67" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D67" s="43" t="inlineStr">
+        <v>135</v>
+      </c>
+      <c r="C67" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D67" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4531,25 +4577,25 @@
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low</t>
+          <t>Nike KD 6 “Texas”</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46297</v>
+        <v>46310</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>220</v>
-      </c>
-      <c r="C68" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D68" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>125</v>
+      </c>
+      <c r="C68" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D68" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
@@ -4559,41 +4605,41 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46298</v>
+        <v>46310</v>
       </c>
       <c r="B69" s="41" t="n">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D69" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D69" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46298</v>
+        <v>46311</v>
       </c>
       <c r="B70" s="33" t="n">
         <v>240</v>
@@ -4603,35 +4649,35 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D70" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D70" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D71" s="43" t="inlineStr">
+      <c r="D71" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4643,107 +4689,107 @@
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C72" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D72" s="42" t="inlineStr">
+        <v>240</v>
+      </c>
+      <c r="C72" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D72" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C73" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D73" s="43" t="inlineStr">
+        <v>250</v>
+      </c>
+      <c r="C73" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D73" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46304</v>
+        <v>46312</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C74" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D74" s="42" t="inlineStr">
+        <v>220</v>
+      </c>
+      <c r="C74" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D74" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="C75" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D75" s="43" t="inlineStr">
+      <c r="D75" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4755,81 +4801,79 @@
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="31" t="n">
-        <v>46305</v>
+        <v>46315</v>
       </c>
       <c r="B76" s="33" t="n">
-        <v>135</v>
-      </c>
-      <c r="C76" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D76" s="42" t="inlineStr">
+        <v>160</v>
+      </c>
+      <c r="C76" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D76" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Texas”</t>
+          <t>Reebok Angel Reese 1 “Reese’s”</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="36" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B77" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C77" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D77" s="43" t="inlineStr">
+        <v>46317</v>
+      </c>
+      <c r="B77" s="41" t="inlineStr"/>
+      <c r="C77" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D77" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>SZA x Vans VANSZA Collection</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="31" t="n">
-        <v>46310</v>
+        <v>46318</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C78" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D78" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D78" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E78" s="30" t="inlineStr">
@@ -4839,23 +4883,23 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Nike Air Force 1 Low “NYC Rat”</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="36" t="n">
-        <v>46311</v>
+        <v>46319</v>
       </c>
       <c r="B79" s="41" t="n">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="C79" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D79" s="43" t="inlineStr">
+      <c r="D79" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4867,23 +4911,23 @@
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="31" t="n">
-        <v>46311</v>
+        <v>46319</v>
       </c>
       <c r="B80" s="33" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="C80" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D80" s="42" t="inlineStr">
+      <c r="D80" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4895,51 +4939,51 @@
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="36" t="n">
-        <v>46311</v>
+        <v>46319</v>
       </c>
       <c r="B81" s="41" t="n">
-        <v>240</v>
+        <v>125</v>
       </c>
       <c r="C81" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D81" s="43" t="inlineStr">
+      <c r="D81" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E81" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F81" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="31" t="n">
-        <v>46311</v>
+        <v>46319</v>
       </c>
       <c r="B82" s="33" t="n">
-        <v>250</v>
-      </c>
-      <c r="C82" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D82" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C82" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D82" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4951,89 +4995,91 @@
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="36" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B83" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C83" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D83" s="43" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C83" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D83" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E83" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F83" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="31" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B84" s="33" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="C84" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D84" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D84" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="36" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B85" s="41" t="inlineStr"/>
-      <c r="C85" s="49" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D85" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>46319</v>
+      </c>
+      <c r="B85" s="41" t="n">
+        <v>170</v>
+      </c>
+      <c r="C85" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D85" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E85" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>SZA x Vans VANSZA Collection</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
@@ -5042,16 +5088,16 @@
         <v>46319</v>
       </c>
       <c r="B86" s="33" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="C86" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D86" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D86" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E86" s="30" t="inlineStr">
@@ -5061,51 +5107,51 @@
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="36" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B87" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C87" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D87" s="43" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C87" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D87" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E87" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="31" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="B88" s="33" t="n">
-        <v>190</v>
-      </c>
-      <c r="C88" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D88" s="42" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="C88" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D88" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5117,25 +5163,25 @@
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="36" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C89" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D89" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C89" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D89" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E89" s="35" t="inlineStr">
@@ -5145,109 +5191,109 @@
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Nike Ja 4 High “University Red”</t>
         </is>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="31" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C90" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D90" s="42" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="C90" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D90" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E90" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Nike Book 2 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="36" t="n">
-        <v>46319</v>
+        <v>46326</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C91" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D91" s="43" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C91" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D91" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E91" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="31" t="n">
-        <v>46319</v>
+        <v>46329</v>
       </c>
       <c r="B92" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C92" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D92" s="42" t="inlineStr">
+        <v>240</v>
+      </c>
+      <c r="C92" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D92" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E92" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="36" t="n">
-        <v>46319</v>
+        <v>46331</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="C93" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D93" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C93" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D93" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E93" s="35" t="inlineStr">
@@ -5257,51 +5303,51 @@
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="31" t="n">
-        <v>46320</v>
+        <v>46331</v>
       </c>
       <c r="B94" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C94" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D94" s="42" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C94" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D94" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E94" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="36" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="B95" s="41" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C95" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D95" s="43" t="inlineStr">
+      <c r="D95" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5313,20 +5359,20 @@
       </c>
       <c r="F95" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
+          <t>Nike Book 2 “Desert Night”</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="31" t="n">
-        <v>46325</v>
+        <v>46333</v>
       </c>
       <c r="B96" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C96" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>240</v>
+      </c>
+      <c r="C96" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D96" s="34" t="inlineStr">
@@ -5336,58 +5382,58 @@
       </c>
       <c r="E96" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 High “University Red”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="36" t="n">
-        <v>46325</v>
+        <v>46333</v>
       </c>
       <c r="B97" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C97" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D97" s="43" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C97" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D97" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E97" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F97" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Halloween”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="31" t="n">
-        <v>46326</v>
+        <v>46333</v>
       </c>
       <c r="B98" s="33" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="C98" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D98" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D98" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E98" s="30" t="inlineStr">
@@ -5397,13 +5443,13 @@
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="36" t="n">
-        <v>46329</v>
+        <v>46335</v>
       </c>
       <c r="B99" s="41" t="n">
         <v>240</v>
@@ -5413,9 +5459,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D99" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D99" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E99" s="35" t="inlineStr">
@@ -5425,23 +5471,23 @@
       </c>
       <c r="F99" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="31" t="n">
-        <v>46331</v>
+        <v>46337</v>
       </c>
       <c r="B100" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C100" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D100" s="42" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C100" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D100" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5453,53 +5499,53 @@
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="36" t="n">
-        <v>46331</v>
+        <v>46337</v>
       </c>
       <c r="B101" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C101" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D101" s="43" t="inlineStr">
+        <v>235</v>
+      </c>
+      <c r="C101" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D101" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E101" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="31" t="n">
-        <v>46332</v>
+        <v>46338</v>
       </c>
       <c r="B102" s="33" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C102" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D102" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D102" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E102" s="30" t="inlineStr">
@@ -5509,109 +5555,109 @@
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Desert Night”</t>
+          <t>Nike Air Bakin “Varsity Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="36" t="n">
-        <v>46333</v>
+        <v>46338</v>
       </c>
       <c r="B103" s="41" t="n">
-        <v>245</v>
-      </c>
-      <c r="C103" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D103" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C103" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D103" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E103" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F103" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="31" t="n">
-        <v>46333</v>
+        <v>46338</v>
       </c>
       <c r="B104" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C104" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D104" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C104" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D104" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E104" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F104" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Nike Air Bakin “Varsity Royal”</t>
         </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="36" t="n">
-        <v>46333</v>
+        <v>46339</v>
       </c>
       <c r="B105" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C105" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D105" s="43" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C105" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D105" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E105" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Air Diamond Turf 2 Patent “Black Red”</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="31" t="n">
-        <v>46335</v>
+        <v>46339</v>
       </c>
       <c r="B106" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C106" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D106" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C106" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D106" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E106" s="30" t="inlineStr">
@@ -5621,25 +5667,25 @@
       </c>
       <c r="F106" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Nike Air Diamond Turf 2</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="36" t="n">
-        <v>46337</v>
+        <v>46340</v>
       </c>
       <c r="B107" s="41" t="n">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="C107" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D107" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D107" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E107" s="35" t="inlineStr">
@@ -5649,44 +5695,44 @@
       </c>
       <c r="F107" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="31" t="n">
-        <v>46337</v>
+        <v>46340</v>
       </c>
       <c r="B108" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C108" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D108" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>240</v>
+      </c>
+      <c r="C108" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D108" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E108" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F108" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
         </is>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="36" t="n">
-        <v>46338</v>
+        <v>46341</v>
       </c>
       <c r="B109" s="41" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C109" s="53" t="inlineStr">
         <is>
@@ -5705,51 +5751,51 @@
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal” 2026</t>
+          <t>Playa Society x Nike A’Two</t>
         </is>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="31" t="n">
-        <v>46338</v>
+        <v>46342</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C110" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D110" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C110" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D110" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E110" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="36" t="n">
-        <v>46338</v>
+        <v>46343</v>
       </c>
       <c r="B111" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C111" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D111" s="43" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C111" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D111" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5761,109 +5807,109 @@
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="31" t="n">
-        <v>46339</v>
+        <v>46345</v>
       </c>
       <c r="B112" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C112" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D112" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C112" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D112" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E112" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F112" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Diamond Turf 2</t>
+          <t>Vans Old Skool 36 Pearlized “Navy”</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="36" t="n">
-        <v>46340</v>
+        <v>46346</v>
       </c>
       <c r="B113" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C113" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D113" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>145</v>
+      </c>
+      <c r="C113" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D113" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E113" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F113" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Book 2 “Be Legendary”</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="31" t="n">
-        <v>46340</v>
+        <v>46346</v>
       </c>
       <c r="B114" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C114" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D114" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C114" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D114" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E114" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F114" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
+          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="36" t="n">
-        <v>46341</v>
+        <v>46347</v>
       </c>
       <c r="B115" s="41" t="n">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C115" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D115" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D115" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E115" s="35" t="inlineStr">
@@ -5873,16 +5919,16 @@
       </c>
       <c r="F115" s="35" t="inlineStr">
         <is>
-          <t>Playa Society x Nike A’Two</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="31" t="n">
-        <v>46342</v>
+        <v>46347</v>
       </c>
       <c r="B116" s="33" t="n">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="C116" s="39" t="inlineStr">
         <is>
@@ -5896,124 +5942,122 @@
       </c>
       <c r="E116" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="36" t="n">
-        <v>46343</v>
+        <v>46347</v>
       </c>
       <c r="B117" s="41" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C117" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D117" s="43" t="inlineStr">
+      <c r="D117" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E117" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F117" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="31" t="n">
-        <v>46345</v>
+        <v>46347</v>
       </c>
       <c r="B118" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C118" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D118" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C118" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D118" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F118" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Navy”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="36" t="n">
-        <v>46346</v>
-      </c>
-      <c r="B119" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C119" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D119" s="43" t="inlineStr">
+        <v>46347</v>
+      </c>
+      <c r="B119" s="41" t="inlineStr"/>
+      <c r="C119" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D119" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E119" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Be Legendary”</t>
+          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="31" t="n">
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="B120" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C120" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D120" s="42" t="inlineStr">
+        <v>165</v>
+      </c>
+      <c r="C120" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D120" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E120" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F120" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6073,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D121" s="43" t="inlineStr">
+      <c r="D121" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6047,47 +6091,47 @@
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="A122" s="31" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B122" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C122" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D122" s="42" t="inlineStr">
+        <v>230</v>
+      </c>
+      <c r="C122" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D122" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F122" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Snow White”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="36" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B123" s="41" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C123" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D123" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D123" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E123" s="35" t="inlineStr">
@@ -6097,53 +6141,53 @@
       </c>
       <c r="F123" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1">
       <c r="A124" s="31" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B124" s="33" t="n">
-        <v>215</v>
-      </c>
-      <c r="C124" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D124" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C124" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D124" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E124" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F124" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Vans Old Skool 36 Pearlized “Black”</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="36" t="n">
-        <v>46347</v>
+        <v>46354</v>
       </c>
       <c r="B125" s="41" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C125" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D125" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D125" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E125" s="35" t="inlineStr">
@@ -6153,51 +6197,49 @@
       </c>
       <c r="F125" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="31" t="n">
-        <v>46347</v>
+        <v>46354</v>
       </c>
       <c r="B126" s="33" t="inlineStr"/>
-      <c r="C126" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D126" s="42" t="inlineStr">
+      <c r="C126" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D126" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E126" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
+          <t>Nike KD 6 “Aunt Pearl” 2026</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="36" t="n">
-        <v>46347</v>
-      </c>
-      <c r="B127" s="41" t="n">
-        <v>165</v>
-      </c>
-      <c r="C127" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D127" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>46354</v>
+      </c>
+      <c r="B127" s="41" t="inlineStr"/>
+      <c r="C127" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D127" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E127" s="35" t="inlineStr">
@@ -6207,51 +6249,51 @@
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" s="31" t="n">
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="B128" s="33" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C128" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D128" s="42" t="inlineStr">
+      <c r="D128" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E128" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F128" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="36" t="n">
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="B129" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C129" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D129" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C129" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D129" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6263,35 +6305,33 @@
       </c>
       <c r="F129" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Nike Caitlin 1 “Warning Code”</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" s="31" t="n">
-        <v>46353</v>
-      </c>
-      <c r="B130" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C130" s="52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D130" s="42" t="inlineStr">
+        <v>46354</v>
+      </c>
+      <c r="B130" s="33" t="inlineStr"/>
+      <c r="C130" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D130" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E130" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F130" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Black”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
@@ -6299,15 +6339,17 @@
       <c r="A131" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B131" s="41" t="inlineStr"/>
+      <c r="B131" s="41" t="n">
+        <v>120</v>
+      </c>
       <c r="C131" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D131" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D131" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E131" s="35" t="inlineStr">
@@ -6317,25 +6359,25 @@
       </c>
       <c r="F131" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1">
       <c r="A132" s="31" t="n">
-        <v>46354</v>
+        <v>46359</v>
       </c>
       <c r="B132" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="C132" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D132" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C132" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D132" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E132" s="30" t="inlineStr">
@@ -6345,77 +6387,79 @@
       </c>
       <c r="F132" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Nike Air Bakin “Black/White”</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1">
       <c r="A133" s="36" t="n">
-        <v>46354</v>
+        <v>46361</v>
       </c>
       <c r="B133" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C133" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D133" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>300</v>
+      </c>
+      <c r="C133" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D133" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E133" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F133" s="35" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
         </is>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="31" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B134" s="33" t="inlineStr"/>
+        <v>46361</v>
+      </c>
+      <c r="B134" s="33" t="n">
+        <v>300</v>
+      </c>
       <c r="C134" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D134" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D134" s="55" t="inlineStr">
+        <is>
+          <t>Confirmed App</t>
         </is>
       </c>
       <c r="E134" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F134" s="30" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Aunt Pearl” 2026</t>
+          <t>Pharrell x adidas Adistar Jellyfish “Auburn Timber”</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c r="A135" s="36" t="n">
-        <v>46354</v>
+        <v>46361</v>
       </c>
       <c r="B135" s="41" t="inlineStr"/>
-      <c r="C135" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D135" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C135" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D135" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E135" s="35" t="inlineStr">
@@ -6425,107 +6469,107 @@
       </c>
       <c r="F135" s="35" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="31" t="n">
-        <v>46354</v>
+        <v>46361</v>
       </c>
       <c r="B136" s="33" t="n">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C136" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D136" s="42" t="inlineStr">
+      <c r="D136" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E136" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F136" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="36" t="n">
-        <v>46354</v>
+        <v>46361</v>
       </c>
       <c r="B137" s="41" t="n">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="C137" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D137" s="43" t="inlineStr">
+      <c r="D137" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E137" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F137" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Warning Code”</t>
+          <t>Pharrell x adidas Adistar Jellyfish</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="A138" s="31" t="n">
-        <v>46359</v>
-      </c>
-      <c r="B138" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C138" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D138" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>46367</v>
+      </c>
+      <c r="B138" s="33" t="inlineStr"/>
+      <c r="C138" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D138" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E138" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F138" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Black/White”</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1">
       <c r="A139" s="36" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B139" s="41" t="inlineStr"/>
+        <v>46367</v>
+      </c>
+      <c r="B139" s="41" t="n">
+        <v>150</v>
+      </c>
       <c r="C139" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D139" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D139" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E139" s="35" t="inlineStr">
@@ -6535,206 +6579,96 @@
       </c>
       <c r="F139" s="35" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" s="31" t="n">
-        <v>46361</v>
+        <v>46367</v>
       </c>
       <c r="B140" s="33" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C140" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D140" s="42" t="inlineStr">
+      <c r="D140" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E140" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F140" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
         </is>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1">
       <c r="A141" s="36" t="n">
-        <v>46361</v>
+        <v>46367</v>
       </c>
       <c r="B141" s="41" t="n">
-        <v>300</v>
-      </c>
-      <c r="C141" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D141" s="43" t="inlineStr">
+        <v>190</v>
+      </c>
+      <c r="C141" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D141" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E141" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F141" s="35" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish</t>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1">
       <c r="A142" s="31" t="n">
-        <v>46367</v>
+        <v>46368</v>
       </c>
       <c r="B142" s="33" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C142" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D142" s="42" t="inlineStr">
+      <c r="D142" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E142" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F142" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Floral” 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="15" customHeight="1">
-      <c r="A143" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B143" s="41" t="inlineStr"/>
-      <c r="C143" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D143" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
-        </is>
-      </c>
-      <c r="E143" s="35" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F143" s="35" t="inlineStr">
-        <is>
-          <t>Free The Youth x Air Jordan 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="15" customHeight="1">
-      <c r="A144" s="31" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B144" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C144" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D144" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
-        </is>
-      </c>
-      <c r="E144" s="30" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F144" s="30" t="inlineStr">
-        <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B145" s="41" t="n">
-        <v>190</v>
-      </c>
-      <c r="C145" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D145" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E145" s="35" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="F145" s="35" t="inlineStr">
-        <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="15" customHeight="1">
-      <c r="A146" s="31" t="n">
-        <v>46368</v>
-      </c>
-      <c r="B146" s="33" t="n">
-        <v>235</v>
-      </c>
-      <c r="C146" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D146" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E146" s="30" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F146" s="30" t="inlineStr">
-        <is>
           <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F146"/>
+  <autoFilter ref="A3:F142"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -6749,7 +6683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6773,9 +6707,9 @@
       <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="51" t="inlineStr">
-        <is>
-          <t>Generated September 18, 2026  ·  10:45 UTC</t>
+      <c r="A2" s="52" t="inlineStr">
+        <is>
+          <t>Generated September 19, 2026  ·  10:30 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -6818,75 +6752,75 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="C4" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D4" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 11 Low “Fiberglass”</t>
+          <t>Nike Kobe 8 Protro “Mambacurial”</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
@@ -6896,23 +6830,23 @@
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low</t>
+          <t>APB x Air Jordan 11 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="36" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>250</v>
+        <v>122</v>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6924,109 +6858,109 @@
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo” 2026</t>
+          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="31" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="D8" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 “Laser”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="36" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C9" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D9" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D9" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One "Green Camo"</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="31" t="n">
-        <v>46283</v>
+        <v>46291</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>250</v>
+        <v>155</v>
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D10" s="42" t="inlineStr">
+      <c r="D10" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Green Camo”</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="36" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D11" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D11" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
@@ -7036,79 +6970,79 @@
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="31" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C12" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="36" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>122</v>
+        <v>255</v>
       </c>
       <c r="C13" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D13" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D13" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="31" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D14" s="42" t="inlineStr">
+      <c r="D14" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7120,72 +7054,70 @@
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>225</v>
-      </c>
-      <c r="C15" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D15" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="31" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B16" s="33" t="n">
-        <v>205</v>
-      </c>
+        <v>46291</v>
+      </c>
+      <c r="B16" s="33" t="inlineStr"/>
       <c r="C16" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D16" s="42" t="inlineStr">
+      <c r="D16" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="C17" s="40" t="inlineStr">
         <is>
@@ -7204,7 +7136,7 @@
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7180,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D19" s="43" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7269,35 +7201,35 @@
         <v>46291</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D20" s="42" t="inlineStr">
+      <c r="D20" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="36" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C21" s="40" t="inlineStr">
         <is>
@@ -7316,23 +7248,23 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D22" s="42" t="inlineStr">
+      <c r="D22" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7344,23 +7276,21 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="36" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B23" s="41" t="n">
-        <v>200</v>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="B23" s="41" t="inlineStr"/>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="43" t="inlineStr">
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7372,23 +7302,23 @@
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D24" s="42" t="inlineStr">
+      <c r="D24" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7400,23 +7330,25 @@
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="36" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B25" s="41" t="inlineStr"/>
+        <v>46295</v>
+      </c>
+      <c r="B25" s="41" t="n">
+        <v>135</v>
+      </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D25" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D25" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
@@ -7426,13 +7358,13 @@
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B26" s="33" t="n">
         <v>210</v>
@@ -7442,147 +7374,149 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D26" s="42" t="inlineStr">
+      <c r="D26" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="36" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D27" s="43" t="inlineStr">
+      <c r="D27" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Nike Kobe Air Force 1 Low</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="31" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D28" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D28" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="36" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B29" s="41" t="inlineStr"/>
+        <v>46298</v>
+      </c>
+      <c r="B29" s="41" t="n">
+        <v>240</v>
+      </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D29" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D29" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="31" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="C30" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D30" s="42" t="inlineStr">
+      <c r="D30" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="36" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="C31" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D31" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D31" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -7592,25 +7526,25 @@
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="n">
-        <v>46296</v>
+        <v>46305</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D32" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D32" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
@@ -7620,13 +7554,13 @@
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Howard” 2026</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="36" t="n">
-        <v>46296</v>
+        <v>46310</v>
       </c>
       <c r="B33" s="41" t="n">
         <v>125</v>
@@ -7636,9 +7570,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D33" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
@@ -7648,69 +7582,69 @@
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="31" t="n">
-        <v>46297</v>
+        <v>46311</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C34" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D34" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D34" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>46298</v>
+        <v>46311</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D35" s="43" t="inlineStr">
+      <c r="D35" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="31" t="n">
-        <v>46298</v>
+        <v>46311</v>
       </c>
       <c r="B36" s="33" t="n">
         <v>240</v>
@@ -7720,35 +7654,35 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D36" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D36" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C37" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D37" s="43" t="inlineStr">
+      <c r="D37" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7760,23 +7694,23 @@
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="31" t="n">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="C38" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D38" s="42" t="inlineStr">
+      <c r="D38" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7788,51 +7722,51 @@
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="B39" s="41" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C39" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D39" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D39" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="C40" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D40" s="42" t="inlineStr">
+      <c r="D40" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7844,23 +7778,23 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Nike Air Force 1 Low “NYC Rat”</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="36" t="n">
-        <v>46311</v>
+        <v>46319</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D41" s="43" t="inlineStr">
+      <c r="D41" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7872,23 +7806,23 @@
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="31" t="n">
-        <v>46311</v>
+        <v>46319</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>240</v>
+        <v>125</v>
       </c>
       <c r="C42" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D42" s="42" t="inlineStr">
+      <c r="D42" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7900,79 +7834,79 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="36" t="n">
-        <v>46311</v>
+        <v>46319</v>
       </c>
       <c r="B43" s="41" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="C43" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D43" s="43" t="inlineStr">
+      <c r="D43" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="31" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D44" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E44" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>46312</v>
+        <v>46320</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D45" s="43" t="inlineStr">
+      <c r="D45" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7984,51 +7918,51 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="31" t="n">
-        <v>46319</v>
+        <v>46326</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D46" s="42" t="inlineStr">
+      <c r="D46" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="36" t="n">
-        <v>46319</v>
+        <v>46329</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D47" s="43" t="inlineStr">
+      <c r="D47" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8040,25 +7974,25 @@
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="31" t="n">
-        <v>46319</v>
+        <v>46333</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D48" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
@@ -8068,53 +8002,53 @@
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="36" t="n">
-        <v>46319</v>
+        <v>46333</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D49" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D49" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="31" t="n">
-        <v>46320</v>
+        <v>46333</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>205</v>
+        <v>245</v>
       </c>
       <c r="C50" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D50" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D50" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E50" s="30" t="inlineStr">
@@ -8124,51 +8058,51 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46326</v>
+        <v>46335</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D51" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D51" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="31" t="n">
-        <v>46329</v>
+        <v>46337</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D52" s="42" t="inlineStr">
+      <c r="D52" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8180,25 +8114,25 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="36" t="n">
-        <v>46333</v>
+        <v>46337</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D53" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
@@ -8208,16 +8142,16 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="31" t="n">
-        <v>46333</v>
+        <v>46340</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
@@ -8236,25 +8170,25 @@
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46333</v>
+        <v>46342</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>215</v>
+        <v>255</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D55" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D55" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
@@ -8264,25 +8198,25 @@
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46335</v>
+        <v>46343</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C56" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D56" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D56" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
@@ -8292,109 +8226,109 @@
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46337</v>
+        <v>46347</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C57" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D57" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D57" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="31" t="n">
-        <v>46337</v>
+        <v>46347</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C58" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D58" s="42" t="inlineStr">
+      <c r="D58" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46340</v>
+        <v>46347</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D59" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D59" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46342</v>
+        <v>46347</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>255</v>
+        <v>165</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D60" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D60" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E60" s="30" t="inlineStr">
@@ -8404,23 +8338,23 @@
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46343</v>
+        <v>46347</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D61" s="43" t="inlineStr">
+      <c r="D61" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8432,53 +8366,53 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>125</v>
+        <v>230</v>
       </c>
       <c r="C62" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D62" s="42" t="inlineStr">
+      <c r="D62" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="36" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D63" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D63" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
@@ -8488,137 +8422,133 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="31" t="n">
-        <v>46347</v>
+        <v>46354</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>215</v>
+        <v>130</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D64" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="36" t="n">
-        <v>46347</v>
-      </c>
-      <c r="B65" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C65" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D65" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>46354</v>
+      </c>
+      <c r="B65" s="41" t="inlineStr"/>
+      <c r="C65" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D65" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46347</v>
+        <v>46354</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D66" s="42" t="inlineStr">
+      <c r="D66" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46353</v>
-      </c>
-      <c r="B67" s="41" t="n">
-        <v>230</v>
-      </c>
+        <v>46354</v>
+      </c>
+      <c r="B67" s="41" t="inlineStr"/>
       <c r="C67" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D67" s="43" t="inlineStr">
+      <c r="D67" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D68" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D68" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
@@ -8628,13 +8558,13 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46354</v>
+        <v>46361</v>
       </c>
       <c r="B69" s="41" t="inlineStr"/>
       <c r="C69" s="40" t="inlineStr">
@@ -8642,57 +8572,55 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D69" s="43" t="inlineStr">
+      <c r="D69" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46354</v>
+        <v>46361</v>
       </c>
       <c r="B70" s="33" t="n">
-        <v>120</v>
+        <v>215</v>
       </c>
       <c r="C70" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D70" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D70" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B71" s="41" t="n">
-        <v>130</v>
-      </c>
+        <v>46367</v>
+      </c>
+      <c r="B71" s="41" t="inlineStr"/>
       <c r="C71" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -8705,23 +8633,25 @@
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B72" s="33" t="inlineStr"/>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
+        <v>46367</v>
+      </c>
+      <c r="B72" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="C72" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D72" s="34" t="inlineStr">
@@ -8736,23 +8666,23 @@
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46354</v>
+        <v>46367</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D73" s="43" t="inlineStr">
+      <c r="D73" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8764,49 +8694,51 @@
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B74" s="33" t="inlineStr"/>
+        <v>46367</v>
+      </c>
+      <c r="B74" s="33" t="n">
+        <v>190</v>
+      </c>
       <c r="C74" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D74" s="42" t="inlineStr">
+      <c r="D74" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46361</v>
+        <v>46368</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="C75" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D75" s="43" t="inlineStr">
+      <c r="D75" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8818,150 +8750,12 @@
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="31" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B76" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C76" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D76" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite One “Floral” 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B77" s="41" t="inlineStr"/>
-      <c r="C77" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D77" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
-        </is>
-      </c>
-      <c r="E77" s="35" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F77" s="35" t="inlineStr">
-        <is>
-          <t>Free The Youth x Air Jordan 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="31" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B78" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C78" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D78" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B79" s="41" t="n">
-        <v>190</v>
-      </c>
-      <c r="C79" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D79" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E79" s="35" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="F79" s="35" t="inlineStr">
-        <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="31" t="n">
-        <v>46368</v>
-      </c>
-      <c r="B80" s="33" t="n">
-        <v>235</v>
-      </c>
-      <c r="C80" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D80" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E80" s="30" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F80" s="30" t="inlineStr">
-        <is>
           <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F80"/>
+  <autoFilter ref="A3:F75"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High Hype Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$142</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -685,7 +685,7 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1581,7 +1581,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 19, 2026  ·  10:30 UTC</t>
+          <t>Generated September 20, 2026  ·  10:51 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1621,15 +1621,15 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="18" t="inlineStr">
@@ -1737,7 +1737,7 @@
         <v>46290</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46295</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1825,19 +1825,19 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E13" s="40" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>7</v>
       </c>
       <c r="G13" s="41" t="n">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="H13" s="42" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="C14" s="31" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>7</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H14" s="43" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>7</v>
       </c>
       <c r="G15" s="41" t="n">
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="H15" s="38" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="C16" s="31" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>7</v>
       </c>
       <c r="G16" s="33" t="n">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="H16" s="43" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B20" s="30" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="B21" s="35" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="E21" s="35" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G21" s="47" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="B22" s="30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="E23" s="35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="B31" s="30" t="inlineStr">
         <is>
-          <t>9/19 – 9/25</t>
+          <t>9/20 – 9/26</t>
         </is>
       </c>
       <c r="C31" s="30" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D31" s="39" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E31" s="30" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -2212,14 +2212,14 @@
       </c>
       <c r="B32" s="35" t="inlineStr">
         <is>
-          <t>9/26 – 10/2</t>
+          <t>9/27 – 10/3</t>
         </is>
       </c>
       <c r="C32" s="35" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D32" s="40" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E32" s="35" t="n">
         <v>5.9</v>
@@ -2233,17 +2233,17 @@
       </c>
       <c r="B33" s="30" t="inlineStr">
         <is>
-          <t>10/3 – 10/9</t>
+          <t>10/4 – 10/10</t>
         </is>
       </c>
       <c r="C33" s="30" t="n">
         <v>7</v>
       </c>
       <c r="D33" s="39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="30" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
@@ -2254,17 +2254,17 @@
       </c>
       <c r="B34" s="35" t="inlineStr">
         <is>
-          <t>10/10 – 10/16</t>
+          <t>10/11 – 10/17</t>
         </is>
       </c>
       <c r="C34" s="35" t="n">
         <v>8</v>
       </c>
       <c r="D34" s="40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E34" s="35" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -2275,17 +2275,17 @@
       </c>
       <c r="B35" s="30" t="inlineStr">
         <is>
-          <t>10/17 – 10/23</t>
+          <t>10/18 – 10/24</t>
         </is>
       </c>
       <c r="C35" s="30" t="n">
+        <v>11</v>
+      </c>
+      <c r="D35" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="D35" s="39" t="n">
-        <v>3</v>
-      </c>
       <c r="E35" s="30" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -2296,14 +2296,14 @@
       </c>
       <c r="B36" s="35" t="inlineStr">
         <is>
-          <t>10/24 – 10/30</t>
+          <t>10/25 – 10/31</t>
         </is>
       </c>
       <c r="C36" s="35" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D36" s="40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E36" s="35" t="n">
         <v>5.2</v>
@@ -2317,17 +2317,17 @@
       </c>
       <c r="B37" s="30" t="inlineStr">
         <is>
-          <t>10/31 – 11/6</t>
+          <t>11/1 – 11/7</t>
         </is>
       </c>
       <c r="C37" s="30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D37" s="39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="30" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
@@ -2338,17 +2338,17 @@
       </c>
       <c r="B38" s="35" t="inlineStr">
         <is>
-          <t>11/7 – 11/13</t>
+          <t>11/8 – 11/14</t>
         </is>
       </c>
       <c r="C38" s="35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D38" s="40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E38" s="35" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="B39" s="30" t="inlineStr">
         <is>
-          <t>11/14 – 11/20</t>
+          <t>11/15 – 11/21</t>
         </is>
       </c>
       <c r="C39" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="D39" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="D39" s="39" t="n">
-        <v>3</v>
-      </c>
       <c r="E39" s="30" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>11/21 – 11/27</t>
+          <t>11/22 – 11/28</t>
         </is>
       </c>
       <c r="C40" s="35" t="n">
@@ -2390,7 +2390,7 @@
         <v>7</v>
       </c>
       <c r="E40" s="35" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -2401,17 +2401,17 @@
       </c>
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>11/28 – 12/4</t>
+          <t>11/29 – 12/5</t>
         </is>
       </c>
       <c r="C41" s="30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D41" s="39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E41" s="30" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
@@ -2422,17 +2422,17 @@
       </c>
       <c r="B42" s="35" t="inlineStr">
         <is>
-          <t>12/5 – 12/11</t>
+          <t>12/6 – 12/12</t>
         </is>
       </c>
       <c r="C42" s="35" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D42" s="40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42" s="35" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
@@ -2443,17 +2443,17 @@
       </c>
       <c r="B43" s="30" t="inlineStr">
         <is>
-          <t>12/12 – 12/18</t>
+          <t>12/13 – 12/19</t>
         </is>
       </c>
       <c r="C43" s="30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="30" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -2732,7 +2732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2758,7 +2758,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 19, 2026  ·  10:30 UTC</t>
+          <t>Generated September 20, 2026  ·  10:51 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2801,10 +2801,10 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="C4" s="48" t="inlineStr">
         <is>
@@ -2818,25 +2818,25 @@
       </c>
       <c r="E4" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 9 OG “Space Jam” 2026</t>
+          <t>PSG x Nike KD 6 "Metallic Silver"</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46284</v>
+        <v>46287</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>110</v>
-      </c>
-      <c r="C5" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>210</v>
+      </c>
+      <c r="C5" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
@@ -2846,25 +2846,25 @@
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Pokémon x adidas 30th Anniversary Collection</t>
+          <t>Nike GT Future “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="n">
-        <v>46284</v>
+        <v>46288</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>122</v>
-      </c>
-      <c r="C6" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>210</v>
+      </c>
+      <c r="C6" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D6" s="43" t="inlineStr">
@@ -2879,20 +2879,20 @@
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>Nike GT Future “Unseen Hours”</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="36" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>140</v>
+      </c>
+      <c r="C7" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D7" s="42" t="inlineStr">
@@ -2902,53 +2902,53 @@
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>Converse SHAI 001 “Green Beam”</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="31" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C8" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D8" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C8" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>Converse SHAI 001 “Ghosted”</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="36" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C9" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>140</v>
+      </c>
+      <c r="C9" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D9" s="42" t="inlineStr">
@@ -2958,25 +2958,25 @@
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 9 OG "Space Jam"</t>
+          <t>Converse SHAI 001 Shroud “Shock”</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="31" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>122</v>
-      </c>
-      <c r="C10" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>140</v>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D10" s="43" t="inlineStr">
@@ -2986,21 +2986,21 @@
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
+          <t>Converse SHAI 001 “Spark”</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="36" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="C11" s="53" t="inlineStr">
         <is>
@@ -3019,48 +3019,48 @@
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Ope Ope”</t>
+          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="31" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C12" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Nike GT Future “Varsity Red”</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="36" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C13" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>205</v>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D13" s="42" t="inlineStr">
@@ -3070,21 +3070,21 @@
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Nike GT Future “Unseen Hours”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="31" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C14" s="54" t="inlineStr">
         <is>
@@ -3098,25 +3098,25 @@
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Ghosted”</t>
+          <t>Billionaire Boys Club x Reebok Club C 85</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="36" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B15" s="41" t="n">
         <v>140</v>
       </c>
-      <c r="C15" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C15" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D15" s="42" t="inlineStr">
@@ -3126,25 +3126,25 @@
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Green Beam”</t>
+          <t>Nike Ja 4 “Jaws”</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="31" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C16" s="54" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>185</v>
+      </c>
+      <c r="C16" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D16" s="43" t="inlineStr">
@@ -3154,25 +3154,25 @@
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 Shroud “Shock”</t>
+          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="36" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C17" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>210</v>
+      </c>
+      <c r="C17" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D17" s="42" t="inlineStr">
@@ -3182,53 +3182,53 @@
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Spark”</t>
+          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C18" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D18" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>155</v>
+      </c>
+      <c r="C18" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>120</v>
-      </c>
-      <c r="C19" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>210</v>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D19" s="42" t="inlineStr">
@@ -3238,81 +3238,81 @@
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Billionaire Boys Club x Reebok Club C 85</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C20" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D20" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>225</v>
-      </c>
-      <c r="C21" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D21" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>160</v>
+      </c>
+      <c r="C21" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C22" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>200</v>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D22" s="43" t="inlineStr">
@@ -3327,25 +3327,25 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws”</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="C23" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D23" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D23" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
@@ -3355,20 +3355,20 @@
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C24" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>140</v>
+      </c>
+      <c r="C24" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D24" s="43" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -3392,26 +3392,26 @@
         <v>46291</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C25" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D25" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C25" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D25" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
@@ -3419,17 +3419,15 @@
       <c r="A26" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B26" s="33" t="n">
-        <v>150</v>
-      </c>
+      <c r="B26" s="33" t="inlineStr"/>
       <c r="C26" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D26" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D26" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
@@ -3439,7 +3437,7 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -3447,25 +3445,27 @@
       <c r="A27" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B27" s="41" t="inlineStr"/>
-      <c r="C27" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D27" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B27" s="41" t="n">
+        <v>180</v>
+      </c>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D27" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -3474,11 +3474,11 @@
         <v>46291</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C28" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>210</v>
+      </c>
+      <c r="C28" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -3502,16 +3502,16 @@
         <v>46291</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C29" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D29" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>200</v>
+      </c>
+      <c r="C29" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D29" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
         </is>
       </c>
     </row>
@@ -3530,16 +3530,16 @@
         <v>46291</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C30" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D30" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -3558,11 +3558,11 @@
         <v>46291</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>160</v>
-      </c>
-      <c r="C31" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>155</v>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D31" s="42" t="inlineStr">
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -3586,16 +3586,16 @@
         <v>46291</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D32" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D32" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -3613,27 +3613,25 @@
       <c r="A33" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B33" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C33" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D33" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B33" s="41" t="inlineStr"/>
+      <c r="C33" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D33" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
@@ -3642,11 +3640,11 @@
         <v>46291</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C34" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>120</v>
+      </c>
+      <c r="C34" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D34" s="43" t="inlineStr">
@@ -3656,12 +3654,12 @@
       </c>
       <c r="E34" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
         </is>
       </c>
     </row>
@@ -3670,16 +3668,16 @@
         <v>46291</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C35" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D35" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
@@ -3689,18 +3687,18 @@
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="31" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="B36" s="33" t="inlineStr"/>
-      <c r="C36" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="C36" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D36" s="43" t="inlineStr">
@@ -3710,58 +3708,58 @@
       </c>
       <c r="E36" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C37" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D37" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C37" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D37" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="31" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C38" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D38" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>249</v>
+      </c>
+      <c r="C38" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E38" s="30" t="inlineStr">
@@ -3771,25 +3769,25 @@
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Hyperice x Nike Air Zoom Hyperslide</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="B39" s="41" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="C39" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D39" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D39" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
@@ -3799,48 +3797,48 @@
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
+          <t>Nike Air Bakin “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C40" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D40" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="36" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>120</v>
-      </c>
-      <c r="C41" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>125</v>
+      </c>
+      <c r="C41" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D41" s="42" t="inlineStr">
@@ -3850,22 +3848,20 @@
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="31" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B42" s="33" t="n">
-        <v>210</v>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="B42" s="33" t="inlineStr"/>
       <c r="C42" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -3883,46 +3879,48 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="36" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B43" s="41" t="inlineStr"/>
+        <v>46295</v>
+      </c>
+      <c r="B43" s="41" t="n">
+        <v>130</v>
+      </c>
       <c r="C43" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D43" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D43" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
+          <t>MoMA x Nike Air Rift 2 Pack</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="31" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C44" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>155</v>
+      </c>
+      <c r="C44" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D44" s="43" t="inlineStr">
@@ -3937,16 +3935,16 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>249</v>
+        <v>200</v>
       </c>
       <c r="C45" s="53" t="inlineStr">
         <is>
@@ -3965,25 +3963,25 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Hyperice x Nike Air Zoom Hyperslide</t>
+          <t>Nike Zoom Huarache 2K4 “UCLA”</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="31" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C46" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D46" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>135</v>
+      </c>
+      <c r="C46" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
@@ -3993,7 +3991,7 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Red”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -4002,65 +4000,67 @@
         <v>46295</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D47" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D47" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="31" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D48" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Air Jordan 1 Low OG “Howard” 2026</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="36" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B49" s="41" t="inlineStr"/>
-      <c r="C49" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46296</v>
+      </c>
+      <c r="B49" s="41" t="n">
+        <v>140</v>
+      </c>
+      <c r="C49" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D49" s="42" t="inlineStr">
@@ -4075,25 +4075,25 @@
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Nike Caitlin 1 “Racer Blue”</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="31" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C50" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D50" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>125</v>
+      </c>
+      <c r="C50" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D50" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E50" s="30" t="inlineStr">
@@ -4103,100 +4103,100 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>MoMA x Nike Air Rift 2 Pack</t>
+          <t>Nike Kobe Air Force 1 Low</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D51" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D51" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="31" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C52" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D52" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>240</v>
+      </c>
+      <c r="C52" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D52" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Nike Zoom Huarache 2K4 “UCLA”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="36" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>135</v>
+        <v>205</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D53" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="31" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
@@ -4210,25 +4210,25 @@
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C55" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C55" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D55" s="42" t="inlineStr">
@@ -4238,51 +4238,53 @@
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Racer Blue”</t>
+          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B56" s="33" t="inlineStr"/>
+        <v>46304</v>
+      </c>
+      <c r="B56" s="33" t="n">
+        <v>170</v>
+      </c>
       <c r="C56" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D56" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D56" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan “Black Pack”</t>
+          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46296</v>
+        <v>46304</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C57" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>130</v>
+      </c>
+      <c r="C57" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D57" s="42" t="inlineStr">
@@ -4292,77 +4294,77 @@
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low</t>
+          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="31" t="n">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="B58" s="33" t="n">
         <v>220</v>
       </c>
-      <c r="C58" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D58" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C58" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D58" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Aminé x New Balance 992 “Outdoor School”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C59" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D59" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>135</v>
+      </c>
+      <c r="C59" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D59" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Nike KD 6 “Texas”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
@@ -4381,25 +4383,25 @@
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46300</v>
+        <v>46310</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D61" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D61" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
@@ -4409,20 +4411,20 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C62" s="54" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>125</v>
+      </c>
+      <c r="C62" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D62" s="43" t="inlineStr">
@@ -4432,25 +4434,25 @@
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="36" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C63" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>240</v>
+      </c>
+      <c r="C63" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D63" s="42" t="inlineStr">
@@ -4460,25 +4462,25 @@
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="31" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C64" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>250</v>
+      </c>
+      <c r="C64" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D64" s="43" t="inlineStr">
@@ -4493,20 +4495,20 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="36" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>220</v>
-      </c>
-      <c r="C65" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>240</v>
+      </c>
+      <c r="C65" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D65" s="42" t="inlineStr">
@@ -4516,21 +4518,21 @@
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Aminé x New Balance 992 “Outdoor School”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
@@ -4544,25 +4546,25 @@
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>135</v>
-      </c>
-      <c r="C67" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>220</v>
+      </c>
+      <c r="C67" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D67" s="42" t="inlineStr">
@@ -4572,25 +4574,25 @@
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Texas”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46310</v>
+        <v>46312</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C68" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>215</v>
+      </c>
+      <c r="C68" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D68" s="43" t="inlineStr">
@@ -4605,48 +4607,46 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="B69" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C69" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D69" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>160</v>
+      </c>
+      <c r="C69" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D69" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Reebok Angel Reese 1 “Reese’s”</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B70" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C70" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46317</v>
+      </c>
+      <c r="B70" s="33" t="inlineStr"/>
+      <c r="C70" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D70" s="43" t="inlineStr">
@@ -4656,21 +4656,21 @@
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>SZA x Vans VANSZA Collection</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
@@ -4689,16 +4689,16 @@
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Air Force 1 Low “NYC Rat”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46311</v>
+        <v>46319</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="C72" s="39" t="inlineStr">
         <is>
@@ -4717,16 +4717,16 @@
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46311</v>
+        <v>46319</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
@@ -4745,16 +4745,16 @@
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>220</v>
+        <v>125</v>
       </c>
       <c r="C74" s="39" t="inlineStr">
         <is>
@@ -4773,20 +4773,20 @@
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C75" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>140</v>
+      </c>
+      <c r="C75" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D75" s="42" t="inlineStr">
@@ -4796,21 +4796,21 @@
       </c>
       <c r="E75" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="31" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="B76" s="33" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="C76" s="54" t="inlineStr">
         <is>
@@ -4824,56 +4824,58 @@
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 “Reese’s”</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="36" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B77" s="41" t="inlineStr"/>
-      <c r="C77" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D77" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>46319</v>
+      </c>
+      <c r="B77" s="41" t="n">
+        <v>150</v>
+      </c>
+      <c r="C77" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D77" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>SZA x Vans VANSZA Collection</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="31" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C78" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D78" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>170</v>
+      </c>
+      <c r="C78" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D78" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E78" s="30" t="inlineStr">
@@ -4883,7 +4885,7 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “NYC Rat”</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
@@ -4892,11 +4894,11 @@
         <v>46319</v>
       </c>
       <c r="B79" s="41" t="n">
-        <v>190</v>
-      </c>
-      <c r="C79" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>145</v>
+      </c>
+      <c r="C79" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D79" s="42" t="inlineStr">
@@ -4911,16 +4913,16 @@
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="31" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B80" s="33" t="n">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="C80" s="39" t="inlineStr">
         <is>
@@ -4934,25 +4936,25 @@
       </c>
       <c r="E80" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="36" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="B81" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C81" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>155</v>
+      </c>
+      <c r="C81" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D81" s="42" t="inlineStr">
@@ -4962,30 +4964,30 @@
       </c>
       <c r="E81" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F81" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="31" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="B82" s="33" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="C82" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D82" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D82" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E82" s="30" t="inlineStr">
@@ -4995,20 +4997,20 @@
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Nike Ja 4 High “University Red”</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="36" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="B83" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C83" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>155</v>
+      </c>
+      <c r="C83" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D83" s="42" t="inlineStr">
@@ -5018,58 +5020,58 @@
       </c>
       <c r="E83" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F83" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>Nike Book 2 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="31" t="n">
-        <v>46319</v>
+        <v>46326</v>
       </c>
       <c r="B84" s="33" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C84" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D84" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D84" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="36" t="n">
-        <v>46319</v>
+        <v>46331</v>
       </c>
       <c r="B85" s="41" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="C85" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D85" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D85" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E85" s="35" t="inlineStr">
@@ -5079,16 +5081,16 @@
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="31" t="n">
-        <v>46319</v>
+        <v>46331</v>
       </c>
       <c r="B86" s="33" t="n">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="C86" s="48" t="inlineStr">
         <is>
@@ -5107,20 +5109,20 @@
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="36" t="n">
-        <v>46320</v>
+        <v>46331</v>
       </c>
       <c r="B87" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C87" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>265</v>
+      </c>
+      <c r="C87" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D87" s="42" t="inlineStr">
@@ -5130,21 +5132,21 @@
       </c>
       <c r="E87" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Nike Air Max Foamdome “Eggplant”</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="31" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="B88" s="33" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C88" s="48" t="inlineStr">
         <is>
@@ -5163,20 +5165,20 @@
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
+          <t>Nike Book 2 “Desert Night”</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="36" t="n">
-        <v>46325</v>
+        <v>46333</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C89" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>240</v>
+      </c>
+      <c r="C89" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D89" s="38" t="inlineStr">
@@ -5186,25 +5188,25 @@
       </c>
       <c r="E89" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 High “University Red”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="31" t="n">
-        <v>46325</v>
+        <v>46333</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C90" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>215</v>
+      </c>
+      <c r="C90" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D90" s="43" t="inlineStr">
@@ -5214,30 +5216,30 @@
       </c>
       <c r="E90" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Halloween”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="36" t="n">
-        <v>46326</v>
+        <v>46333</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="C91" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D91" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D91" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E91" s="35" t="inlineStr">
@@ -5247,13 +5249,13 @@
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="31" t="n">
-        <v>46329</v>
+        <v>46335</v>
       </c>
       <c r="B92" s="33" t="n">
         <v>240</v>
@@ -5263,9 +5265,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D92" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D92" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E92" s="30" t="inlineStr">
@@ -5275,20 +5277,20 @@
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="36" t="n">
-        <v>46331</v>
+        <v>46337</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C93" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>200</v>
+      </c>
+      <c r="C93" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D93" s="42" t="inlineStr">
@@ -5303,20 +5305,20 @@
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="31" t="n">
-        <v>46331</v>
+        <v>46337</v>
       </c>
       <c r="B94" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C94" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>235</v>
+      </c>
+      <c r="C94" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D94" s="43" t="inlineStr">
@@ -5326,30 +5328,30 @@
       </c>
       <c r="E94" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="36" t="n">
-        <v>46332</v>
+        <v>46338</v>
       </c>
       <c r="B95" s="41" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C95" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D95" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D95" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E95" s="35" t="inlineStr">
@@ -5359,48 +5361,48 @@
       </c>
       <c r="F95" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Desert Night”</t>
+          <t>Nike Air Bakin “Varsity Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="31" t="n">
-        <v>46333</v>
+        <v>46338</v>
       </c>
       <c r="B96" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C96" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D96" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C96" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D96" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E96" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="36" t="n">
-        <v>46333</v>
+        <v>46338</v>
       </c>
       <c r="B97" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C97" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>170</v>
+      </c>
+      <c r="C97" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D97" s="42" t="inlineStr">
@@ -5410,58 +5412,58 @@
       </c>
       <c r="E97" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F97" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Air Bakin “Varsity Royal”</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="31" t="n">
-        <v>46333</v>
+        <v>46339</v>
       </c>
       <c r="B98" s="33" t="n">
-        <v>245</v>
-      </c>
-      <c r="C98" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D98" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C98" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D98" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E98" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Nike Air Diamond Turf 2 Patent “Black Red”</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="36" t="n">
-        <v>46335</v>
+        <v>46339</v>
       </c>
       <c r="B99" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C99" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D99" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C99" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D99" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E99" s="35" t="inlineStr">
@@ -5471,53 +5473,53 @@
       </c>
       <c r="F99" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Nike Air Diamond Turf 2</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="31" t="n">
-        <v>46337</v>
+        <v>46340</v>
       </c>
       <c r="B100" s="33" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C100" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D100" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D100" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E100" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="36" t="n">
-        <v>46337</v>
+        <v>46340</v>
       </c>
       <c r="B101" s="41" t="n">
-        <v>235</v>
-      </c>
-      <c r="C101" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D101" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>240</v>
+      </c>
+      <c r="C101" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D101" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E101" s="35" t="inlineStr">
@@ -5527,16 +5529,16 @@
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="31" t="n">
-        <v>46338</v>
+        <v>46341</v>
       </c>
       <c r="B102" s="33" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C102" s="48" t="inlineStr">
         <is>
@@ -5555,48 +5557,48 @@
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal” 2026</t>
+          <t>Playa Society x Nike A’Two</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="36" t="n">
-        <v>46338</v>
+        <v>46342</v>
       </c>
       <c r="B103" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C103" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D103" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C103" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D103" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E103" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F103" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="31" t="n">
-        <v>46338</v>
+        <v>46342</v>
       </c>
       <c r="B104" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C104" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>230</v>
+      </c>
+      <c r="C104" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D104" s="43" t="inlineStr">
@@ -5611,20 +5613,20 @@
       </c>
       <c r="F104" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="36" t="n">
-        <v>46339</v>
+        <v>46343</v>
       </c>
       <c r="B105" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C105" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>200</v>
+      </c>
+      <c r="C105" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D105" s="42" t="inlineStr">
@@ -5639,20 +5641,20 @@
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Diamond Turf 2 Patent “Black Red”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="31" t="n">
-        <v>46339</v>
+        <v>46345</v>
       </c>
       <c r="B106" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C106" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C106" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D106" s="43" t="inlineStr">
@@ -5662,137 +5664,135 @@
       </c>
       <c r="E106" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F106" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Diamond Turf 2</t>
+          <t>Vans Old Skool 36 Pearlized “Navy”</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="36" t="n">
-        <v>46340</v>
+        <v>46346</v>
       </c>
       <c r="B107" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C107" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D107" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>145</v>
+      </c>
+      <c r="C107" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D107" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E107" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F107" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Book 2 “Be Legendary”</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="31" t="n">
-        <v>46340</v>
+        <v>46346</v>
       </c>
       <c r="B108" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C108" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D108" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C108" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D108" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E108" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F108" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
+          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
         </is>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="36" t="n">
-        <v>46341</v>
+        <v>46347</v>
       </c>
       <c r="B109" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C109" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D109" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>215</v>
+      </c>
+      <c r="C109" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D109" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E109" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>Playa Society x Nike A’Two</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="31" t="n">
-        <v>46342</v>
+        <v>46347</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="C110" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D110" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D110" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E110" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="36" t="n">
-        <v>46343</v>
-      </c>
-      <c r="B111" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C111" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46347</v>
+      </c>
+      <c r="B111" s="41" t="inlineStr"/>
+      <c r="C111" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D111" s="42" t="inlineStr">
@@ -5802,25 +5802,25 @@
       </c>
       <c r="E111" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
         </is>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="31" t="n">
-        <v>46345</v>
+        <v>46347</v>
       </c>
       <c r="B112" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C112" s="54" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>165</v>
+      </c>
+      <c r="C112" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D112" s="43" t="inlineStr">
@@ -5830,25 +5830,25 @@
       </c>
       <c r="E112" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F112" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Navy”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="36" t="n">
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="B113" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C113" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>125</v>
+      </c>
+      <c r="C113" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D113" s="42" t="inlineStr">
@@ -5863,20 +5863,20 @@
       </c>
       <c r="F113" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Be Legendary”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="31" t="n">
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="B114" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C114" s="54" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>140</v>
+      </c>
+      <c r="C114" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D114" s="43" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="E114" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F114" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
@@ -5900,16 +5900,16 @@
         <v>46347</v>
       </c>
       <c r="B115" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C115" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D115" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>230</v>
+      </c>
+      <c r="C115" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D115" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E115" s="35" t="inlineStr">
@@ -5919,25 +5919,25 @@
       </c>
       <c r="F115" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Snow White”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="31" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B116" s="33" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C116" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D116" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D116" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E116" s="30" t="inlineStr">
@@ -5947,16 +5947,16 @@
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="36" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B117" s="41" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C117" s="40" t="inlineStr">
         <is>
@@ -5975,20 +5975,20 @@
       </c>
       <c r="F117" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="31" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B118" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C118" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>130</v>
+      </c>
+      <c r="C118" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D118" s="43" t="inlineStr">
@@ -5998,23 +5998,23 @@
       </c>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F118" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Vans Old Skool 36 Pearlized “Black”</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="36" t="n">
-        <v>46347</v>
+        <v>46354</v>
       </c>
       <c r="B119" s="41" t="inlineStr"/>
-      <c r="C119" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C119" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D119" s="42" t="inlineStr">
@@ -6024,30 +6024,28 @@
       </c>
       <c r="E119" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
+          <t>Nike KD 6 “Aunt Pearl” 2026</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="31" t="n">
-        <v>46347</v>
-      </c>
-      <c r="B120" s="33" t="n">
-        <v>165</v>
-      </c>
-      <c r="C120" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D120" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>46354</v>
+      </c>
+      <c r="B120" s="33" t="inlineStr"/>
+      <c r="C120" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D120" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E120" s="30" t="inlineStr">
@@ -6057,16 +6055,16 @@
       </c>
       <c r="F120" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="36" t="n">
-        <v>46347</v>
+        <v>46354</v>
       </c>
       <c r="B121" s="41" t="n">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="C121" s="40" t="inlineStr">
         <is>
@@ -6085,20 +6083,20 @@
       </c>
       <c r="F121" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="A122" s="31" t="n">
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="B122" s="33" t="n">
-        <v>230</v>
-      </c>
-      <c r="C122" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>140</v>
+      </c>
+      <c r="C122" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D122" s="43" t="inlineStr">
@@ -6108,22 +6106,20 @@
       </c>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F122" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike Caitlin 1 “Warning Code”</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="36" t="n">
-        <v>46353</v>
-      </c>
-      <c r="B123" s="41" t="n">
-        <v>240</v>
-      </c>
+        <v>46354</v>
+      </c>
+      <c r="B123" s="41" t="inlineStr"/>
       <c r="C123" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6141,35 +6137,35 @@
       </c>
       <c r="F123" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1">
       <c r="A124" s="31" t="n">
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="B124" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C124" s="54" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D124" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>120</v>
+      </c>
+      <c r="C124" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D124" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E124" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F124" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Black”</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -6203,9 +6199,11 @@
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="31" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B126" s="33" t="inlineStr"/>
+        <v>46359</v>
+      </c>
+      <c r="B126" s="33" t="n">
+        <v>170</v>
+      </c>
       <c r="C126" s="48" t="inlineStr">
         <is>
           <t>MED</t>
@@ -6223,43 +6221,43 @@
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Aunt Pearl” 2026</t>
+          <t>Nike Air Bakin “Black/White”</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="36" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B127" s="41" t="inlineStr"/>
-      <c r="C127" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D127" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>46361</v>
+      </c>
+      <c r="B127" s="41" t="n">
+        <v>300</v>
+      </c>
+      <c r="C127" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D127" s="55" t="inlineStr">
+        <is>
+          <t>Confirmed App</t>
         </is>
       </c>
       <c r="E127" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Pharrell x adidas Adistar Jellyfish “Auburn Timber”</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" s="31" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B128" s="33" t="n">
-        <v>190</v>
-      </c>
+        <v>46361</v>
+      </c>
+      <c r="B128" s="33" t="inlineStr"/>
       <c r="C128" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6272,25 +6270,25 @@
       </c>
       <c r="E128" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F128" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="36" t="n">
-        <v>46354</v>
+        <v>46361</v>
       </c>
       <c r="B129" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C129" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>215</v>
+      </c>
+      <c r="C129" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D129" s="42" t="inlineStr">
@@ -6300,23 +6298,25 @@
       </c>
       <c r="E129" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F129" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Warning Code”</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" s="31" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B130" s="33" t="inlineStr"/>
-      <c r="C130" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46361</v>
+      </c>
+      <c r="B130" s="33" t="n">
+        <v>300</v>
+      </c>
+      <c r="C130" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D130" s="43" t="inlineStr">
@@ -6326,81 +6326,81 @@
       </c>
       <c r="E130" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F130" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1">
       <c r="A131" s="36" t="n">
-        <v>46354</v>
+        <v>46361</v>
       </c>
       <c r="B131" s="41" t="n">
-        <v>120</v>
-      </c>
-      <c r="C131" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D131" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>300</v>
+      </c>
+      <c r="C131" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D131" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E131" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F131" s="35" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Pharrell x adidas Adistar Jellyfish</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1">
       <c r="A132" s="31" t="n">
-        <v>46359</v>
+        <v>46367</v>
       </c>
       <c r="B132" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C132" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D132" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>150</v>
+      </c>
+      <c r="C132" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D132" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E132" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F132" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Black/White”</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1">
       <c r="A133" s="36" t="n">
-        <v>46361</v>
+        <v>46367</v>
       </c>
       <c r="B133" s="41" t="n">
-        <v>300</v>
-      </c>
-      <c r="C133" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>240</v>
+      </c>
+      <c r="C133" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D133" s="42" t="inlineStr">
@@ -6410,48 +6410,48 @@
       </c>
       <c r="E133" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F133" s="35" t="inlineStr">
         <is>
-          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
         </is>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="31" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B134" s="33" t="n">
-        <v>300</v>
-      </c>
-      <c r="C134" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D134" s="55" t="inlineStr">
-        <is>
-          <t>Confirmed App</t>
+        <v>46367</v>
+      </c>
+      <c r="B134" s="33" t="inlineStr"/>
+      <c r="C134" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D134" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E134" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F134" s="30" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish “Auburn Timber”</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c r="A135" s="36" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B135" s="41" t="inlineStr"/>
+        <v>46367</v>
+      </c>
+      <c r="B135" s="41" t="n">
+        <v>190</v>
+      </c>
       <c r="C135" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6464,21 +6464,21 @@
       </c>
       <c r="E135" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F135" s="35" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="31" t="n">
-        <v>46361</v>
+        <v>46368</v>
       </c>
       <c r="B136" s="33" t="n">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="C136" s="39" t="inlineStr">
         <is>
@@ -6497,16 +6497,16 @@
       </c>
       <c r="F136" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="36" t="n">
-        <v>46361</v>
+        <v>46375</v>
       </c>
       <c r="B137" s="41" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="C137" s="53" t="inlineStr">
         <is>
@@ -6520,28 +6520,30 @@
       </c>
       <c r="E137" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F137" s="35" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish</t>
+          <t>Nike GT Future “Triple Black”</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="A138" s="31" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B138" s="33" t="inlineStr"/>
+        <v>46375</v>
+      </c>
+      <c r="B138" s="33" t="n">
+        <v>220</v>
+      </c>
       <c r="C138" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D138" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D138" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E138" s="30" t="inlineStr">
@@ -6551,16 +6553,16 @@
       </c>
       <c r="F138" s="30" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Air Jordan 4 “Pink Thunder”</t>
         </is>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1">
       <c r="A139" s="36" t="n">
-        <v>46367</v>
+        <v>46375</v>
       </c>
       <c r="B139" s="41" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="C139" s="40" t="inlineStr">
         <is>
@@ -6574,25 +6576,25 @@
       </c>
       <c r="E139" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F139" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Fly Streetwear x Nike SB Air Force 1 Low “University Gold”</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" s="31" t="n">
-        <v>46367</v>
+        <v>46375</v>
       </c>
       <c r="B140" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C140" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>170</v>
+      </c>
+      <c r="C140" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D140" s="43" t="inlineStr">
@@ -6607,68 +6609,12 @@
       </c>
       <c r="F140" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Floral” 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="15" customHeight="1">
-      <c r="A141" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B141" s="41" t="n">
-        <v>190</v>
-      </c>
-      <c r="C141" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D141" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E141" s="35" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="F141" s="35" t="inlineStr">
-        <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="15" customHeight="1">
-      <c r="A142" s="31" t="n">
-        <v>46368</v>
-      </c>
-      <c r="B142" s="33" t="n">
-        <v>235</v>
-      </c>
-      <c r="C142" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D142" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E142" s="30" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F142" s="30" t="inlineStr">
-        <is>
-          <t>Air Jordan 11 “Space Jam” 2026</t>
+          <t>Nike Air Zoom Flight The Glove “Royal Blue”</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F142"/>
+  <autoFilter ref="A3:F140"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -6683,7 +6629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6709,7 +6655,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 19, 2026  ·  10:30 UTC</t>
+          <t>Generated September 20, 2026  ·  10:51 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -6752,38 +6698,38 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>122</v>
-      </c>
-      <c r="C4" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D4" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D4" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro GS “Mismatch”</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
@@ -6797,77 +6743,77 @@
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Mambacurial”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>APB x Air Jordan 11 Low Pack</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="36" t="n">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>122</v>
+        <v>255</v>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D7" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low “Mismatch” (GS)</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
@@ -6881,40 +6827,40 @@
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>225</v>
-      </c>
-      <c r="C9" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D9" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -6922,9 +6868,7 @@
       <c r="A10" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B10" s="33" t="n">
-        <v>155</v>
-      </c>
+      <c r="B10" s="33" t="inlineStr"/>
       <c r="C10" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6937,12 +6881,12 @@
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6895,7 @@
         <v>46291</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
@@ -6965,12 +6909,12 @@
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -6986,9 +6930,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
@@ -6998,7 +6942,7 @@
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -7007,16 +6951,16 @@
         <v>46291</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C13" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E13" s="35" t="inlineStr">
@@ -7026,7 +6970,7 @@
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -7035,7 +6979,7 @@
         <v>46291</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
@@ -7049,12 +6993,12 @@
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -7063,16 +7007,16 @@
         <v>46291</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C15" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D15" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D15" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
@@ -7082,7 +7026,7 @@
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7034,9 @@
       <c r="A16" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B16" s="33" t="inlineStr"/>
+      <c r="B16" s="33" t="n">
+        <v>210</v>
+      </c>
       <c r="C16" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -7108,13 +7054,13 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="36" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B17" s="41" t="n">
         <v>180</v>
@@ -7131,30 +7077,30 @@
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="C18" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
@@ -7164,17 +7110,15 @@
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="36" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B19" s="41" t="n">
-        <v>200</v>
-      </c>
+        <v>46295</v>
+      </c>
+      <c r="B19" s="41" t="inlineStr"/>
       <c r="C19" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -7187,21 +7131,21 @@
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
@@ -7220,7 +7164,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7173,7 @@
         <v>46295</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C21" s="40" t="inlineStr">
         <is>
@@ -7248,7 +7192,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7201,7 @@
         <v>46295</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
@@ -7271,47 +7215,49 @@
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="36" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B23" s="41" t="inlineStr"/>
+        <v>46296</v>
+      </c>
+      <c r="B23" s="41" t="n">
+        <v>155</v>
+      </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D23" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Air Jordan 1 Low OG “Howard” 2026</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="31" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
@@ -7330,16 +7276,16 @@
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Nike Kobe Air Force 1 Low</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="36" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>135</v>
+        <v>220</v>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
@@ -7353,30 +7299,30 @@
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="31" t="n">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="C26" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D26" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
@@ -7386,16 +7332,16 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="36" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
@@ -7409,58 +7355,58 @@
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="31" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D28" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D28" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="36" t="n">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D29" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D29" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -7470,44 +7416,44 @@
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="31" t="n">
-        <v>46298</v>
+        <v>46310</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="C30" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D30" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="36" t="n">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C31" s="40" t="inlineStr">
         <is>
@@ -7526,16 +7472,16 @@
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
@@ -7549,30 +7495,30 @@
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="36" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="C33" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D33" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D33" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
@@ -7582,7 +7528,7 @@
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7537,7 @@
         <v>46311</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C34" s="39" t="inlineStr">
         <is>
@@ -7610,16 +7556,16 @@
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
@@ -7633,21 +7579,21 @@
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="31" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B36" s="33" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C36" s="39" t="inlineStr">
         <is>
@@ -7661,21 +7607,21 @@
       </c>
       <c r="E36" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="C37" s="40" t="inlineStr">
         <is>
@@ -7694,16 +7640,16 @@
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Nike Air Force 1 Low “NYC Rat”</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="31" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="C38" s="39" t="inlineStr">
         <is>
@@ -7717,21 +7663,21 @@
       </c>
       <c r="E38" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B39" s="41" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C39" s="40" t="inlineStr">
         <is>
@@ -7745,21 +7691,21 @@
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C40" s="39" t="inlineStr">
         <is>
@@ -7773,12 +7719,12 @@
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “NYC Rat”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
@@ -7787,16 +7733,16 @@
         <v>46319</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D41" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D41" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
@@ -7806,16 +7752,16 @@
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="31" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="C42" s="39" t="inlineStr">
         <is>
@@ -7829,21 +7775,21 @@
       </c>
       <c r="E42" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="36" t="n">
-        <v>46319</v>
+        <v>46326</v>
       </c>
       <c r="B43" s="41" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C43" s="40" t="inlineStr">
         <is>
@@ -7862,16 +7808,16 @@
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="31" t="n">
-        <v>46319</v>
+        <v>46333</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
@@ -7885,21 +7831,21 @@
       </c>
       <c r="E44" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>46320</v>
+        <v>46333</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
@@ -7918,25 +7864,25 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="31" t="n">
-        <v>46326</v>
+        <v>46333</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D46" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
@@ -7946,13 +7892,13 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="36" t="n">
-        <v>46329</v>
+        <v>46335</v>
       </c>
       <c r="B47" s="41" t="n">
         <v>240</v>
@@ -7962,9 +7908,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D47" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D47" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
@@ -7974,44 +7920,44 @@
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="31" t="n">
-        <v>46333</v>
+        <v>46337</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D48" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="36" t="n">
-        <v>46333</v>
+        <v>46337</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
@@ -8030,16 +7976,16 @@
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="31" t="n">
-        <v>46333</v>
+        <v>46340</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="C50" s="39" t="inlineStr">
         <is>
@@ -8058,16 +8004,16 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
@@ -8081,21 +8027,21 @@
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="31" t="n">
-        <v>46337</v>
+        <v>46342</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
@@ -8114,16 +8060,16 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="36" t="n">
-        <v>46337</v>
+        <v>46343</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
@@ -8137,30 +8083,30 @@
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="31" t="n">
-        <v>46340</v>
+        <v>46347</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D54" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D54" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
@@ -8170,44 +8116,44 @@
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46342</v>
+        <v>46347</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D55" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D55" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46343</v>
+        <v>46347</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>200</v>
+        <v>165</v>
       </c>
       <c r="C56" s="39" t="inlineStr">
         <is>
@@ -8221,12 +8167,12 @@
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -8235,16 +8181,16 @@
         <v>46347</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>230</v>
+        <v>125</v>
       </c>
       <c r="C57" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D57" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D57" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
@@ -8254,7 +8200,7 @@
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -8263,35 +8209,35 @@
         <v>46347</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C58" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D58" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D58" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
@@ -8310,16 +8256,16 @@
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
@@ -8338,44 +8284,42 @@
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46347</v>
-      </c>
-      <c r="B61" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C61" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D61" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>46354</v>
+      </c>
+      <c r="B61" s="41" t="inlineStr"/>
+      <c r="C61" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D61" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C62" s="39" t="inlineStr">
         <is>
@@ -8389,22 +8333,20 @@
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="36" t="n">
-        <v>46353</v>
-      </c>
-      <c r="B63" s="41" t="n">
-        <v>240</v>
-      </c>
+        <v>46354</v>
+      </c>
+      <c r="B63" s="41" t="inlineStr"/>
       <c r="C63" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -8422,7 +8364,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8373,7 @@
         <v>46354</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
@@ -8450,7 +8392,7 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -8458,10 +8400,12 @@
       <c r="A65" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B65" s="41" t="inlineStr"/>
-      <c r="C65" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
+      <c r="B65" s="41" t="n">
+        <v>130</v>
+      </c>
+      <c r="C65" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D65" s="38" t="inlineStr">
@@ -8471,22 +8415,20 @@
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B66" s="33" t="n">
-        <v>190</v>
-      </c>
+        <v>46361</v>
+      </c>
+      <c r="B66" s="33" t="inlineStr"/>
       <c r="C66" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -8499,20 +8441,22 @@
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B67" s="41" t="inlineStr"/>
+        <v>46361</v>
+      </c>
+      <c r="B67" s="41" t="n">
+        <v>215</v>
+      </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -8525,21 +8469,21 @@
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46354</v>
+        <v>46367</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
@@ -8553,20 +8497,22 @@
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B69" s="41" t="inlineStr"/>
+        <v>46367</v>
+      </c>
+      <c r="B69" s="41" t="n">
+        <v>240</v>
+      </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -8579,30 +8525,28 @@
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B70" s="33" t="n">
-        <v>215</v>
-      </c>
+        <v>46367</v>
+      </c>
+      <c r="B70" s="33" t="inlineStr"/>
       <c r="C70" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D70" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D70" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E70" s="30" t="inlineStr">
@@ -8612,7 +8556,7 @@
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
@@ -8620,43 +8564,45 @@
       <c r="A71" s="36" t="n">
         <v>46367</v>
       </c>
-      <c r="B71" s="41" t="inlineStr"/>
+      <c r="B71" s="41" t="n">
+        <v>190</v>
+      </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D71" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D71" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46367</v>
+        <v>46368</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="C72" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D72" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D72" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E72" s="30" t="inlineStr">
@@ -8666,16 +8612,16 @@
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46367</v>
+        <v>46375</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
@@ -8689,30 +8635,30 @@
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Floral” 2026</t>
+          <t>Air Jordan 4 “Pink Thunder”</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46367</v>
+        <v>46375</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="C74" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D74" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D74" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
@@ -8722,40 +8668,12 @@
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="36" t="n">
-        <v>46368</v>
-      </c>
-      <c r="B75" s="41" t="n">
-        <v>235</v>
-      </c>
-      <c r="C75" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D75" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E75" s="35" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="F75" s="35" t="inlineStr">
-        <is>
-          <t>Air Jordan 11 “Space Jam” 2026</t>
+          <t>Fly Streetwear x Nike SB Air Force 1 Low “University Gold”</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F75"/>
+  <autoFilter ref="A3:F74"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High Hype Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$140</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1581,7 +1581,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 20, 2026  ·  10:51 UTC</t>
+          <t>Generated September 21, 2026  ·  12:15 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1621,7 +1621,7 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="14" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="18" t="inlineStr">
@@ -1737,7 +1737,7 @@
         <v>46290</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46295</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46290</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" s="40" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
@@ -1871,7 +1871,7 @@
         <v>46291</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>7</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H14" s="43" t="inlineStr">
         <is>
@@ -1893,19 +1893,19 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
         <v>46291</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
@@ -1916,18 +1916,18 @@
         <v>7</v>
       </c>
       <c r="G15" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="H15" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="H15" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
@@ -1939,7 +1939,7 @@
         <v>46291</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
@@ -1949,9 +1949,7 @@
       <c r="F16" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="33" t="n">
-        <v>200</v>
-      </c>
+      <c r="G16" s="30" t="inlineStr"/>
       <c r="H16" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
@@ -2012,7 +2010,7 @@
         </is>
       </c>
       <c r="B20" s="30" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
@@ -2028,7 +2026,7 @@
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -2046,7 +2044,7 @@
         </is>
       </c>
       <c r="E21" s="35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" s="47" t="inlineStr">
         <is>
@@ -2191,7 +2189,7 @@
       </c>
       <c r="B31" s="30" t="inlineStr">
         <is>
-          <t>9/20 – 9/26</t>
+          <t>9/21 – 9/27</t>
         </is>
       </c>
       <c r="C31" s="30" t="n">
@@ -2212,7 +2210,7 @@
       </c>
       <c r="B32" s="35" t="inlineStr">
         <is>
-          <t>9/27 – 10/3</t>
+          <t>9/28 – 10/4</t>
         </is>
       </c>
       <c r="C32" s="35" t="n">
@@ -2233,7 +2231,7 @@
       </c>
       <c r="B33" s="30" t="inlineStr">
         <is>
-          <t>10/4 – 10/10</t>
+          <t>10/5 – 10/11</t>
         </is>
       </c>
       <c r="C33" s="30" t="n">
@@ -2254,7 +2252,7 @@
       </c>
       <c r="B34" s="35" t="inlineStr">
         <is>
-          <t>10/11 – 10/17</t>
+          <t>10/12 – 10/18</t>
         </is>
       </c>
       <c r="C34" s="35" t="n">
@@ -2275,17 +2273,17 @@
       </c>
       <c r="B35" s="30" t="inlineStr">
         <is>
-          <t>10/18 – 10/24</t>
+          <t>10/19 – 10/25</t>
         </is>
       </c>
       <c r="C35" s="30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D35" s="39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -2296,17 +2294,17 @@
       </c>
       <c r="B36" s="35" t="inlineStr">
         <is>
-          <t>10/25 – 10/31</t>
+          <t>10/26 – 11/1</t>
         </is>
       </c>
       <c r="C36" s="35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" s="40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="35" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -2317,7 +2315,7 @@
       </c>
       <c r="B37" s="30" t="inlineStr">
         <is>
-          <t>11/1 – 11/7</t>
+          <t>11/2 – 11/8</t>
         </is>
       </c>
       <c r="C37" s="30" t="n">
@@ -2338,17 +2336,17 @@
       </c>
       <c r="B38" s="35" t="inlineStr">
         <is>
-          <t>11/8 – 11/14</t>
+          <t>11/9 – 11/15</t>
         </is>
       </c>
       <c r="C38" s="35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D38" s="40" t="n">
         <v>4</v>
       </c>
       <c r="E38" s="35" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -2359,17 +2357,17 @@
       </c>
       <c r="B39" s="30" t="inlineStr">
         <is>
-          <t>11/15 – 11/21</t>
+          <t>11/16 – 11/22</t>
         </is>
       </c>
       <c r="C39" s="30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D39" s="39" t="n">
         <v>8</v>
       </c>
       <c r="E39" s="30" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -2380,7 +2378,7 @@
       </c>
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>11/22 – 11/28</t>
+          <t>11/23 – 11/29</t>
         </is>
       </c>
       <c r="C40" s="35" t="n">
@@ -2401,17 +2399,17 @@
       </c>
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>11/29 – 12/5</t>
+          <t>11/30 – 12/6</t>
         </is>
       </c>
       <c r="C41" s="30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41" s="39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" s="30" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
@@ -2422,7 +2420,7 @@
       </c>
       <c r="B42" s="35" t="inlineStr">
         <is>
-          <t>12/6 – 12/12</t>
+          <t>12/7 – 12/13</t>
         </is>
       </c>
       <c r="C42" s="35" t="n">
@@ -2443,7 +2441,7 @@
       </c>
       <c r="B43" s="30" t="inlineStr">
         <is>
-          <t>12/13 – 12/19</t>
+          <t>12/14 – 12/20</t>
         </is>
       </c>
       <c r="C43" s="30" t="n">
@@ -2551,7 +2549,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2567,7 +2565,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2593,7 +2591,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2643,7 +2641,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -2732,7 +2730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2758,7 +2756,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 20, 2026  ·  10:51 UTC</t>
+          <t>Generated September 21, 2026  ·  12:15 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3000,26 +2998,26 @@
         <v>46290</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C11" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D11" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D11" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
@@ -3028,16 +3026,16 @@
         <v>46290</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>225</v>
-      </c>
-      <c r="C12" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D12" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>205</v>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
@@ -3047,7 +3045,7 @@
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
@@ -3056,11 +3054,11 @@
         <v>46290</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C13" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>120</v>
+      </c>
+      <c r="C13" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D13" s="42" t="inlineStr">
@@ -3070,12 +3068,12 @@
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Billionaire Boys Club x Reebok Club C 85</t>
         </is>
       </c>
     </row>
@@ -3084,11 +3082,11 @@
         <v>46290</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="C14" s="54" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>140</v>
+      </c>
+      <c r="C14" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D14" s="43" t="inlineStr">
@@ -3098,12 +3096,12 @@
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Billionaire Boys Club x Reebok Club C 85</t>
+          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
         </is>
       </c>
     </row>
@@ -3196,26 +3194,26 @@
         <v>46291</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C18" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3222,7 @@
         <v>46291</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C19" s="40" t="inlineStr">
         <is>
@@ -3243,7 +3241,7 @@
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -3252,11 +3250,11 @@
         <v>46291</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>125</v>
+      </c>
+      <c r="C20" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D20" s="34" t="inlineStr">
@@ -3266,12 +3264,12 @@
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -3280,11 +3278,11 @@
         <v>46291</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>160</v>
-      </c>
-      <c r="C21" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>140</v>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D21" s="42" t="inlineStr">
@@ -3294,12 +3292,12 @@
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -3308,16 +3306,16 @@
         <v>46291</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C22" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D22" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C22" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
@@ -3327,7 +3325,7 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
@@ -3335,17 +3333,15 @@
       <c r="A23" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B23" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C23" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D23" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B23" s="41" t="inlineStr"/>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
@@ -3355,7 +3351,7 @@
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -3364,26 +3360,26 @@
         <v>46291</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D24" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D24" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E24" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -3392,11 +3388,11 @@
         <v>46291</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C25" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>210</v>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D25" s="38" t="inlineStr">
@@ -3411,7 +3407,7 @@
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -3419,15 +3415,17 @@
       <c r="A26" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B26" s="33" t="inlineStr"/>
-      <c r="C26" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D26" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B26" s="33" t="n">
+        <v>200</v>
+      </c>
+      <c r="C26" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
@@ -3437,7 +3435,7 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
         </is>
       </c>
     </row>
@@ -3446,16 +3444,16 @@
         <v>46291</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D27" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D27" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
@@ -3465,7 +3463,7 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -3474,26 +3472,26 @@
         <v>46291</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D28" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D28" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -3502,11 +3500,11 @@
         <v>46291</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C29" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>150</v>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D29" s="38" t="inlineStr">
@@ -3521,7 +3519,7 @@
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -3529,12 +3527,10 @@
       <c r="A30" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B30" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C30" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B30" s="33" t="inlineStr"/>
+      <c r="C30" s="54" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D30" s="43" t="inlineStr">
@@ -3544,12 +3540,12 @@
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
@@ -3560,24 +3556,24 @@
       <c r="B31" s="41" t="n">
         <v>155</v>
       </c>
-      <c r="C31" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D31" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="C31" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D31" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
@@ -3586,16 +3582,16 @@
         <v>46291</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D32" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D32" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
@@ -3605,7 +3601,7 @@
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -3613,25 +3609,27 @@
       <c r="A33" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B33" s="41" t="inlineStr"/>
-      <c r="C33" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D33" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B33" s="41" t="n">
+        <v>255</v>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D33" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3804,7 @@
         <v>46295</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C40" s="39" t="inlineStr">
         <is>
@@ -3825,7 +3823,7 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3832,7 @@
         <v>46295</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
@@ -3848,12 +3846,12 @@
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
@@ -3861,15 +3859,17 @@
       <c r="A42" s="31" t="n">
         <v>46295</v>
       </c>
-      <c r="B42" s="33" t="inlineStr"/>
+      <c r="B42" s="33" t="n">
+        <v>180</v>
+      </c>
       <c r="C42" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D42" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E42" s="30" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
         </is>
       </c>
     </row>
@@ -3888,16 +3888,16 @@
         <v>46295</v>
       </c>
       <c r="B43" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C43" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D43" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>125</v>
+      </c>
+      <c r="C43" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D43" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>MoMA x Nike Air Rift 2 Pack</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
@@ -3915,9 +3915,7 @@
       <c r="A44" s="31" t="n">
         <v>46295</v>
       </c>
-      <c r="B44" s="33" t="n">
-        <v>155</v>
-      </c>
+      <c r="B44" s="33" t="inlineStr"/>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -3935,7 +3933,7 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
@@ -3944,16 +3942,16 @@
         <v>46295</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="C45" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D45" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D45" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
@@ -3963,7 +3961,7 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Nike Zoom Huarache 2K4 “UCLA”</t>
+          <t>MoMA x Nike Air Rift 2 Pack</t>
         </is>
       </c>
     </row>
@@ -3972,16 +3970,16 @@
         <v>46295</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D46" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D46" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
@@ -3991,7 +3989,7 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
@@ -4000,11 +3998,11 @@
         <v>46295</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C47" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>200</v>
+      </c>
+      <c r="C47" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D47" s="42" t="inlineStr">
@@ -4014,12 +4012,12 @@
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Nike Zoom Huarache 2K4 “UCLA”</t>
         </is>
       </c>
     </row>
@@ -4140,16 +4138,16 @@
         <v>46298</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D52" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D52" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
@@ -4159,7 +4157,7 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
@@ -4168,16 +4166,16 @@
         <v>46298</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D53" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
@@ -4187,7 +4185,7 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
@@ -4394,24 +4392,24 @@
       <c r="B61" s="41" t="n">
         <v>125</v>
       </c>
-      <c r="C61" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D61" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C61" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D61" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
@@ -4422,24 +4420,24 @@
       <c r="B62" s="33" t="n">
         <v>125</v>
       </c>
-      <c r="C62" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D62" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="C62" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D62" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4696,7 @@
         <v>46319</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="C72" s="39" t="inlineStr">
         <is>
@@ -4717,7 +4715,7 @@
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4738,12 @@
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
@@ -4754,11 +4752,11 @@
         <v>46319</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C74" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>140</v>
+      </c>
+      <c r="C74" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D74" s="43" t="inlineStr">
@@ -4768,12 +4766,12 @@
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
@@ -4782,11 +4780,11 @@
         <v>46319</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C75" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C75" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D75" s="42" t="inlineStr">
@@ -4796,12 +4794,12 @@
       </c>
       <c r="E75" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
@@ -4810,26 +4808,26 @@
         <v>46319</v>
       </c>
       <c r="B76" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C76" s="54" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D76" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>150</v>
+      </c>
+      <c r="C76" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D76" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
@@ -4838,11 +4836,11 @@
         <v>46319</v>
       </c>
       <c r="B77" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="C77" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>170</v>
+      </c>
+      <c r="C77" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D77" s="38" t="inlineStr">
@@ -4857,7 +4855,7 @@
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
@@ -4866,16 +4864,16 @@
         <v>46319</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="C78" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D78" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D78" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E78" s="30" t="inlineStr">
@@ -4885,7 +4883,7 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
@@ -4894,11 +4892,11 @@
         <v>46319</v>
       </c>
       <c r="B79" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C79" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>190</v>
+      </c>
+      <c r="C79" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D79" s="42" t="inlineStr">
@@ -4913,7 +4911,7 @@
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
@@ -5174,16 +5172,16 @@
         <v>46333</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C89" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D89" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D89" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E89" s="35" t="inlineStr">
@@ -5193,7 +5191,7 @@
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
@@ -5202,16 +5200,16 @@
         <v>46333</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="C90" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D90" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D90" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E90" s="30" t="inlineStr">
@@ -5221,7 +5219,7 @@
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5228,7 @@
         <v>46333</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C91" s="40" t="inlineStr">
         <is>
@@ -5249,7 +5247,7 @@
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5284,7 @@
         <v>46337</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="C93" s="40" t="inlineStr">
         <is>
@@ -5300,12 +5298,12 @@
       </c>
       <c r="E93" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5312,7 @@
         <v>46337</v>
       </c>
       <c r="B94" s="33" t="n">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="C94" s="39" t="inlineStr">
         <is>
@@ -5328,12 +5326,12 @@
       </c>
       <c r="E94" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5732,7 @@
         <v>46347</v>
       </c>
       <c r="B109" s="41" t="n">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="C109" s="40" t="inlineStr">
         <is>
@@ -5753,7 +5751,7 @@
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5760,7 @@
         <v>46347</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C110" s="39" t="inlineStr">
         <is>
@@ -5781,7 +5779,7 @@
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -5789,10 +5787,12 @@
       <c r="A111" s="36" t="n">
         <v>46347</v>
       </c>
-      <c r="B111" s="41" t="inlineStr"/>
-      <c r="C111" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B111" s="41" t="n">
+        <v>140</v>
+      </c>
+      <c r="C111" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D111" s="42" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="E111" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
@@ -5816,26 +5816,26 @@
         <v>46347</v>
       </c>
       <c r="B112" s="33" t="n">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="C112" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D112" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D112" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E112" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F112" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
         <v>46347</v>
       </c>
       <c r="B113" s="41" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C113" s="40" t="inlineStr">
         <is>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E113" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F113" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
@@ -5874,9 +5874,9 @@
       <c r="B114" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C114" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C114" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D114" s="43" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F114" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Snow White”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
@@ -5899,27 +5899,25 @@
       <c r="A115" s="36" t="n">
         <v>46347</v>
       </c>
-      <c r="B115" s="41" t="n">
-        <v>230</v>
-      </c>
-      <c r="C115" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D115" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B115" s="41" t="inlineStr"/>
+      <c r="C115" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D115" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E115" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F115" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5926,7 @@
         <v>46353</v>
       </c>
       <c r="B116" s="33" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C116" s="39" t="inlineStr">
         <is>
@@ -5942,12 +5940,12 @@
       </c>
       <c r="E116" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5954,7 @@
         <v>46353</v>
       </c>
       <c r="B117" s="41" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C117" s="40" t="inlineStr">
         <is>
@@ -5970,12 +5968,12 @@
       </c>
       <c r="E117" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F117" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
@@ -6011,10 +6009,12 @@
       <c r="A119" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B119" s="41" t="inlineStr"/>
-      <c r="C119" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B119" s="41" t="n">
+        <v>190</v>
+      </c>
+      <c r="C119" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D119" s="42" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Aunt Pearl” 2026</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
@@ -6037,25 +6037,27 @@
       <c r="A120" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B120" s="33" t="inlineStr"/>
-      <c r="C120" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D120" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B120" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="C120" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D120" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E120" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F120" s="30" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Nike Caitlin 1 “Warning Code”</t>
         </is>
       </c>
     </row>
@@ -6063,9 +6065,7 @@
       <c r="A121" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B121" s="41" t="n">
-        <v>190</v>
-      </c>
+      <c r="B121" s="41" t="inlineStr"/>
       <c r="C121" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="F121" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
@@ -6092,16 +6092,16 @@
         <v>46354</v>
       </c>
       <c r="B122" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C122" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D122" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>120</v>
+      </c>
+      <c r="C122" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D122" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E122" s="30" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="F122" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Warning Code”</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -6119,15 +6119,17 @@
       <c r="A123" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B123" s="41" t="inlineStr"/>
+      <c r="B123" s="41" t="n">
+        <v>130</v>
+      </c>
       <c r="C123" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D123" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D123" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E123" s="35" t="inlineStr">
@@ -6137,7 +6139,7 @@
       </c>
       <c r="F123" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
@@ -6145,17 +6147,15 @@
       <c r="A124" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B124" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="C124" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D124" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B124" s="33" t="inlineStr"/>
+      <c r="C124" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D124" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E124" s="30" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="F124" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Nike KD 6 “Aunt Pearl” 2026</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,10 @@
       <c r="A125" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B125" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C125" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B125" s="41" t="inlineStr"/>
+      <c r="C125" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
         </is>
       </c>
       <c r="D125" s="38" t="inlineStr">
@@ -6188,25 +6186,25 @@
       </c>
       <c r="E125" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F125" s="35" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="31" t="n">
-        <v>46359</v>
+        <v>46357</v>
       </c>
       <c r="B126" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C126" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>190</v>
+      </c>
+      <c r="C126" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D126" s="43" t="inlineStr">
@@ -6221,35 +6219,35 @@
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Black/White”</t>
+          <t>Nike LeBron 24 “Chosen 1s”</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="36" t="n">
-        <v>46361</v>
+        <v>46359</v>
       </c>
       <c r="B127" s="41" t="n">
-        <v>300</v>
+        <v>170</v>
       </c>
       <c r="C127" s="53" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D127" s="55" t="inlineStr">
-        <is>
-          <t>Confirmed App</t>
+      <c r="D127" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E127" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish “Auburn Timber”</t>
+          <t>Nike Air Bakin “Black/White”</t>
         </is>
       </c>
     </row>
@@ -6347,9 +6345,9 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D131" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D131" s="55" t="inlineStr">
+        <is>
+          <t>Confirmed App</t>
         </is>
       </c>
       <c r="E131" s="35" t="inlineStr">
@@ -6359,35 +6357,35 @@
       </c>
       <c r="F131" s="35" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish</t>
+          <t>Pharrell x adidas Adistar Jellyfish “Auburn Timber”</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1">
       <c r="A132" s="31" t="n">
-        <v>46367</v>
+        <v>46361</v>
       </c>
       <c r="B132" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C132" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D132" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>300</v>
+      </c>
+      <c r="C132" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D132" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E132" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F132" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Pharrell x adidas Adistar Jellyfish</t>
         </is>
       </c>
     </row>
@@ -6450,35 +6448,35 @@
         <v>46367</v>
       </c>
       <c r="B135" s="41" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C135" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D135" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D135" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E135" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F135" s="35" t="inlineStr">
         <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="31" t="n">
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="B136" s="33" t="n">
-        <v>235</v>
+        <v>190</v>
       </c>
       <c r="C136" s="39" t="inlineStr">
         <is>
@@ -6492,25 +6490,25 @@
       </c>
       <c r="E136" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F136" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam” 2026</t>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="36" t="n">
-        <v>46375</v>
+        <v>46368</v>
       </c>
       <c r="B137" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C137" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>235</v>
+      </c>
+      <c r="C137" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D137" s="42" t="inlineStr">
@@ -6520,12 +6518,12 @@
       </c>
       <c r="E137" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F137" s="35" t="inlineStr">
         <is>
-          <t>Nike GT Future “Triple Black”</t>
+          <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
@@ -6613,8 +6611,36 @@
         </is>
       </c>
     </row>
+    <row r="141" ht="15" customHeight="1">
+      <c r="A141" s="36" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B141" s="41" t="n">
+        <v>210</v>
+      </c>
+      <c r="C141" s="53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D141" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E141" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F141" s="35" t="inlineStr">
+        <is>
+          <t>Nike GT Future “Triple Black”</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:F140"/>
+  <autoFilter ref="A3:F141"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -6629,7 +6655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6655,7 +6681,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 20, 2026  ·  10:51 UTC</t>
+          <t>Generated September 21, 2026  ·  12:15 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -6757,7 +6783,7 @@
         <v>46291</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
@@ -6776,7 +6802,7 @@
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -6785,26 +6811,26 @@
         <v>46291</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D7" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -6812,9 +6838,7 @@
       <c r="A8" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B8" s="33" t="n">
-        <v>200</v>
-      </c>
+      <c r="B8" s="33" t="inlineStr"/>
       <c r="C8" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6832,7 +6856,7 @@
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -6841,26 +6865,26 @@
         <v>46291</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D9" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -6868,15 +6892,17 @@
       <c r="A10" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B10" s="33" t="inlineStr"/>
+      <c r="B10" s="33" t="n">
+        <v>210</v>
+      </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D10" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
@@ -6886,7 +6912,7 @@
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -6895,16 +6921,16 @@
         <v>46291</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D11" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D11" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
@@ -6914,7 +6940,7 @@
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -6923,26 +6949,26 @@
         <v>46291</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="C12" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -6951,26 +6977,26 @@
         <v>46291</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C13" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D13" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D13" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -6979,7 +7005,7 @@
         <v>46291</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
@@ -6993,12 +7019,12 @@
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7033,7 @@
         <v>46291</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>150</v>
+        <v>255</v>
       </c>
       <c r="C15" s="40" t="inlineStr">
         <is>
@@ -7021,12 +7047,12 @@
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7089,7 @@
         <v>46295</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C17" s="40" t="inlineStr">
         <is>
@@ -7082,7 +7108,7 @@
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7117,7 @@
         <v>46295</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="C18" s="39" t="inlineStr">
         <is>
@@ -7105,12 +7131,12 @@
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
@@ -7118,15 +7144,17 @@
       <c r="A19" s="36" t="n">
         <v>46295</v>
       </c>
-      <c r="B19" s="41" t="inlineStr"/>
+      <c r="B19" s="41" t="n">
+        <v>180</v>
+      </c>
       <c r="C19" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D19" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D19" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
@@ -7136,7 +7164,7 @@
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7173,7 @@
         <v>46295</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
@@ -7164,7 +7192,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
@@ -7172,17 +7200,15 @@
       <c r="A21" s="36" t="n">
         <v>46295</v>
       </c>
-      <c r="B21" s="41" t="n">
-        <v>135</v>
-      </c>
+      <c r="B21" s="41" t="inlineStr"/>
       <c r="C21" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D21" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D21" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
@@ -7192,7 +7218,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Air Force 1 Low “Black Rat”</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7227,7 @@
         <v>46295</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
@@ -7215,12 +7241,12 @@
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
@@ -7313,16 +7339,16 @@
         <v>46298</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C26" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D26" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D26" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
@@ -7332,7 +7358,7 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
@@ -7341,16 +7367,16 @@
         <v>46298</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D27" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D27" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
@@ -7360,7 +7386,7 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
@@ -7649,7 +7675,7 @@
         <v>46319</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="C38" s="39" t="inlineStr">
         <is>
@@ -7668,7 +7694,7 @@
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
@@ -7691,12 +7717,12 @@
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
@@ -7705,26 +7731,26 @@
         <v>46319</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C40" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D40" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
@@ -7733,16 +7759,16 @@
         <v>46319</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D41" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D41" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
@@ -7752,7 +7778,7 @@
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
@@ -7817,16 +7843,16 @@
         <v>46333</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D44" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D44" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E44" s="30" t="inlineStr">
@@ -7836,7 +7862,7 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
@@ -7845,16 +7871,16 @@
         <v>46333</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D45" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D45" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
@@ -7864,7 +7890,7 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7899,7 @@
         <v>46333</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
@@ -7892,7 +7918,7 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7955,7 @@
         <v>46337</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
@@ -7943,12 +7969,12 @@
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -7957,7 +7983,7 @@
         <v>46337</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
@@ -7971,12 +7997,12 @@
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8123,7 @@
         <v>46347</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
@@ -8116,7 +8142,7 @@
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8151,7 @@
         <v>46347</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
@@ -8144,7 +8170,7 @@
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -8153,26 +8179,26 @@
         <v>46347</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="C56" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D56" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D56" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8207,7 @@
         <v>46347</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C57" s="40" t="inlineStr">
         <is>
@@ -8195,12 +8221,12 @@
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
@@ -8209,16 +8235,16 @@
         <v>46347</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="C58" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D58" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D58" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
@@ -8228,7 +8254,7 @@
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8263,7 @@
         <v>46353</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
@@ -8251,12 +8277,12 @@
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8291,7 @@
         <v>46353</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
@@ -8279,12 +8305,12 @@
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
@@ -8292,25 +8318,27 @@
       <c r="A61" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B61" s="41" t="inlineStr"/>
-      <c r="C61" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D61" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B61" s="41" t="n">
+        <v>190</v>
+      </c>
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D61" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
@@ -8318,9 +8346,7 @@
       <c r="A62" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B62" s="33" t="n">
-        <v>190</v>
-      </c>
+      <c r="B62" s="33" t="inlineStr"/>
       <c r="C62" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -8338,7 +8364,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
@@ -8346,15 +8372,17 @@
       <c r="A63" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B63" s="41" t="inlineStr"/>
+      <c r="B63" s="41" t="n">
+        <v>120</v>
+      </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D63" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D63" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
@@ -8364,7 +8392,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8401,7 @@
         <v>46354</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
@@ -8392,7 +8420,7 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
@@ -8400,12 +8428,10 @@
       <c r="A65" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B65" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C65" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B65" s="41" t="inlineStr"/>
+      <c r="C65" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
         </is>
       </c>
       <c r="D65" s="38" t="inlineStr">
@@ -8415,20 +8441,22 @@
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B66" s="33" t="inlineStr"/>
+        <v>46357</v>
+      </c>
+      <c r="B66" s="33" t="n">
+        <v>190</v>
+      </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -8441,12 +8469,12 @@
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Nike LeBron 24 “Chosen 1s”</t>
         </is>
       </c>
     </row>
@@ -8454,9 +8482,7 @@
       <c r="A67" s="36" t="n">
         <v>46361</v>
       </c>
-      <c r="B67" s="41" t="n">
-        <v>215</v>
-      </c>
+      <c r="B67" s="41" t="inlineStr"/>
       <c r="C67" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -8474,25 +8500,25 @@
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46367</v>
+        <v>46361</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D68" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D68" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
@@ -8502,7 +8528,7 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
@@ -8565,35 +8591,35 @@
         <v>46367</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D71" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D71" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>235</v>
+        <v>190</v>
       </c>
       <c r="C72" s="39" t="inlineStr">
         <is>
@@ -8607,21 +8633,21 @@
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam” 2026</t>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46375</v>
+        <v>46368</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
@@ -8640,7 +8666,7 @@
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Pink Thunder”</t>
+          <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
@@ -8649,31 +8675,59 @@
         <v>46375</v>
       </c>
       <c r="B74" s="33" t="n">
+        <v>220</v>
+      </c>
+      <c r="C74" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D74" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E74" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F74" s="30" t="inlineStr">
+        <is>
+          <t>Air Jordan 4 “Pink Thunder”</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="36" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B75" s="41" t="n">
         <v>120</v>
       </c>
-      <c r="C74" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D74" s="34" t="inlineStr">
+      <c r="C75" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D75" s="38" t="inlineStr">
         <is>
           <t>SNKRS App</t>
         </is>
       </c>
-      <c r="E74" s="30" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="F74" s="30" t="inlineStr">
+      <c r="E75" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F75" s="35" t="inlineStr">
         <is>
           <t>Fly Streetwear x Nike SB Air Force 1 Low “University Gold”</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F74"/>
+  <autoFilter ref="A3:F75"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High Hype Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -679,13 +679,13 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1581,7 +1581,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 21, 2026  ·  12:15 UTC</t>
+          <t>Generated September 22, 2026  ·  11:09 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1621,11 +1621,11 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="16" t="n">
@@ -1634,7 +1634,7 @@
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>$182</t>
+          <t>$181</t>
         </is>
       </c>
       <c r="H5" s="19" t="n"/>
@@ -1737,7 +1737,7 @@
         <v>46290</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46295</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46290</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" s="40" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>46291</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>46291</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46291</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="B20" s="30" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="B22" s="30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="E22" s="30" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G22" s="49" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="E23" s="35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="B31" s="30" t="inlineStr">
         <is>
-          <t>9/21 – 9/27</t>
+          <t>9/22 – 9/28</t>
         </is>
       </c>
       <c r="C31" s="30" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D31" s="39" t="n">
         <v>13</v>
       </c>
       <c r="E31" s="30" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
@@ -2210,14 +2210,14 @@
       </c>
       <c r="B32" s="35" t="inlineStr">
         <is>
-          <t>9/28 – 10/4</t>
+          <t>9/29 – 10/5</t>
         </is>
       </c>
       <c r="C32" s="35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D32" s="40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E32" s="35" t="n">
         <v>5.9</v>
@@ -2231,17 +2231,17 @@
       </c>
       <c r="B33" s="30" t="inlineStr">
         <is>
-          <t>10/5 – 10/11</t>
+          <t>10/6 – 10/12</t>
         </is>
       </c>
       <c r="C33" s="30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D33" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="30" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B34" s="35" t="inlineStr">
         <is>
-          <t>10/12 – 10/18</t>
+          <t>10/13 – 10/19</t>
         </is>
       </c>
       <c r="C34" s="35" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="B35" s="30" t="inlineStr">
         <is>
-          <t>10/19 – 10/25</t>
+          <t>10/20 – 10/26</t>
         </is>
       </c>
       <c r="C35" s="30" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B36" s="35" t="inlineStr">
         <is>
-          <t>10/26 – 11/1</t>
+          <t>10/27 – 11/2</t>
         </is>
       </c>
       <c r="C36" s="35" t="n">
@@ -2315,17 +2315,17 @@
       </c>
       <c r="B37" s="30" t="inlineStr">
         <is>
-          <t>11/2 – 11/8</t>
+          <t>11/3 – 11/9</t>
         </is>
       </c>
       <c r="C37" s="30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D37" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="30" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="B38" s="35" t="inlineStr">
         <is>
-          <t>11/9 – 11/15</t>
+          <t>11/10 – 11/16</t>
         </is>
       </c>
       <c r="C38" s="35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D38" s="40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38" s="35" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -2357,17 +2357,17 @@
       </c>
       <c r="B39" s="30" t="inlineStr">
         <is>
-          <t>11/16 – 11/22</t>
+          <t>11/17 – 11/23</t>
         </is>
       </c>
       <c r="C39" s="30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D39" s="39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E39" s="30" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>11/23 – 11/29</t>
+          <t>11/24 – 11/30</t>
         </is>
       </c>
       <c r="C40" s="35" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>11/30 – 12/6</t>
+          <t>12/1 – 12/7</t>
         </is>
       </c>
       <c r="C41" s="30" t="n">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="B42" s="35" t="inlineStr">
         <is>
-          <t>12/7 – 12/13</t>
+          <t>12/8 – 12/14</t>
         </is>
       </c>
       <c r="C42" s="35" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="B43" s="30" t="inlineStr">
         <is>
-          <t>12/14 – 12/20</t>
+          <t>12/15 – 12/21</t>
         </is>
       </c>
       <c r="C43" s="30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D43" s="39" t="n">
         <v>2</v>
       </c>
       <c r="E43" s="30" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
     </row>
   </sheetData>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2756,7 +2756,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 21, 2026  ·  12:15 UTC</t>
+          <t>Generated September 22, 2026  ·  11:09 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="C4" s="48" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>PSG x Nike KD 6 "Metallic Silver"</t>
+          <t>Nike GT Future “Varsity Red”</t>
         </is>
       </c>
     </row>
@@ -2830,11 +2830,11 @@
         <v>46287</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C5" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>110</v>
+      </c>
+      <c r="C5" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Nike GT Future “Varsity Red”</t>
+          <t>Pokémon x adidas Superstar "Pikachu White"</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       <c r="B8" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C8" s="54" t="inlineStr">
+      <c r="C8" s="53" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2972,7 +2972,7 @@
       <c r="B10" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C10" s="54" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3112,7 +3112,7 @@
       <c r="B15" s="41" t="n">
         <v>140</v>
       </c>
-      <c r="C15" s="53" t="inlineStr">
+      <c r="C15" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3168,7 +3168,7 @@
       <c r="B17" s="41" t="n">
         <v>210</v>
       </c>
-      <c r="C17" s="53" t="inlineStr">
+      <c r="C17" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3194,11 +3194,11 @@
         <v>46291</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>160</v>
-      </c>
-      <c r="C18" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>200</v>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D18" s="43" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -3222,16 +3222,16 @@
         <v>46291</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C19" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D19" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>125</v>
+      </c>
+      <c r="C19" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D19" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -3250,16 +3250,16 @@
         <v>46291</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C20" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D20" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -3278,16 +3278,16 @@
         <v>46291</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C21" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D21" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C21" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D21" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
@@ -3305,17 +3305,15 @@
       <c r="A22" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B22" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C22" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D22" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B22" s="33" t="inlineStr"/>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
@@ -3325,7 +3323,7 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -3333,25 +3331,27 @@
       <c r="A23" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B23" s="41" t="inlineStr"/>
+      <c r="B23" s="41" t="n">
+        <v>180</v>
+      </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D23" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
         <v>46291</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E24" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -3388,11 +3388,11 @@
         <v>46291</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C25" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>200</v>
+      </c>
+      <c r="C25" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D25" s="38" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
         </is>
       </c>
     </row>
@@ -3418,24 +3418,24 @@
       <c r="B26" s="33" t="n">
         <v>200</v>
       </c>
-      <c r="C26" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D26" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D26" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
         <v>46291</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -3472,26 +3472,26 @@
         <v>46291</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D28" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -3499,27 +3499,25 @@
       <c r="A29" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B29" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="C29" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D29" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B29" s="41" t="inlineStr"/>
+      <c r="C29" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
@@ -3527,25 +3525,27 @@
       <c r="A30" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B30" s="33" t="inlineStr"/>
-      <c r="C30" s="54" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D30" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B30" s="33" t="n">
+        <v>155</v>
+      </c>
+      <c r="C30" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
@@ -3554,16 +3554,16 @@
         <v>46291</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C31" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D31" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -3582,26 +3582,26 @@
         <v>46291</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>210</v>
+        <v>255</v>
       </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D32" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D32" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
@@ -3610,26 +3610,26 @@
         <v>46291</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C33" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D33" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>160</v>
+      </c>
+      <c r="C33" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D33" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       <c r="B37" s="41" t="n">
         <v>170</v>
       </c>
-      <c r="C37" s="53" t="inlineStr">
+      <c r="C37" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3778,7 +3778,7 @@
       <c r="B39" s="41" t="n">
         <v>170</v>
       </c>
-      <c r="C39" s="53" t="inlineStr">
+      <c r="C39" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3944,7 +3944,7 @@
       <c r="B45" s="41" t="n">
         <v>130</v>
       </c>
-      <c r="C45" s="53" t="inlineStr">
+      <c r="C45" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4000,7 +4000,7 @@
       <c r="B47" s="41" t="n">
         <v>200</v>
       </c>
-      <c r="C47" s="53" t="inlineStr">
+      <c r="C47" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4023,29 +4023,29 @@
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="31" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C48" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D48" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>120</v>
+      </c>
+      <c r="C48" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Howard” 2026</t>
+          <t>Tom Sachs x Nike General Purpose Shoe “Demerits”</t>
         </is>
       </c>
     </row>
@@ -4054,26 +4054,26 @@
         <v>46296</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C49" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D49" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>155</v>
+      </c>
+      <c r="C49" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D49" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Racer Blue”</t>
+          <t>Air Jordan 1 Low OG “Howard” 2026</t>
         </is>
       </c>
     </row>
@@ -4082,11 +4082,11 @@
         <v>46296</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C50" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>140</v>
+      </c>
+      <c r="C50" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D50" s="43" t="inlineStr">
@@ -4101,53 +4101,53 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low</t>
+          <t>Nike Caitlin 1 “Racer Blue”</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>220</v>
+        <v>125</v>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D51" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D51" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Nike Kobe Air Force 1 Low</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="31" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D52" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D52" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
@@ -4166,16 +4166,16 @@
         <v>46298</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D53" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
@@ -4185,48 +4185,48 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="31" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D54" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46303</v>
+        <v>46300</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C55" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>200</v>
+      </c>
+      <c r="C55" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D55" s="42" t="inlineStr">
@@ -4236,25 +4236,25 @@
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C56" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C56" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D56" s="43" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
+          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
         </is>
       </c>
     </row>
@@ -4278,11 +4278,11 @@
         <v>46304</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C57" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>170</v>
+      </c>
+      <c r="C57" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D57" s="42" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
+          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
         </is>
       </c>
     </row>
@@ -4306,11 +4306,11 @@
         <v>46304</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>220</v>
-      </c>
-      <c r="C58" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C58" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D58" s="43" t="inlineStr">
@@ -4320,23 +4320,23 @@
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Aminé x New Balance 992 “Outdoor School”</t>
+          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>135</v>
-      </c>
-      <c r="C59" s="53" t="inlineStr">
+        <v>220</v>
+      </c>
+      <c r="C59" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4348,12 +4348,12 @@
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Texas”</t>
+          <t>Aminé x New Balance 992 “Outdoor School”</t>
         </is>
       </c>
     </row>
@@ -4362,11 +4362,11 @@
         <v>46305</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C60" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>135</v>
+      </c>
+      <c r="C60" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D60" s="43" t="inlineStr">
@@ -4376,25 +4376,25 @@
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Nike KD 6 “Texas”</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46310</v>
+        <v>46305</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C61" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>180</v>
+      </c>
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D61" s="42" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
@@ -4420,42 +4420,42 @@
       <c r="B62" s="33" t="n">
         <v>125</v>
       </c>
-      <c r="C62" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D62" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C62" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D62" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="36" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>240</v>
+        <v>125</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D63" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D63" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
         <v>46311</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
         <v>46311</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
         <v>46311</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
@@ -4549,16 +4549,16 @@
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
@@ -4572,12 +4572,12 @@
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
         <v>46312</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
@@ -4605,20 +4605,20 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46315</v>
+        <v>46312</v>
       </c>
       <c r="B69" s="41" t="n">
-        <v>160</v>
-      </c>
-      <c r="C69" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>215</v>
+      </c>
+      <c r="C69" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D69" s="42" t="inlineStr">
@@ -4628,21 +4628,23 @@
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 “Reese’s”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B70" s="33" t="inlineStr"/>
-      <c r="C70" s="54" t="inlineStr">
+        <v>46315</v>
+      </c>
+      <c r="B70" s="33" t="n">
+        <v>160</v>
+      </c>
+      <c r="C70" s="53" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4654,25 +4656,23 @@
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>SZA x Vans VANSZA Collection</t>
+          <t>Reebok Angel Reese 1 “Reese’s”</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B71" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C71" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46317</v>
+      </c>
+      <c r="B71" s="41" t="inlineStr"/>
+      <c r="C71" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D71" s="42" t="inlineStr">
@@ -4682,21 +4682,21 @@
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “NYC Rat”</t>
+          <t>SZA x Vans VANSZA Collection</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C72" s="39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Nike Air Force 1 Low “NYC Rat”</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
@@ -4752,11 +4752,11 @@
         <v>46319</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C74" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>125</v>
+      </c>
+      <c r="C74" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D74" s="43" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
@@ -4780,11 +4780,11 @@
         <v>46319</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C75" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>140</v>
+      </c>
+      <c r="C75" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D75" s="42" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="E75" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
@@ -4808,26 +4808,26 @@
         <v>46319</v>
       </c>
       <c r="B76" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C76" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D76" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C76" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D76" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
@@ -4836,11 +4836,11 @@
         <v>46319</v>
       </c>
       <c r="B77" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C77" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>150</v>
+      </c>
+      <c r="C77" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D77" s="38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
@@ -4864,16 +4864,16 @@
         <v>46319</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C78" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D78" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D78" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E78" s="30" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
@@ -4892,11 +4892,11 @@
         <v>46319</v>
       </c>
       <c r="B79" s="41" t="n">
-        <v>190</v>
-      </c>
-      <c r="C79" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>145</v>
+      </c>
+      <c r="C79" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D79" s="42" t="inlineStr">
@@ -4911,16 +4911,16 @@
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="31" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B80" s="33" t="n">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="C80" s="39" t="inlineStr">
         <is>
@@ -4934,25 +4934,25 @@
       </c>
       <c r="E80" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="36" t="n">
-        <v>46325</v>
+        <v>46320</v>
       </c>
       <c r="B81" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C81" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>205</v>
+      </c>
+      <c r="C81" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D81" s="42" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="E81" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F81" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       <c r="B83" s="41" t="n">
         <v>155</v>
       </c>
-      <c r="C83" s="53" t="inlineStr">
+      <c r="C83" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5023,20 +5023,20 @@
       </c>
       <c r="F83" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Halloween”</t>
+          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="31" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="B84" s="33" t="n">
-        <v>215</v>
-      </c>
-      <c r="C84" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>155</v>
+      </c>
+      <c r="C84" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D84" s="43" t="inlineStr">
@@ -5046,25 +5046,25 @@
       </c>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Nike Book 2 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="36" t="n">
-        <v>46331</v>
+        <v>46326</v>
       </c>
       <c r="B85" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C85" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>215</v>
+      </c>
+      <c r="C85" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D85" s="42" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="E85" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
         </is>
       </c>
     </row>
@@ -5116,9 +5116,9 @@
         <v>46331</v>
       </c>
       <c r="B87" s="41" t="n">
-        <v>265</v>
-      </c>
-      <c r="C87" s="53" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C87" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5135,16 +5135,16 @@
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max Foamdome “Eggplant”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="31" t="n">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="B88" s="33" t="n">
-        <v>145</v>
+        <v>265</v>
       </c>
       <c r="C88" s="48" t="inlineStr">
         <is>
@@ -5163,20 +5163,20 @@
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Desert Night”</t>
+          <t>Nike Air Max Foamdome “Eggplant”</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="36" t="n">
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C89" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>145</v>
+      </c>
+      <c r="C89" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D89" s="42" t="inlineStr">
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E89" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Book 2 “Desert Night”</t>
         </is>
       </c>
     </row>
@@ -5200,16 +5200,16 @@
         <v>46333</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="C90" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D90" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D90" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E90" s="30" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
         <v>46333</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C91" s="40" t="inlineStr">
         <is>
@@ -5247,13 +5247,13 @@
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="31" t="n">
-        <v>46335</v>
+        <v>46333</v>
       </c>
       <c r="B92" s="33" t="n">
         <v>240</v>
@@ -5270,40 +5270,40 @@
       </c>
       <c r="E92" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="36" t="n">
-        <v>46337</v>
+        <v>46335</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C93" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D93" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D93" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E93" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
         <v>46337</v>
       </c>
       <c r="B94" s="33" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="C94" s="39" t="inlineStr">
         <is>
@@ -5326,30 +5326,30 @@
       </c>
       <c r="E94" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="36" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B95" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C95" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D95" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>200</v>
+      </c>
+      <c r="C95" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D95" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E95" s="35" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="F95" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal” 2026</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
@@ -5368,26 +5368,26 @@
         <v>46338</v>
       </c>
       <c r="B96" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C96" s="54" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D96" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>170</v>
+      </c>
+      <c r="C96" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D96" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E96" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
+          <t>Nike Air Bakin “Varsity Royal” 2026</t>
         </is>
       </c>
     </row>
@@ -5396,11 +5396,11 @@
         <v>46338</v>
       </c>
       <c r="B97" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C97" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C97" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D97" s="42" t="inlineStr">
@@ -5410,18 +5410,18 @@
       </c>
       <c r="E97" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F97" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal”</t>
+          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="31" t="n">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="B98" s="33" t="n">
         <v>170</v>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Diamond Turf 2 Patent “Black Red”</t>
+          <t>Nike Air Bakin “Varsity Royal”</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       <c r="B99" s="41" t="n">
         <v>170</v>
       </c>
-      <c r="C99" s="53" t="inlineStr">
+      <c r="C99" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5471,35 +5471,35 @@
       </c>
       <c r="F99" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Diamond Turf 2</t>
+          <t>Nike Air Diamond Turf 2 Patent “Black Red”</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="31" t="n">
-        <v>46340</v>
+        <v>46339</v>
       </c>
       <c r="B100" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C100" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D100" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C100" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D100" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E100" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Air Diamond Turf 2</t>
         </is>
       </c>
     </row>
@@ -5508,11 +5508,11 @@
         <v>46340</v>
       </c>
       <c r="B101" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C101" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>255</v>
+      </c>
+      <c r="C101" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D101" s="38" t="inlineStr">
@@ -5527,16 +5527,16 @@
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="31" t="n">
-        <v>46341</v>
+        <v>46340</v>
       </c>
       <c r="B102" s="33" t="n">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="C102" s="48" t="inlineStr">
         <is>
@@ -5550,25 +5550,25 @@
       </c>
       <c r="E102" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>Playa Society x Nike A’Two</t>
+          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="36" t="n">
-        <v>46342</v>
+        <v>46341</v>
       </c>
       <c r="B103" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C103" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>155</v>
+      </c>
+      <c r="C103" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D103" s="38" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="E103" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F103" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Playa Society x Nike A’Two</t>
         </is>
       </c>
     </row>
@@ -5592,35 +5592,35 @@
         <v>46342</v>
       </c>
       <c r="B104" s="33" t="n">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="C104" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D104" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D104" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E104" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F104" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="36" t="n">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="B105" s="41" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="C105" s="40" t="inlineStr">
         <is>
@@ -5639,20 +5639,20 @@
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="31" t="n">
-        <v>46345</v>
+        <v>46343</v>
       </c>
       <c r="B106" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C106" s="54" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>200</v>
+      </c>
+      <c r="C106" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D106" s="43" t="inlineStr">
@@ -5662,25 +5662,25 @@
       </c>
       <c r="E106" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F106" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Navy”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="36" t="n">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="B107" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C107" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C107" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D107" s="42" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="E107" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F107" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Be Legendary”</t>
+          <t>Vans Old Skool 36 Pearlized “Navy”</t>
         </is>
       </c>
     </row>
@@ -5704,11 +5704,11 @@
         <v>46346</v>
       </c>
       <c r="B108" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C108" s="54" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>145</v>
+      </c>
+      <c r="C108" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D108" s="43" t="inlineStr">
@@ -5718,25 +5718,25 @@
       </c>
       <c r="E108" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F108" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
+          <t>Nike Book 2 “Be Legendary”</t>
         </is>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="36" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B109" s="41" t="n">
-        <v>165</v>
-      </c>
-      <c r="C109" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>130</v>
+      </c>
+      <c r="C109" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D109" s="42" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E109" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
         <v>46347</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="C110" s="39" t="inlineStr">
         <is>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="E110" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -5788,11 +5788,11 @@
         <v>46347</v>
       </c>
       <c r="B111" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C111" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>125</v>
+      </c>
+      <c r="C111" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D111" s="42" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Snow White”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -5816,16 +5816,16 @@
         <v>46347</v>
       </c>
       <c r="B112" s="33" t="n">
-        <v>230</v>
-      </c>
-      <c r="C112" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D112" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C112" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D112" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E112" s="30" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="F112" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
@@ -5844,26 +5844,26 @@
         <v>46347</v>
       </c>
       <c r="B113" s="41" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C113" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D113" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D113" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E113" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F113" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
         <v>46347</v>
       </c>
       <c r="B114" s="33" t="n">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="C114" s="39" t="inlineStr">
         <is>
@@ -5886,12 +5886,12 @@
       </c>
       <c r="E114" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F114" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
@@ -5899,10 +5899,12 @@
       <c r="A115" s="36" t="n">
         <v>46347</v>
       </c>
-      <c r="B115" s="41" t="inlineStr"/>
-      <c r="C115" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B115" s="41" t="n">
+        <v>140</v>
+      </c>
+      <c r="C115" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D115" s="42" t="inlineStr">
@@ -5912,25 +5914,23 @@
       </c>
       <c r="E115" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F115" s="35" t="inlineStr">
         <is>
-          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="31" t="n">
-        <v>46353</v>
-      </c>
-      <c r="B116" s="33" t="n">
-        <v>230</v>
-      </c>
-      <c r="C116" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46347</v>
+      </c>
+      <c r="B116" s="33" t="inlineStr"/>
+      <c r="C116" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D116" s="43" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E116" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
         <v>46353</v>
       </c>
       <c r="B117" s="41" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C117" s="40" t="inlineStr">
         <is>
@@ -5968,12 +5968,12 @@
       </c>
       <c r="E117" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F117" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
@@ -5982,11 +5982,11 @@
         <v>46353</v>
       </c>
       <c r="B118" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C118" s="54" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>240</v>
+      </c>
+      <c r="C118" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D118" s="43" t="inlineStr">
@@ -5996,25 +5996,25 @@
       </c>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F118" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Black”</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="36" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B119" s="41" t="n">
-        <v>190</v>
-      </c>
-      <c r="C119" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>130</v>
+      </c>
+      <c r="C119" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D119" s="42" t="inlineStr">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="E119" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Vans Old Skool 36 Pearlized “Black”</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="31" t="n">
-        <v>46357</v>
+        <v>46354</v>
       </c>
       <c r="B126" s="33" t="n">
         <v>190</v>
@@ -6219,20 +6219,20 @@
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Chosen 1s”</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="36" t="n">
-        <v>46359</v>
+        <v>46357</v>
       </c>
       <c r="B127" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C127" s="53" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>190</v>
+      </c>
+      <c r="C127" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D127" s="42" t="inlineStr">
@@ -6247,18 +6247,20 @@
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Black/White”</t>
+          <t>Nike LeBron 24 “Chosen 1s”</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" s="31" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B128" s="33" t="inlineStr"/>
-      <c r="C128" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46359</v>
+      </c>
+      <c r="B128" s="33" t="n">
+        <v>170</v>
+      </c>
+      <c r="C128" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D128" s="43" t="inlineStr">
@@ -6268,12 +6270,12 @@
       </c>
       <c r="E128" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F128" s="30" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Nike Air Bakin “Black/White”</t>
         </is>
       </c>
     </row>
@@ -6281,9 +6283,7 @@
       <c r="A129" s="36" t="n">
         <v>46361</v>
       </c>
-      <c r="B129" s="41" t="n">
-        <v>215</v>
-      </c>
+      <c r="B129" s="41" t="inlineStr"/>
       <c r="C129" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="F129" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
@@ -6310,11 +6310,11 @@
         <v>46361</v>
       </c>
       <c r="B130" s="33" t="n">
-        <v>300</v>
-      </c>
-      <c r="C130" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>215</v>
+      </c>
+      <c r="C130" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D130" s="43" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E130" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F130" s="30" t="inlineStr">
         <is>
-          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
@@ -6340,14 +6340,14 @@
       <c r="B131" s="41" t="n">
         <v>300</v>
       </c>
-      <c r="C131" s="53" t="inlineStr">
+      <c r="C131" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D131" s="55" t="inlineStr">
-        <is>
-          <t>Confirmed App</t>
+      <c r="D131" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E131" s="35" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F131" s="35" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish “Auburn Timber”</t>
+          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
         </is>
       </c>
     </row>
@@ -6373,9 +6373,9 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D132" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D132" s="55" t="inlineStr">
+        <is>
+          <t>Confirmed App</t>
         </is>
       </c>
       <c r="E132" s="30" t="inlineStr">
@@ -6385,20 +6385,20 @@
       </c>
       <c r="F132" s="30" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish</t>
+          <t>Pharrell x adidas Adistar Jellyfish “Auburn Timber”</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1">
       <c r="A133" s="36" t="n">
-        <v>46367</v>
+        <v>46361</v>
       </c>
       <c r="B133" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C133" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>300</v>
+      </c>
+      <c r="C133" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D133" s="42" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E133" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F133" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Floral” 2026</t>
+          <t>Pharrell x adidas Adistar Jellyfish</t>
         </is>
       </c>
     </row>
@@ -6421,25 +6421,27 @@
       <c r="A134" s="31" t="n">
         <v>46367</v>
       </c>
-      <c r="B134" s="33" t="inlineStr"/>
+      <c r="B134" s="33" t="n">
+        <v>240</v>
+      </c>
       <c r="C134" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D134" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D134" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E134" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F134" s="30" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
         </is>
       </c>
     </row>
@@ -6447,9 +6449,7 @@
       <c r="A135" s="36" t="n">
         <v>46367</v>
       </c>
-      <c r="B135" s="41" t="n">
-        <v>150</v>
-      </c>
+      <c r="B135" s="41" t="inlineStr"/>
       <c r="C135" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="F135" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
@@ -6476,35 +6476,35 @@
         <v>46367</v>
       </c>
       <c r="B136" s="33" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C136" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D136" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D136" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E136" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F136" s="30" t="inlineStr">
         <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="36" t="n">
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="B137" s="41" t="n">
-        <v>235</v>
+        <v>190</v>
       </c>
       <c r="C137" s="40" t="inlineStr">
         <is>
@@ -6518,21 +6518,21 @@
       </c>
       <c r="E137" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F137" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam” 2026</t>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="A138" s="31" t="n">
-        <v>46375</v>
+        <v>46368</v>
       </c>
       <c r="B138" s="33" t="n">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="C138" s="39" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="F138" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Pink Thunder”</t>
+          <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6618,7 @@
       <c r="B141" s="41" t="n">
         <v>210</v>
       </c>
-      <c r="C141" s="53" t="inlineStr">
+      <c r="C141" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -6639,8 +6639,64 @@
         </is>
       </c>
     </row>
+    <row r="142" ht="15" customHeight="1">
+      <c r="A142" s="31" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B142" s="33" t="n">
+        <v>220</v>
+      </c>
+      <c r="C142" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D142" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E142" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F142" s="30" t="inlineStr">
+        <is>
+          <t>Air Jordan 4 “Pink Thunder”</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="15" customHeight="1">
+      <c r="A143" s="36" t="n">
+        <v>46377</v>
+      </c>
+      <c r="B143" s="41" t="n">
+        <v>140</v>
+      </c>
+      <c r="C143" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D143" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E143" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F143" s="35" t="inlineStr">
+        <is>
+          <t>Nike Caitlin 1 “Chiefs”</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:F141"/>
+  <autoFilter ref="A3:F143"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -6681,7 +6737,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 21, 2026  ·  12:15 UTC</t>
+          <t>Generated September 22, 2026  ·  11:09 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -8318,9 +8374,7 @@
       <c r="A61" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B61" s="41" t="n">
-        <v>190</v>
-      </c>
+      <c r="B61" s="41" t="inlineStr"/>
       <c r="C61" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -8338,7 +8392,7 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
@@ -8346,15 +8400,17 @@
       <c r="A62" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B62" s="33" t="inlineStr"/>
+      <c r="B62" s="33" t="n">
+        <v>120</v>
+      </c>
       <c r="C62" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D62" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D62" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
@@ -8364,7 +8420,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8429,7 @@
         <v>46354</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
@@ -8392,7 +8448,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
@@ -8400,12 +8456,10 @@
       <c r="A64" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B64" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C64" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="B64" s="33" t="inlineStr"/>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
         </is>
       </c>
       <c r="D64" s="34" t="inlineStr">
@@ -8415,12 +8469,12 @@
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
@@ -8428,25 +8482,27 @@
       <c r="A65" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B65" s="41" t="inlineStr"/>
-      <c r="C65" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D65" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B65" s="41" t="n">
+        <v>190</v>
+      </c>
+      <c r="C65" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D65" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
@@ -8675,26 +8731,26 @@
         <v>46375</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="C74" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D74" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D74" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Pink Thunder”</t>
+          <t>Fly Streetwear x Nike SB Air Force 1 Low “University Gold”</t>
         </is>
       </c>
     </row>
@@ -8703,26 +8759,26 @@
         <v>46375</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="C75" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D75" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D75" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Fly Streetwear x Nike SB Air Force 1 Low “University Gold”</t>
+          <t>Air Jordan 4 “Pink Thunder”</t>
         </is>
       </c>
     </row>

--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High Hype Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$143</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -648,10 +648,10 @@
     <xf numFmtId="166" fontId="10" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -685,7 +685,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -808,12 +808,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Charts'!$A$2:$A$9</f>
+              <f>'Charts'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$B$2:$B$9</f>
+              <f>'Charts'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1581,7 +1581,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 22, 2026  ·  11:09 UTC</t>
+          <t>Generated September 23, 2026  ·  10:59 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1621,20 +1621,20 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="14" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="16" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>$181</t>
+          <t>$182</t>
         </is>
       </c>
       <c r="H5" s="19" t="n"/>
@@ -1737,7 +1737,7 @@
         <v>46290</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46295</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1825,19 +1825,19 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="40" t="inlineStr">
         <is>
@@ -1848,18 +1848,18 @@
         <v>7</v>
       </c>
       <c r="G13" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="H13" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="H13" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Nike Air Max 1000.3</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="C14" s="31" t="n">
-        <v>46291</v>
+        <v>46289</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
@@ -1882,9 +1882,9 @@
         <v>7</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="H14" s="43" t="inlineStr">
+        <v>180</v>
+      </c>
+      <c r="H14" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -1893,19 +1893,19 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
@@ -1916,9 +1916,9 @@
         <v>7</v>
       </c>
       <c r="G15" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="H15" s="42" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="H15" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -1927,7 +1927,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
@@ -1939,7 +1939,7 @@
         <v>46291</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
@@ -1949,8 +1949,10 @@
       <c r="F16" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="30" t="inlineStr"/>
-      <c r="H16" s="43" t="inlineStr">
+      <c r="G16" s="33" t="n">
+        <v>200</v>
+      </c>
+      <c r="H16" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2010,7 +2012,7 @@
         </is>
       </c>
       <c r="B20" s="30" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
@@ -2026,7 +2028,7 @@
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -2036,7 +2038,7 @@
         </is>
       </c>
       <c r="B21" s="35" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
@@ -2044,7 +2046,7 @@
         </is>
       </c>
       <c r="E21" s="35" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G21" s="47" t="inlineStr">
         <is>
@@ -2052,7 +2054,7 @@
         </is>
       </c>
       <c r="H21" s="35" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
@@ -2096,7 +2098,7 @@
         </is>
       </c>
       <c r="E23" s="35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -2139,318 +2141,328 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" ht="10" customHeight="1"/>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="10" customHeight="1"/>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>Weekly Outlook (Next 13 Weeks)</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>Dates</t>
         </is>
       </c>
-      <c r="C30" s="29" t="inlineStr">
+      <c r="C31" s="29" t="inlineStr">
         <is>
           <t>Releases</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr">
+      <c r="D31" s="29" t="inlineStr">
         <is>
           <t>HIGH+EXTREME</t>
         </is>
       </c>
-      <c r="E30" s="29" t="inlineStr">
+      <c r="E31" s="29" t="inlineStr">
         <is>
           <t>Avg Hype Score</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>9/22 – 9/28</t>
-        </is>
-      </c>
-      <c r="C31" s="30" t="n">
-        <v>33</v>
-      </c>
-      <c r="D31" s="39" t="n">
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>9/23 – 9/29</t>
+        </is>
+      </c>
+      <c r="C32" s="30" t="n">
+        <v>37</v>
+      </c>
+      <c r="D32" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>9/30 – 10/6</t>
+        </is>
+      </c>
+      <c r="C33" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="D33" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" s="35" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>10/7 – 10/13</t>
+        </is>
+      </c>
+      <c r="C34" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="30" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="35" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="B35" s="35" t="inlineStr">
+        <is>
+          <t>10/14 – 10/20</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="D35" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" s="35" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>10/21 – 10/27</t>
+        </is>
+      </c>
+      <c r="C36" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" s="30" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="35" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="B37" s="35" t="inlineStr">
+        <is>
+          <t>10/28 – 11/3</t>
+        </is>
+      </c>
+      <c r="C37" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="35" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="inlineStr">
+        <is>
+          <t>11/4 – 11/10</t>
+        </is>
+      </c>
+      <c r="C38" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="30" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>11/11 – 11/17</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="n">
         <v>13</v>
       </c>
-      <c r="E31" s="30" t="n">
+      <c r="D39" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="35" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
+        <is>
+          <t>11/18 – 11/24</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" s="30" t="n">
         <v>5.2</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="35" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="B32" s="35" t="inlineStr">
-        <is>
-          <t>9/29 – 10/5</t>
-        </is>
-      </c>
-      <c r="C32" s="35" t="n">
-        <v>19</v>
-      </c>
-      <c r="D32" s="40" t="n">
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>11/25 – 12/1</t>
+        </is>
+      </c>
+      <c r="C41" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="E32" s="35" t="n">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="B33" s="30" t="inlineStr">
-        <is>
-          <t>10/6 – 10/12</t>
-        </is>
-      </c>
-      <c r="C33" s="30" t="n">
+      <c r="D41" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E41" s="35" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>12/2 – 12/8</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="D33" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="30" t="n">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="35" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="B34" s="35" t="inlineStr">
-        <is>
-          <t>10/13 – 10/19</t>
-        </is>
-      </c>
-      <c r="C34" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="D34" s="40" t="n">
+      <c r="D42" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="30" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="35" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="B43" s="35" t="inlineStr">
+        <is>
+          <t>12/9 – 12/15</t>
+        </is>
+      </c>
+      <c r="C43" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="E34" s="35" t="n">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="B35" s="30" t="inlineStr">
-        <is>
-          <t>10/20 – 10/26</t>
-        </is>
-      </c>
-      <c r="C35" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="D35" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E35" s="30" t="n">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="35" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="B36" s="35" t="inlineStr">
-        <is>
-          <t>10/27 – 11/2</t>
-        </is>
-      </c>
-      <c r="C36" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D36" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="35" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="B37" s="30" t="inlineStr">
-        <is>
-          <t>11/3 – 11/9</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" s="30" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="35" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>11/10 – 11/16</t>
-        </is>
-      </c>
-      <c r="C38" s="35" t="n">
-        <v>12</v>
-      </c>
-      <c r="D38" s="40" t="n">
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="B44" s="30" t="inlineStr">
+        <is>
+          <t>12/16 – 12/22</t>
+        </is>
+      </c>
+      <c r="C44" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="E38" s="35" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="30" t="inlineStr">
-        <is>
-          <t>Week 9</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="inlineStr">
-        <is>
-          <t>11/17 – 11/23</t>
-        </is>
-      </c>
-      <c r="C39" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="D39" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E39" s="30" t="n">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="35" t="inlineStr">
-        <is>
-          <t>Week 10</t>
-        </is>
-      </c>
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>11/24 – 11/30</t>
-        </is>
-      </c>
-      <c r="C40" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="D40" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="E40" s="35" t="n">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="B41" s="30" t="inlineStr">
-        <is>
-          <t>12/1 – 12/7</t>
-        </is>
-      </c>
-      <c r="C41" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="D41" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" s="30" t="n">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="35" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="B42" s="35" t="inlineStr">
-        <is>
-          <t>12/8 – 12/14</t>
-        </is>
-      </c>
-      <c r="C42" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="D42" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="E42" s="35" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="30" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="B43" s="30" t="inlineStr">
-        <is>
-          <t>12/15 – 12/21</t>
-        </is>
-      </c>
-      <c r="C43" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" s="39" t="n">
+      <c r="D44" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="E43" s="30" t="n">
+      <c r="E44" s="30" t="n">
         <v>5.2</v>
       </c>
     </row>
@@ -2462,7 +2474,7 @@
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
@@ -2484,7 +2496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2549,7 +2561,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2565,7 +2577,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2583,7 +2595,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2591,7 +2603,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2599,7 +2611,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2607,7 +2619,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -2641,7 +2653,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2671,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2667,7 +2679,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -2715,6 +2727,16 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2730,7 +2752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2756,7 +2778,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 22, 2026  ·  11:09 UTC</t>
+          <t>Generated September 23, 2026  ·  10:59 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2799,7 +2821,7 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B4" s="33" t="n">
         <v>210</v>
@@ -2809,7 +2831,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2821,23 +2843,23 @@
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Nike GT Future “Varsity Red”</t>
+          <t>Nike GT Future “Unseen Hours”</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="C5" s="50" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2849,35 +2871,35 @@
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Pokémon x adidas Superstar "Pikachu White"</t>
+          <t>Pokémon x adidas Megaride F50 "Rayquaza"</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C6" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D6" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C6" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Nike GT Future “Unseen Hours”</t>
+          <t>Converse SHAI 001 “Green Beam”</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2915,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D7" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2905,7 +2927,7 @@
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Green Beam”</t>
+          <t>Converse SHAI 001 “Ghosted”</t>
         </is>
       </c>
     </row>
@@ -2914,26 +2936,26 @@
         <v>46289</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C8" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Ghosted”</t>
+          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2971,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="D9" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2977,7 +2999,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="43" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -2995,29 +3017,29 @@
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="36" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>225</v>
-      </c>
-      <c r="C11" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D11" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>180</v>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Nike Air Max 1000.3</t>
         </is>
       </c>
     </row>
@@ -3026,16 +3048,16 @@
         <v>46290</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C12" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
@@ -3045,7 +3067,7 @@
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3083,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="42" t="inlineStr">
+      <c r="D13" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3082,26 +3104,26 @@
         <v>46290</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C14" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D14" s="43" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3139,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D15" s="42" t="inlineStr">
+      <c r="D15" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3129,7 +3151,7 @@
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws”</t>
+          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
         </is>
       </c>
     </row>
@@ -3138,14 +3160,14 @@
         <v>46290</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="C16" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D16" s="43" t="inlineStr">
+      <c r="D16" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3157,7 +3179,7 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
+          <t>Nike Ja 4 “Jaws”</t>
         </is>
       </c>
     </row>
@@ -3166,14 +3188,14 @@
         <v>46290</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="C17" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D17" s="42" t="inlineStr">
+      <c r="D17" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3185,23 +3207,23 @@
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
+          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="31" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C18" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D18" s="43" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C18" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3213,7 +3235,7 @@
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
         </is>
       </c>
     </row>
@@ -3222,26 +3244,26 @@
         <v>46291</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="C19" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D19" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
         </is>
       </c>
     </row>
@@ -3250,14 +3272,14 @@
         <v>46291</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D20" s="43" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3269,7 +3291,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3300,7 @@
         <v>46291</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>180</v>
+        <v>125</v>
       </c>
       <c r="C21" s="54" t="inlineStr">
         <is>
@@ -3297,7 +3319,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -3305,25 +3327,27 @@
       <c r="A22" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B22" s="33" t="inlineStr"/>
+      <c r="B22" s="33" t="n">
+        <v>255</v>
+      </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D22" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
@@ -3332,26 +3356,26 @@
         <v>46291</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -3359,17 +3383,15 @@
       <c r="A24" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B24" s="33" t="n">
-        <v>210</v>
-      </c>
+      <c r="B24" s="33" t="inlineStr"/>
       <c r="C24" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D24" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D24" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E24" s="30" t="inlineStr">
@@ -3379,7 +3401,7 @@
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -3388,11 +3410,11 @@
         <v>46291</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C25" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>210</v>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D25" s="38" t="inlineStr">
@@ -3407,7 +3429,7 @@
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -3416,26 +3438,26 @@
         <v>46291</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C26" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D26" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C26" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
@@ -3444,26 +3466,26 @@
         <v>46291</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C27" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D27" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>200</v>
+      </c>
+      <c r="C27" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D27" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3494,7 @@
         <v>46291</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -3486,12 +3508,12 @@
       </c>
       <c r="E28" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -3499,25 +3521,27 @@
       <c r="A29" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B29" s="41" t="inlineStr"/>
-      <c r="C29" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D29" s="42" t="inlineStr">
+      <c r="B29" s="41" t="n">
+        <v>200</v>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D29" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -3528,24 +3552,24 @@
       <c r="B30" s="33" t="n">
         <v>155</v>
       </c>
-      <c r="C30" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D30" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -3554,16 +3578,16 @@
         <v>46291</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="C31" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D31" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D31" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -3573,7 +3597,7 @@
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -3581,27 +3605,25 @@
       <c r="A32" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B32" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C32" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D32" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B32" s="33" t="inlineStr"/>
+      <c r="C32" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
@@ -3610,26 +3632,26 @@
         <v>46291</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C33" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D33" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D33" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
@@ -3638,26 +3660,26 @@
         <v>46291</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="C34" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D34" s="43" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C34" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -3666,80 +3688,80 @@
         <v>46291</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C35" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D35" s="42" t="inlineStr">
+        <v>120</v>
+      </c>
+      <c r="C35" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="31" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B36" s="33" t="inlineStr"/>
-      <c r="C36" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D36" s="43" t="inlineStr">
+        <v>46291</v>
+      </c>
+      <c r="B36" s="33" t="n">
+        <v>210</v>
+      </c>
+      <c r="C36" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D36" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B37" s="41" t="n">
-        <v>170</v>
-      </c>
+        <v>46293</v>
+      </c>
+      <c r="B37" s="41" t="inlineStr"/>
       <c r="C37" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D37" s="42" t="inlineStr">
+      <c r="D37" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
+          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3777,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D38" s="43" t="inlineStr">
+      <c r="D38" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3783,7 +3805,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D39" s="42" t="inlineStr">
+      <c r="D39" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3795,25 +3817,25 @@
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Red”</t>
+          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>135</v>
-      </c>
-      <c r="C40" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D40" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C40" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D40" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
@@ -3823,7 +3845,7 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Air Bakin “Varsity Red”</t>
         </is>
       </c>
     </row>
@@ -3832,26 +3854,26 @@
         <v>46295</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D41" s="42" t="inlineStr">
+      <c r="D41" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3882,7 @@
         <v>46295</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C42" s="39" t="inlineStr">
         <is>
@@ -3879,7 +3901,7 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -3888,26 +3910,26 @@
         <v>46295</v>
       </c>
       <c r="B43" s="41" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="C43" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D43" s="42" t="inlineStr">
+      <c r="D43" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
@@ -3915,13 +3937,15 @@
       <c r="A44" s="31" t="n">
         <v>46295</v>
       </c>
-      <c r="B44" s="33" t="inlineStr"/>
+      <c r="B44" s="33" t="n">
+        <v>125</v>
+      </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D44" s="43" t="inlineStr">
+      <c r="D44" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3933,7 +3957,7 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
@@ -3970,14 +3994,14 @@
         <v>46295</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C46" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D46" s="43" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C46" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D46" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3989,7 +4013,7 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Nike Zoom Huarache 2K4 “UCLA”</t>
         </is>
       </c>
     </row>
@@ -3998,14 +4022,14 @@
         <v>46295</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="C47" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D47" s="42" t="inlineStr">
+      <c r="D47" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4017,23 +4041,23 @@
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Nike Zoom Huarache 2K4 “UCLA”</t>
+          <t>Tom Sachs x Nike General Purpose Shoe “Demerits”</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="31" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C48" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D48" s="43" t="inlineStr">
+      <c r="D48" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4045,7 +4069,7 @@
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Tom Sachs x Nike General Purpose Shoe “Demerits”</t>
+          <t>Nike Caitlin 1 “Racer Blue”</t>
         </is>
       </c>
     </row>
@@ -4054,26 +4078,26 @@
         <v>46296</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D49" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D49" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Howard” 2026</t>
+          <t>Kobe Bryant x Nike Air Force 1 Low “Black Purple Stardust”</t>
         </is>
       </c>
     </row>
@@ -4082,14 +4106,14 @@
         <v>46296</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C50" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D50" s="43" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C50" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D50" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4101,35 +4125,35 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Racer Blue”</t>
+          <t>Nike Kobe Air Force 1 Low</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D51" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D51" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
@@ -4138,16 +4162,16 @@
         <v>46297</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D52" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D52" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
@@ -4157,7 +4181,7 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Air Jordan 6 Low “Black Pink Foam”</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4197,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="42" t="inlineStr">
+      <c r="D53" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4194,7 +4218,7 @@
         <v>46298</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
@@ -4213,91 +4237,91 @@
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 16 “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D55" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D55" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46303</v>
+        <v>46300</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C56" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D56" s="43" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C56" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D56" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C57" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D57" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C57" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D57" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
+          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
         </is>
       </c>
     </row>
@@ -4306,26 +4330,26 @@
         <v>46304</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C58" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D58" s="43" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C58" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D58" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
+          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
         </is>
       </c>
     </row>
@@ -4334,54 +4358,54 @@
         <v>46304</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>220</v>
-      </c>
-      <c r="C59" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D59" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C59" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D59" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Aminé x New Balance 992 “Outdoor School”</t>
+          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>135</v>
+        <v>220</v>
       </c>
       <c r="C60" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D60" s="43" t="inlineStr">
+      <c r="D60" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Texas”</t>
+          <t>Aminé x New Balance 992 “Outdoor School”</t>
         </is>
       </c>
     </row>
@@ -4390,42 +4414,42 @@
         <v>46305</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C61" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D61" s="42" t="inlineStr">
+        <v>135</v>
+      </c>
+      <c r="C61" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D61" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Nike KD 6 “Texas”</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46310</v>
+        <v>46305</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C62" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D62" s="43" t="inlineStr">
+        <v>180</v>
+      </c>
+      <c r="C62" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D62" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4437,7 +4461,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
@@ -4448,42 +4472,42 @@
       <c r="B63" s="41" t="n">
         <v>125</v>
       </c>
-      <c r="C63" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D63" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C63" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D63" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="31" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>240</v>
+        <v>125</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D64" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
@@ -4493,7 +4517,7 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
@@ -4502,14 +4526,14 @@
         <v>46311</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D65" s="42" t="inlineStr">
+      <c r="D65" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4521,7 +4545,7 @@
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
@@ -4530,14 +4554,14 @@
         <v>46311</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D66" s="43" t="inlineStr">
+      <c r="D66" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4549,7 +4573,7 @@
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -4558,14 +4582,14 @@
         <v>46311</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D67" s="42" t="inlineStr">
+      <c r="D67" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4577,35 +4601,35 @@
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D68" s="43" t="inlineStr">
+      <c r="D68" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -4614,14 +4638,14 @@
         <v>46312</v>
       </c>
       <c r="B69" s="41" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D69" s="42" t="inlineStr">
+      <c r="D69" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4633,105 +4657,105 @@
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46315</v>
+        <v>46312</v>
       </c>
       <c r="B70" s="33" t="n">
-        <v>160</v>
-      </c>
-      <c r="C70" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D70" s="43" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C70" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D70" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 “Reese’s”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B71" s="41" t="inlineStr"/>
+        <v>46315</v>
+      </c>
+      <c r="B71" s="41" t="n">
+        <v>160</v>
+      </c>
       <c r="C71" s="50" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D71" s="42" t="inlineStr">
+      <c r="D71" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>SZA x Vans VANSZA Collection</t>
+          <t>Reebok Angel Reese 1 “Reese’s”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B72" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C72" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D72" s="43" t="inlineStr">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="33" t="inlineStr"/>
+      <c r="C72" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D72" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “NYC Rat”</t>
+          <t>SZA x Vans VANSZA Collection</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D73" s="42" t="inlineStr">
+      <c r="D73" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4743,35 +4767,35 @@
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Nike Air Force 1 Low “NYC Rat”</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C74" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D74" s="43" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C74" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D74" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>PUMA Hali 1 “Pacers”</t>
         </is>
       </c>
     </row>
@@ -4780,14 +4804,14 @@
         <v>46319</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C75" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D75" s="42" t="inlineStr">
+        <v>190</v>
+      </c>
+      <c r="C75" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D75" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4799,7 +4823,7 @@
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
@@ -4808,26 +4832,26 @@
         <v>46319</v>
       </c>
       <c r="B76" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C76" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D76" s="43" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C76" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D76" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
@@ -4836,16 +4860,16 @@
         <v>46319</v>
       </c>
       <c r="B77" s="41" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C77" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D77" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D77" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E77" s="35" t="inlineStr">
@@ -4855,7 +4879,7 @@
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
@@ -4864,16 +4888,16 @@
         <v>46319</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="C78" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D78" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D78" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E78" s="30" t="inlineStr">
@@ -4883,7 +4907,7 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
@@ -4892,26 +4916,26 @@
         <v>46319</v>
       </c>
       <c r="B79" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C79" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D79" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C79" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D79" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E79" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
@@ -4920,16 +4944,16 @@
         <v>46319</v>
       </c>
       <c r="B80" s="33" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C80" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D80" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D80" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E80" s="30" t="inlineStr">
@@ -4939,53 +4963,53 @@
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="36" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B81" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C81" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D81" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>170</v>
+      </c>
+      <c r="C81" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D81" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E81" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F81" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="31" t="n">
-        <v>46325</v>
+        <v>46319</v>
       </c>
       <c r="B82" s="33" t="n">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="C82" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D82" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D82" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E82" s="30" t="inlineStr">
@@ -4995,35 +5019,35 @@
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 High “University Red”</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="36" t="n">
-        <v>46325</v>
+        <v>46320</v>
       </c>
       <c r="B83" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C83" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D83" s="42" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C83" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D83" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E83" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F83" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5063,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D84" s="43" t="inlineStr">
+      <c r="D84" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5051,51 +5075,51 @@
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Halloween”</t>
+          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="36" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="B85" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C85" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D85" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C85" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D85" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E85" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Nike Ja 4 High “University Red”</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="31" t="n">
-        <v>46331</v>
+        <v>46325</v>
       </c>
       <c r="B86" s="33" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="C86" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D86" s="43" t="inlineStr">
+      <c r="D86" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5107,35 +5131,35 @@
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
+          <t>Nike Book 2 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="36" t="n">
-        <v>46331</v>
+        <v>46326</v>
       </c>
       <c r="B87" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C87" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D87" s="42" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C87" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D87" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E87" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
@@ -5151,9 +5175,9 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D88" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D88" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E88" s="30" t="inlineStr">
@@ -5163,23 +5187,23 @@
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max Foamdome “Eggplant”</t>
+          <t>Nike Air Max Foamdome “Eggplant” 2026</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="36" t="n">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="C89" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D89" s="42" t="inlineStr">
+      <c r="D89" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5191,137 +5215,137 @@
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Desert Night”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="31" t="n">
-        <v>46333</v>
+        <v>46331</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>215</v>
-      </c>
-      <c r="C90" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D90" s="43" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C90" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D90" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E90" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="36" t="n">
-        <v>46333</v>
+        <v>46331</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>245</v>
-      </c>
-      <c r="C91" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D91" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>265</v>
+      </c>
+      <c r="C91" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D91" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E91" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Nike Air Max Foamdome “Eggplant”</t>
         </is>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="31" t="n">
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="B92" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C92" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D92" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>145</v>
+      </c>
+      <c r="C92" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D92" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E92" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Nike Book 2 “Desert Night”</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="36" t="n">
-        <v>46335</v>
+        <v>46333</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C93" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D93" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D93" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E93" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="31" t="n">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="B94" s="33" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C94" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D94" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D94" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E94" s="30" t="inlineStr">
@@ -5331,53 +5355,53 @@
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="36" t="n">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="B95" s="41" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C95" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D95" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D95" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E95" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F95" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="31" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B96" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C96" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D96" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>200</v>
+      </c>
+      <c r="C96" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D96" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E96" s="30" t="inlineStr">
@@ -5387,35 +5411,35 @@
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal” 2026</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="36" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B97" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C97" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D97" s="42" t="inlineStr">
+        <v>235</v>
+      </c>
+      <c r="C97" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D97" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E97" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F97" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -5431,9 +5455,9 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D98" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D98" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E98" s="30" t="inlineStr">
@@ -5443,41 +5467,41 @@
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal”</t>
+          <t>Nike Air Bakin “Varsity Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="36" t="n">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="B99" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C99" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D99" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C99" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D99" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E99" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F99" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Diamond Turf 2 Patent “Black Red”</t>
+          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="31" t="n">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="B100" s="33" t="n">
         <v>170</v>
@@ -5487,7 +5511,7 @@
           <t>MED</t>
         </is>
       </c>
-      <c r="D100" s="43" t="inlineStr">
+      <c r="D100" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5499,76 +5523,76 @@
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Diamond Turf 2</t>
+          <t>Nike Air Bakin “Varsity Royal”</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="36" t="n">
-        <v>46340</v>
+        <v>46339</v>
       </c>
       <c r="B101" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C101" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D101" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C101" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D101" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E101" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Air Diamond Turf 2 Patent “Black Red”</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="31" t="n">
-        <v>46340</v>
+        <v>46339</v>
       </c>
       <c r="B102" s="33" t="n">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="C102" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D102" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D102" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E102" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
+          <t>Nike Air Diamond Turf 2</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="36" t="n">
-        <v>46341</v>
+        <v>46340</v>
       </c>
       <c r="B103" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C103" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>255</v>
+      </c>
+      <c r="C103" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D103" s="38" t="inlineStr">
@@ -5578,25 +5602,25 @@
       </c>
       <c r="E103" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F103" s="35" t="inlineStr">
         <is>
-          <t>Playa Society x Nike A’Two</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="31" t="n">
-        <v>46342</v>
+        <v>46340</v>
       </c>
       <c r="B104" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C104" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>240</v>
+      </c>
+      <c r="C104" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D104" s="34" t="inlineStr">
@@ -5611,25 +5635,25 @@
       </c>
       <c r="F104" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
         </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="36" t="n">
-        <v>46342</v>
+        <v>46341</v>
       </c>
       <c r="B105" s="41" t="n">
-        <v>230</v>
-      </c>
-      <c r="C105" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D105" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>155</v>
+      </c>
+      <c r="C105" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D105" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E105" s="35" t="inlineStr">
@@ -5639,79 +5663,79 @@
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Playa Society x Nike A’Two</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="31" t="n">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="B106" s="33" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C106" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D106" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D106" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E106" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F106" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="36" t="n">
-        <v>46345</v>
+        <v>46342</v>
       </c>
       <c r="B107" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C107" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D107" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>240</v>
+      </c>
+      <c r="C107" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D107" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E107" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F107" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Navy”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="31" t="n">
-        <v>46346</v>
+        <v>46343</v>
       </c>
       <c r="B108" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C108" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D108" s="43" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C108" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D108" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5723,13 +5747,13 @@
       </c>
       <c r="F108" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Be Legendary”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="36" t="n">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="B109" s="41" t="n">
         <v>130</v>
@@ -5739,75 +5763,75 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D109" s="42" t="inlineStr">
+      <c r="D109" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E109" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
+          <t>Vans Old Skool 36 Pearlized “Navy”</t>
         </is>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="31" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>165</v>
-      </c>
-      <c r="C110" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D110" s="43" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C110" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D110" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E110" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Nike Book 2 “Be Legendary”</t>
         </is>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="36" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B111" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C111" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D111" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C111" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D111" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E111" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
         </is>
       </c>
     </row>
@@ -5816,26 +5840,26 @@
         <v>46347</v>
       </c>
       <c r="B112" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C112" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D112" s="43" t="inlineStr">
+        <v>165</v>
+      </c>
+      <c r="C112" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D112" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E112" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F112" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Snow White”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -5844,16 +5868,16 @@
         <v>46347</v>
       </c>
       <c r="B113" s="41" t="n">
-        <v>230</v>
+        <v>125</v>
       </c>
       <c r="C113" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D113" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D113" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E113" s="35" t="inlineStr">
@@ -5863,7 +5887,7 @@
       </c>
       <c r="F113" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -5872,26 +5896,26 @@
         <v>46347</v>
       </c>
       <c r="B114" s="33" t="n">
-        <v>215</v>
-      </c>
-      <c r="C114" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D114" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C114" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D114" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E114" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F114" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
@@ -5900,16 +5924,16 @@
         <v>46347</v>
       </c>
       <c r="B115" s="41" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="C115" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D115" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D115" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E115" s="35" t="inlineStr">
@@ -5919,7 +5943,7 @@
       </c>
       <c r="F115" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -5927,81 +5951,81 @@
       <c r="A116" s="31" t="n">
         <v>46347</v>
       </c>
-      <c r="B116" s="33" t="inlineStr"/>
-      <c r="C116" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D116" s="43" t="inlineStr">
+      <c r="B116" s="33" t="n">
+        <v>215</v>
+      </c>
+      <c r="C116" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D116" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E116" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="36" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B117" s="41" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="C117" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D117" s="42" t="inlineStr">
+      <c r="D117" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E117" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F117" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="31" t="n">
-        <v>46353</v>
-      </c>
-      <c r="B118" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C118" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D118" s="43" t="inlineStr">
+        <v>46347</v>
+      </c>
+      <c r="B118" s="33" t="inlineStr"/>
+      <c r="C118" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D118" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F118" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
         </is>
       </c>
     </row>
@@ -6010,42 +6034,42 @@
         <v>46353</v>
       </c>
       <c r="B119" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C119" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D119" s="42" t="inlineStr">
+        <v>230</v>
+      </c>
+      <c r="C119" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D119" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E119" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Black”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="31" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B120" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C120" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D120" s="43" t="inlineStr">
+        <v>240</v>
+      </c>
+      <c r="C120" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D120" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6057,33 +6081,35 @@
       </c>
       <c r="F120" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Warning Code”</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="36" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B121" s="41" t="inlineStr"/>
-      <c r="C121" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D121" s="42" t="inlineStr">
+        <v>46353</v>
+      </c>
+      <c r="B121" s="41" t="n">
+        <v>130</v>
+      </c>
+      <c r="C121" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D121" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E121" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F121" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Vans Old Skool 36 Pearlized “Black”</t>
         </is>
       </c>
     </row>
@@ -6092,16 +6118,16 @@
         <v>46354</v>
       </c>
       <c r="B122" s="33" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="C122" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D122" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D122" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E122" s="30" t="inlineStr">
@@ -6111,7 +6137,7 @@
       </c>
       <c r="F122" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
@@ -6120,16 +6146,16 @@
         <v>46354</v>
       </c>
       <c r="B123" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C123" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D123" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C123" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D123" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E123" s="35" t="inlineStr">
@@ -6139,7 +6165,7 @@
       </c>
       <c r="F123" s="35" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Nike Caitlin 1 “Warning Code”</t>
         </is>
       </c>
     </row>
@@ -6147,15 +6173,17 @@
       <c r="A124" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B124" s="33" t="inlineStr"/>
-      <c r="C124" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D124" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B124" s="33" t="n">
+        <v>240</v>
+      </c>
+      <c r="C124" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D124" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E124" s="30" t="inlineStr">
@@ -6165,7 +6193,7 @@
       </c>
       <c r="F124" s="30" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Aunt Pearl” 2026</t>
+          <t>Nike Air Foamposite Pro “FSU”</t>
         </is>
       </c>
     </row>
@@ -6173,10 +6201,12 @@
       <c r="A125" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B125" s="41" t="inlineStr"/>
-      <c r="C125" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
+      <c r="B125" s="41" t="n">
+        <v>120</v>
+      </c>
+      <c r="C125" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D125" s="38" t="inlineStr">
@@ -6186,12 +6216,12 @@
       </c>
       <c r="E125" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F125" s="35" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -6199,15 +6229,13 @@
       <c r="A126" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B126" s="33" t="n">
-        <v>190</v>
-      </c>
+      <c r="B126" s="33" t="inlineStr"/>
       <c r="C126" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D126" s="43" t="inlineStr">
+      <c r="D126" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6219,25 +6247,25 @@
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="36" t="n">
-        <v>46357</v>
+        <v>46354</v>
       </c>
       <c r="B127" s="41" t="n">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="C127" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D127" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D127" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E127" s="35" t="inlineStr">
@@ -6247,23 +6275,21 @@
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Chosen 1s”</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" s="31" t="n">
-        <v>46359</v>
-      </c>
-      <c r="B128" s="33" t="n">
-        <v>170</v>
-      </c>
+        <v>46354</v>
+      </c>
+      <c r="B128" s="33" t="inlineStr"/>
       <c r="C128" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D128" s="43" t="inlineStr">
+      <c r="D128" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6275,23 +6301,23 @@
       </c>
       <c r="F128" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Black/White”</t>
+          <t>Nike KD 6 “Aunt Pearl” 2026</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="36" t="n">
-        <v>46361</v>
+        <v>46354</v>
       </c>
       <c r="B129" s="41" t="inlineStr"/>
-      <c r="C129" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D129" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="C129" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D129" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E129" s="35" t="inlineStr">
@@ -6301,63 +6327,63 @@
       </c>
       <c r="F129" s="35" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" s="31" t="n">
-        <v>46361</v>
+        <v>46357</v>
       </c>
       <c r="B130" s="33" t="n">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="C130" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D130" s="43" t="inlineStr">
+      <c r="D130" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E130" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F130" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Nike LeBron 24 “Chosen 1s”</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1">
       <c r="A131" s="36" t="n">
-        <v>46361</v>
+        <v>46359</v>
       </c>
       <c r="B131" s="41" t="n">
-        <v>300</v>
+        <v>170</v>
       </c>
       <c r="C131" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D131" s="42" t="inlineStr">
+      <c r="D131" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E131" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F131" s="35" t="inlineStr">
         <is>
-          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
+          <t>Nike Air Bakin “Black White”</t>
         </is>
       </c>
     </row>
@@ -6365,27 +6391,25 @@
       <c r="A132" s="31" t="n">
         <v>46361</v>
       </c>
-      <c r="B132" s="33" t="n">
-        <v>300</v>
-      </c>
-      <c r="C132" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D132" s="55" t="inlineStr">
-        <is>
-          <t>Confirmed App</t>
+      <c r="B132" s="33" t="inlineStr"/>
+      <c r="C132" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D132" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E132" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F132" s="30" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish “Auburn Timber”</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
@@ -6394,108 +6418,110 @@
         <v>46361</v>
       </c>
       <c r="B133" s="41" t="n">
-        <v>300</v>
-      </c>
-      <c r="C133" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D133" s="42" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C133" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D133" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E133" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F133" s="35" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="31" t="n">
-        <v>46367</v>
+        <v>46361</v>
       </c>
       <c r="B134" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C134" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D134" s="43" t="inlineStr">
+        <v>300</v>
+      </c>
+      <c r="C134" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D134" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E134" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F134" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Floral” 2026</t>
+          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c r="A135" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B135" s="41" t="inlineStr"/>
-      <c r="C135" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D135" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>46361</v>
+      </c>
+      <c r="B135" s="41" t="n">
+        <v>300</v>
+      </c>
+      <c r="C135" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D135" s="55" t="inlineStr">
+        <is>
+          <t>Confirmed App</t>
         </is>
       </c>
       <c r="E135" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F135" s="35" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Pharrell x adidas Adistar Jellyfish “Auburn Timber”</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="31" t="n">
-        <v>46367</v>
+        <v>46361</v>
       </c>
       <c r="B136" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C136" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D136" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>300</v>
+      </c>
+      <c r="C136" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D136" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E136" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F136" s="30" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Pharrell x adidas Adistar Jellyfish</t>
         </is>
       </c>
     </row>
@@ -6504,64 +6530,62 @@
         <v>46367</v>
       </c>
       <c r="B137" s="41" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="C137" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D137" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D137" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E137" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F137" s="35" t="inlineStr">
         <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="A138" s="31" t="n">
-        <v>46368</v>
+        <v>46367</v>
       </c>
       <c r="B138" s="33" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C138" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D138" s="43" t="inlineStr">
+      <c r="D138" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E138" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F138" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam” 2026</t>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
         </is>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1">
       <c r="A139" s="36" t="n">
-        <v>46375</v>
-      </c>
-      <c r="B139" s="41" t="n">
-        <v>120</v>
-      </c>
+        <v>46367</v>
+      </c>
+      <c r="B139" s="41" t="inlineStr"/>
       <c r="C139" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6574,28 +6598,28 @@
       </c>
       <c r="E139" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F139" s="35" t="inlineStr">
         <is>
-          <t>Fly Streetwear x Nike SB Air Force 1 Low “University Gold”</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" s="31" t="n">
-        <v>46375</v>
+        <v>46367</v>
       </c>
       <c r="B140" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C140" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D140" s="43" t="inlineStr">
+        <v>190</v>
+      </c>
+      <c r="C140" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D140" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6607,35 +6631,35 @@
       </c>
       <c r="F140" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Flight The Glove “Royal Blue”</t>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1">
       <c r="A141" s="36" t="n">
-        <v>46375</v>
+        <v>46368</v>
       </c>
       <c r="B141" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C141" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D141" s="42" t="inlineStr">
+        <v>235</v>
+      </c>
+      <c r="C141" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D141" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E141" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F141" s="35" t="inlineStr">
         <is>
-          <t>Nike GT Future “Triple Black”</t>
+          <t>Air Jordan 11 “Space Jam” 2026</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6675,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D142" s="43" t="inlineStr">
+      <c r="D142" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6669,34 +6693,118 @@
     </row>
     <row r="143" ht="15" customHeight="1">
       <c r="A143" s="36" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B143" s="41" t="n">
+        <v>120</v>
+      </c>
+      <c r="C143" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D143" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E143" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F143" s="35" t="inlineStr">
+        <is>
+          <t>Fly Streetwear x Nike SB Air Force 1 Low “University Gold”</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="15" customHeight="1">
+      <c r="A144" s="31" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B144" s="33" t="n">
+        <v>170</v>
+      </c>
+      <c r="C144" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D144" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E144" s="30" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F144" s="30" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom Flight The Glove “Royal Blue”</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="15" customHeight="1">
+      <c r="A145" s="36" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B145" s="41" t="n">
+        <v>210</v>
+      </c>
+      <c r="C145" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D145" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E145" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F145" s="35" t="inlineStr">
+        <is>
+          <t>Nike GT Future “Triple Black”</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="15" customHeight="1">
+      <c r="A146" s="31" t="n">
         <v>46377</v>
       </c>
-      <c r="B143" s="41" t="n">
+      <c r="B146" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C143" s="54" t="inlineStr">
+      <c r="C146" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D143" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E143" s="35" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="F143" s="35" t="inlineStr">
+      <c r="D146" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E146" s="30" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F146" s="30" t="inlineStr">
         <is>
           <t>Nike Caitlin 1 “Chiefs”</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F143"/>
+  <autoFilter ref="A3:F146"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -6711,7 +6819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6737,7 +6845,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 22, 2026  ·  11:09 UTC</t>
+          <t>Generated September 23, 2026  ·  10:59 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -6780,14 +6888,14 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>225</v>
-      </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
+        <v>180</v>
+      </c>
+      <c r="C4" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D4" s="34" t="inlineStr">
@@ -6797,96 +6905,96 @@
       </c>
       <c r="E4" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Nike Air Max 1000.3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C6" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D6" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="36" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>140</v>
+        <v>205</v>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D7" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
@@ -6894,13 +7002,15 @@
       <c r="A8" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B8" s="33" t="inlineStr"/>
+      <c r="B8" s="33" t="n">
+        <v>200</v>
+      </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6912,7 +7022,7 @@
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -6921,7 +7031,7 @@
         <v>46291</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
@@ -6940,7 +7050,7 @@
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
@@ -6949,16 +7059,16 @@
         <v>46291</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D10" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
@@ -6968,7 +7078,7 @@
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -6976,27 +7086,25 @@
       <c r="A11" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B11" s="41" t="n">
-        <v>200</v>
-      </c>
+      <c r="B11" s="41" t="inlineStr"/>
       <c r="C11" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D11" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -7005,26 +7113,26 @@
         <v>46291</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="C12" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7141,7 @@
         <v>46291</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C13" s="40" t="inlineStr">
         <is>
@@ -7047,12 +7155,12 @@
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -7061,26 +7169,26 @@
         <v>46291</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D14" s="43" t="inlineStr">
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -7089,16 +7197,16 @@
         <v>46291</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>255</v>
+        <v>155</v>
       </c>
       <c r="C15" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D15" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D15" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
@@ -7108,7 +7216,7 @@
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -7117,16 +7225,16 @@
         <v>46291</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="C16" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D16" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
@@ -7136,25 +7244,25 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="36" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="C17" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D17" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
@@ -7164,13 +7272,13 @@
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="31" t="n">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="B18" s="33" t="n">
         <v>210</v>
@@ -7180,19 +7288,19 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D18" s="43" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
@@ -7201,16 +7309,16 @@
         <v>46295</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="C19" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D19" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
@@ -7220,7 +7328,7 @@
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
@@ -7229,16 +7337,16 @@
         <v>46295</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D20" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
@@ -7248,7 +7356,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -7256,25 +7364,27 @@
       <c r="A21" s="36" t="n">
         <v>46295</v>
       </c>
-      <c r="B21" s="41" t="inlineStr"/>
+      <c r="B21" s="41" t="n">
+        <v>210</v>
+      </c>
       <c r="C21" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D21" s="42" t="inlineStr">
+      <c r="D21" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Black Rat”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
@@ -7283,14 +7393,14 @@
         <v>46295</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D22" s="43" t="inlineStr">
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7302,7 +7412,7 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
@@ -7311,26 +7421,26 @@
         <v>46296</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Howard” 2026</t>
+          <t>Kobe Bryant x Nike Air Force 1 Low “Black Purple Stardust”</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7456,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D24" s="43" t="inlineStr">
+      <c r="D24" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7392,17 +7502,17 @@
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="31" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>205</v>
+        <v>150</v>
       </c>
       <c r="C26" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D26" s="43" t="inlineStr">
+      <c r="D26" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7414,7 +7524,7 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Air Jordan 6 Low “Black Pink Foam”</t>
         </is>
       </c>
     </row>
@@ -7423,16 +7533,16 @@
         <v>46298</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D27" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
@@ -7442,53 +7552,53 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="31" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>200</v>
+        <v>245</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D28" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Air Jordan 16 “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="36" t="n">
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D29" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D29" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -7498,25 +7608,25 @@
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="31" t="n">
-        <v>46310</v>
+        <v>46300</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="C30" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D30" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
@@ -7526,53 +7636,53 @@
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="36" t="n">
-        <v>46311</v>
+        <v>46305</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="C31" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D31" s="42" t="inlineStr">
+      <c r="D31" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D32" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D32" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
@@ -7582,7 +7692,7 @@
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7708,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D33" s="42" t="inlineStr">
+      <c r="D33" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7610,7 +7720,7 @@
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7736,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D34" s="43" t="inlineStr">
+      <c r="D34" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7638,147 +7748,147 @@
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D35" s="42" t="inlineStr">
+      <c r="D35" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="31" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B36" s="33" t="n">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="C36" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D36" s="43" t="inlineStr">
+      <c r="D36" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46318</v>
+        <v>46312</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="C37" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D37" s="42" t="inlineStr">
+      <c r="D37" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “NYC Rat”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="31" t="n">
-        <v>46319</v>
+        <v>46312</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C38" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D38" s="43" t="inlineStr">
+      <c r="D38" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E38" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B39" s="41" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C39" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D39" s="42" t="inlineStr">
+      <c r="D39" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Nike Air Force 1 Low “NYC Rat”</t>
         </is>
       </c>
     </row>
@@ -7787,16 +7897,16 @@
         <v>46319</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C40" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D40" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D40" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E40" s="30" t="inlineStr">
@@ -7806,7 +7916,7 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
@@ -7815,98 +7925,98 @@
         <v>46319</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D41" s="42" t="inlineStr">
+      <c r="D41" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="31" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="C42" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D42" s="43" t="inlineStr">
+      <c r="D42" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E42" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="36" t="n">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="B43" s="41" t="n">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="C43" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D43" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D43" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="31" t="n">
-        <v>46333</v>
+        <v>46320</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D44" s="43" t="inlineStr">
+      <c r="D44" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -7918,25 +8028,25 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D45" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D45" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
@@ -7946,7 +8056,7 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
@@ -7955,16 +8065,16 @@
         <v>46333</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D46" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D46" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
@@ -7974,16 +8084,16 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="36" t="n">
-        <v>46335</v>
+        <v>46333</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
@@ -7997,30 +8107,30 @@
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Black Mummy Duck”</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="31" t="n">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D48" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
@@ -8030,7 +8140,7 @@
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8156,7 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D49" s="42" t="inlineStr">
+      <c r="D49" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8064,19 +8174,19 @@
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="31" t="n">
-        <v>46340</v>
+        <v>46337</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="C50" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D50" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D50" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E50" s="30" t="inlineStr">
@@ -8086,13 +8196,13 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46342</v>
+        <v>46340</v>
       </c>
       <c r="B51" s="41" t="n">
         <v>255</v>
@@ -8114,7 +8224,7 @@
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
@@ -8123,44 +8233,44 @@
         <v>46342</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D52" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D52" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="36" t="n">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D53" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
@@ -8170,35 +8280,35 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="31" t="n">
-        <v>46347</v>
+        <v>46343</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D54" s="43" t="inlineStr">
+      <c r="D54" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
@@ -8207,26 +8317,26 @@
         <v>46347</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D55" s="42" t="inlineStr">
+      <c r="D55" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
@@ -8235,16 +8345,16 @@
         <v>46347</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>230</v>
+        <v>125</v>
       </c>
       <c r="C56" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D56" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D56" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
@@ -8254,7 +8364,7 @@
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
@@ -8263,26 +8373,26 @@
         <v>46347</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C57" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D57" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D57" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
@@ -8291,54 +8401,54 @@
         <v>46347</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="C58" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D58" s="43" t="inlineStr">
+      <c r="D58" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D59" s="42" t="inlineStr">
+      <c r="D59" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
@@ -8347,40 +8457,42 @@
         <v>46353</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D60" s="43" t="inlineStr">
+      <c r="D60" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B61" s="41" t="inlineStr"/>
+        <v>46353</v>
+      </c>
+      <c r="B61" s="41" t="n">
+        <v>240</v>
+      </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D61" s="42" t="inlineStr">
+      <c r="D61" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8392,7 +8504,7 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
@@ -8401,16 +8513,16 @@
         <v>46354</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="C62" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D62" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D62" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
@@ -8420,7 +8532,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8541,7 @@
         <v>46354</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
@@ -8448,7 +8560,7 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Nike Air Foamposite Pro “FSU”</t>
         </is>
       </c>
     </row>
@@ -8456,10 +8568,12 @@
       <c r="A64" s="31" t="n">
         <v>46354</v>
       </c>
-      <c r="B64" s="33" t="inlineStr"/>
-      <c r="C64" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
+      <c r="B64" s="33" t="n">
+        <v>120</v>
+      </c>
+      <c r="C64" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D64" s="34" t="inlineStr">
@@ -8469,12 +8583,12 @@
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
@@ -8482,15 +8596,13 @@
       <c r="A65" s="36" t="n">
         <v>46354</v>
       </c>
-      <c r="B65" s="41" t="n">
-        <v>190</v>
-      </c>
+      <c r="B65" s="41" t="inlineStr"/>
       <c r="C65" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D65" s="42" t="inlineStr">
+      <c r="D65" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8502,25 +8614,25 @@
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46357</v>
+        <v>46354</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D66" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D66" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E66" s="30" t="inlineStr">
@@ -8530,23 +8642,23 @@
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Chosen 1s”</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46361</v>
+        <v>46354</v>
       </c>
       <c r="B67" s="41" t="inlineStr"/>
-      <c r="C67" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D67" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="C67" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D67" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
@@ -8556,79 +8668,79 @@
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46361</v>
+        <v>46357</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D68" s="43" t="inlineStr">
+      <c r="D68" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Nike LeBron 24 “Chosen 1s”</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B69" s="41" t="n">
-        <v>240</v>
-      </c>
+        <v>46361</v>
+      </c>
+      <c r="B69" s="41" t="inlineStr"/>
       <c r="C69" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D69" s="42" t="inlineStr">
+      <c r="D69" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Floral” 2026</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B70" s="33" t="inlineStr"/>
+        <v>46361</v>
+      </c>
+      <c r="B70" s="33" t="n">
+        <v>215</v>
+      </c>
       <c r="C70" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D70" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D70" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E70" s="30" t="inlineStr">
@@ -8638,7 +8750,7 @@
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
@@ -8675,14 +8787,14 @@
         <v>46367</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="C72" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D72" s="43" t="inlineStr">
+      <c r="D72" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -8694,25 +8806,23 @@
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46368</v>
-      </c>
-      <c r="B73" s="41" t="n">
-        <v>235</v>
-      </c>
+        <v>46367</v>
+      </c>
+      <c r="B73" s="41" t="inlineStr"/>
       <c r="C73" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D73" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D73" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
@@ -8722,25 +8832,25 @@
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam” 2026</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46375</v>
+        <v>46367</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="C74" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D74" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D74" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
@@ -8750,40 +8860,96 @@
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Fly Streetwear x Nike SB Air Force 1 Low “University Gold”</t>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
+        <v>46368</v>
+      </c>
+      <c r="B75" s="41" t="n">
+        <v>235</v>
+      </c>
+      <c r="C75" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D75" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E75" s="35" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F75" s="35" t="inlineStr">
+        <is>
+          <t>Air Jordan 11 “Space Jam” 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="31" t="n">
         <v>46375</v>
       </c>
-      <c r="B75" s="41" t="n">
+      <c r="B76" s="33" t="n">
         <v>220</v>
       </c>
-      <c r="C75" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D75" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E75" s="35" t="inlineStr">
+      <c r="C76" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D76" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="F75" s="35" t="inlineStr">
+      <c r="F76" s="30" t="inlineStr">
         <is>
           <t>Air Jordan 4 “Pink Thunder”</t>
         </is>
       </c>
     </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="36" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B77" s="41" t="n">
+        <v>120</v>
+      </c>
+      <c r="C77" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D77" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E77" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F77" s="35" t="inlineStr">
+        <is>
+          <t>Fly Streetwear x Nike SB Air Force 1 Low “University Gold”</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:F75"/>
+  <autoFilter ref="A3:F77"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High Hype Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -685,7 +685,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1581,7 +1581,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 23, 2026  ·  10:59 UTC</t>
+          <t>Generated September 24, 2026  ·  11:18 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1621,20 +1621,20 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="16" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>$182</t>
+          <t>$179</t>
         </is>
       </c>
       <c r="H5" s="19" t="n"/>
@@ -1737,7 +1737,7 @@
         <v>46290</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46295</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46289</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="40" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>46289</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="39" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>46290</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
@@ -1939,7 +1939,7 @@
         <v>46291</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
@@ -1950,11 +1950,11 @@
         <v>7</v>
       </c>
       <c r="G16" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="H16" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>150</v>
+      </c>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="B20" s="30" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="E21" s="35" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G21" s="47" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="H21" s="35" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="B22" s="30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="E22" s="30" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G22" s="49" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="46" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="B25" s="35" t="n">
@@ -2124,17 +2124,17 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="B26" s="30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="46" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B27" s="35" t="n">
@@ -2144,7 +2144,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="B28" s="30" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="B32" s="30" t="inlineStr">
         <is>
-          <t>9/23 – 9/29</t>
+          <t>9/24 – 9/30</t>
         </is>
       </c>
       <c r="C32" s="30" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D32" s="39" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E32" s="30" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
@@ -2222,17 +2222,17 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>9/30 – 10/6</t>
+          <t>10/1 – 10/7</t>
         </is>
       </c>
       <c r="C33" s="35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D33" s="40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E33" s="35" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B34" s="30" t="inlineStr">
         <is>
-          <t>10/7 – 10/13</t>
+          <t>10/8 – 10/14</t>
         </is>
       </c>
       <c r="C34" s="30" t="n">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="B35" s="35" t="inlineStr">
         <is>
-          <t>10/14 – 10/20</t>
+          <t>10/15 – 10/21</t>
         </is>
       </c>
       <c r="C35" s="35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E35" s="35" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -2285,14 +2285,14 @@
       </c>
       <c r="B36" s="30" t="inlineStr">
         <is>
-          <t>10/21 – 10/27</t>
+          <t>10/22 – 10/28</t>
         </is>
       </c>
       <c r="C36" s="30" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D36" s="39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36" s="30" t="n">
         <v>5.2</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B37" s="35" t="inlineStr">
         <is>
-          <t>10/28 – 11/3</t>
+          <t>10/29 – 11/4</t>
         </is>
       </c>
       <c r="C37" s="35" t="n">
@@ -2327,17 +2327,17 @@
       </c>
       <c r="B38" s="30" t="inlineStr">
         <is>
-          <t>11/4 – 11/10</t>
+          <t>11/5 – 11/11</t>
         </is>
       </c>
       <c r="C38" s="30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D38" s="39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E38" s="30" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -2348,17 +2348,17 @@
       </c>
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>11/11 – 11/17</t>
+          <t>11/12 – 11/18</t>
         </is>
       </c>
       <c r="C39" s="35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D39" s="40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" s="35" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -2369,17 +2369,17 @@
       </c>
       <c r="B40" s="30" t="inlineStr">
         <is>
-          <t>11/18 – 11/24</t>
+          <t>11/19 – 11/25</t>
         </is>
       </c>
       <c r="C40" s="30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D40" s="39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40" s="30" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>11/25 – 12/1</t>
+          <t>11/26 – 12/2</t>
         </is>
       </c>
       <c r="C41" s="35" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B42" s="30" t="inlineStr">
         <is>
-          <t>12/2 – 12/8</t>
+          <t>12/3 – 12/9</t>
         </is>
       </c>
       <c r="C42" s="30" t="n">
@@ -2432,17 +2432,17 @@
       </c>
       <c r="B43" s="35" t="inlineStr">
         <is>
-          <t>12/9 – 12/15</t>
+          <t>12/10 – 12/16</t>
         </is>
       </c>
       <c r="C43" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D43" s="40" t="n">
         <v>5</v>
       </c>
       <c r="E43" s="35" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="B44" s="30" t="inlineStr">
         <is>
-          <t>12/16 – 12/22</t>
+          <t>12/17 – 12/23</t>
         </is>
       </c>
       <c r="C44" s="30" t="n">
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -2703,7 +2703,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2713,17 +2713,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2733,7 +2733,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2752,7 +2752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2778,7 +2778,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 23, 2026  ·  10:59 UTC</t>
+          <t>Generated September 24, 2026  ·  11:18 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2821,14 +2821,14 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C4" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>140</v>
+      </c>
+      <c r="C4" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D4" s="42" t="inlineStr">
@@ -2838,40 +2838,40 @@
       </c>
       <c r="E4" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Nike GT Future “Unseen Hours”</t>
+          <t>Converse SHAI 001 “Ghosted”</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C5" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D5" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D5" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Pokémon x adidas Megaride F50 "Rayquaza"</t>
+          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
         <v>46289</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C7" s="50" t="inlineStr">
         <is>
@@ -2922,12 +2922,12 @@
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Ghosted”</t>
+          <t>PUMA MB.06 "Shooting Star"</t>
         </is>
       </c>
     </row>
@@ -2936,26 +2936,26 @@
         <v>46289</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C8" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D8" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C8" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
+          <t>Converse SHAI 001 Shroud “Shock”</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 Shroud “Shock”</t>
+          <t>Converse SHAI 001 “Spark”</t>
         </is>
       </c>
     </row>
@@ -2992,11 +2992,11 @@
         <v>46289</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C10" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>180</v>
+      </c>
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
@@ -3006,21 +3006,21 @@
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Spark”</t>
+          <t>Nike Air Max 1000.3</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="36" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
@@ -3034,12 +3034,12 @@
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 1000.3</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
@@ -3048,26 +3048,26 @@
         <v>46290</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>225</v>
-      </c>
-      <c r="C12" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D12" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C12" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
         </is>
       </c>
     </row>
@@ -3076,26 +3076,26 @@
         <v>46290</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>120</v>
-      </c>
-      <c r="C13" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D13" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Billionaire Boys Club x Reebok Club C 85</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
@@ -3104,11 +3104,11 @@
         <v>46290</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C14" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>120</v>
+      </c>
+      <c r="C14" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D14" s="42" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Billionaire Boys Club x Reebok Club C 85</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
+          <t>Nike Ja 4 “Jaws”</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
         <v>46290</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="C16" s="48" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws”</t>
+          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
         <v>46290</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="C17" s="54" t="inlineStr">
         <is>
@@ -3207,25 +3207,25 @@
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
+          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C18" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D18" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>150</v>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,10 @@
       <c r="A19" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B19" s="41" t="n">
-        <v>160</v>
-      </c>
-      <c r="C19" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="B19" s="41" t="inlineStr"/>
+      <c r="C19" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D19" s="43" t="inlineStr">
@@ -3263,7 +3261,7 @@
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
@@ -3272,16 +3270,16 @@
         <v>46291</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D20" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>155</v>
+      </c>
+      <c r="C20" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
@@ -3291,7 +3289,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
@@ -3300,16 +3298,16 @@
         <v>46291</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C21" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D21" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
@@ -3319,7 +3317,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -3328,26 +3326,26 @@
         <v>46291</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C22" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D22" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>160</v>
+      </c>
+      <c r="C22" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
         </is>
       </c>
     </row>
@@ -3356,26 +3354,26 @@
         <v>46291</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D23" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D23" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3381,9 @@
       <c r="A24" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B24" s="33" t="inlineStr"/>
+      <c r="B24" s="33" t="n">
+        <v>200</v>
+      </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -3410,11 +3410,11 @@
         <v>46291</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C25" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>125</v>
+      </c>
+      <c r="C25" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D25" s="38" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -3438,16 +3438,16 @@
         <v>46291</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C26" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D26" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -3465,17 +3465,15 @@
       <c r="A27" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B27" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C27" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D27" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B27" s="41" t="inlineStr"/>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
@@ -3485,7 +3483,7 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -3496,9 +3494,9 @@
       <c r="B28" s="33" t="n">
         <v>180</v>
       </c>
-      <c r="C28" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="C28" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
@@ -3508,12 +3506,12 @@
       </c>
       <c r="E28" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
@@ -3522,26 +3520,26 @@
         <v>46291</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D29" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D29" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -3550,16 +3548,16 @@
         <v>46291</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C30" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D30" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
@@ -3569,7 +3567,7 @@
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -3578,11 +3576,11 @@
         <v>46291</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="C31" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>200</v>
+      </c>
+      <c r="C31" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D31" s="38" t="inlineStr">
@@ -3597,7 +3595,7 @@
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
         </is>
       </c>
     </row>
@@ -3605,10 +3603,12 @@
       <c r="A32" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B32" s="33" t="inlineStr"/>
-      <c r="C32" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="B32" s="33" t="n">
+        <v>200</v>
+      </c>
+      <c r="C32" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D32" s="42" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -3634,24 +3634,24 @@
       <c r="B33" s="41" t="n">
         <v>155</v>
       </c>
-      <c r="C33" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D33" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -3660,11 +3660,11 @@
         <v>46291</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C34" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>120</v>
+      </c>
+      <c r="C34" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D34" s="42" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="E34" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
         </is>
       </c>
     </row>
@@ -3688,11 +3688,11 @@
         <v>46291</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>120</v>
-      </c>
-      <c r="C35" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>210</v>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D35" s="43" t="inlineStr">
@@ -3702,25 +3702,23 @@
       </c>
       <c r="E35" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="31" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B36" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C36" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46293</v>
+      </c>
+      <c r="B36" s="33" t="inlineStr"/>
+      <c r="C36" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D36" s="42" t="inlineStr">
@@ -3730,20 +3728,22 @@
       </c>
       <c r="E36" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B37" s="41" t="inlineStr"/>
+        <v>46294</v>
+      </c>
+      <c r="B37" s="41" t="n">
+        <v>249</v>
+      </c>
       <c r="C37" s="54" t="inlineStr">
         <is>
           <t>MED</t>
@@ -3756,12 +3756,12 @@
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
+          <t>Hyperice x Nike Air Zoom Hyperslide</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
         <v>46294</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>249</v>
+        <v>170</v>
       </c>
       <c r="C38" s="48" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Hyperice x Nike Air Zoom Hyperslide</t>
+          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
         </is>
       </c>
     </row>
@@ -3817,20 +3817,20 @@
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
+          <t>Nike Air Bakin “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C40" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>125</v>
+      </c>
+      <c r="C40" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D40" s="42" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Red”</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
@@ -3854,16 +3854,16 @@
         <v>46295</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C41" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D41" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>130</v>
+      </c>
+      <c r="C41" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D41" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>MoMA x Nike Air Rift 2 Pack</t>
         </is>
       </c>
     </row>
@@ -3882,16 +3882,16 @@
         <v>46295</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>135</v>
-      </c>
-      <c r="C42" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D42" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>200</v>
+      </c>
+      <c r="C42" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D42" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E42" s="30" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Zoom Huarache 2K4 “UCLA”</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
         <v>46295</v>
       </c>
       <c r="B43" s="41" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="C43" s="40" t="inlineStr">
         <is>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
@@ -3938,16 +3938,16 @@
         <v>46295</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D44" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E44" s="30" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -3966,26 +3966,26 @@
         <v>46295</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C45" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D45" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C45" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D45" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>MoMA x Nike Air Rift 2 Pack</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
         <v>46295</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="C46" s="48" t="inlineStr">
         <is>
@@ -4013,20 +4013,18 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Nike Zoom Huarache 2K4 “UCLA”</t>
+          <t>Tom Sachs x Nike General Purpose Shoe “Demerits”</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="36" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B47" s="41" t="n">
-        <v>120</v>
-      </c>
-      <c r="C47" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>46296</v>
+      </c>
+      <c r="B47" s="41" t="inlineStr"/>
+      <c r="C47" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D47" s="43" t="inlineStr">
@@ -4041,7 +4039,7 @@
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Tom Sachs x Nike General Purpose Shoe “Demerits”</t>
+          <t>Nike Air Max 95 “Liverpool”</t>
         </is>
       </c>
     </row>
@@ -4190,16 +4188,16 @@
         <v>46298</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D53" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
@@ -4209,7 +4207,7 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
@@ -4218,16 +4216,16 @@
         <v>46298</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D54" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D54" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
@@ -4237,7 +4235,7 @@
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 16 “Black Pack”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4244,7 @@
         <v>46298</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
@@ -4265,7 +4263,7 @@
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 16 “Black Pack”</t>
         </is>
       </c>
     </row>
@@ -4299,14 +4297,14 @@
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46303</v>
+        <v>46301</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C57" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>135</v>
+      </c>
+      <c r="C57" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D57" s="43" t="inlineStr">
@@ -4316,21 +4314,21 @@
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
+          <t>Nike Sabrina 4 “90s Kid”</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="31" t="n">
-        <v>46304</v>
+        <v>46301</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="C58" s="48" t="inlineStr">
         <is>
@@ -4349,20 +4347,20 @@
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
+          <t>Nike Sabrina 4 “Light Work”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46304</v>
+        <v>46301</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C59" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>175</v>
+      </c>
+      <c r="C59" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D59" s="43" t="inlineStr">
@@ -4372,21 +4370,21 @@
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
+          <t>Nike Air Max Goadome Low “Black Croc”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46304</v>
+        <v>46301</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="C60" s="48" t="inlineStr">
         <is>
@@ -4400,30 +4398,30 @@
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Aminé x New Balance 992 “Outdoor School”</t>
+          <t>Nike Air Max Goadome Low “Navy Croc”</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46305</v>
+        <v>46302</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>135</v>
-      </c>
-      <c r="C61" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D61" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>150</v>
+      </c>
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D61" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
@@ -4433,20 +4431,20 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Texas”</t>
+          <t>Nike Air Force 1 ’01 “Subway Rat”</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46305</v>
+        <v>46303</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C62" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>130</v>
+      </c>
+      <c r="C62" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D62" s="42" t="inlineStr">
@@ -4456,25 +4454,25 @@
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="36" t="n">
-        <v>46310</v>
+        <v>46304</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C63" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>130</v>
+      </c>
+      <c r="C63" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D63" s="43" t="inlineStr">
@@ -4484,30 +4482,30 @@
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="31" t="n">
-        <v>46310</v>
+        <v>46304</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C64" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D64" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C64" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D64" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
@@ -4517,20 +4515,20 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="36" t="n">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C65" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>220</v>
+      </c>
+      <c r="C65" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D65" s="43" t="inlineStr">
@@ -4540,21 +4538,21 @@
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Aminé x New Balance 992 “Outdoor School”</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46311</v>
+        <v>46305</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
@@ -4568,25 +4566,25 @@
       </c>
       <c r="E66" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46311</v>
+        <v>46305</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C67" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>135</v>
+      </c>
+      <c r="C67" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D67" s="43" t="inlineStr">
@@ -4601,25 +4599,25 @@
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike KD 6 “Texas”</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D68" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D68" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
@@ -4629,20 +4627,20 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46312</v>
+        <v>46310</v>
       </c>
       <c r="B69" s="41" t="n">
-        <v>220</v>
-      </c>
-      <c r="C69" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>125</v>
+      </c>
+      <c r="C69" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D69" s="43" t="inlineStr">
@@ -4657,16 +4655,16 @@
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B70" s="33" t="n">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="C70" s="39" t="inlineStr">
         <is>
@@ -4680,25 +4678,25 @@
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46315</v>
+        <v>46311</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>160</v>
-      </c>
-      <c r="C71" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>240</v>
+      </c>
+      <c r="C71" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D71" s="43" t="inlineStr">
@@ -4708,23 +4706,25 @@
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 “Reese’s”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B72" s="33" t="inlineStr"/>
-      <c r="C72" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>46311</v>
+      </c>
+      <c r="B72" s="33" t="n">
+        <v>250</v>
+      </c>
+      <c r="C72" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D72" s="42" t="inlineStr">
@@ -4734,21 +4734,21 @@
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>SZA x Vans VANSZA Collection</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46318</v>
+        <v>46312</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
@@ -4762,25 +4762,25 @@
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “NYC Rat”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46318</v>
+        <v>46312</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C74" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>215</v>
+      </c>
+      <c r="C74" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D74" s="42" t="inlineStr">
@@ -4790,25 +4790,25 @@
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>PUMA Hali 1 “Pacers”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46319</v>
+        <v>46315</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>190</v>
-      </c>
-      <c r="C75" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>160</v>
+      </c>
+      <c r="C75" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D75" s="43" t="inlineStr">
@@ -4818,25 +4818,23 @@
       </c>
       <c r="E75" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Reebok Angel Reese 1 “Reese’s”</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="31" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B76" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C76" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46317</v>
+      </c>
+      <c r="B76" s="33" t="inlineStr"/>
+      <c r="C76" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D76" s="42" t="inlineStr">
@@ -4846,21 +4844,21 @@
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>SZA x Vans VANSZA Collection</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="36" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B77" s="41" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C77" s="40" t="inlineStr">
         <is>
@@ -4879,16 +4877,16 @@
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Nike Air Force 1 Low “NYC Rat”</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="31" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C78" s="48" t="inlineStr">
         <is>
@@ -4907,13 +4905,13 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Nike Sabrina 4 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="36" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B79" s="41" t="n">
         <v>130</v>
@@ -4930,12 +4928,12 @@
       </c>
       <c r="E79" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>PUMA Hali 1 “Pacers”</t>
         </is>
       </c>
     </row>
@@ -4944,16 +4942,16 @@
         <v>46319</v>
       </c>
       <c r="B80" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C80" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D80" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C80" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D80" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E80" s="30" t="inlineStr">
@@ -4963,7 +4961,7 @@
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Nike Air Diamond Turf 2 “White Black”</t>
         </is>
       </c>
     </row>
@@ -4972,16 +4970,16 @@
         <v>46319</v>
       </c>
       <c r="B81" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C81" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D81" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>190</v>
+      </c>
+      <c r="C81" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D81" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E81" s="35" t="inlineStr">
@@ -4991,7 +4989,7 @@
       </c>
       <c r="F81" s="35" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
@@ -5000,11 +4998,11 @@
         <v>46319</v>
       </c>
       <c r="B82" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C82" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>125</v>
+      </c>
+      <c r="C82" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D82" s="42" t="inlineStr">
@@ -5019,16 +5017,16 @@
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="36" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B83" s="41" t="n">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="C83" s="40" t="inlineStr">
         <is>
@@ -5047,16 +5045,16 @@
       </c>
       <c r="F83" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="31" t="n">
-        <v>46325</v>
+        <v>46319</v>
       </c>
       <c r="B84" s="33" t="n">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C84" s="48" t="inlineStr">
         <is>
@@ -5075,53 +5073,53 @@
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="36" t="n">
-        <v>46325</v>
+        <v>46319</v>
       </c>
       <c r="B85" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C85" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D85" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C85" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D85" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E85" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 High “University Red”</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="31" t="n">
-        <v>46325</v>
+        <v>46319</v>
       </c>
       <c r="B86" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C86" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D86" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>150</v>
+      </c>
+      <c r="C86" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D86" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E86" s="30" t="inlineStr">
@@ -5131,44 +5129,44 @@
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Halloween”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="36" t="n">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="B87" s="41" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C87" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D87" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D87" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E87" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Nike Air Force 1 Low “Ghostface Black”</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="31" t="n">
-        <v>46331</v>
+        <v>46319</v>
       </c>
       <c r="B88" s="33" t="n">
-        <v>265</v>
+        <v>170</v>
       </c>
       <c r="C88" s="48" t="inlineStr">
         <is>
@@ -5187,16 +5185,16 @@
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max Foamdome “Eggplant” 2026</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="36" t="n">
-        <v>46331</v>
+        <v>46319</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>210</v>
+        <v>145</v>
       </c>
       <c r="C89" s="54" t="inlineStr">
         <is>
@@ -5215,20 +5213,20 @@
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="31" t="n">
-        <v>46331</v>
+        <v>46320</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C90" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>205</v>
+      </c>
+      <c r="C90" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D90" s="42" t="inlineStr">
@@ -5238,21 +5236,21 @@
       </c>
       <c r="E90" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="36" t="n">
-        <v>46331</v>
+        <v>46325</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>265</v>
+        <v>155</v>
       </c>
       <c r="C91" s="54" t="inlineStr">
         <is>
@@ -5271,25 +5269,25 @@
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max Foamdome “Eggplant”</t>
+          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
         </is>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="31" t="n">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="B92" s="33" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="C92" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D92" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D92" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E92" s="30" t="inlineStr">
@@ -5299,20 +5297,20 @@
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Desert Night”</t>
+          <t>Nike Ja 4 High “University Red”</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="36" t="n">
-        <v>46333</v>
+        <v>46325</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>215</v>
-      </c>
-      <c r="C93" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>155</v>
+      </c>
+      <c r="C93" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D93" s="43" t="inlineStr">
@@ -5322,30 +5320,30 @@
       </c>
       <c r="E93" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Book 2 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="31" t="n">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="B94" s="33" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="C94" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D94" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D94" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E94" s="30" t="inlineStr">
@@ -5355,20 +5353,20 @@
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="36" t="n">
-        <v>46333</v>
+        <v>46331</v>
       </c>
       <c r="B95" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C95" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>265</v>
+      </c>
+      <c r="C95" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D95" s="38" t="inlineStr">
@@ -5378,25 +5376,25 @@
       </c>
       <c r="E95" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F95" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Nike Air Max Foamdome “Eggplant” 2026</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="31" t="n">
-        <v>46337</v>
+        <v>46331</v>
       </c>
       <c r="B96" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C96" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>210</v>
+      </c>
+      <c r="C96" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D96" s="42" t="inlineStr">
@@ -5411,20 +5409,20 @@
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="36" t="n">
-        <v>46337</v>
+        <v>46331</v>
       </c>
       <c r="B97" s="41" t="n">
-        <v>235</v>
-      </c>
-      <c r="C97" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>210</v>
+      </c>
+      <c r="C97" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D97" s="43" t="inlineStr">
@@ -5434,30 +5432,30 @@
       </c>
       <c r="E97" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F97" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="31" t="n">
-        <v>46338</v>
+        <v>46331</v>
       </c>
       <c r="B98" s="33" t="n">
-        <v>170</v>
+        <v>265</v>
       </c>
       <c r="C98" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D98" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D98" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E98" s="30" t="inlineStr">
@@ -5467,20 +5465,20 @@
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal” 2026</t>
+          <t>Nike Air Max Foamdome “Eggplant”</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="36" t="n">
-        <v>46338</v>
+        <v>46332</v>
       </c>
       <c r="B99" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C99" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>145</v>
+      </c>
+      <c r="C99" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D99" s="43" t="inlineStr">
@@ -5490,53 +5488,53 @@
       </c>
       <c r="E99" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F99" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
+          <t>Nike Book 2 “Desert Night”</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="31" t="n">
-        <v>46338</v>
+        <v>46333</v>
       </c>
       <c r="B100" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C100" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D100" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>240</v>
+      </c>
+      <c r="C100" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D100" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E100" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal”</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="36" t="n">
-        <v>46339</v>
+        <v>46333</v>
       </c>
       <c r="B101" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C101" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>215</v>
+      </c>
+      <c r="C101" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D101" s="43" t="inlineStr">
@@ -5546,86 +5544,86 @@
       </c>
       <c r="E101" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Diamond Turf 2 Patent “Black Red”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="31" t="n">
-        <v>46339</v>
+        <v>46333</v>
       </c>
       <c r="B102" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C102" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D102" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>245</v>
+      </c>
+      <c r="C102" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D102" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E102" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Diamond Turf 2</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="36" t="n">
-        <v>46340</v>
+        <v>46337</v>
       </c>
       <c r="B103" s="41" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C103" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D103" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D103" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E103" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F103" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="31" t="n">
-        <v>46340</v>
+        <v>46337</v>
       </c>
       <c r="B104" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C104" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D104" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>235</v>
+      </c>
+      <c r="C104" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D104" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E104" s="30" t="inlineStr">
@@ -5635,16 +5633,16 @@
       </c>
       <c r="F104" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="36" t="n">
-        <v>46341</v>
+        <v>46338</v>
       </c>
       <c r="B105" s="41" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C105" s="54" t="inlineStr">
         <is>
@@ -5663,53 +5661,53 @@
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>Playa Society x Nike A’Two</t>
+          <t>Nike Air Bakin “Varsity Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="31" t="n">
-        <v>46342</v>
+        <v>46338</v>
       </c>
       <c r="B106" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C106" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D106" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C106" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D106" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E106" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F106" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="36" t="n">
-        <v>46342</v>
+        <v>46338</v>
       </c>
       <c r="B107" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C107" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D107" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C107" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D107" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E107" s="35" t="inlineStr">
@@ -5719,16 +5717,16 @@
       </c>
       <c r="F107" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Nike Air Bakin “Varsity Royal”</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="31" t="n">
-        <v>46343</v>
+        <v>46339</v>
       </c>
       <c r="B108" s="33" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="C108" s="39" t="inlineStr">
         <is>
@@ -5747,20 +5745,20 @@
       </c>
       <c r="F108" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="36" t="n">
-        <v>46345</v>
+        <v>46339</v>
       </c>
       <c r="B109" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C109" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>170</v>
+      </c>
+      <c r="C109" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D109" s="43" t="inlineStr">
@@ -5770,21 +5768,21 @@
       </c>
       <c r="E109" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Navy”</t>
+          <t>Nike Air Diamond Turf 2 Patent “Black Red”</t>
         </is>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="31" t="n">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C110" s="48" t="inlineStr">
         <is>
@@ -5803,53 +5801,53 @@
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Be Legendary”</t>
+          <t>Nike Air Diamond Turf 2</t>
         </is>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="36" t="n">
-        <v>46346</v>
+        <v>46340</v>
       </c>
       <c r="B111" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C111" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D111" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C111" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D111" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E111" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="31" t="n">
-        <v>46347</v>
+        <v>46340</v>
       </c>
       <c r="B112" s="33" t="n">
-        <v>165</v>
-      </c>
-      <c r="C112" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D112" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>240</v>
+      </c>
+      <c r="C112" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D112" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E112" s="30" t="inlineStr">
@@ -5859,25 +5857,25 @@
       </c>
       <c r="F112" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="36" t="n">
-        <v>46347</v>
+        <v>46340</v>
       </c>
       <c r="B113" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C113" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D113" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C113" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D113" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E113" s="35" t="inlineStr">
@@ -5887,16 +5885,16 @@
       </c>
       <c r="F113" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>CPFM x Nike Flea 1 “Barely”</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="31" t="n">
-        <v>46347</v>
+        <v>46340</v>
       </c>
       <c r="B114" s="33" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="C114" s="48" t="inlineStr">
         <is>
@@ -5915,20 +5913,20 @@
       </c>
       <c r="F114" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Snow White”</t>
+          <t>Nike Zoom Hyperflight “Green Apple”</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="36" t="n">
-        <v>46347</v>
+        <v>46341</v>
       </c>
       <c r="B115" s="41" t="n">
-        <v>230</v>
-      </c>
-      <c r="C115" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>155</v>
+      </c>
+      <c r="C115" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D115" s="38" t="inlineStr">
@@ -5943,25 +5941,25 @@
       </c>
       <c r="F115" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Playa Society x Nike A’Two</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="31" t="n">
-        <v>46347</v>
+        <v>46342</v>
       </c>
       <c r="B116" s="33" t="n">
-        <v>215</v>
+        <v>255</v>
       </c>
       <c r="C116" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D116" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D116" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E116" s="30" t="inlineStr">
@@ -5971,25 +5969,25 @@
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="36" t="n">
-        <v>46347</v>
+        <v>46342</v>
       </c>
       <c r="B117" s="41" t="n">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="C117" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D117" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D117" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E117" s="35" t="inlineStr">
@@ -5999,18 +5997,20 @@
       </c>
       <c r="F117" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="31" t="n">
-        <v>46347</v>
-      </c>
-      <c r="B118" s="33" t="inlineStr"/>
-      <c r="C118" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>46343</v>
+      </c>
+      <c r="B118" s="33" t="n">
+        <v>200</v>
+      </c>
+      <c r="C118" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D118" s="42" t="inlineStr">
@@ -6020,25 +6020,25 @@
       </c>
       <c r="E118" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F118" s="30" t="inlineStr">
         <is>
-          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="36" t="n">
-        <v>46353</v>
+        <v>46345</v>
       </c>
       <c r="B119" s="41" t="n">
-        <v>230</v>
-      </c>
-      <c r="C119" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>130</v>
+      </c>
+      <c r="C119" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D119" s="43" t="inlineStr">
@@ -6048,25 +6048,25 @@
       </c>
       <c r="E119" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Vans Old Skool 36 Pearlized “Navy”</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="31" t="n">
-        <v>46353</v>
+        <v>46346</v>
       </c>
       <c r="B120" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C120" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>145</v>
+      </c>
+      <c r="C120" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D120" s="42" t="inlineStr">
@@ -6081,20 +6081,20 @@
       </c>
       <c r="F120" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Nike Book 2 “Be Legendary”</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="36" t="n">
-        <v>46353</v>
+        <v>46346</v>
       </c>
       <c r="B121" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C121" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>190</v>
+      </c>
+      <c r="C121" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D121" s="43" t="inlineStr">
@@ -6104,25 +6104,25 @@
       </c>
       <c r="E121" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F121" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Black”</t>
+          <t>Nike Air Max 95 “ACG”</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="A122" s="31" t="n">
-        <v>46354</v>
+        <v>46346</v>
       </c>
       <c r="B122" s="33" t="n">
-        <v>190</v>
-      </c>
-      <c r="C122" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>130</v>
+      </c>
+      <c r="C122" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D122" s="42" t="inlineStr">
@@ -6132,30 +6132,30 @@
       </c>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F122" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="36" t="n">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B123" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C123" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D123" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>230</v>
+      </c>
+      <c r="C123" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D123" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E123" s="35" t="inlineStr">
@@ -6165,53 +6165,53 @@
       </c>
       <c r="F123" s="35" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Warning Code”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1">
       <c r="A124" s="31" t="n">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B124" s="33" t="n">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="C124" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D124" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D124" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E124" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F124" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “FSU”</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="36" t="n">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B125" s="41" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C125" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D125" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D125" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E125" s="35" t="inlineStr">
@@ -6221,18 +6221,18 @@
       </c>
       <c r="F125" s="35" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="31" t="n">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B126" s="33" t="inlineStr"/>
-      <c r="C126" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="C126" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D126" s="42" t="inlineStr">
@@ -6242,51 +6242,53 @@
       </c>
       <c r="E126" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="36" t="n">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B127" s="41" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="C127" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D127" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D127" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E127" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>Nike SB Dunk Low “Green Patent”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" s="31" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B128" s="33" t="inlineStr"/>
-      <c r="C128" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>46347</v>
+      </c>
+      <c r="B128" s="33" t="n">
+        <v>125</v>
+      </c>
+      <c r="C128" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D128" s="42" t="inlineStr">
@@ -6301,42 +6303,44 @@
       </c>
       <c r="F128" s="30" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Aunt Pearl” 2026</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="36" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B129" s="41" t="inlineStr"/>
-      <c r="C129" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D129" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>46347</v>
+      </c>
+      <c r="B129" s="41" t="n">
+        <v>140</v>
+      </c>
+      <c r="C129" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D129" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E129" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F129" s="35" t="inlineStr">
         <is>
-          <t>Social Status x Air Jordan 1 Low OG</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" s="31" t="n">
-        <v>46357</v>
+        <v>46353</v>
       </c>
       <c r="B130" s="33" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="C130" s="39" t="inlineStr">
         <is>
@@ -6350,25 +6354,25 @@
       </c>
       <c r="E130" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F130" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Chosen 1s”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1">
       <c r="A131" s="36" t="n">
-        <v>46359</v>
+        <v>46353</v>
       </c>
       <c r="B131" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C131" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>240</v>
+      </c>
+      <c r="C131" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D131" s="43" t="inlineStr">
@@ -6383,18 +6387,20 @@
       </c>
       <c r="F131" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Black White”</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1">
       <c r="A132" s="31" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B132" s="33" t="inlineStr"/>
-      <c r="C132" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>46353</v>
+      </c>
+      <c r="B132" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="C132" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D132" s="42" t="inlineStr">
@@ -6404,50 +6410,48 @@
       </c>
       <c r="E132" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F132" s="30" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Vans Old Skool 36 Pearlized “Black”</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1">
       <c r="A133" s="36" t="n">
-        <v>46361</v>
+        <v>46354</v>
       </c>
       <c r="B133" s="41" t="n">
-        <v>215</v>
+        <v>130</v>
       </c>
       <c r="C133" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D133" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D133" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E133" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F133" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Nike SB Dunk Low “Green Patent”</t>
         </is>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="31" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B134" s="33" t="n">
-        <v>300</v>
-      </c>
+        <v>46354</v>
+      </c>
+      <c r="B134" s="33" t="inlineStr"/>
       <c r="C134" s="48" t="inlineStr">
         <is>
           <t>MED</t>
@@ -6460,53 +6464,51 @@
       </c>
       <c r="E134" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F134" s="30" t="inlineStr">
         <is>
-          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
+          <t>Nike KD 6 “Aunt Pearl” 2026</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c r="A135" s="36" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B135" s="41" t="n">
-        <v>300</v>
-      </c>
-      <c r="C135" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D135" s="55" t="inlineStr">
-        <is>
-          <t>Confirmed App</t>
+        <v>46354</v>
+      </c>
+      <c r="B135" s="41" t="inlineStr"/>
+      <c r="C135" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D135" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E135" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F135" s="35" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish “Auburn Timber”</t>
+          <t>Social Status x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="31" t="n">
-        <v>46361</v>
+        <v>46354</v>
       </c>
       <c r="B136" s="33" t="n">
-        <v>300</v>
-      </c>
-      <c r="C136" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>190</v>
+      </c>
+      <c r="C136" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D136" s="42" t="inlineStr">
@@ -6516,46 +6518,46 @@
       </c>
       <c r="E136" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F136" s="30" t="inlineStr">
         <is>
-          <t>Pharrell x adidas Adistar Jellyfish</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="36" t="n">
-        <v>46367</v>
+        <v>46354</v>
       </c>
       <c r="B137" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="C137" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D137" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>140</v>
+      </c>
+      <c r="C137" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D137" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E137" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F137" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Nike Caitlin 1 “Warning Code”</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="A138" s="31" t="n">
-        <v>46367</v>
+        <v>46354</v>
       </c>
       <c r="B138" s="33" t="n">
         <v>240</v>
@@ -6565,9 +6567,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D138" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D138" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E138" s="30" t="inlineStr">
@@ -6577,15 +6579,17 @@
       </c>
       <c r="F138" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Floral” 2026</t>
+          <t>Nike Air Foamposite Pro “FSU”</t>
         </is>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1">
       <c r="A139" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B139" s="41" t="inlineStr"/>
+        <v>46354</v>
+      </c>
+      <c r="B139" s="41" t="n">
+        <v>120</v>
+      </c>
       <c r="C139" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6598,22 +6602,20 @@
       </c>
       <c r="E139" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F139" s="35" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" s="31" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B140" s="33" t="n">
-        <v>190</v>
-      </c>
+        <v>46354</v>
+      </c>
+      <c r="B140" s="33" t="inlineStr"/>
       <c r="C140" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -6631,16 +6633,16 @@
       </c>
       <c r="F140" s="30" t="inlineStr">
         <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1">
       <c r="A141" s="36" t="n">
-        <v>46368</v>
+        <v>46357</v>
       </c>
       <c r="B141" s="41" t="n">
-        <v>235</v>
+        <v>190</v>
       </c>
       <c r="C141" s="40" t="inlineStr">
         <is>
@@ -6654,25 +6656,25 @@
       </c>
       <c r="E141" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F141" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam” 2026</t>
+          <t>Nike LeBron 24 “Chosen 1s”</t>
         </is>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1">
       <c r="A142" s="31" t="n">
-        <v>46375</v>
+        <v>46359</v>
       </c>
       <c r="B142" s="33" t="n">
-        <v>220</v>
-      </c>
-      <c r="C142" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>170</v>
+      </c>
+      <c r="C142" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D142" s="42" t="inlineStr">
@@ -6682,81 +6684,79 @@
       </c>
       <c r="E142" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F142" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Pink Thunder”</t>
+          <t>Nike Air Bakin “Black White”</t>
         </is>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1">
       <c r="A143" s="36" t="n">
-        <v>46375</v>
+        <v>46361</v>
       </c>
       <c r="B143" s="41" t="n">
-        <v>120</v>
-      </c>
-      <c r="C143" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D143" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>300</v>
+      </c>
+      <c r="C143" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D143" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E143" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F143" s="35" t="inlineStr">
         <is>
-          <t>Fly Streetwear x Nike SB Air Force 1 Low “University Gold”</t>
+          <t>Pharrell Williams x adidas Adistar Jellyfish “Dark Brown Frozen Green”</t>
         </is>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1">
       <c r="A144" s="31" t="n">
-        <v>46375</v>
+        <v>46361</v>
       </c>
       <c r="B144" s="33" t="n">
-        <v>170</v>
+        <v>300</v>
       </c>
       <c r="C144" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D144" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D144" s="55" t="inlineStr">
+        <is>
+          <t>Confirmed App</t>
         </is>
       </c>
       <c r="E144" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F144" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Flight The Glove “Royal Blue”</t>
+          <t>Pharrell x adidas Adistar Jellyfish “Auburn Timber”</t>
         </is>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
       <c r="A145" s="36" t="n">
-        <v>46375</v>
-      </c>
-      <c r="B145" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C145" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>46361</v>
+      </c>
+      <c r="B145" s="41" t="inlineStr"/>
+      <c r="C145" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D145" s="43" t="inlineStr">
@@ -6766,45 +6766,379 @@
       </c>
       <c r="E145" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F145" s="35" t="inlineStr">
         <is>
-          <t>Nike GT Future “Triple Black”</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1">
       <c r="A146" s="31" t="n">
+        <v>46361</v>
+      </c>
+      <c r="B146" s="33" t="n">
+        <v>215</v>
+      </c>
+      <c r="C146" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D146" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E146" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F146" s="30" t="inlineStr">
+        <is>
+          <t>Air Jordan 10 “Sacramento”</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="15" customHeight="1">
+      <c r="A147" s="36" t="n">
+        <v>46361</v>
+      </c>
+      <c r="B147" s="41" t="n">
+        <v>300</v>
+      </c>
+      <c r="C147" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D147" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E147" s="35" t="inlineStr">
+        <is>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="F147" s="35" t="inlineStr">
+        <is>
+          <t>Pharrell x adidas Adistar Jellyfish</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="15" customHeight="1">
+      <c r="A148" s="31" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B148" s="33" t="inlineStr"/>
+      <c r="C148" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D148" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E148" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F148" s="30" t="inlineStr">
+        <is>
+          <t>Free The Youth x Air Jordan 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="15" customHeight="1">
+      <c r="A149" s="36" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B149" s="41" t="n">
+        <v>150</v>
+      </c>
+      <c r="C149" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D149" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E149" s="35" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F149" s="35" t="inlineStr">
+        <is>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="15" customHeight="1">
+      <c r="A150" s="31" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B150" s="33" t="n">
+        <v>240</v>
+      </c>
+      <c r="C150" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D150" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E150" s="30" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F150" s="30" t="inlineStr">
+        <is>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="15" customHeight="1">
+      <c r="A151" s="36" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B151" s="41" t="n">
+        <v>190</v>
+      </c>
+      <c r="C151" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D151" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E151" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F151" s="35" t="inlineStr">
+        <is>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="15" customHeight="1">
+      <c r="A152" s="31" t="n">
+        <v>46368</v>
+      </c>
+      <c r="B152" s="33" t="n">
+        <v>235</v>
+      </c>
+      <c r="C152" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D152" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E152" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F152" s="30" t="inlineStr">
+        <is>
+          <t>Air Jordan 11 “Space Jam” 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="15" customHeight="1">
+      <c r="A153" s="36" t="n">
+        <v>46368</v>
+      </c>
+      <c r="B153" s="41" t="n">
+        <v>135</v>
+      </c>
+      <c r="C153" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D153" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E153" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F153" s="35" t="inlineStr">
+        <is>
+          <t>PaisaBoys x Nike SB P-Rod 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="15" customHeight="1">
+      <c r="A154" s="31" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B154" s="33" t="n">
+        <v>210</v>
+      </c>
+      <c r="C154" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D154" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E154" s="30" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F154" s="30" t="inlineStr">
+        <is>
+          <t>Nike GT Future “Triple Black”</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="15" customHeight="1">
+      <c r="A155" s="36" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B155" s="41" t="n">
+        <v>220</v>
+      </c>
+      <c r="C155" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D155" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E155" s="35" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F155" s="35" t="inlineStr">
+        <is>
+          <t>Air Jordan 4 “Pink Thunder”</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="15" customHeight="1">
+      <c r="A156" s="31" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B156" s="33" t="n">
+        <v>120</v>
+      </c>
+      <c r="C156" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D156" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
+        </is>
+      </c>
+      <c r="E156" s="30" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F156" s="30" t="inlineStr">
+        <is>
+          <t>Fly Streetwear x Nike SB Air Force 1 Low “University Gold”</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="15" customHeight="1">
+      <c r="A157" s="36" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B157" s="41" t="n">
+        <v>170</v>
+      </c>
+      <c r="C157" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D157" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E157" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F157" s="35" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom Flight The Glove “Royal Blue”</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="15" customHeight="1">
+      <c r="A158" s="31" t="n">
         <v>46377</v>
       </c>
-      <c r="B146" s="33" t="n">
+      <c r="B158" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C146" s="48" t="inlineStr">
+      <c r="C158" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D146" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
-        </is>
-      </c>
-      <c r="E146" s="30" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="F146" s="30" t="inlineStr">
+      <c r="D158" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E158" s="30" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F158" s="30" t="inlineStr">
         <is>
           <t>Nike Caitlin 1 “Chiefs”</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F146"/>
+  <autoFilter ref="A3:F158"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -6819,7 +7153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6845,7 +7179,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 23, 2026  ·  10:59 UTC</t>
+          <t>Generated September 24, 2026  ·  11:18 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -6947,16 +7281,16 @@
         <v>46290</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>225</v>
-      </c>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
-        </is>
-      </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>205</v>
+      </c>
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
@@ -6966,7 +7300,7 @@
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
@@ -6975,16 +7309,16 @@
         <v>46290</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D7" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>225</v>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
+        </is>
+      </c>
+      <c r="D7" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
@@ -6994,7 +7328,7 @@
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
         </is>
       </c>
     </row>
@@ -7003,16 +7337,16 @@
         <v>46291</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
@@ -7022,7 +7356,7 @@
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -7031,26 +7365,26 @@
         <v>46291</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -7059,26 +7393,26 @@
         <v>46291</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D10" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7420,9 @@
       <c r="A11" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B11" s="41" t="inlineStr"/>
+      <c r="B11" s="41" t="n">
+        <v>200</v>
+      </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -7104,7 +7440,7 @@
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -7113,16 +7449,16 @@
         <v>46291</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="C12" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D12" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
@@ -7132,7 +7468,7 @@
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
@@ -7140,27 +7476,25 @@
       <c r="A13" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B13" s="41" t="n">
-        <v>180</v>
-      </c>
+      <c r="B13" s="41" t="inlineStr"/>
       <c r="C13" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
@@ -7169,26 +7503,26 @@
         <v>46291</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C14" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D14" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
@@ -7197,16 +7531,16 @@
         <v>46291</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C15" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D15" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D15" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
@@ -7216,7 +7550,7 @@
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
@@ -7225,26 +7559,26 @@
         <v>46291</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="C16" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D16" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7587,7 @@
         <v>46291</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="C17" s="40" t="inlineStr">
         <is>
@@ -7267,12 +7601,12 @@
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7643,7 @@
         <v>46295</v>
       </c>
       <c r="B19" s="41" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C19" s="40" t="inlineStr">
         <is>
@@ -7328,7 +7662,7 @@
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
@@ -7337,16 +7671,16 @@
         <v>46295</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
@@ -7356,7 +7690,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
@@ -7365,26 +7699,26 @@
         <v>46295</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="C21" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D21" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D21" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7727,7 @@
         <v>46295</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="C22" s="39" t="inlineStr">
         <is>
@@ -7407,12 +7741,12 @@
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
@@ -7420,9 +7754,7 @@
       <c r="A23" s="36" t="n">
         <v>46296</v>
       </c>
-      <c r="B23" s="41" t="n">
-        <v>125</v>
-      </c>
+      <c r="B23" s="41" t="inlineStr"/>
       <c r="C23" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -7440,7 +7772,7 @@
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Kobe Bryant x Nike Air Force 1 Low “Black Purple Stardust”</t>
+          <t>Nike Air Max 95 “Liverpool”</t>
         </is>
       </c>
     </row>
@@ -7468,35 +7800,35 @@
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low</t>
+          <t>Kobe Bryant x Nike Air Force 1 Low “Black Purple Stardust”</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="36" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>220</v>
+        <v>125</v>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D25" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D25" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Nike Kobe Air Force 1 Low</t>
         </is>
       </c>
     </row>
@@ -7505,16 +7837,16 @@
         <v>46297</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="C26" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D26" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
@@ -7524,16 +7856,16 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 Low “Black Pink Foam”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="36" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="B27" s="41" t="n">
-        <v>205</v>
+        <v>150</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
@@ -7552,7 +7884,7 @@
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Air Jordan 6 Low “Black Pink Foam”</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7893,7 @@
         <v>46298</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C28" s="39" t="inlineStr">
         <is>
@@ -7580,7 +7912,7 @@
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 16 “Black Pack”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
@@ -7589,16 +7921,16 @@
         <v>46298</v>
       </c>
       <c r="B29" s="41" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D29" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D29" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -7608,44 +7940,44 @@
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="31" t="n">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>200</v>
+        <v>245</v>
       </c>
       <c r="C30" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D30" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Air Jordan 16 “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="36" t="n">
-        <v>46305</v>
+        <v>46300</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C31" s="40" t="inlineStr">
         <is>
@@ -7659,21 +7991,21 @@
       </c>
       <c r="E31" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="n">
-        <v>46310</v>
+        <v>46302</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
@@ -7692,16 +8024,16 @@
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Nike Air Force 1 ’01 “Subway Rat”</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="36" t="n">
-        <v>46311</v>
+        <v>46305</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="C33" s="40" t="inlineStr">
         <is>
@@ -7715,30 +8047,30 @@
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="31" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="C34" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D34" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
@@ -7748,7 +8080,7 @@
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
@@ -7757,7 +8089,7 @@
         <v>46311</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
@@ -7776,7 +8108,7 @@
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -7785,7 +8117,7 @@
         <v>46311</v>
       </c>
       <c r="B36" s="33" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C36" s="39" t="inlineStr">
         <is>
@@ -7804,16 +8136,16 @@
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C37" s="40" t="inlineStr">
         <is>
@@ -7827,12 +8159,12 @@
       </c>
       <c r="E37" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
@@ -7841,7 +8173,7 @@
         <v>46312</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C38" s="39" t="inlineStr">
         <is>
@@ -7860,16 +8192,16 @@
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>46318</v>
+        <v>46312</v>
       </c>
       <c r="B39" s="41" t="n">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="C39" s="40" t="inlineStr">
         <is>
@@ -7883,21 +8215,21 @@
       </c>
       <c r="E39" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “NYC Rat”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="C40" s="39" t="inlineStr">
         <is>
@@ -7916,7 +8248,7 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Nike Air Force 1 Low “NYC Rat”</t>
         </is>
       </c>
     </row>
@@ -7925,7 +8257,7 @@
         <v>46319</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="C41" s="40" t="inlineStr">
         <is>
@@ -7939,12 +8271,12 @@
       </c>
       <c r="E41" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
@@ -7981,91 +8313,91 @@
         <v>46319</v>
       </c>
       <c r="B43" s="41" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C43" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D43" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D43" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="31" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>205</v>
+        <v>150</v>
       </c>
       <c r="C44" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D44" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E44" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>46326</v>
+        <v>46319</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D45" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D45" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Nike Air Force 1 Low “Ghostface Black”</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="31" t="n">
-        <v>46333</v>
+        <v>46320</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
@@ -8084,25 +8416,25 @@
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="36" t="n">
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="B47" s="41" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D47" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D47" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
@@ -8112,7 +8444,7 @@
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
@@ -8146,10 +8478,10 @@
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="36" t="n">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
@@ -8163,30 +8495,30 @@
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="31" t="n">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C50" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D50" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D50" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E50" s="30" t="inlineStr">
@@ -8196,53 +8528,53 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46340</v>
+        <v>46337</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D51" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D51" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="31" t="n">
-        <v>46342</v>
+        <v>46337</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D52" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D52" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
@@ -8252,13 +8584,13 @@
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="36" t="n">
-        <v>46342</v>
+        <v>46339</v>
       </c>
       <c r="B53" s="41" t="n">
         <v>240</v>
@@ -8268,9 +8600,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D53" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D53" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
@@ -8280,53 +8612,53 @@
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="31" t="n">
-        <v>46343</v>
+        <v>46340</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D54" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46347</v>
+        <v>46342</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D55" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D55" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E55" s="35" t="inlineStr">
@@ -8336,25 +8668,25 @@
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46347</v>
+        <v>46342</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="C56" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D56" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D56" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
@@ -8364,25 +8696,25 @@
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46347</v>
+        <v>46343</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="C57" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D57" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D57" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
@@ -8392,16 +8724,16 @@
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="31" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="C58" s="39" t="inlineStr">
         <is>
@@ -8415,12 +8747,12 @@
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Nike Air Max 95 “ACG”</t>
         </is>
       </c>
     </row>
@@ -8429,16 +8761,16 @@
         <v>46347</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D59" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D59" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
@@ -8448,16 +8780,16 @@
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C60" s="39" t="inlineStr">
         <is>
@@ -8476,16 +8808,16 @@
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Bred” 2026</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
@@ -8504,16 +8836,16 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="C62" s="39" t="inlineStr">
         <is>
@@ -8527,30 +8859,30 @@
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="36" t="n">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>240</v>
+        <v>125</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D63" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D63" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
@@ -8560,43 +8892,45 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “FSU”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="31" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D64" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D64" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E64" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Instant Skateboards x Nike SB Air Force 1</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="36" t="n">
-        <v>46354</v>
-      </c>
-      <c r="B65" s="41" t="inlineStr"/>
+        <v>46353</v>
+      </c>
+      <c r="B65" s="41" t="n">
+        <v>240</v>
+      </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -8614,7 +8948,7 @@
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro College Football Pack</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
@@ -8674,7 +9008,7 @@
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46357</v>
+        <v>46354</v>
       </c>
       <c r="B68" s="33" t="n">
         <v>190</v>
@@ -8696,98 +9030,98 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Chosen 1s”</t>
+          <t>Nike Kobe 3 Low Protro “Dynamic Yellow”</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46361</v>
-      </c>
-      <c r="B69" s="41" t="inlineStr"/>
+        <v>46354</v>
+      </c>
+      <c r="B69" s="41" t="n">
+        <v>240</v>
+      </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D69" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D69" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>SoleFly x Air Jordan 5</t>
+          <t>Nike Air Foamposite Pro “FSU”</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46361</v>
+        <v>46354</v>
       </c>
       <c r="B70" s="33" t="n">
-        <v>215</v>
+        <v>120</v>
       </c>
       <c r="C70" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D70" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D70" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E70" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 10 “Sacramento”</t>
+          <t>Instant Skateboards x Nike SB Air Force 1</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46367</v>
-      </c>
-      <c r="B71" s="41" t="n">
-        <v>150</v>
-      </c>
+        <v>46354</v>
+      </c>
+      <c r="B71" s="41" t="inlineStr"/>
       <c r="C71" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D71" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D71" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>JAIDE x Air Jordan 1 Low OG</t>
+          <t>Nike Air Foamposite Pro College Football Pack</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46367</v>
+        <v>46357</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="C72" s="39" t="inlineStr">
         <is>
@@ -8806,13 +9140,13 @@
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Floral” 2026</t>
+          <t>Nike LeBron 24 “Chosen 1s”</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46367</v>
+        <v>46361</v>
       </c>
       <c r="B73" s="41" t="inlineStr"/>
       <c r="C73" s="40" t="inlineStr">
@@ -8820,9 +9154,9 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D73" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D73" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
@@ -8832,16 +9166,16 @@
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Free The Youth x Air Jordan 3</t>
+          <t>SoleFly x Air Jordan 5</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46367</v>
+        <v>46361</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C74" s="39" t="inlineStr">
         <is>
@@ -8855,30 +9189,28 @@
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+          <t>Air Jordan 10 “Sacramento”</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46368</v>
-      </c>
-      <c r="B75" s="41" t="n">
-        <v>235</v>
-      </c>
+        <v>46367</v>
+      </c>
+      <c r="B75" s="41" t="inlineStr"/>
       <c r="C75" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D75" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D75" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
@@ -8888,25 +9220,25 @@
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam” 2026</t>
+          <t>Free The Youth x Air Jordan 3</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="31" t="n">
-        <v>46375</v>
+        <v>46367</v>
       </c>
       <c r="B76" s="33" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="C76" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D76" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D76" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E76" s="30" t="inlineStr">
@@ -8916,40 +9248,152 @@
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Pink Thunder”</t>
+          <t>JAIDE x Air Jordan 1 Low OG</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="36" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B77" s="41" t="n">
+        <v>240</v>
+      </c>
+      <c r="C77" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D77" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E77" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F77" s="35" t="inlineStr">
+        <is>
+          <t>Nike Air Foamposite One “Floral” 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="31" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B78" s="33" t="n">
+        <v>190</v>
+      </c>
+      <c r="C78" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D78" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E78" s="30" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F78" s="30" t="inlineStr">
+        <is>
+          <t>Jalen Brunson x Nike Kobe 3 Low Protro “Arancia”</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="36" t="n">
+        <v>46368</v>
+      </c>
+      <c r="B79" s="41" t="n">
+        <v>235</v>
+      </c>
+      <c r="C79" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D79" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E79" s="35" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F79" s="35" t="inlineStr">
+        <is>
+          <t>Air Jordan 11 “Space Jam” 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="31" t="n">
         <v>46375</v>
       </c>
-      <c r="B77" s="41" t="n">
+      <c r="B80" s="33" t="n">
+        <v>220</v>
+      </c>
+      <c r="C80" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D80" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
+        </is>
+      </c>
+      <c r="E80" s="30" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F80" s="30" t="inlineStr">
+        <is>
+          <t>Air Jordan 4 “Pink Thunder”</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="36" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B81" s="41" t="n">
         <v>120</v>
       </c>
-      <c r="C77" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D77" s="38" t="inlineStr">
+      <c r="C81" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D81" s="38" t="inlineStr">
         <is>
           <t>SNKRS App</t>
         </is>
       </c>
-      <c r="E77" s="35" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="F77" s="35" t="inlineStr">
+      <c r="E81" s="35" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="F81" s="35" t="inlineStr">
         <is>
           <t>Fly Streetwear x Nike SB Air Force 1 Low “University Gold”</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F77"/>
+  <autoFilter ref="A3:F81"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/reports/sneaker_releases.xlsx
+++ b/reports/sneaker_releases.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="High Hype Alerts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$158</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Releases'!$A$3:$F$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'High Hype Alerts'!$A$3:$F$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -648,10 +648,10 @@
     <xf numFmtId="166" fontId="10" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -685,7 +685,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -808,12 +808,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Charts'!$A$2:$A$10</f>
+              <f>'Charts'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$B$2:$B$10</f>
+              <f>'Charts'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1581,7 +1581,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated September 24, 2026  ·  11:18 UTC</t>
+          <t>Generated September 25, 2026  ·  11:23 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1621,20 +1621,20 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B5" s="13" t="n"/>
       <c r="C5" s="14" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="16" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>$179</t>
+          <t>$182</t>
         </is>
       </c>
       <c r="H5" s="19" t="n"/>
@@ -1725,7 +1725,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>J Balvin x Air Jordan 4 “Amazonas”</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="C10" s="31" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>46354</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" s="37" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46295</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
@@ -1825,16 +1825,16 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D13" s="35" t="n">
         <v>0</v>
@@ -1848,27 +1848,27 @@
         <v>7</v>
       </c>
       <c r="G13" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="H13" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>205</v>
+      </c>
+      <c r="H13" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 1000.3</t>
+          <t>Air Jordan 5 WMNS "Sunset"</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C14" s="31" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D14" s="30" t="n">
         <v>0</v>
@@ -1882,9 +1882,9 @@
         <v>7</v>
       </c>
       <c r="G14" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="H14" s="42" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="H14" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -1893,16 +1893,16 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D15" s="35" t="n">
         <v>1</v>
@@ -1916,9 +1916,9 @@
         <v>7</v>
       </c>
       <c r="G15" s="41" t="n">
-        <v>205</v>
-      </c>
-      <c r="H15" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="H15" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -1927,7 +1927,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
@@ -1939,7 +1939,7 @@
         <v>46291</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
@@ -1949,12 +1949,10 @@
       <c r="F16" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="H16" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="G16" s="30" t="inlineStr"/>
+      <c r="H16" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2010,7 @@
         </is>
       </c>
       <c r="B20" s="30" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
@@ -2028,7 +2026,7 @@
         </is>
       </c>
       <c r="H20" s="30" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
@@ -2038,7 +2036,7 @@
         </is>
       </c>
       <c r="B21" s="35" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
@@ -2046,7 +2044,7 @@
         </is>
       </c>
       <c r="E21" s="35" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G21" s="47" t="inlineStr">
         <is>
@@ -2054,7 +2052,7 @@
         </is>
       </c>
       <c r="H21" s="35" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
@@ -2072,7 +2070,7 @@
         </is>
       </c>
       <c r="E22" s="30" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G22" s="49" t="inlineStr">
         <is>
@@ -2098,372 +2096,362 @@
         </is>
       </c>
       <c r="E23" s="35" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="B24" s="30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="46" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B25" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="B26" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="46" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="B27" s="35" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="44" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="B28" s="30" t="n">
+    <row r="28" ht="10" customHeight="1"/>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>Weekly Outlook (Next 13 Weeks)</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>Releases</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="inlineStr">
+        <is>
+          <t>HIGH+EXTREME</t>
+        </is>
+      </c>
+      <c r="E30" s="29" t="inlineStr">
+        <is>
+          <t>Avg Hype Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>9/25 – 10/1</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>40</v>
+      </c>
+      <c r="D31" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" s="30" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="35" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>10/2 – 10/8</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="D32" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" s="35" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>10/9 – 10/15</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="30" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="35" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="B34" s="35" t="inlineStr">
+        <is>
+          <t>10/16 – 10/22</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" s="35" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>10/23 – 10/29</t>
+        </is>
+      </c>
+      <c r="C35" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="D35" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" s="30" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="35" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="B36" s="35" t="inlineStr">
+        <is>
+          <t>10/30 – 11/5</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" s="40" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" ht="10" customHeight="1"/>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>Weekly Outlook (Next 13 Weeks)</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="29" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="B31" s="29" t="inlineStr">
-        <is>
-          <t>Dates</t>
-        </is>
-      </c>
-      <c r="C31" s="29" t="inlineStr">
-        <is>
-          <t>Releases</t>
-        </is>
-      </c>
-      <c r="D31" s="29" t="inlineStr">
-        <is>
-          <t>HIGH+EXTREME</t>
-        </is>
-      </c>
-      <c r="E31" s="29" t="inlineStr">
-        <is>
-          <t>Avg Hype Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>9/24 – 9/30</t>
-        </is>
-      </c>
-      <c r="C32" s="30" t="n">
-        <v>43</v>
-      </c>
-      <c r="D32" s="39" t="n">
-        <v>19</v>
-      </c>
-      <c r="E32" s="30" t="n">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="35" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="B33" s="35" t="inlineStr">
-        <is>
-          <t>10/1 – 10/7</t>
-        </is>
-      </c>
-      <c r="C33" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="D33" s="40" t="n">
+      <c r="E36" s="35" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>11/6 – 11/12</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="D37" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" s="30" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>11/13 – 11/19</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="D38" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" s="35" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>11/20 – 11/26</t>
+        </is>
+      </c>
+      <c r="C39" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="E33" s="35" t="n">
+      <c r="D39" s="39" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="B34" s="30" t="inlineStr">
-        <is>
-          <t>10/8 – 10/14</t>
-        </is>
-      </c>
-      <c r="C34" s="30" t="n">
+      <c r="E39" s="30" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>11/27 – 12/3</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="D40" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" s="35" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>12/4 – 12/10</t>
+        </is>
+      </c>
+      <c r="C41" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" s="30" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="B42" s="35" t="inlineStr">
+        <is>
+          <t>12/11 – 12/17</t>
+        </is>
+      </c>
+      <c r="C42" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="D34" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="30" t="n">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="35" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="B35" s="35" t="inlineStr">
-        <is>
-          <t>10/15 – 10/21</t>
-        </is>
-      </c>
-      <c r="C35" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="D35" s="40" t="n">
+      <c r="D42" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" s="35" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="30" t="inlineStr">
+        <is>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="inlineStr">
+        <is>
+          <t>12/18 – 12/24</t>
+        </is>
+      </c>
+      <c r="C43" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="E35" s="35" t="n">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="30" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="B36" s="30" t="inlineStr">
-        <is>
-          <t>10/22 – 10/28</t>
-        </is>
-      </c>
-      <c r="C36" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="D36" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="E36" s="30" t="n">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="35" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="B37" s="35" t="inlineStr">
-        <is>
-          <t>10/29 – 11/4</t>
-        </is>
-      </c>
-      <c r="C37" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D37" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="35" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="30" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="B38" s="30" t="inlineStr">
-        <is>
-          <t>11/5 – 11/11</t>
-        </is>
-      </c>
-      <c r="C38" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="D38" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="E38" s="30" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="35" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>11/12 – 11/18</t>
-        </is>
-      </c>
-      <c r="C39" s="35" t="n">
-        <v>14</v>
-      </c>
-      <c r="D39" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="E39" s="35" t="n">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
-        <is>
-          <t>Week 9</t>
-        </is>
-      </c>
-      <c r="B40" s="30" t="inlineStr">
-        <is>
-          <t>11/19 – 11/25</t>
-        </is>
-      </c>
-      <c r="C40" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="D40" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="E40" s="30" t="n">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="35" t="inlineStr">
-        <is>
-          <t>Week 10</t>
-        </is>
-      </c>
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>11/26 – 12/2</t>
-        </is>
-      </c>
-      <c r="C41" s="35" t="n">
-        <v>12</v>
-      </c>
-      <c r="D41" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="E41" s="35" t="n">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="30" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="B42" s="30" t="inlineStr">
-        <is>
-          <t>12/3 – 12/9</t>
-        </is>
-      </c>
-      <c r="C42" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="D42" s="39" t="n">
+      <c r="D43" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="E42" s="30" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="35" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="B43" s="35" t="inlineStr">
-        <is>
-          <t>12/10 – 12/16</t>
-        </is>
-      </c>
-      <c r="C43" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="D43" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="E43" s="35" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="30" t="inlineStr">
-        <is>
-          <t>Week 13</t>
-        </is>
-      </c>
-      <c r="B44" s="30" t="inlineStr">
-        <is>
-          <t>12/17 – 12/23</t>
-        </is>
-      </c>
-      <c r="C44" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D44" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E44" s="30" t="n">
-        <v>5.2</v>
+      <c r="E43" s="30" t="n">
+        <v>5.3</v>
       </c>
     </row>
   </sheetData>
@@ -2474,7 +2462,7 @@
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
@@ -2496,7 +2484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2561,7 +2549,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2577,7 +2565,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2595,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2603,7 +2591,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2611,7 +2599,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2619,7 +2607,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -2637,7 +2625,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2653,7 +2641,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
@@ -2671,7 +2659,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2679,17 +2667,17 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2703,40 +2691,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2752,7 +2730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2778,7 +2756,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Generated September 24, 2026  ·  11:18 UTC</t>
+          <t>Generated September 25, 2026  ·  11:23 UTC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2821,185 +2799,185 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="31" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C4" s="53" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E4" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Ghosted”</t>
+          <t>Billionaire Boys Club x Reebok Club C 85</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="36" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B5" s="41" t="n">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E5" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 1000.3 “Pure Platinum”</t>
+          <t>Air Jordan 5 “Sunset” 2026</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="31" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B6" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C6" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="42" t="inlineStr">
+      <c r="C6" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F6" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Green Beam”</t>
+          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="36" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B7" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C7" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D7" s="43" t="inlineStr">
+        <v>205</v>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>PUMA MB.06 "Shooting Star"</t>
+          <t>Air Jordan 5 WMNS "Sunset"</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="31" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B8" s="33" t="n">
         <v>140</v>
       </c>
-      <c r="C8" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="C8" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 Shroud “Shock”</t>
+          <t>Nike Ja 4 “Jaws”</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="36" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B9" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C9" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D9" s="43" t="inlineStr">
+        <v>185</v>
+      </c>
+      <c r="C9" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Converse SHAI 001 “Spark”</t>
+          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="31" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C10" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C10" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3011,51 +2989,49 @@
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max 1000.3</t>
+          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B11" s="41" t="n">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D11" s="43" t="inlineStr">
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Sunset” 2026</t>
+          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="31" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B12" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C12" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D12" s="42" t="inlineStr">
+        <v>46291</v>
+      </c>
+      <c r="B12" s="33" t="inlineStr"/>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3067,20 +3043,20 @@
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws” (Deep Water)</t>
+          <t>APB x Nike Dunk Low Pack</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B13" s="41" t="n">
-        <v>225</v>
-      </c>
-      <c r="C13" s="37" t="inlineStr">
-        <is>
-          <t>EXTREME</t>
+        <v>180</v>
+      </c>
+      <c r="C13" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D13" s="38" t="inlineStr">
@@ -3090,86 +3066,86 @@
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F13" s="35" t="inlineStr">
         <is>
-          <t>J Balvin x Air Jordan 4 “Lemonade”</t>
+          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="C14" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>210</v>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>Billionaire Boys Club x Reebok Club C 85</t>
+          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B15" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C15" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D15" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>180</v>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D15" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F15" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Jaws”</t>
+          <t>Mowalola x Air Jordan 14 Mule</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C16" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D16" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
@@ -3179,35 +3155,35 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>Taller De Rafa x Nike Air Max Goadome Low</t>
+          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="36" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B17" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C17" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D17" s="43" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Gomu Gomu”</t>
+          <t>Air Jordan 4014 “Ferrari”</t>
         </is>
       </c>
     </row>
@@ -3216,26 +3192,26 @@
         <v>46291</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C18" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
+          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
         </is>
       </c>
     </row>
@@ -3243,25 +3219,27 @@
       <c r="A19" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B19" s="41" t="inlineStr"/>
-      <c r="C19" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="B19" s="41" t="n">
+        <v>150</v>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D19" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F19" s="35" t="inlineStr">
         <is>
-          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
+          <t>Victor Victor x Nike Air Force 1 ’01 “Court Purple”</t>
         </is>
       </c>
     </row>
@@ -3269,27 +3247,25 @@
       <c r="A20" s="31" t="n">
         <v>46291</v>
       </c>
-      <c r="B20" s="33" t="n">
-        <v>155</v>
-      </c>
-      <c r="C20" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D20" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B20" s="33" t="inlineStr"/>
+      <c r="C20" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>NOCTA x Nike KD 19</t>
+          <t>Pokemon x adidas ZX 8000 “Mewtwo”</t>
         </is>
       </c>
     </row>
@@ -3298,16 +3274,16 @@
         <v>46291</v>
       </c>
       <c r="B21" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C21" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D21" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>155</v>
+      </c>
+      <c r="C21" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D21" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
@@ -3317,7 +3293,7 @@
       </c>
       <c r="F21" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca” 2026</t>
+          <t>NOCTA x Nike KD 19</t>
         </is>
       </c>
     </row>
@@ -3326,26 +3302,26 @@
         <v>46291</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>160</v>
-      </c>
-      <c r="C22" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D22" s="42" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
+          <t>Nike Kobe 3 Protro “Orca” 2026</t>
         </is>
       </c>
     </row>
@@ -3354,26 +3330,26 @@
         <v>46291</v>
       </c>
       <c r="B23" s="41" t="n">
-        <v>255</v>
-      </c>
-      <c r="C23" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D23" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>160</v>
+      </c>
+      <c r="C23" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F23" s="35" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14</t>
+          <t>Bad Bunny x adidas Badbo 1.0 “Puerto Rican Night”</t>
         </is>
       </c>
     </row>
@@ -3382,26 +3358,26 @@
         <v>46291</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="C24" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D24" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D24" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E24" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 23 Hyper Pink</t>
+          <t>Mowalola x Air Jordan 14</t>
         </is>
       </c>
     </row>
@@ -3410,16 +3386,16 @@
         <v>46291</v>
       </c>
       <c r="B25" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C25" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D25" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>200</v>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr">
@@ -3429,7 +3405,7 @@
       </c>
       <c r="F25" s="35" t="inlineStr">
         <is>
-          <t>Nike SB P-Rod 1 “Light British Tan”</t>
+          <t>Nike LeBron 23 Hyper Pink</t>
         </is>
       </c>
     </row>
@@ -3438,16 +3414,16 @@
         <v>46291</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C26" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D26" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>125</v>
+      </c>
+      <c r="C26" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
@@ -3457,7 +3433,7 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Cracked Leather” Pack</t>
+          <t>Nike SB P-Rod 1 “Light British Tan”</t>
         </is>
       </c>
     </row>
@@ -3465,25 +3441,27 @@
       <c r="A27" s="36" t="n">
         <v>46291</v>
       </c>
-      <c r="B27" s="41" t="inlineStr"/>
-      <c r="C27" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D27" s="43" t="inlineStr">
+      <c r="B27" s="41" t="n">
+        <v>120</v>
+      </c>
+      <c r="C27" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D27" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F27" s="35" t="inlineStr">
         <is>
-          <t>APB x Nike Dunk Low Pack</t>
+          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
         </is>
       </c>
     </row>
@@ -3492,16 +3470,16 @@
         <v>46291</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C28" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D28" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>210</v>
+      </c>
+      <c r="C28" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D28" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
@@ -3511,81 +3489,79 @@
       </c>
       <c r="F28" s="30" t="inlineStr">
         <is>
-          <t>One Piece x Nike Air Max Plus “Devil Fruits” Collection</t>
+          <t>Nike Kobe 3 Protro “Orca”</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="36" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B29" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C29" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D29" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>46293</v>
+      </c>
+      <c r="B29" s="41" t="inlineStr"/>
+      <c r="C29" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="F29" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 9 Elite Low Protro “EYBL”</t>
+          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="31" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="C30" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>249</v>
+      </c>
+      <c r="C30" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D30" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
         <is>
-          <t>Mowalola x Air Jordan 14 Mule</t>
+          <t>Hyperice x Nike Air Zoom Hyperslide</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="36" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="B31" s="41" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="C31" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D31" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D31" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -3595,107 +3571,107 @@
       </c>
       <c r="F31" s="35" t="inlineStr">
         <is>
-          <t>Nike Cryoshot Mercurial Vapor 1 OG</t>
+          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="31" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C32" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D32" s="42" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C32" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 4014 “Ferrari”</t>
+          <t>Nike Air Bakin “Varsity Red”</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="36" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B33" s="41" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="C33" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D33" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG “Last Dance at the Garden”</t>
+          <t>Union LA x Nike Dunk Low “Bamboo”</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="31" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="C34" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D34" s="42" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C34" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D34" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E34" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>Bad Bunny x adidas Badbo 1.1 Low</t>
+          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="36" t="n">
-        <v>46291</v>
+        <v>46295</v>
       </c>
       <c r="B35" s="41" t="n">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="C35" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D35" s="43" t="inlineStr">
+      <c r="D35" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3707,49 +3683,51 @@
       </c>
       <c r="F35" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 3 Protro “Orca”</t>
+          <t>Nike Air Force 1 Low “Leopard”</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="31" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B36" s="33" t="inlineStr"/>
+        <v>46295</v>
+      </c>
+      <c r="B36" s="33" t="n">
+        <v>130</v>
+      </c>
       <c r="C36" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D36" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>Kith x ASICS Gel Lyte III Remastered “Salmon Toe”</t>
+          <t>MoMA x Nike Air Rift 2 Pack</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="36" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B37" s="41" t="n">
-        <v>249</v>
+        <v>200</v>
       </c>
       <c r="C37" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D37" s="43" t="inlineStr">
+      <c r="D37" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3761,23 +3739,23 @@
       </c>
       <c r="F37" s="35" t="inlineStr">
         <is>
-          <t>Hyperice x Nike Air Zoom Hyperslide</t>
+          <t>Nike Zoom Huarache 2K4 “UCLA”</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="31" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C38" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D38" s="42" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="C38" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D38" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3789,23 +3767,23 @@
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Bakin OG “Varsity Red” 2026</t>
+          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="36" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B39" s="41" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="C39" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D39" s="43" t="inlineStr">
+      <c r="D39" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3817,23 +3795,21 @@
       </c>
       <c r="F39" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Red”</t>
+          <t>Tom Sachs x Nike General Purpose Shoe “Demerits”</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="31" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B40" s="33" t="n">
-        <v>125</v>
-      </c>
+        <v>46296</v>
+      </c>
+      <c r="B40" s="33" t="inlineStr"/>
       <c r="C40" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D40" s="42" t="inlineStr">
+      <c r="D40" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3845,25 +3821,25 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Leopard”</t>
+          <t>Nike Air Max 95 “Liverpool”</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="36" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B41" s="41" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C41" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D41" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D41" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E41" s="35" t="inlineStr">
@@ -3873,23 +3849,23 @@
       </c>
       <c r="F41" s="35" t="inlineStr">
         <is>
-          <t>MoMA x Nike Air Rift 2 Pack</t>
+          <t>Nike Caitlin 1 “Racer Blue”</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="31" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C42" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D42" s="42" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C42" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D42" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3901,23 +3877,23 @@
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>Nike Zoom Huarache 2K4 “UCLA”</t>
+          <t>Kobe Bryant x Nike Air Force 1 Low “Black Purple Stardust”</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="36" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B43" s="41" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C43" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D43" s="43" t="inlineStr">
+      <c r="D43" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -3929,20 +3905,20 @@
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe AD Protro “Purple Stardust” 2026</t>
+          <t>Nike Kobe Air Force 1 Low</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="31" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>135</v>
-      </c>
-      <c r="C44" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>225</v>
+      </c>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>EXTREME</t>
         </is>
       </c>
       <c r="D44" s="34" t="inlineStr">
@@ -3952,30 +3928,30 @@
       </c>
       <c r="E44" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F44" s="30" t="inlineStr">
         <is>
-          <t>Union LA x Nike Dunk Low “Bamboo”</t>
+          <t>J Balvin x Air Jordan 4 “Amazonas”</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="36" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B45" s="41" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C45" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D45" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D45" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E45" s="35" t="inlineStr">
@@ -3985,133 +3961,135 @@
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 MCS “Black Metallic Gold”</t>
+          <t>Air Jordan 4 “Light Army”</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="31" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>120</v>
-      </c>
-      <c r="C46" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D46" s="42" t="inlineStr">
+        <v>150</v>
+      </c>
+      <c r="C46" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F46" s="30" t="inlineStr">
         <is>
-          <t>Tom Sachs x Nike General Purpose Shoe “Demerits”</t>
+          <t>Air Jordan 6 Low “Black Pink Foam”</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="36" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B47" s="41" t="inlineStr"/>
+        <v>46298</v>
+      </c>
+      <c r="B47" s="41" t="n">
+        <v>205</v>
+      </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D47" s="43" t="inlineStr">
+      <c r="D47" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E47" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F47" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Liverpool”</t>
+          <t>Air Jordan 3 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="31" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>140</v>
-      </c>
-      <c r="C48" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D48" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>245</v>
+      </c>
+      <c r="C48" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F48" s="30" t="inlineStr">
         <is>
-          <t>Nike Caitlin 1 “Racer Blue”</t>
+          <t>Air Jordan 16 “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="36" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B49" s="41" t="n">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D49" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D49" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F49" s="35" t="inlineStr">
         <is>
-          <t>Kobe Bryant x Nike Air Force 1 Low “Black Purple Stardust”</t>
+          <t>Air Jordan 14 Low “Black Ostrich”</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="31" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="C50" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D50" s="42" t="inlineStr">
+      <c r="D50" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4123,128 +4101,128 @@
       </c>
       <c r="F50" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low</t>
+          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="B51" s="41" t="n">
-        <v>220</v>
-      </c>
-      <c r="C51" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D51" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>135</v>
+      </c>
+      <c r="C51" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D51" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F51" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 4 “Light Army”</t>
+          <t>Nike Sabrina 4 “90s Kid”</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="31" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C52" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D52" s="42" t="inlineStr">
+        <v>135</v>
+      </c>
+      <c r="C52" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D52" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E52" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 6 Low “Black Pink Foam”</t>
+          <t>Nike Sabrina 4 “Light Work”</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="36" t="n">
-        <v>46298</v>
+        <v>46301</v>
       </c>
       <c r="B53" s="41" t="n">
-        <v>240</v>
-      </c>
-      <c r="C53" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D53" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>175</v>
+      </c>
+      <c r="C53" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D53" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F53" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Low “Black Ostrich”</t>
+          <t>Nike Air Max Goadome Low “Black Croc”</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="31" t="n">
-        <v>46298</v>
+        <v>46301</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C54" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D54" s="42" t="inlineStr">
+        <v>175</v>
+      </c>
+      <c r="C54" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D54" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Fireside”</t>
+          <t>Nike Air Max Goadome Low “Navy Croc”</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="36" t="n">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="B55" s="41" t="n">
-        <v>245</v>
+        <v>150</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
@@ -4258,84 +4236,84 @@
       </c>
       <c r="E55" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F55" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 16 “Black Pack”</t>
+          <t>Nike Air Force 1 ’01 “Subway Rat”</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="31" t="n">
-        <v>46300</v>
+        <v>46303</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>200</v>
-      </c>
-      <c r="C56" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D56" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C56" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D56" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E56" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F56" s="30" t="inlineStr">
         <is>
-          <t>Nike Kobe 10 Low Protro “5 AM Flight”</t>
+          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="36" t="n">
-        <v>46301</v>
+        <v>46304</v>
       </c>
       <c r="B57" s="41" t="n">
-        <v>135</v>
-      </c>
-      <c r="C57" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D57" s="43" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C57" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D57" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E57" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F57" s="35" t="inlineStr">
         <is>
-          <t>Nike Sabrina 4 “90s Kid”</t>
+          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="31" t="n">
-        <v>46301</v>
+        <v>46304</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="C58" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D58" s="42" t="inlineStr">
+      <c r="D58" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4347,81 +4325,81 @@
       </c>
       <c r="F58" s="30" t="inlineStr">
         <is>
-          <t>Nike Sabrina 4 “Light Work”</t>
+          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="36" t="n">
-        <v>46301</v>
+        <v>46304</v>
       </c>
       <c r="B59" s="41" t="n">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="C59" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D59" s="43" t="inlineStr">
+      <c r="D59" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E59" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="F59" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max Goadome Low “Black Croc”</t>
+          <t>Aminé x New Balance 992 “Outdoor School”</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="31" t="n">
-        <v>46301</v>
+        <v>46305</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>175</v>
-      </c>
-      <c r="C60" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D60" s="42" t="inlineStr">
+        <v>180</v>
+      </c>
+      <c r="C60" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D60" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E60" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max Goadome Low “Navy Croc”</t>
+          <t>Air Jordan 1 High OG “Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="36" t="n">
-        <v>46302</v>
+        <v>46305</v>
       </c>
       <c r="B61" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="C61" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D61" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>135</v>
+      </c>
+      <c r="C61" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D61" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E61" s="35" t="inlineStr">
@@ -4431,79 +4409,79 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’01 “Subway Rat”</t>
+          <t>Nike KD 6 “Texas”</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="31" t="n">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C62" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D62" s="42" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C62" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D62" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Marshmallow”</t>
+          <t>Jordan Tatum 5 “Sunrise”</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="36" t="n">
-        <v>46304</v>
+        <v>46310</v>
       </c>
       <c r="B63" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C63" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D63" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>125</v>
+      </c>
+      <c r="C63" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D63" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E63" s="35" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Snow Camo”</t>
+          <t>NCAA x Nike Air Force 1 Low Pack</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="31" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C64" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D64" s="42" t="inlineStr">
+        <v>250</v>
+      </c>
+      <c r="C64" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D64" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4515,51 +4493,51 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Griffey Max 1 “Cincinnati Reds”</t>
+          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="36" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="B65" s="41" t="n">
-        <v>220</v>
-      </c>
-      <c r="C65" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D65" s="43" t="inlineStr">
+        <v>250</v>
+      </c>
+      <c r="C65" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D65" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Aminé x New Balance 992 “Outdoor School”</t>
+          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="31" t="n">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D66" s="42" t="inlineStr">
+      <c r="D66" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4571,107 +4549,105 @@
       </c>
       <c r="F66" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG “Royal” 2026</t>
+          <t>Air Jordan 5 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="36" t="n">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="B67" s="41" t="n">
-        <v>135</v>
-      </c>
-      <c r="C67" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D67" s="43" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C67" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D67" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
         <is>
-          <t>Nike KD 6 “Texas”</t>
+          <t>Air Jordan 12 “Fireside”</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="31" t="n">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C68" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D68" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>160</v>
+      </c>
+      <c r="C68" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D68" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Reebok</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>NCAA x Nike Air Force 1 Low Pack</t>
+          <t>Reebok Angel Reese 1 “Reese’s”</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="36" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B69" s="41" t="n">
-        <v>125</v>
-      </c>
-      <c r="C69" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D69" s="43" t="inlineStr">
+        <v>46317</v>
+      </c>
+      <c r="B69" s="41" t="inlineStr"/>
+      <c r="C69" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D69" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E69" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F69" s="35" t="inlineStr">
         <is>
-          <t>Jordan Tatum 5 “Sunrise”</t>
+          <t>SZA x Vans VANSZA Collection</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="31" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="B70" s="33" t="n">
-        <v>250</v>
-      </c>
-      <c r="C70" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D70" s="42" t="inlineStr">
+        <v>145</v>
+      </c>
+      <c r="C70" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D70" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4683,23 +4659,23 @@
       </c>
       <c r="F70" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Glow in the Dark”</t>
+          <t>Nike Sabrina 4 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="36" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="B71" s="41" t="n">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D71" s="43" t="inlineStr">
+      <c r="D71" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4711,161 +4687,163 @@
       </c>
       <c r="F71" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Phantom”</t>
+          <t>Nike Air Force 1 Low “NYC Rat”</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="31" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>250</v>
-      </c>
-      <c r="C72" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D72" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C72" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D72" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E72" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro PRM “Glow in the Dark”</t>
+          <t>PUMA Hali 1 “Pacers”</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="36" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B73" s="41" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D73" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D73" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E73" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F73" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 5 “Halloween”</t>
+          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="31" t="n">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="B74" s="33" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C74" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D74" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D74" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 12 “Fireside”</t>
+          <t>Nike Air Force 1 Low “Ghostface Black”</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="B75" s="41" t="n">
-        <v>160</v>
-      </c>
-      <c r="C75" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D75" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>170</v>
+      </c>
+      <c r="C75" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D75" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E75" s="35" t="inlineStr">
         <is>
-          <t>Reebok</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F75" s="35" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 “Reese’s”</t>
+          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="31" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B76" s="33" t="inlineStr"/>
-      <c r="C76" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D76" s="42" t="inlineStr">
+        <v>46319</v>
+      </c>
+      <c r="B76" s="33" t="n">
+        <v>145</v>
+      </c>
+      <c r="C76" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D76" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>SZA x Vans VANSZA Collection</t>
+          <t>Nike Ja 4 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="36" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B77" s="41" t="n">
-        <v>140</v>
-      </c>
-      <c r="C77" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D77" s="43" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C77" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D77" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4877,23 +4855,23 @@
       </c>
       <c r="F77" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “NYC Rat”</t>
+          <t>Nike Air Diamond Turf 2 “White Black”</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="31" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B78" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C78" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D78" s="42" t="inlineStr">
+        <v>190</v>
+      </c>
+      <c r="C78" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D78" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4905,35 +4883,35 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>Nike Sabrina 4 “Halloween”</t>
+          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="36" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B79" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C79" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D79" s="43" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C79" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D79" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E79" s="35" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F79" s="35" t="inlineStr">
         <is>
-          <t>PUMA Hali 1 “Pacers”</t>
+          <t>Nike Air Force 1 Low “Ghostface”</t>
         </is>
       </c>
     </row>
@@ -4942,26 +4920,26 @@
         <v>46319</v>
       </c>
       <c r="B80" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C80" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D80" s="42" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="C80" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D80" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E80" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Diamond Turf 2 “White Black”</t>
+          <t>Air Jordan 1 Low “Halloween”</t>
         </is>
       </c>
     </row>
@@ -4970,14 +4948,14 @@
         <v>46319</v>
       </c>
       <c r="B81" s="41" t="n">
-        <v>190</v>
-      </c>
-      <c r="C81" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D81" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C81" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D81" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -4989,7 +4967,7 @@
       </c>
       <c r="F81" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “Reverse Blue Spark”</t>
+          <t>Nike Ja 4 “Radar”</t>
         </is>
       </c>
     </row>
@@ -4998,42 +4976,42 @@
         <v>46319</v>
       </c>
       <c r="B82" s="33" t="n">
-        <v>125</v>
-      </c>
-      <c r="C82" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D82" s="42" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C82" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D82" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E82" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface”</t>
+          <t>Vans Old Skool 36 Pearlized “Red”</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="36" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B83" s="41" t="n">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="C83" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D83" s="43" t="inlineStr">
+      <c r="D83" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5045,25 +5023,25 @@
       </c>
       <c r="F83" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low “Halloween”</t>
+          <t>Air Jordan 41 “University Red”</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="31" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="B84" s="33" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="C84" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D84" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D84" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E84" s="30" t="inlineStr">
@@ -5073,53 +5051,53 @@
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Radar”</t>
+          <t>Nike Ja 4 High “University Red”</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="36" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="B85" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C85" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D85" s="43" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="C85" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D85" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E85" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F85" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Red”</t>
+          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="31" t="n">
-        <v>46319</v>
+        <v>46325</v>
       </c>
       <c r="B86" s="33" t="n">
-        <v>150</v>
-      </c>
-      <c r="C86" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D86" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>155</v>
+      </c>
+      <c r="C86" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D86" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E86" s="30" t="inlineStr">
@@ -5129,44 +5107,44 @@
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>NIGO x J-Hope x Nike Air Force 1 ’01</t>
+          <t>Nike Book 2 “Halloween”</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="36" t="n">
-        <v>46319</v>
+        <v>46326</v>
       </c>
       <c r="B87" s="41" t="n">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="C87" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D87" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D87" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E87" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F87" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low “Ghostface Black”</t>
+          <t>Air Jordan 14 “Forest Green”</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="31" t="n">
-        <v>46319</v>
+        <v>46331</v>
       </c>
       <c r="B88" s="33" t="n">
-        <v>170</v>
+        <v>265</v>
       </c>
       <c r="C88" s="48" t="inlineStr">
         <is>
@@ -5185,23 +5163,23 @@
       </c>
       <c r="F88" s="30" t="inlineStr">
         <is>
-          <t>Jason Williams x SLAM x Nike Zoom Hyperflight “Platinum”</t>
+          <t>Nike Air Max Foamdome “Eggplant” 2026</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="36" t="n">
-        <v>46319</v>
+        <v>46331</v>
       </c>
       <c r="B89" s="41" t="n">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="C89" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D89" s="43" t="inlineStr">
+      <c r="D89" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5213,51 +5191,51 @@
       </c>
       <c r="F89" s="35" t="inlineStr">
         <is>
-          <t>Nike Ja 4 “Halloween”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="31" t="n">
-        <v>46320</v>
+        <v>46331</v>
       </c>
       <c r="B90" s="33" t="n">
-        <v>205</v>
-      </c>
-      <c r="C90" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D90" s="42" t="inlineStr">
+        <v>210</v>
+      </c>
+      <c r="C90" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D90" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E90" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 41 “University Red”</t>
+          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
         </is>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="36" t="n">
-        <v>46325</v>
+        <v>46331</v>
       </c>
       <c r="B91" s="41" t="n">
-        <v>155</v>
+        <v>265</v>
       </c>
       <c r="C91" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D91" s="43" t="inlineStr">
+      <c r="D91" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5269,25 +5247,25 @@
       </c>
       <c r="F91" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 Halloween “Oogie Boogie”</t>
+          <t>Nike Air Max Foamdome “Eggplant”</t>
         </is>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="31" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="B92" s="33" t="n">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="C92" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D92" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D92" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E92" s="30" t="inlineStr">
@@ -5297,53 +5275,53 @@
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>Nike Ja 4 High “University Red”</t>
+          <t>Nike Book 2 “Desert Night”</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="36" t="n">
-        <v>46325</v>
+        <v>46333</v>
       </c>
       <c r="B93" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C93" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D93" s="43" t="inlineStr">
+        <v>215</v>
+      </c>
+      <c r="C93" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D93" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E93" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F93" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Halloween”</t>
+          <t>Air Jordan 6 “White Infrared” 2026</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="31" t="n">
-        <v>46326</v>
+        <v>46333</v>
       </c>
       <c r="B94" s="33" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="C94" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D94" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D94" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E94" s="30" t="inlineStr">
@@ -5353,20 +5331,20 @@
       </c>
       <c r="F94" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 14 “Forest Green”</t>
+          <t>Air Jordan 17 Low “Black Pack”</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="36" t="n">
-        <v>46331</v>
+        <v>46333</v>
       </c>
       <c r="B95" s="41" t="n">
-        <v>265</v>
-      </c>
-      <c r="C95" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>240</v>
+      </c>
+      <c r="C95" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="D95" s="38" t="inlineStr">
@@ -5376,56 +5354,56 @@
       </c>
       <c r="E95" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F95" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max Foamdome “Eggplant” 2026</t>
+          <t>Air Jordan 15 “Snakeskin”</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="31" t="n">
-        <v>46331</v>
+        <v>46337</v>
       </c>
       <c r="B96" s="33" t="n">
-        <v>210</v>
-      </c>
-      <c r="C96" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D96" s="42" t="inlineStr">
+        <v>235</v>
+      </c>
+      <c r="C96" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D96" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E96" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F96" s="30" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “Statue of Liberty”</t>
+          <t>Air Jordan 11 “Light British Tan”</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="36" t="n">
-        <v>46331</v>
+        <v>46337</v>
       </c>
       <c r="B97" s="41" t="n">
-        <v>210</v>
-      </c>
-      <c r="C97" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D97" s="43" t="inlineStr">
+        <v>200</v>
+      </c>
+      <c r="C97" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D97" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5437,25 +5415,25 @@
       </c>
       <c r="F97" s="35" t="inlineStr">
         <is>
-          <t>Victor Wembanyama x Nike GT Cut 4 “State of Liberty”</t>
+          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="31" t="n">
-        <v>46331</v>
+        <v>46338</v>
       </c>
       <c r="B98" s="33" t="n">
-        <v>265</v>
+        <v>170</v>
       </c>
       <c r="C98" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D98" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D98" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E98" s="30" t="inlineStr">
@@ -5465,135 +5443,135 @@
       </c>
       <c r="F98" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Max Foamdome “Eggplant”</t>
+          <t>Nike Air Bakin “Varsity Royal” 2026</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="36" t="n">
-        <v>46332</v>
+        <v>46338</v>
       </c>
       <c r="B99" s="41" t="n">
-        <v>145</v>
-      </c>
-      <c r="C99" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D99" s="43" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="C99" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D99" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E99" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F99" s="35" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Desert Night”</t>
+          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="31" t="n">
-        <v>46333</v>
+        <v>46338</v>
       </c>
       <c r="B100" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C100" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D100" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C100" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D100" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E100" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F100" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 15 “Snakeskin”</t>
+          <t>Nike Air Bakin “Varsity Royal”</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="36" t="n">
-        <v>46333</v>
+        <v>46339</v>
       </c>
       <c r="B101" s="41" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C101" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D101" s="43" t="inlineStr">
+      <c r="D101" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E101" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F101" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 6 “White Infrared” 2026</t>
+          <t>Nike Air Foamposite One “Mummy”</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="31" t="n">
-        <v>46333</v>
+        <v>46339</v>
       </c>
       <c r="B102" s="33" t="n">
-        <v>245</v>
-      </c>
-      <c r="C102" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D102" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>170</v>
+      </c>
+      <c r="C102" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D102" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E102" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F102" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 17 Low “Black Pack”</t>
+          <t>Nike Air Diamond Turf 2 Patent “Black Red”</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="36" t="n">
-        <v>46337</v>
+        <v>46339</v>
       </c>
       <c r="B103" s="41" t="n">
-        <v>200</v>
-      </c>
-      <c r="C103" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D103" s="43" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C103" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D103" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5605,44 +5583,44 @@
       </c>
       <c r="F103" s="35" t="inlineStr">
         <is>
-          <t>Nike Kobe 8 Protro “Shanghai Fireworks”</t>
+          <t>Nike Air Diamond Turf 2</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="31" t="n">
-        <v>46337</v>
+        <v>46339</v>
       </c>
       <c r="B104" s="33" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C104" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D104" s="42" t="inlineStr">
+      <c r="D104" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E104" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F104" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Light British Tan”</t>
+          <t>Nike Air Foamposite One “Phantom”</t>
         </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="36" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="B105" s="41" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C105" s="54" t="inlineStr">
         <is>
@@ -5661,109 +5639,109 @@
       </c>
       <c r="F105" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal” 2026</t>
+          <t>CPFM x Nike Flea 1 “Barely”</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="31" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="B106" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C106" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D106" s="42" t="inlineStr">
+        <v>170</v>
+      </c>
+      <c r="C106" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D106" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E106" s="30" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F106" s="30" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Lime Pop”</t>
+          <t>Nike Zoom Hyperflight “Green Apple”</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="36" t="n">
-        <v>46338</v>
+        <v>46340</v>
       </c>
       <c r="B107" s="41" t="n">
-        <v>170</v>
-      </c>
-      <c r="C107" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D107" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>255</v>
+      </c>
+      <c r="C107" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D107" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E107" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F107" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Bakin “Varsity Royal”</t>
+          <t>Air Jordan 11 “Green Screen”</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="31" t="n">
-        <v>46339</v>
+        <v>46340</v>
       </c>
       <c r="B108" s="33" t="n">
         <v>240</v>
       </c>
-      <c r="C108" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D108" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="C108" s="48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D108" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E108" s="30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F108" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite One “Mummy”</t>
+          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
         </is>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="36" t="n">
-        <v>46339</v>
+        <v>46341</v>
       </c>
       <c r="B109" s="41" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C109" s="54" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D109" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D109" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E109" s="35" t="inlineStr">
@@ -5773,25 +5751,25 @@
       </c>
       <c r="F109" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Diamond Turf 2 Patent “Black Red”</t>
+          <t>Playa Society x Nike A’Two</t>
         </is>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="31" t="n">
-        <v>46339</v>
+        <v>46342</v>
       </c>
       <c r="B110" s="33" t="n">
-        <v>170</v>
-      </c>
-      <c r="C110" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D110" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>240</v>
+      </c>
+      <c r="C110" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D110" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E110" s="30" t="inlineStr">
@@ -5801,13 +5779,13 @@
       </c>
       <c r="F110" s="30" t="inlineStr">
         <is>
-          <t>Nike Air Diamond Turf 2</t>
+          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
         </is>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="36" t="n">
-        <v>46340</v>
+        <v>46342</v>
       </c>
       <c r="B111" s="41" t="n">
         <v>255</v>
@@ -5829,79 +5807,79 @@
       </c>
       <c r="F111" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Green Screen”</t>
+          <t>Air Jordan 11 “Space Jam Galaxy”</t>
         </is>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="31" t="n">
-        <v>46340</v>
+        <v>46343</v>
       </c>
       <c r="B112" s="33" t="n">
-        <v>240</v>
-      </c>
-      <c r="C112" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D112" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>200</v>
+      </c>
+      <c r="C112" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D112" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E112" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F112" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Boot NRG “Iridescent”</t>
+          <t>Nike LeBron 24 “Shooting Star”</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="36" t="n">
-        <v>46340</v>
+        <v>46345</v>
       </c>
       <c r="B113" s="41" t="n">
-        <v>180</v>
-      </c>
-      <c r="C113" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D113" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C113" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D113" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E113" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F113" s="35" t="inlineStr">
         <is>
-          <t>CPFM x Nike Flea 1 “Barely”</t>
+          <t>Vans Old Skool 36 Pearlized “Navy”</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="31" t="n">
-        <v>46340</v>
+        <v>46346</v>
       </c>
       <c r="B114" s="33" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="C114" s="48" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="D114" s="42" t="inlineStr">
+      <c r="D114" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -5913,25 +5891,25 @@
       </c>
       <c r="F114" s="30" t="inlineStr">
         <is>
-          <t>Nike Zoom Hyperflight “Green Apple”</t>
+          <t>Nike Book 2 “Be Legendary”</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="36" t="n">
-        <v>46341</v>
+        <v>46346</v>
       </c>
       <c r="B115" s="41" t="n">
-        <v>155</v>
-      </c>
-      <c r="C115" s="54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D115" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>190</v>
+      </c>
+      <c r="C115" s="40" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D115" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E115" s="35" t="inlineStr">
@@ -5941,79 +5919,79 @@
       </c>
       <c r="F115" s="35" t="inlineStr">
         <is>
-          <t>Playa Society x Nike A’Two</t>
+          <t>Nike Air Max 95 “ACG”</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="31" t="n">
-        <v>46342</v>
+        <v>46346</v>
       </c>
       <c r="B116" s="33" t="n">
-        <v>255</v>
-      </c>
-      <c r="C116" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D116" s="34" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+        <v>130</v>
+      </c>
+      <c r="C116" s="53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D116" s="43" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E116" s="30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F116" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 11 “Space Jam Galaxy”</t>
+          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="36" t="n">
-        <v>46342</v>
+        <v>46347</v>
       </c>
       <c r="B117" s="41" t="n">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="C117" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D117" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="D117" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E117" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F117" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro “Mummy Duck”</t>
+          <t>Air Jordan 3 “Santa”</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="31" t="n">
-        <v>46343</v>
+        <v>46347</v>
       </c>
       <c r="B118" s="33" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="C118" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D118" s="42" t="inlineStr">
+      <c r="D118" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6025,53 +6003,53 @@
       </c>
       <c r="F118" s="30" t="inlineStr">
         <is>
-          <t>Nike LeBron 24 “Shooting Star”</t>
+          <t>Oregon Ducks Nike Air Force 1 Low 2026</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="36" t="n">
-        <v>46345</v>
+        <v>46347</v>
       </c>
       <c r="B119" s="41" t="n">
-        <v>130</v>
-      </c>
-      <c r="C119" s="50" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D119" s="43" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C119" s="54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D119" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E119" s="35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F119" s="35" t="inlineStr">
         <is>
-          <t>Vans Old Skool 36 Pearlized “Navy”</t>
+          <t>Nike Caitlin 1 “Snow White”</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="31" t="n">
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="B120" s="33" t="n">
-        <v>145</v>
-      </c>
-      <c r="C120" s="48" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D120" s="42" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+        <v>230</v>
+      </c>
+      <c r="C120" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D120" s="34" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E120" s="30" t="inlineStr">
@@ -6081,63 +6059,63 @@
       </c>
       <c r="F120" s="30" t="inlineStr">
         <is>
-          <t>Nike Book 2 “Be Legendary”</t>
+          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="36" t="n">
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="B121" s="41" t="n">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C121" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D121" s="43" t="inlineStr">
+      <c r="D121" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E121" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="F121" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 “ACG”</t>
+          <t>Air Jordan 3 “Not Nice”</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="A122" s="31" t="n">
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="B122" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C122" s="53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D122" s="42" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="C122" s="39" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D122" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E122" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F122" s="30" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 3 “Lucid Pink”</t>
+          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
         </is>
       </c>
     </row>
@@ -6145,43 +6123,41 @@
       <c r="A123" s="36" t="n">
         <v>46347</v>
       </c>
-      <c r="B123" s="41" t="n">
-        <v>230</v>
-      </c>
-      <c r="C123" s="40" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D123" s="38" t="inlineStr">
-        <is>
-          <t>SNKRS App</t>
+      <c r="B123" s="41" t="inlineStr"/>
+      <c r="C123" s="50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D123" s="42" t="inlineStr">
+        <is>
+          <t>Online + Retail</t>
         </is>
       </c>
       <c r="E123" s="35" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="F123" s="35" t="inlineStr">
         <is>
-          <t>Oregon Ducks x Nike Air Foamposite Pro “Mummy Duck” (Phantom)</t>
+          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1">
       <c r="A124" s="31" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B124" s="33" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C124" s="39" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D124" s="42" t="inlineStr">
+      <c r="D124" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6193,23 +6169,23 @@
       </c>
       <c r="F124" s="30" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Not Nice”</t>
+          <t>Air Jordan 4 “Bred” 2026</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="36" t="n">
-        <v>46347</v>
+        <v>46353</v>
       </c>
       <c r="B125" s="41" t="n">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="C125" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D125" s="43" t="inlineStr">
+      <c r="D125" s="42" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
@@ -6221,79 +6197,81 @@
       </c>
       <c r="F125" s="35" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low Pony Hair “Team Red”</t>
+          <t>Nike Air Foamposite Pro “Dr. Doom”</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="31" t="n">
-        <v>46347</v>
-      </c>
-      <c r="B126" s="33" t="inlineStr"/>
+        <v>46353</v>
+      </c>
+      <c r="B126" s="33" t="n">
+        <v>130</v>
+      </c>
       <c r="C126" s="53" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D126" s="42" t="inlineStr">
+      <c r="D126" s="43" t="inlineStr">
         <is>
           <t>Online + Retail</t>
         </is>
       </c>
       <c r="E126" s="30" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F126" s="30" t="inlineStr">
         <is>
-          <t>UNheardof x adidas Adistar Control 5 “Doggy Runner”</t>
+          <t>Vans Old Skool 36 Pearlized “Black”</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="36" t="n">
-        <v>46347</v>
+        <v>46354</v>
       </c>
       <c r="B127" s="41" t="n">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="C127" s="40" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D127" s="43" t="inlineStr">
-        <is>
-          <t>Online + Retail</t>
+      <c r="D127" s="38" t="inlineStr">
+        <is>
+          <t>SNKRS App</t>
         </is>
       </c>
       <c r="E127" s="35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="F127" s="35" t="inlineStr">
         <is>
-          <t>Air Jordan 3 “Santa”</t>
+          <t>Nike Air Foamposite Pro “FSU”</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" s="31" t="n">
-        <v>46347</v>
+        <v>46354</v>
       </c>
       <c r="B128" s="33" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
 